--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -10,14 +10,14 @@
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$D$1:$O$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$D$1:$O$438</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4250" uniqueCount="1386">
   <si>
     <t>单号</t>
   </si>
@@ -3044,6 +3044,1137 @@
   </si>
   <si>
     <t>堆子前镇便民服务中心（全拨事业）、</t>
+  </si>
+  <si>
+    <t>[2021]第299号</t>
+  </si>
+  <si>
+    <t>张开辉</t>
+  </si>
+  <si>
+    <t>安义县价格认定监测中心</t>
+  </si>
+  <si>
+    <t>综合交通运输事业发展中心</t>
+  </si>
+  <si>
+    <t>县综合交通运输事业发展中心</t>
+  </si>
+  <si>
+    <t>[2021]第300号</t>
+  </si>
+  <si>
+    <t>郭晓露</t>
+  </si>
+  <si>
+    <t>2020-9-1</t>
+  </si>
+  <si>
+    <t>农业产业化办</t>
+  </si>
+  <si>
+    <t>[2021]第301号</t>
+  </si>
+  <si>
+    <t>邹敏</t>
+  </si>
+  <si>
+    <t>大汾镇便民服务中心（全拨事业）</t>
+  </si>
+  <si>
+    <t>[2021]第302号</t>
+  </si>
+  <si>
+    <t>廖新福</t>
+  </si>
+  <si>
+    <t>劳动人事争议仲裁院</t>
+  </si>
+  <si>
+    <t>县劳动人事争议仲裁院（全拨事业）</t>
+  </si>
+  <si>
+    <t>[2021]第303号</t>
+  </si>
+  <si>
+    <t>康敏</t>
+  </si>
+  <si>
+    <t>高坪镇便民服务中心（全拨事业）</t>
+  </si>
+  <si>
+    <t>[2021]第304号</t>
+  </si>
+  <si>
+    <t>蒋宝群</t>
+  </si>
+  <si>
+    <t>交通运输综合行政执法大队</t>
+  </si>
+  <si>
+    <t>县交通运输综合行政执法大队（全拨事业）</t>
+  </si>
+  <si>
+    <t>[2021]第305号</t>
+  </si>
+  <si>
+    <t>郑瑞锟</t>
+  </si>
+  <si>
+    <t>县综合交通运输事业发展中心（全额拨款）</t>
+  </si>
+  <si>
+    <t>[2021]第306号</t>
+  </si>
+  <si>
+    <t>蓝婷</t>
+  </si>
+  <si>
+    <t>南江卫生院</t>
+  </si>
+  <si>
+    <t>南江卫生院（差额拨款）</t>
+  </si>
+  <si>
+    <t>[2021]第307号</t>
+  </si>
+  <si>
+    <t>行政</t>
+  </si>
+  <si>
+    <t>李海华</t>
+  </si>
+  <si>
+    <t>堆子前镇党委书记</t>
+  </si>
+  <si>
+    <t>大汾镇党委书记</t>
+  </si>
+  <si>
+    <t>[2021]第308号</t>
+  </si>
+  <si>
+    <t>朱永生</t>
+  </si>
+  <si>
+    <t>大汾镇党委副书记、镇长</t>
+  </si>
+  <si>
+    <t>[2021]第309号</t>
+  </si>
+  <si>
+    <t>李勤国</t>
+  </si>
+  <si>
+    <t>戴家埔乡党委副书记、政法委员</t>
+  </si>
+  <si>
+    <t>[2021]第310号</t>
+  </si>
+  <si>
+    <t>李开文</t>
+  </si>
+  <si>
+    <t>草林镇党委委员、纪委书记、监察办主任</t>
+  </si>
+  <si>
+    <t>大汾镇党委副书记、政法委员</t>
+  </si>
+  <si>
+    <t>[2021]第311号</t>
+  </si>
+  <si>
+    <t>钟音</t>
+  </si>
+  <si>
+    <t>雩田镇党委委员、宣传员、统战员</t>
+  </si>
+  <si>
+    <t>大汾镇党委委员、纪委书记、监察办主任</t>
+  </si>
+  <si>
+    <t>[2021]第312号</t>
+  </si>
+  <si>
+    <t>肖春</t>
+  </si>
+  <si>
+    <t>营盘圩乡党委委员、组织员、宣传员、统战员</t>
+  </si>
+  <si>
+    <t>大汾镇党委委员、组织员</t>
+  </si>
+  <si>
+    <t>[2021]第313号</t>
+  </si>
+  <si>
+    <t>彭强</t>
+  </si>
+  <si>
+    <t>汤湖镇人大副主席</t>
+  </si>
+  <si>
+    <t>大汾镇党委委员、人武部长</t>
+  </si>
+  <si>
+    <t>[2021]第314号</t>
+  </si>
+  <si>
+    <t>邝春平</t>
+  </si>
+  <si>
+    <t>营盘圩乡政府副乡长</t>
+  </si>
+  <si>
+    <t>大汾镇政府副镇长</t>
+  </si>
+  <si>
+    <t>[2021]第315号</t>
+  </si>
+  <si>
+    <t>袁军</t>
+  </si>
+  <si>
+    <t>遂川县汤湖镇政府事业干部</t>
+  </si>
+  <si>
+    <t>遂川县大汾镇综合执法队队长</t>
+  </si>
+  <si>
+    <t>[2021]第-1号</t>
+  </si>
+  <si>
+    <t>刘薇</t>
+  </si>
+  <si>
+    <t>[2021]第-2号</t>
+  </si>
+  <si>
+    <t>黄衍庭</t>
+  </si>
+  <si>
+    <t>[2021]退1号</t>
+  </si>
+  <si>
+    <t>退休</t>
+  </si>
+  <si>
+    <t>樊命生</t>
+  </si>
+  <si>
+    <t>2021-07-01</t>
+  </si>
+  <si>
+    <t>遂川县教育体育发展中心</t>
+  </si>
+  <si>
+    <t>[2021]退2号</t>
+  </si>
+  <si>
+    <t>钟健生</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>[2021]退3号</t>
+  </si>
+  <si>
+    <t>李丙英</t>
+  </si>
+  <si>
+    <t>[2021]退4号</t>
+  </si>
+  <si>
+    <t>肖智辉</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>[2021]退5号</t>
+  </si>
+  <si>
+    <t>李永生</t>
+  </si>
+  <si>
+    <t>2021-06-01</t>
+  </si>
+  <si>
+    <t>遂川二中</t>
+  </si>
+  <si>
+    <t>[2021]退6号</t>
+  </si>
+  <si>
+    <t>罗彦</t>
+  </si>
+  <si>
+    <t>2021-05-01</t>
+  </si>
+  <si>
+    <t>遂川中学</t>
+  </si>
+  <si>
+    <t>[2021]退7号</t>
+  </si>
+  <si>
+    <t>胡建国</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
+  </si>
+  <si>
+    <t>上海警备区希望小学</t>
+  </si>
+  <si>
+    <t>[2021]退8号</t>
+  </si>
+  <si>
+    <t>冯令通</t>
+  </si>
+  <si>
+    <t>[2021]退9号</t>
+  </si>
+  <si>
+    <t>李井邻</t>
+  </si>
+  <si>
+    <t>高坪北京西站小学</t>
+  </si>
+  <si>
+    <t>[2021]退10号</t>
+  </si>
+  <si>
+    <t>张军</t>
+  </si>
+  <si>
+    <t>碧洲中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退11号</t>
+  </si>
+  <si>
+    <t>彭应萌</t>
+  </si>
+  <si>
+    <t>遂川县文物办</t>
+  </si>
+  <si>
+    <t>[2021]退12号</t>
+  </si>
+  <si>
+    <t>丛桂武</t>
+  </si>
+  <si>
+    <t>[2021]退13号</t>
+  </si>
+  <si>
+    <t>叶秋生</t>
+  </si>
+  <si>
+    <t>2021-08-01</t>
+  </si>
+  <si>
+    <t>草林中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退14号</t>
+  </si>
+  <si>
+    <t>蒋美英</t>
+  </si>
+  <si>
+    <t>[2021]退15号</t>
+  </si>
+  <si>
+    <t>郭满生</t>
+  </si>
+  <si>
+    <t>城乡居民养老保险局</t>
+  </si>
+  <si>
+    <t>[2021]退16号</t>
+  </si>
+  <si>
+    <t>李小平</t>
+  </si>
+  <si>
+    <t>滁洲中心学校</t>
+  </si>
+  <si>
+    <t>[2021]退17号</t>
+  </si>
+  <si>
+    <t>张秋红</t>
+  </si>
+  <si>
+    <t>大汾中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退18号</t>
+  </si>
+  <si>
+    <t>古富渊</t>
+  </si>
+  <si>
+    <t>2021-10-01</t>
+  </si>
+  <si>
+    <t>[2021]退19号</t>
+  </si>
+  <si>
+    <t>张诗安</t>
+  </si>
+  <si>
+    <t>戴家埔中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退20号</t>
+  </si>
+  <si>
+    <t>古霭华</t>
+  </si>
+  <si>
+    <t>[2021]退21号</t>
+  </si>
+  <si>
+    <t>戚优忠</t>
+  </si>
+  <si>
+    <t>堆前中学</t>
+  </si>
+  <si>
+    <t>[2021]退22号</t>
+  </si>
+  <si>
+    <t>郭小勇</t>
+  </si>
+  <si>
+    <t>发展和改革委员会</t>
+  </si>
+  <si>
+    <t>[2021]退23号</t>
+  </si>
+  <si>
+    <t>郭晓春</t>
+  </si>
+  <si>
+    <t>扶贫办公室</t>
+  </si>
+  <si>
+    <t>[2021]退24号</t>
+  </si>
+  <si>
+    <t>刘小平</t>
+  </si>
+  <si>
+    <t>[2021]退25号</t>
+  </si>
+  <si>
+    <t>王亚萍</t>
+  </si>
+  <si>
+    <t>高坪镇林业工作站</t>
+  </si>
+  <si>
+    <t>[2021]退26号</t>
+  </si>
+  <si>
+    <t>冯宙民</t>
+  </si>
+  <si>
+    <t>公安局</t>
+  </si>
+  <si>
+    <t>[2021]退27号</t>
+  </si>
+  <si>
+    <t>郭冬生</t>
+  </si>
+  <si>
+    <t>[2021]退28号</t>
+  </si>
+  <si>
+    <t>胡平生</t>
+  </si>
+  <si>
+    <t>[2021]退29号</t>
+  </si>
+  <si>
+    <t>颜义生</t>
+  </si>
+  <si>
+    <t>公安局森林分局</t>
+  </si>
+  <si>
+    <t>[2021]退30号</t>
+  </si>
+  <si>
+    <t>肖万林</t>
+  </si>
+  <si>
+    <t>[2021]退31号</t>
+  </si>
+  <si>
+    <t>洪坚</t>
+  </si>
+  <si>
+    <t>[2021]退32号</t>
+  </si>
+  <si>
+    <t>曾庆锋</t>
+  </si>
+  <si>
+    <t>[2021]退33号</t>
+  </si>
+  <si>
+    <t>叶伟荣</t>
+  </si>
+  <si>
+    <t>[2021]退34号</t>
+  </si>
+  <si>
+    <t>肖群女</t>
+  </si>
+  <si>
+    <t>[2021]退35号</t>
+  </si>
+  <si>
+    <t>吴检生</t>
+  </si>
+  <si>
+    <t>禾源中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退36号</t>
+  </si>
+  <si>
+    <t>邹平生</t>
+  </si>
+  <si>
+    <t>环境保护局</t>
+  </si>
+  <si>
+    <t>[2021]退37号</t>
+  </si>
+  <si>
+    <t>唐玄生</t>
+  </si>
+  <si>
+    <t>黄坑中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退38号</t>
+  </si>
+  <si>
+    <t>彭学根</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>机关事务管理局</t>
+  </si>
+  <si>
+    <t>[2021]退39号</t>
+  </si>
+  <si>
+    <t>杨小毛</t>
+  </si>
+  <si>
+    <t>疾病预防控制中心</t>
+  </si>
+  <si>
+    <t>[2021]退40号</t>
+  </si>
+  <si>
+    <t>高院平</t>
+  </si>
+  <si>
+    <t>[2021]退41号</t>
+  </si>
+  <si>
+    <t>万承明</t>
+  </si>
+  <si>
+    <t>[2021]退42号</t>
+  </si>
+  <si>
+    <t>肖平</t>
+  </si>
+  <si>
+    <t>教育体育局</t>
+  </si>
+  <si>
+    <t>[2021]退43号</t>
+  </si>
+  <si>
+    <t>刘晓林</t>
+  </si>
+  <si>
+    <t>[2021]退44号</t>
+  </si>
+  <si>
+    <t>陈光杰</t>
+  </si>
+  <si>
+    <t>[2021]退45号</t>
+  </si>
+  <si>
+    <t>何斌</t>
+  </si>
+  <si>
+    <t>[2021]退46号</t>
+  </si>
+  <si>
+    <t>何观元</t>
+  </si>
+  <si>
+    <t>[2021]退47号</t>
+  </si>
+  <si>
+    <t>叶惠兰</t>
+  </si>
+  <si>
+    <t>[2021]退48号</t>
+  </si>
+  <si>
+    <t>肖同花</t>
+  </si>
+  <si>
+    <t>枚江中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退49号</t>
+  </si>
+  <si>
+    <t>周年根</t>
+  </si>
+  <si>
+    <t>[2021]退50号</t>
+  </si>
+  <si>
+    <t>周建强</t>
+  </si>
+  <si>
+    <t>[2021]退51号</t>
+  </si>
+  <si>
+    <t>陈刚</t>
+  </si>
+  <si>
+    <t>[2021]退52号</t>
+  </si>
+  <si>
+    <t>彭春秀</t>
+  </si>
+  <si>
+    <t>2021-01-01</t>
+  </si>
+  <si>
+    <t>[2021]退53号</t>
+  </si>
+  <si>
+    <t>郭晓明</t>
+  </si>
+  <si>
+    <t>农业综合开发办公室</t>
+  </si>
+  <si>
+    <t>[2021]退54号</t>
+  </si>
+  <si>
+    <t>彭学仪</t>
+  </si>
+  <si>
+    <t>泉江小学</t>
+  </si>
+  <si>
+    <t>[2021]退55号</t>
+  </si>
+  <si>
+    <t>邓院生</t>
+  </si>
+  <si>
+    <t>泉江镇人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退56号</t>
+  </si>
+  <si>
+    <t>曾南云</t>
+  </si>
+  <si>
+    <t>[2021]退57号</t>
+  </si>
+  <si>
+    <t>彭贞爱</t>
+  </si>
+  <si>
+    <t>泉江中学（遂川思源实验学校）</t>
+  </si>
+  <si>
+    <t>[2021]退58号</t>
+  </si>
+  <si>
+    <t>江路秀</t>
+  </si>
+  <si>
+    <t>[2021]退59号</t>
+  </si>
+  <si>
+    <t>冯头根</t>
+  </si>
+  <si>
+    <t>[2021]退60号</t>
+  </si>
+  <si>
+    <t>王淑华</t>
+  </si>
+  <si>
+    <t>[2021]退61号</t>
+  </si>
+  <si>
+    <t>潘曼彬</t>
+  </si>
+  <si>
+    <t>人力资源和社会保障局</t>
+  </si>
+  <si>
+    <t>[2021]退62号</t>
+  </si>
+  <si>
+    <t>郭萍华</t>
+  </si>
+  <si>
+    <t>[2021]退63号</t>
+  </si>
+  <si>
+    <t>邓南放</t>
+  </si>
+  <si>
+    <t>人民代表大会常务委员会</t>
+  </si>
+  <si>
+    <t>[2021]退64号</t>
+  </si>
+  <si>
+    <t>郭江华</t>
+  </si>
+  <si>
+    <t>[2021]退65号</t>
+  </si>
+  <si>
+    <t>郭电英</t>
+  </si>
+  <si>
+    <t>[2021]退66号</t>
+  </si>
+  <si>
+    <t>肖玉兰</t>
+  </si>
+  <si>
+    <t>[2021]退67号</t>
+  </si>
+  <si>
+    <t>曾高峰</t>
+  </si>
+  <si>
+    <t>[2021]退68号</t>
+  </si>
+  <si>
+    <t>钟文英</t>
+  </si>
+  <si>
+    <t>[2021]退69号</t>
+  </si>
+  <si>
+    <t>叶红缨</t>
+  </si>
+  <si>
+    <t>[2021]退70号</t>
+  </si>
+  <si>
+    <t>肖秋生</t>
+  </si>
+  <si>
+    <t>人民政府办公室</t>
+  </si>
+  <si>
+    <t>[2021]退71号</t>
+  </si>
+  <si>
+    <t>刘绪忠</t>
+  </si>
+  <si>
+    <t>[2021]退72号</t>
+  </si>
+  <si>
+    <t>吴慧兰</t>
+  </si>
+  <si>
+    <t>融媒体中心（广播电视台）</t>
+  </si>
+  <si>
+    <t>[2021]退73号</t>
+  </si>
+  <si>
+    <t>李世传</t>
+  </si>
+  <si>
+    <t>上坑中心学校</t>
+  </si>
+  <si>
+    <t>[2021]退74号</t>
+  </si>
+  <si>
+    <t>邹隆霞</t>
+  </si>
+  <si>
+    <t>[2021]退75号</t>
+  </si>
+  <si>
+    <t>温东江</t>
+  </si>
+  <si>
+    <t>审计局</t>
+  </si>
+  <si>
+    <t>[2021]退76号</t>
+  </si>
+  <si>
+    <t>曾荣生</t>
+  </si>
+  <si>
+    <t>市场和质量监督管理局</t>
+  </si>
+  <si>
+    <t>[2021]退77号</t>
+  </si>
+  <si>
+    <t>陈德才</t>
+  </si>
+  <si>
+    <t>[2021]退78号</t>
+  </si>
+  <si>
+    <t>邓德寿</t>
+  </si>
+  <si>
+    <t>[2021]退79号</t>
+  </si>
+  <si>
+    <t>江路达</t>
+  </si>
+  <si>
+    <t>双桥乡人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退80号</t>
+  </si>
+  <si>
+    <t>肖锡光</t>
+  </si>
+  <si>
+    <t>双桥中心学校</t>
+  </si>
+  <si>
+    <t>[2021]退81号</t>
+  </si>
+  <si>
+    <t>肖人才</t>
+  </si>
+  <si>
+    <t>[2021]退82号</t>
+  </si>
+  <si>
+    <t>谢忠善</t>
+  </si>
+  <si>
+    <t>[2021]退83号</t>
+  </si>
+  <si>
+    <t>龙承辉</t>
+  </si>
+  <si>
+    <t>[2021]退84号</t>
+  </si>
+  <si>
+    <t>周樟根</t>
+  </si>
+  <si>
+    <t>水南明德小学</t>
+  </si>
+  <si>
+    <t>[2021]退85号</t>
+  </si>
+  <si>
+    <t>[2021]退86号</t>
+  </si>
+  <si>
+    <t>郭建燕</t>
+  </si>
+  <si>
+    <t>[2021]退87号</t>
+  </si>
+  <si>
+    <t>刘春风</t>
+  </si>
+  <si>
+    <t>[2021]退88号</t>
+  </si>
+  <si>
+    <t>梁智华</t>
+  </si>
+  <si>
+    <t>[2021]退89号</t>
+  </si>
+  <si>
+    <t>刘冬生</t>
+  </si>
+  <si>
+    <t>卫生健康综合监督执法局</t>
+  </si>
+  <si>
+    <t>[2021]退90号</t>
+  </si>
+  <si>
+    <t>钟文盛</t>
+  </si>
+  <si>
+    <t>[2021]退91号</t>
+  </si>
+  <si>
+    <t>骆绍球</t>
+  </si>
+  <si>
+    <t>五斗江乡人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退92号</t>
+  </si>
+  <si>
+    <t>郭晓晨</t>
+  </si>
+  <si>
+    <t>新江乡人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退93号</t>
+  </si>
+  <si>
+    <t>邱汉琳</t>
+  </si>
+  <si>
+    <t>衙前镇人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退94号</t>
+  </si>
+  <si>
+    <t>朱德明</t>
+  </si>
+  <si>
+    <t>衙前中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退95号</t>
+  </si>
+  <si>
+    <t>彭传文</t>
+  </si>
+  <si>
+    <t>[2021]退96号</t>
+  </si>
+  <si>
+    <t>黄启明</t>
+  </si>
+  <si>
+    <t>扬芬中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退97号</t>
+  </si>
+  <si>
+    <t>彭迪安</t>
+  </si>
+  <si>
+    <t>扬芬中学</t>
+  </si>
+  <si>
+    <t>[2021]退98号</t>
+  </si>
+  <si>
+    <t>彭虹</t>
+  </si>
+  <si>
+    <t>瑶厦中学</t>
+  </si>
+  <si>
+    <t>[2021]退99号</t>
+  </si>
+  <si>
+    <t>邓建国</t>
+  </si>
+  <si>
+    <t>[2021]退100号</t>
+  </si>
+  <si>
+    <t>胡伟灼</t>
+  </si>
+  <si>
+    <t>[2021]退101号</t>
+  </si>
+  <si>
+    <t>彭应红</t>
+  </si>
+  <si>
+    <t>[2021]退102号</t>
+  </si>
+  <si>
+    <t>彭曙萍</t>
+  </si>
+  <si>
+    <t>荧屏小学</t>
+  </si>
+  <si>
+    <t>[2021]退103号</t>
+  </si>
+  <si>
+    <t>郭长根</t>
+  </si>
+  <si>
+    <t>雩田第三中学</t>
+  </si>
+  <si>
+    <t>[2021]退104号</t>
+  </si>
+  <si>
+    <t>蒋护清</t>
+  </si>
+  <si>
+    <t>[2021]退105号</t>
+  </si>
+  <si>
+    <t>张春红</t>
+  </si>
+  <si>
+    <t>雩田镇人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退106号</t>
+  </si>
+  <si>
+    <t>康定金</t>
+  </si>
+  <si>
+    <t>雩田中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退107号</t>
+  </si>
+  <si>
+    <t>彭学炫</t>
+  </si>
+  <si>
+    <t>[2021]退108号</t>
+  </si>
+  <si>
+    <t>郭燕生</t>
+  </si>
+  <si>
+    <t>[2021]退109号</t>
+  </si>
+  <si>
+    <t>罗小科</t>
+  </si>
+  <si>
+    <t>[2021]退110号</t>
+  </si>
+  <si>
+    <t>彭宏悠</t>
+  </si>
+  <si>
+    <t>[2021]退111号</t>
+  </si>
+  <si>
+    <t>项翠娥</t>
+  </si>
+  <si>
+    <t>[2021]退112号</t>
+  </si>
+  <si>
+    <t>熊道圳</t>
+  </si>
+  <si>
+    <t>雩田中学</t>
+  </si>
+  <si>
+    <t>[2021]退113号</t>
+  </si>
+  <si>
+    <t>彭桥生</t>
+  </si>
+  <si>
+    <t>珠田乡人民政府</t>
+  </si>
+  <si>
+    <t>[2021]退114号</t>
+  </si>
+  <si>
+    <t>李先智</t>
+  </si>
+  <si>
+    <t>珠田中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退115号</t>
+  </si>
+  <si>
+    <t>曾梅香</t>
+  </si>
+  <si>
+    <t>[2021]退116号</t>
+  </si>
+  <si>
+    <t>住房和城乡建设局</t>
+  </si>
+  <si>
+    <t>[2021]退117号</t>
+  </si>
+  <si>
+    <t>曾建忠</t>
+  </si>
+  <si>
+    <t>左安中心小学</t>
+  </si>
+  <si>
+    <t>[2021]退118号</t>
+  </si>
+  <si>
+    <t>詹林生</t>
+  </si>
+  <si>
+    <t>县委党校</t>
+  </si>
+  <si>
+    <t>[2021]退119号</t>
+  </si>
+  <si>
+    <t>赖晓红</t>
+  </si>
+  <si>
+    <t>中国工农红军正人红军小学</t>
+  </si>
+  <si>
+    <t>[2021]退120号</t>
+  </si>
+  <si>
+    <t>钟书先</t>
+  </si>
+  <si>
+    <t>中国人民政治协商会议委员会</t>
   </si>
 </sst>
 </file>
@@ -3051,11 +4182,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3084,47 +4215,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3137,41 +4236,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3190,9 +4267,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3273,19 +4404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3303,49 +4452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3357,13 +4482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3375,19 +4500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3405,7 +4542,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3417,37 +4572,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3478,45 +4609,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3554,6 +4646,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3587,10 +4718,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3599,133 +4730,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4118,7 +5249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S299"/>
+  <dimension ref="A1:S438"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -4225,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K2" s="8">
         <v>500</v>
@@ -4284,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K3" s="8">
         <v>500</v>
@@ -4343,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K4" s="8">
         <v>500</v>
@@ -4461,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K6" s="8">
         <v>500</v>
@@ -4520,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K7" s="8">
         <v>500</v>
@@ -4638,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K9" s="8">
         <v>500</v>
@@ -4756,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K11" s="8">
         <v>500</v>
@@ -4929,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K14" s="8">
         <v>500</v>
@@ -4988,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K15" s="8">
         <v>500</v>
@@ -5047,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K16" s="8">
         <v>500</v>
@@ -5556,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K25" s="8">
         <v>500</v>
@@ -6890,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="9" t="s">
@@ -12392,9 +13523,7 @@
       <c r="B147" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="C147" s="4"/>
       <c r="D147" s="4" t="s">
         <v>607</v>
       </c>
@@ -12416,9 +13545,7 @@
       <c r="J147" s="4">
         <v>2035</v>
       </c>
-      <c r="K147" s="8">
-        <v>500</v>
-      </c>
+      <c r="K147" s="8"/>
       <c r="L147" s="9" t="s">
         <v>324</v>
       </c>
@@ -12449,9 +13576,7 @@
       <c r="B148" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="C148" s="4"/>
       <c r="D148" s="4" t="s">
         <v>612</v>
       </c>
@@ -12473,9 +13598,7 @@
       <c r="J148" s="4">
         <v>2035</v>
       </c>
-      <c r="K148" s="8">
-        <v>500</v>
-      </c>
+      <c r="K148" s="8"/>
       <c r="L148" s="9" t="s">
         <v>324</v>
       </c>
@@ -12506,9 +13629,7 @@
       <c r="B149" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="C149" s="4"/>
       <c r="D149" s="4" t="s">
         <v>616</v>
       </c>
@@ -12530,9 +13651,7 @@
       <c r="J149" s="4">
         <v>2035</v>
       </c>
-      <c r="K149" s="8">
-        <v>500</v>
-      </c>
+      <c r="K149" s="8"/>
       <c r="L149" s="9" t="s">
         <v>324</v>
       </c>
@@ -14790,7 +15909,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K189" s="8">
         <v>500</v>
@@ -14904,7 +16023,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K191" s="8">
         <v>500</v>
@@ -15022,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="J193" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K193" s="8">
         <v>500</v>
@@ -15081,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K194" s="8">
         <v>500</v>
@@ -15140,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K195" s="8">
         <v>500</v>
@@ -16341,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="4">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K216" s="8">
         <v>500</v>
@@ -20053,7 +21172,7 @@
         <v>0</v>
       </c>
       <c r="J284" s="22">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K284" s="8"/>
       <c r="L284" s="9" t="s">
@@ -20461,7 +21580,7 @@
         <v>0</v>
       </c>
       <c r="J292" s="22">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K292" s="8"/>
       <c r="L292" s="9" t="s">
@@ -20665,7 +21784,7 @@
         <v>0</v>
       </c>
       <c r="J296" s="22">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K296" s="8"/>
       <c r="L296" s="9" t="s">
@@ -20818,7 +21937,7 @@
         <v>0</v>
       </c>
       <c r="J299" s="22">
-        <v>1875</v>
+        <v>1895</v>
       </c>
       <c r="K299" s="8"/>
       <c r="L299" s="9" t="s">
@@ -20840,8 +21959,6411 @@
       <c r="R299" s="7"/>
       <c r="S299" s="7"/>
     </row>
+    <row r="300" spans="1:19">
+      <c r="A300" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E300" s="22">
+        <v>0</v>
+      </c>
+      <c r="F300" s="22">
+        <v>1620</v>
+      </c>
+      <c r="G300" s="22">
+        <v>554</v>
+      </c>
+      <c r="H300" s="22">
+        <v>0</v>
+      </c>
+      <c r="I300" s="22">
+        <v>0</v>
+      </c>
+      <c r="J300" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K300" s="22">
+        <v>0</v>
+      </c>
+      <c r="L300" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="M300" s="4"/>
+      <c r="N300" s="14" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O300" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P300" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="Q300" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R300" s="7"/>
+      <c r="S300" s="7"/>
+    </row>
+    <row r="301" spans="1:19">
+      <c r="A301" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E301" s="22">
+        <v>0</v>
+      </c>
+      <c r="F301" s="22">
+        <v>1840</v>
+      </c>
+      <c r="G301" s="22">
+        <v>1126</v>
+      </c>
+      <c r="H301" s="22">
+        <v>0</v>
+      </c>
+      <c r="I301" s="22">
+        <v>0</v>
+      </c>
+      <c r="J301" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K301" s="22">
+        <v>0</v>
+      </c>
+      <c r="L301" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="M301" s="4"/>
+      <c r="N301" s="14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="O301" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P301" s="7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="Q301" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R301" s="7"/>
+      <c r="S301" s="7"/>
+    </row>
+    <row r="302" spans="1:19">
+      <c r="A302" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B302" t="s">
+        <v>18</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E302" s="22">
+        <v>0</v>
+      </c>
+      <c r="F302" s="22">
+        <v>0</v>
+      </c>
+      <c r="G302" s="22">
+        <v>0</v>
+      </c>
+      <c r="H302" s="22">
+        <v>1660</v>
+      </c>
+      <c r="I302" s="22">
+        <v>0</v>
+      </c>
+      <c r="J302" s="22">
+        <v>1895</v>
+      </c>
+      <c r="K302" s="22">
+        <v>0</v>
+      </c>
+      <c r="L302" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M302" s="4"/>
+      <c r="N302" s="14" t="s">
+        <v>965</v>
+      </c>
+      <c r="O302" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="P302" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q302" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="R302" s="7"/>
+      <c r="S302" s="7"/>
+    </row>
+    <row r="303" spans="1:19">
+      <c r="A303" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B303" t="s">
+        <v>18</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E303" s="22">
+        <v>0</v>
+      </c>
+      <c r="F303" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G303" s="22">
+        <v>746</v>
+      </c>
+      <c r="H303" s="22">
+        <v>0</v>
+      </c>
+      <c r="I303" s="22">
+        <v>0</v>
+      </c>
+      <c r="J303" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K303" s="22">
+        <v>0</v>
+      </c>
+      <c r="L303" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M303" s="4"/>
+      <c r="N303" s="14" t="s">
+        <v>908</v>
+      </c>
+      <c r="O303" s="14" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P303" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q303" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="R303" s="7"/>
+      <c r="S303" s="7"/>
+    </row>
+    <row r="304" spans="1:19">
+      <c r="A304" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B304" t="s">
+        <v>18</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E304" s="22">
+        <v>0</v>
+      </c>
+      <c r="F304" s="22">
+        <v>0</v>
+      </c>
+      <c r="G304" s="22">
+        <v>0</v>
+      </c>
+      <c r="H304" s="22">
+        <v>1660</v>
+      </c>
+      <c r="I304" s="22">
+        <v>0</v>
+      </c>
+      <c r="J304" s="22">
+        <v>1895</v>
+      </c>
+      <c r="K304" s="22">
+        <v>0</v>
+      </c>
+      <c r="L304" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M304" s="4"/>
+      <c r="N304" s="14" t="s">
+        <v>965</v>
+      </c>
+      <c r="O304" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="P304" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q304" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="R304" s="7"/>
+      <c r="S304" s="7"/>
+    </row>
+    <row r="305" ht="27" spans="1:19">
+      <c r="A305" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B305" t="s">
+        <v>18</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E305" s="22">
+        <v>0</v>
+      </c>
+      <c r="F305" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G305" s="22">
+        <v>620</v>
+      </c>
+      <c r="H305" s="22">
+        <v>0</v>
+      </c>
+      <c r="I305" s="22">
+        <v>0</v>
+      </c>
+      <c r="J305" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K305" s="22">
+        <v>0</v>
+      </c>
+      <c r="L305" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M305" s="4"/>
+      <c r="N305" s="14" t="s">
+        <v>908</v>
+      </c>
+      <c r="O305" s="14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="P305" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q305" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="R305" s="7"/>
+      <c r="S305" s="7"/>
+    </row>
+    <row r="306" ht="27" spans="1:19">
+      <c r="A306" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B306" t="s">
+        <v>18</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E306" s="22">
+        <v>0</v>
+      </c>
+      <c r="F306" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G306" s="22">
+        <v>746</v>
+      </c>
+      <c r="H306" s="22">
+        <v>0</v>
+      </c>
+      <c r="I306" s="22">
+        <v>0</v>
+      </c>
+      <c r="J306" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K306" s="22">
+        <v>0</v>
+      </c>
+      <c r="L306" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M306" s="4"/>
+      <c r="N306" s="14" t="s">
+        <v>908</v>
+      </c>
+      <c r="O306" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P306" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q306" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R306" s="7"/>
+      <c r="S306" s="7"/>
+    </row>
+    <row r="307" spans="1:19">
+      <c r="A307" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B307" t="s">
+        <v>18</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E307" s="22">
+        <v>0</v>
+      </c>
+      <c r="F307" s="22">
+        <v>1510</v>
+      </c>
+      <c r="G307" s="22">
+        <v>436</v>
+      </c>
+      <c r="H307" s="22">
+        <v>0</v>
+      </c>
+      <c r="I307" s="22">
+        <v>0</v>
+      </c>
+      <c r="J307" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K307" s="22">
+        <v>0</v>
+      </c>
+      <c r="L307" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="M307" s="4"/>
+      <c r="N307" s="14" t="s">
+        <v>893</v>
+      </c>
+      <c r="O307" s="14" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P307" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="Q307" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="R307" s="7"/>
+      <c r="S307" s="7"/>
+    </row>
+    <row r="308" spans="1:19">
+      <c r="A308" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E308" s="22">
+        <v>1260</v>
+      </c>
+      <c r="F308" s="22">
+        <v>2162</v>
+      </c>
+      <c r="G308" s="22">
+        <v>0</v>
+      </c>
+      <c r="H308" s="22">
+        <v>0</v>
+      </c>
+      <c r="I308" s="22">
+        <v>0</v>
+      </c>
+      <c r="J308" s="22">
+        <v>2265</v>
+      </c>
+      <c r="K308" s="22">
+        <v>0</v>
+      </c>
+      <c r="L308" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M308" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="N308" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="O308" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P308" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="Q308" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="R308" s="7"/>
+      <c r="S308" s="7"/>
+    </row>
+    <row r="309" spans="1:19">
+      <c r="A309" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E309" s="22">
+        <v>1170</v>
+      </c>
+      <c r="F309" s="22">
+        <v>1907</v>
+      </c>
+      <c r="G309" s="22">
+        <v>0</v>
+      </c>
+      <c r="H309" s="22">
+        <v>0</v>
+      </c>
+      <c r="I309" s="22">
+        <v>0</v>
+      </c>
+      <c r="J309" s="22">
+        <v>2265</v>
+      </c>
+      <c r="K309" s="22">
+        <v>0</v>
+      </c>
+      <c r="L309" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M309" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="N309" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="O309" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P309" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q309" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="R309" s="7"/>
+      <c r="S309" s="7"/>
+    </row>
+    <row r="310" spans="1:19">
+      <c r="A310" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E310" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F310" s="22">
+        <v>2058</v>
+      </c>
+      <c r="G310" s="22">
+        <v>0</v>
+      </c>
+      <c r="H310" s="22">
+        <v>0</v>
+      </c>
+      <c r="I310" s="22">
+        <v>0</v>
+      </c>
+      <c r="J310" s="22">
+        <v>2265</v>
+      </c>
+      <c r="K310" s="22">
+        <v>0</v>
+      </c>
+      <c r="L310" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M310" s="4"/>
+      <c r="N310" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="O310" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P310" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="Q310" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="R310" s="7"/>
+      <c r="S310" s="7"/>
+    </row>
+    <row r="311" ht="27" spans="1:19">
+      <c r="A311" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E311" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F311" s="22">
+        <v>1964</v>
+      </c>
+      <c r="G311" s="22">
+        <v>0</v>
+      </c>
+      <c r="H311" s="22">
+        <v>0</v>
+      </c>
+      <c r="I311" s="22">
+        <v>0</v>
+      </c>
+      <c r="J311" s="22">
+        <v>2115</v>
+      </c>
+      <c r="K311" s="22">
+        <v>0</v>
+      </c>
+      <c r="L311" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M311" s="4"/>
+      <c r="N311" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O311" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P311" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Q311" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="R311" s="7"/>
+      <c r="S311" s="7"/>
+    </row>
+    <row r="312" ht="27" spans="1:19">
+      <c r="A312" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E312" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F312" s="22">
+        <v>2115</v>
+      </c>
+      <c r="G312" s="22">
+        <v>0</v>
+      </c>
+      <c r="H312" s="22">
+        <v>0</v>
+      </c>
+      <c r="I312" s="22">
+        <v>0</v>
+      </c>
+      <c r="J312" s="22">
+        <v>2115</v>
+      </c>
+      <c r="K312" s="22">
+        <v>0</v>
+      </c>
+      <c r="L312" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M312" s="4"/>
+      <c r="N312" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="O312" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P312" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="Q312" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="R312" s="7"/>
+      <c r="S312" s="7"/>
+    </row>
+    <row r="313" ht="27" spans="1:19">
+      <c r="A313" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E313" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F313" s="22">
+        <v>1571</v>
+      </c>
+      <c r="G313" s="22">
+        <v>0</v>
+      </c>
+      <c r="H313" s="22">
+        <v>0</v>
+      </c>
+      <c r="I313" s="22">
+        <v>0</v>
+      </c>
+      <c r="J313" s="22">
+        <v>2115</v>
+      </c>
+      <c r="K313" s="22">
+        <v>0</v>
+      </c>
+      <c r="L313" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M313" s="4"/>
+      <c r="N313" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="O313" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P313" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Q313" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="R313" s="7"/>
+      <c r="S313" s="7"/>
+    </row>
+    <row r="314" spans="1:19">
+      <c r="A314" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E314" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F314" s="22">
+        <v>1618</v>
+      </c>
+      <c r="G314" s="22">
+        <v>0</v>
+      </c>
+      <c r="H314" s="22">
+        <v>0</v>
+      </c>
+      <c r="I314" s="22">
+        <v>0</v>
+      </c>
+      <c r="J314" s="22">
+        <v>2115</v>
+      </c>
+      <c r="K314" s="22">
+        <v>0</v>
+      </c>
+      <c r="L314" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M314" s="4"/>
+      <c r="N314" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O314" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P314" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q314" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="R314" s="7"/>
+      <c r="S314" s="7"/>
+    </row>
+    <row r="315" spans="1:19">
+      <c r="A315" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E315" s="22">
+        <v>1010</v>
+      </c>
+      <c r="F315" s="22">
+        <v>1739</v>
+      </c>
+      <c r="G315" s="22">
+        <v>0</v>
+      </c>
+      <c r="H315" s="22">
+        <v>0</v>
+      </c>
+      <c r="I315" s="22">
+        <v>0</v>
+      </c>
+      <c r="J315" s="22">
+        <v>2115</v>
+      </c>
+      <c r="K315" s="22">
+        <v>0</v>
+      </c>
+      <c r="L315" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="M315" s="4"/>
+      <c r="N315" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="O315" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="P315" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q315" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R315" s="7"/>
+      <c r="S315" s="7"/>
+    </row>
+    <row r="316" spans="1:19">
+      <c r="A316" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E316" s="22">
+        <v>0</v>
+      </c>
+      <c r="F316" s="22">
+        <v>1620</v>
+      </c>
+      <c r="G316" s="22">
+        <v>692</v>
+      </c>
+      <c r="H316" s="22">
+        <v>0</v>
+      </c>
+      <c r="I316" s="22">
+        <v>0</v>
+      </c>
+      <c r="J316" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K316" s="22">
+        <v>0</v>
+      </c>
+      <c r="L316" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="M316" s="4"/>
+      <c r="N316" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="O316" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="P316" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="Q316" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="R316" s="7"/>
+      <c r="S316" s="7"/>
+    </row>
+    <row r="317" spans="1:19">
+      <c r="A317" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E317" s="22">
+        <v>0</v>
+      </c>
+      <c r="F317" s="22">
+        <v>1620</v>
+      </c>
+      <c r="G317" s="22">
+        <v>692</v>
+      </c>
+      <c r="H317" s="22">
+        <v>0</v>
+      </c>
+      <c r="I317" s="22">
+        <v>0</v>
+      </c>
+      <c r="J317" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K317" s="22">
+        <v>0</v>
+      </c>
+      <c r="L317" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M317" s="4"/>
+      <c r="N317" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O317" s="14" t="s">
+        <v>821</v>
+      </c>
+      <c r="P317" s="7"/>
+      <c r="Q317" s="3"/>
+      <c r="R317" s="7"/>
+      <c r="S317" s="7"/>
+    </row>
+    <row r="318" spans="1:19">
+      <c r="A318" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E318" s="22">
+        <v>0</v>
+      </c>
+      <c r="F318" s="22">
+        <v>1620</v>
+      </c>
+      <c r="G318" s="22">
+        <v>554</v>
+      </c>
+      <c r="H318" s="22">
+        <v>0</v>
+      </c>
+      <c r="I318" s="22">
+        <v>0</v>
+      </c>
+      <c r="J318" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K318" s="22">
+        <v>0</v>
+      </c>
+      <c r="L318" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M318" s="4"/>
+      <c r="N318" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O318" s="14" t="s">
+        <v>821</v>
+      </c>
+      <c r="P318" s="7"/>
+      <c r="Q318" s="3"/>
+      <c r="R318" s="7"/>
+      <c r="S318" s="7"/>
+    </row>
+    <row r="319" spans="1:15">
+      <c r="A319" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E319" s="4">
+        <v>5653</v>
+      </c>
+      <c r="F319" s="4">
+        <v>0</v>
+      </c>
+      <c r="G319" s="4">
+        <v>0</v>
+      </c>
+      <c r="H319" s="4">
+        <v>0</v>
+      </c>
+      <c r="I319" s="4">
+        <v>0</v>
+      </c>
+      <c r="J319" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K319" s="7">
+        <v>0</v>
+      </c>
+      <c r="L319" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M319" s="4"/>
+      <c r="N319" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O319" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15">
+      <c r="A320" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E320" s="4">
+        <v>7003</v>
+      </c>
+      <c r="F320" s="4">
+        <v>0</v>
+      </c>
+      <c r="G320" s="4">
+        <v>0</v>
+      </c>
+      <c r="H320" s="4">
+        <v>0</v>
+      </c>
+      <c r="I320" s="4">
+        <v>0</v>
+      </c>
+      <c r="J320" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K320" s="7">
+        <v>0</v>
+      </c>
+      <c r="L320" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M320" s="4"/>
+      <c r="N320" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O320" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15">
+      <c r="A321" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E321" s="4">
+        <v>4825</v>
+      </c>
+      <c r="F321" s="4">
+        <v>0</v>
+      </c>
+      <c r="G321" s="4">
+        <v>0</v>
+      </c>
+      <c r="H321" s="4">
+        <v>0</v>
+      </c>
+      <c r="I321" s="4">
+        <v>0</v>
+      </c>
+      <c r="J321" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K321" s="7">
+        <v>0</v>
+      </c>
+      <c r="L321" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M321" s="4"/>
+      <c r="N321" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O321" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15">
+      <c r="A322" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E322" s="4">
+        <v>5624</v>
+      </c>
+      <c r="F322" s="4">
+        <v>0</v>
+      </c>
+      <c r="G322" s="4">
+        <v>0</v>
+      </c>
+      <c r="H322" s="4">
+        <v>0</v>
+      </c>
+      <c r="I322" s="4">
+        <v>0</v>
+      </c>
+      <c r="J322" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K322" s="7">
+        <v>0</v>
+      </c>
+      <c r="L322" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M322" s="4"/>
+      <c r="N322" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O322" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15">
+      <c r="A323" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E323" s="4">
+        <v>6872</v>
+      </c>
+      <c r="F323" s="4">
+        <v>0</v>
+      </c>
+      <c r="G323" s="4">
+        <v>0</v>
+      </c>
+      <c r="H323" s="4">
+        <v>0</v>
+      </c>
+      <c r="I323" s="4">
+        <v>0</v>
+      </c>
+      <c r="J323" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K323" s="7">
+        <v>0</v>
+      </c>
+      <c r="L323" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M323" s="4"/>
+      <c r="N323" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O323" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15">
+      <c r="A324" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E324" s="4">
+        <v>6872</v>
+      </c>
+      <c r="F324" s="4">
+        <v>0</v>
+      </c>
+      <c r="G324" s="4">
+        <v>0</v>
+      </c>
+      <c r="H324" s="4">
+        <v>0</v>
+      </c>
+      <c r="I324" s="4">
+        <v>0</v>
+      </c>
+      <c r="J324" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K324" s="7">
+        <v>0</v>
+      </c>
+      <c r="L324" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M324" s="4"/>
+      <c r="N324" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O324" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15">
+      <c r="A325" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E325" s="4">
+        <v>4950</v>
+      </c>
+      <c r="F325" s="4">
+        <v>0</v>
+      </c>
+      <c r="G325" s="4">
+        <v>0</v>
+      </c>
+      <c r="H325" s="4">
+        <v>0</v>
+      </c>
+      <c r="I325" s="4">
+        <v>0</v>
+      </c>
+      <c r="J325" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K325" s="7">
+        <v>400</v>
+      </c>
+      <c r="L325" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M325" s="4"/>
+      <c r="N325" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O325" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15">
+      <c r="A326" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E326" s="4">
+        <v>5578</v>
+      </c>
+      <c r="F326" s="4">
+        <v>0</v>
+      </c>
+      <c r="G326" s="4">
+        <v>0</v>
+      </c>
+      <c r="H326" s="4">
+        <v>0</v>
+      </c>
+      <c r="I326" s="4">
+        <v>0</v>
+      </c>
+      <c r="J326" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K326" s="7">
+        <v>400</v>
+      </c>
+      <c r="L326" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M326" s="4"/>
+      <c r="N326" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O326" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15">
+      <c r="A327" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E327" s="4">
+        <v>5337</v>
+      </c>
+      <c r="F327" s="4">
+        <v>0</v>
+      </c>
+      <c r="G327" s="4">
+        <v>0</v>
+      </c>
+      <c r="H327" s="4">
+        <v>0</v>
+      </c>
+      <c r="I327" s="4">
+        <v>0</v>
+      </c>
+      <c r="J327" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K327" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L327" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M327" s="4"/>
+      <c r="N327" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O327" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15">
+      <c r="A328" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E328" s="4">
+        <v>5095</v>
+      </c>
+      <c r="F328" s="4">
+        <v>0</v>
+      </c>
+      <c r="G328" s="4">
+        <v>0</v>
+      </c>
+      <c r="H328" s="4">
+        <v>0</v>
+      </c>
+      <c r="I328" s="4">
+        <v>0</v>
+      </c>
+      <c r="J328" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K328" s="7">
+        <v>400</v>
+      </c>
+      <c r="L328" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M328" s="4"/>
+      <c r="N328" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="O328" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15">
+      <c r="A329" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E329" s="4">
+        <v>3817</v>
+      </c>
+      <c r="F329" s="4">
+        <v>0</v>
+      </c>
+      <c r="G329" s="4">
+        <v>0</v>
+      </c>
+      <c r="H329" s="4">
+        <v>0</v>
+      </c>
+      <c r="I329" s="4">
+        <v>0</v>
+      </c>
+      <c r="J329" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K329" s="7">
+        <v>0</v>
+      </c>
+      <c r="L329" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M329" s="4"/>
+      <c r="N329" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O329" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15">
+      <c r="A330" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E330" s="4">
+        <v>4845</v>
+      </c>
+      <c r="F330" s="4">
+        <v>0</v>
+      </c>
+      <c r="G330" s="4">
+        <v>0</v>
+      </c>
+      <c r="H330" s="4">
+        <v>0</v>
+      </c>
+      <c r="I330" s="4">
+        <v>0</v>
+      </c>
+      <c r="J330" s="4">
+        <v>3615</v>
+      </c>
+      <c r="K330" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L330" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M330" s="4"/>
+      <c r="N330" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="O330" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15">
+      <c r="A331" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E331" s="4">
+        <v>5458</v>
+      </c>
+      <c r="F331" s="4">
+        <v>0</v>
+      </c>
+      <c r="G331" s="4">
+        <v>0</v>
+      </c>
+      <c r="H331" s="4">
+        <v>0</v>
+      </c>
+      <c r="I331" s="4">
+        <v>0</v>
+      </c>
+      <c r="J331" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K331" s="7">
+        <v>400</v>
+      </c>
+      <c r="L331" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M331" s="4"/>
+      <c r="N331" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="O331" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15">
+      <c r="A332" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E332" s="4">
+        <v>3500</v>
+      </c>
+      <c r="F332" s="4">
+        <v>0</v>
+      </c>
+      <c r="G332" s="4">
+        <v>0</v>
+      </c>
+      <c r="H332" s="4">
+        <v>0</v>
+      </c>
+      <c r="I332" s="4">
+        <v>0</v>
+      </c>
+      <c r="J332" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K332" s="7">
+        <v>0</v>
+      </c>
+      <c r="L332" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M332" s="4"/>
+      <c r="N332" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="O332" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15">
+      <c r="A333" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5238</v>
+      </c>
+      <c r="F333" s="4">
+        <v>0</v>
+      </c>
+      <c r="G333" s="4">
+        <v>0</v>
+      </c>
+      <c r="H333" s="4">
+        <v>0</v>
+      </c>
+      <c r="I333" s="4">
+        <v>0</v>
+      </c>
+      <c r="J333" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K333" s="7">
+        <v>0</v>
+      </c>
+      <c r="L333" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M333" s="4"/>
+      <c r="N333" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O333" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15">
+      <c r="A334" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D334" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E334" s="4">
+        <v>5689</v>
+      </c>
+      <c r="F334" s="4">
+        <v>0</v>
+      </c>
+      <c r="G334" s="4">
+        <v>0</v>
+      </c>
+      <c r="H334" s="4">
+        <v>0</v>
+      </c>
+      <c r="I334" s="4">
+        <v>0</v>
+      </c>
+      <c r="J334" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K334" s="7">
+        <v>960</v>
+      </c>
+      <c r="L334" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M334" s="4"/>
+      <c r="N334" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="O334" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15">
+      <c r="A335" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E335" s="4">
+        <v>4864</v>
+      </c>
+      <c r="F335" s="4">
+        <v>0</v>
+      </c>
+      <c r="G335" s="4">
+        <v>0</v>
+      </c>
+      <c r="H335" s="4">
+        <v>0</v>
+      </c>
+      <c r="I335" s="4">
+        <v>0</v>
+      </c>
+      <c r="J335" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K335" s="7">
+        <v>810</v>
+      </c>
+      <c r="L335" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M335" s="4"/>
+      <c r="N335" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="O335" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15">
+      <c r="A336" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E336" s="4">
+        <v>5578</v>
+      </c>
+      <c r="F336" s="4">
+        <v>0</v>
+      </c>
+      <c r="G336" s="4">
+        <v>0</v>
+      </c>
+      <c r="H336" s="4">
+        <v>0</v>
+      </c>
+      <c r="I336" s="4">
+        <v>0</v>
+      </c>
+      <c r="J336" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K336" s="7">
+        <v>810</v>
+      </c>
+      <c r="L336" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M336" s="4"/>
+      <c r="N336" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="O336" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15">
+      <c r="A337" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E337" s="4">
+        <v>5327</v>
+      </c>
+      <c r="F337" s="4">
+        <v>0</v>
+      </c>
+      <c r="G337" s="4">
+        <v>0</v>
+      </c>
+      <c r="H337" s="4">
+        <v>0</v>
+      </c>
+      <c r="I337" s="4">
+        <v>0</v>
+      </c>
+      <c r="J337" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K337" s="7">
+        <v>1105</v>
+      </c>
+      <c r="L337" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M337" s="4"/>
+      <c r="N337" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O337" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15">
+      <c r="A338" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E338" s="4">
+        <v>5568</v>
+      </c>
+      <c r="F338" s="4">
+        <v>0</v>
+      </c>
+      <c r="G338" s="4">
+        <v>0</v>
+      </c>
+      <c r="H338" s="4">
+        <v>0</v>
+      </c>
+      <c r="I338" s="4">
+        <v>0</v>
+      </c>
+      <c r="J338" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K338" s="7">
+        <v>1010</v>
+      </c>
+      <c r="L338" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M338" s="4"/>
+      <c r="N338" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O338" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15">
+      <c r="A339" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E339" s="4">
+        <v>4234</v>
+      </c>
+      <c r="F339" s="4">
+        <v>0</v>
+      </c>
+      <c r="G339" s="4">
+        <v>0</v>
+      </c>
+      <c r="H339" s="4">
+        <v>0</v>
+      </c>
+      <c r="I339" s="4">
+        <v>0</v>
+      </c>
+      <c r="J339" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K339" s="7">
+        <v>660</v>
+      </c>
+      <c r="L339" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M339" s="4"/>
+      <c r="N339" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="O339" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15">
+      <c r="A340" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D340" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E340" s="4">
+        <v>4568</v>
+      </c>
+      <c r="F340" s="4">
+        <v>0</v>
+      </c>
+      <c r="G340" s="4">
+        <v>0</v>
+      </c>
+      <c r="H340" s="4">
+        <v>0</v>
+      </c>
+      <c r="I340" s="4">
+        <v>0</v>
+      </c>
+      <c r="J340" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K340" s="7">
+        <v>650</v>
+      </c>
+      <c r="L340" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M340" s="4"/>
+      <c r="N340" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O340" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15">
+      <c r="A341" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E341" s="4">
+        <v>4845</v>
+      </c>
+      <c r="F341" s="4">
+        <v>0</v>
+      </c>
+      <c r="G341" s="4">
+        <v>0</v>
+      </c>
+      <c r="H341" s="4">
+        <v>0</v>
+      </c>
+      <c r="I341" s="4">
+        <v>0</v>
+      </c>
+      <c r="J341" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K341" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L341" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M341" s="4"/>
+      <c r="N341" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O341" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15">
+      <c r="A342" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E342" s="4">
+        <v>3377</v>
+      </c>
+      <c r="F342" s="4">
+        <v>0</v>
+      </c>
+      <c r="G342" s="4">
+        <v>0</v>
+      </c>
+      <c r="H342" s="4">
+        <v>0</v>
+      </c>
+      <c r="I342" s="4">
+        <v>0</v>
+      </c>
+      <c r="J342" s="4">
+        <v>2135</v>
+      </c>
+      <c r="K342" s="7">
+        <v>500</v>
+      </c>
+      <c r="L342" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M342" s="4"/>
+      <c r="N342" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O342" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15">
+      <c r="A343" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E343" s="4">
+        <v>1870.4</v>
+      </c>
+      <c r="F343" s="4">
+        <v>0</v>
+      </c>
+      <c r="G343" s="4">
+        <v>0</v>
+      </c>
+      <c r="H343" s="4">
+        <v>0</v>
+      </c>
+      <c r="I343" s="4">
+        <v>0</v>
+      </c>
+      <c r="J343" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K343" s="7">
+        <v>0</v>
+      </c>
+      <c r="L343" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M343" s="4"/>
+      <c r="N343" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="O343" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15">
+      <c r="A344" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E344" s="4">
+        <v>6095</v>
+      </c>
+      <c r="F344" s="4">
+        <v>0</v>
+      </c>
+      <c r="G344" s="4">
+        <v>0</v>
+      </c>
+      <c r="H344" s="4">
+        <v>0</v>
+      </c>
+      <c r="I344" s="4">
+        <v>0</v>
+      </c>
+      <c r="J344" s="4">
+        <v>3515</v>
+      </c>
+      <c r="K344" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L344" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M344" s="4"/>
+      <c r="N344" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O344" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15">
+      <c r="A345" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E345" s="4">
+        <v>5834</v>
+      </c>
+      <c r="F345" s="4">
+        <v>0</v>
+      </c>
+      <c r="G345" s="4">
+        <v>0</v>
+      </c>
+      <c r="H345" s="4">
+        <v>0</v>
+      </c>
+      <c r="I345" s="4">
+        <v>0</v>
+      </c>
+      <c r="J345" s="4">
+        <v>3430</v>
+      </c>
+      <c r="K345" s="7">
+        <v>650</v>
+      </c>
+      <c r="L345" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M345" s="4"/>
+      <c r="N345" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O345" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15">
+      <c r="A346" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E346" s="4">
+        <v>6168</v>
+      </c>
+      <c r="F346" s="4">
+        <v>0</v>
+      </c>
+      <c r="G346" s="4">
+        <v>0</v>
+      </c>
+      <c r="H346" s="4">
+        <v>0</v>
+      </c>
+      <c r="I346" s="4">
+        <v>0</v>
+      </c>
+      <c r="J346" s="4">
+        <v>3515</v>
+      </c>
+      <c r="K346" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L346" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M346" s="4"/>
+      <c r="N346" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O346" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15">
+      <c r="A347" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E347" s="4">
+        <v>5380</v>
+      </c>
+      <c r="F347" s="4">
+        <v>0</v>
+      </c>
+      <c r="G347" s="4">
+        <v>0</v>
+      </c>
+      <c r="H347" s="4">
+        <v>0</v>
+      </c>
+      <c r="I347" s="4">
+        <v>0</v>
+      </c>
+      <c r="J347" s="4">
+        <v>3345</v>
+      </c>
+      <c r="K347" s="7">
+        <v>1050</v>
+      </c>
+      <c r="L347" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M347" s="4"/>
+      <c r="N347" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="O347" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15">
+      <c r="A348" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E348" s="4">
+        <v>5380</v>
+      </c>
+      <c r="F348" s="4">
+        <v>0</v>
+      </c>
+      <c r="G348" s="4">
+        <v>0</v>
+      </c>
+      <c r="H348" s="4">
+        <v>0</v>
+      </c>
+      <c r="I348" s="4">
+        <v>0</v>
+      </c>
+      <c r="J348" s="4">
+        <v>3345</v>
+      </c>
+      <c r="K348" s="7">
+        <v>1150</v>
+      </c>
+      <c r="L348" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M348" s="4"/>
+      <c r="N348" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="O348" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15">
+      <c r="A349" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E349" s="4">
+        <v>5524</v>
+      </c>
+      <c r="F349" s="4">
+        <v>0</v>
+      </c>
+      <c r="G349" s="4">
+        <v>0</v>
+      </c>
+      <c r="H349" s="4">
+        <v>0</v>
+      </c>
+      <c r="I349" s="4">
+        <v>0</v>
+      </c>
+      <c r="J349" s="4">
+        <v>3125</v>
+      </c>
+      <c r="K349" s="7">
+        <v>650</v>
+      </c>
+      <c r="L349" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M349" s="4"/>
+      <c r="N349" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="O349" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15">
+      <c r="A350" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E350" s="4">
+        <v>4568</v>
+      </c>
+      <c r="F350" s="4">
+        <v>0</v>
+      </c>
+      <c r="G350" s="4">
+        <v>0</v>
+      </c>
+      <c r="H350" s="4">
+        <v>0</v>
+      </c>
+      <c r="I350" s="4">
+        <v>0</v>
+      </c>
+      <c r="J350" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K350" s="7">
+        <v>950</v>
+      </c>
+      <c r="L350" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M350" s="4"/>
+      <c r="N350" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="O350" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15">
+      <c r="A351" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E351" s="4">
+        <v>3466</v>
+      </c>
+      <c r="F351" s="4">
+        <v>0</v>
+      </c>
+      <c r="G351" s="4">
+        <v>0</v>
+      </c>
+      <c r="H351" s="4">
+        <v>0</v>
+      </c>
+      <c r="I351" s="4">
+        <v>0</v>
+      </c>
+      <c r="J351" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K351" s="7">
+        <v>0</v>
+      </c>
+      <c r="L351" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M351" s="4"/>
+      <c r="N351" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="O351" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15">
+      <c r="A352" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E352" s="4">
+        <v>4377</v>
+      </c>
+      <c r="F352" s="4">
+        <v>0</v>
+      </c>
+      <c r="G352" s="4">
+        <v>0</v>
+      </c>
+      <c r="H352" s="4">
+        <v>0</v>
+      </c>
+      <c r="I352" s="4">
+        <v>0</v>
+      </c>
+      <c r="J352" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K352" s="7">
+        <v>0</v>
+      </c>
+      <c r="L352" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M352" s="4"/>
+      <c r="N352" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="O352" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15">
+      <c r="A353" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E353" s="4">
+        <v>5458</v>
+      </c>
+      <c r="F353" s="4">
+        <v>0</v>
+      </c>
+      <c r="G353" s="4">
+        <v>0</v>
+      </c>
+      <c r="H353" s="4">
+        <v>0</v>
+      </c>
+      <c r="I353" s="4">
+        <v>0</v>
+      </c>
+      <c r="J353" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K353" s="7">
+        <v>400</v>
+      </c>
+      <c r="L353" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M353" s="4"/>
+      <c r="N353" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O353" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15">
+      <c r="A354" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E354" s="4">
+        <v>3741</v>
+      </c>
+      <c r="F354" s="4">
+        <v>0</v>
+      </c>
+      <c r="G354" s="4">
+        <v>0</v>
+      </c>
+      <c r="H354" s="4">
+        <v>0</v>
+      </c>
+      <c r="I354" s="4">
+        <v>0</v>
+      </c>
+      <c r="J354" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K354" s="7">
+        <v>650</v>
+      </c>
+      <c r="L354" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M354" s="4"/>
+      <c r="N354" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O354" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15">
+      <c r="A355" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E355" s="4">
+        <v>6413</v>
+      </c>
+      <c r="F355" s="4">
+        <v>0</v>
+      </c>
+      <c r="G355" s="4">
+        <v>0</v>
+      </c>
+      <c r="H355" s="4">
+        <v>0</v>
+      </c>
+      <c r="I355" s="4">
+        <v>0</v>
+      </c>
+      <c r="J355" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K355" s="7">
+        <v>850</v>
+      </c>
+      <c r="L355" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M355" s="4"/>
+      <c r="N355" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="O355" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15">
+      <c r="A356" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E356" s="4">
+        <v>2738</v>
+      </c>
+      <c r="F356" s="4">
+        <v>0</v>
+      </c>
+      <c r="G356" s="4">
+        <v>0</v>
+      </c>
+      <c r="H356" s="4">
+        <v>0</v>
+      </c>
+      <c r="I356" s="4">
+        <v>0</v>
+      </c>
+      <c r="J356" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K356" s="7">
+        <v>0</v>
+      </c>
+      <c r="L356" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M356" s="4"/>
+      <c r="N356" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O356" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15">
+      <c r="A357" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E357" s="4">
+        <v>4278</v>
+      </c>
+      <c r="F357" s="4">
+        <v>0</v>
+      </c>
+      <c r="G357" s="4">
+        <v>0</v>
+      </c>
+      <c r="H357" s="4">
+        <v>0</v>
+      </c>
+      <c r="I357" s="4">
+        <v>0</v>
+      </c>
+      <c r="J357" s="4">
+        <v>2595</v>
+      </c>
+      <c r="K357" s="7">
+        <v>0</v>
+      </c>
+      <c r="L357" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M357" s="4"/>
+      <c r="N357" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="O357" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15">
+      <c r="A358" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E358" s="4">
+        <v>4424</v>
+      </c>
+      <c r="F358" s="4">
+        <v>0</v>
+      </c>
+      <c r="G358" s="4">
+        <v>0</v>
+      </c>
+      <c r="H358" s="4">
+        <v>0</v>
+      </c>
+      <c r="I358" s="4">
+        <v>0</v>
+      </c>
+      <c r="J358" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K358" s="7">
+        <v>650</v>
+      </c>
+      <c r="L358" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M358" s="4"/>
+      <c r="N358" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="O358" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15">
+      <c r="A359" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E359" s="4">
+        <v>4568</v>
+      </c>
+      <c r="F359" s="4">
+        <v>0</v>
+      </c>
+      <c r="G359" s="4">
+        <v>0</v>
+      </c>
+      <c r="H359" s="4">
+        <v>0</v>
+      </c>
+      <c r="I359" s="4">
+        <v>0</v>
+      </c>
+      <c r="J359" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K359" s="7">
+        <v>650</v>
+      </c>
+      <c r="L359" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M359" s="4"/>
+      <c r="N359" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="O359" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15">
+      <c r="A360" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E360" s="4">
+        <v>5495</v>
+      </c>
+      <c r="F360" s="4">
+        <v>0</v>
+      </c>
+      <c r="G360" s="4">
+        <v>0</v>
+      </c>
+      <c r="H360" s="4">
+        <v>0</v>
+      </c>
+      <c r="I360" s="4">
+        <v>0</v>
+      </c>
+      <c r="J360" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K360" s="7">
+        <v>0</v>
+      </c>
+      <c r="L360" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M360" s="4"/>
+      <c r="N360" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="O360" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15">
+      <c r="A361" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E361" s="4">
+        <v>8278</v>
+      </c>
+      <c r="F361" s="4">
+        <v>0</v>
+      </c>
+      <c r="G361" s="4">
+        <v>0</v>
+      </c>
+      <c r="H361" s="4">
+        <v>0</v>
+      </c>
+      <c r="I361" s="4">
+        <v>0</v>
+      </c>
+      <c r="J361" s="4">
+        <v>2335</v>
+      </c>
+      <c r="K361" s="7">
+        <v>0</v>
+      </c>
+      <c r="L361" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M361" s="4"/>
+      <c r="N361" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="O361" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15">
+      <c r="A362" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E362" s="4">
+        <v>3895</v>
+      </c>
+      <c r="F362" s="4">
+        <v>0</v>
+      </c>
+      <c r="G362" s="4">
+        <v>0</v>
+      </c>
+      <c r="H362" s="4">
+        <v>0</v>
+      </c>
+      <c r="I362" s="4">
+        <v>0</v>
+      </c>
+      <c r="J362" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K362" s="7">
+        <v>400</v>
+      </c>
+      <c r="L362" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M362" s="4"/>
+      <c r="N362" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="O362" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15">
+      <c r="A363" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E363" s="4">
+        <v>4134</v>
+      </c>
+      <c r="F363" s="4">
+        <v>0</v>
+      </c>
+      <c r="G363" s="4">
+        <v>0</v>
+      </c>
+      <c r="H363" s="4">
+        <v>0</v>
+      </c>
+      <c r="I363" s="4">
+        <v>0</v>
+      </c>
+      <c r="J363" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K363" s="7">
+        <v>0</v>
+      </c>
+      <c r="L363" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M363" s="4"/>
+      <c r="N363" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="O363" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15">
+      <c r="A364" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E364" s="4">
+        <v>3974</v>
+      </c>
+      <c r="F364" s="4">
+        <v>0</v>
+      </c>
+      <c r="G364" s="4">
+        <v>0</v>
+      </c>
+      <c r="H364" s="4">
+        <v>0</v>
+      </c>
+      <c r="I364" s="4">
+        <v>0</v>
+      </c>
+      <c r="J364" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K364" s="7">
+        <v>0</v>
+      </c>
+      <c r="L364" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M364" s="4"/>
+      <c r="N364" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="O364" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15">
+      <c r="A365" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E365" s="4">
+        <v>4067</v>
+      </c>
+      <c r="F365" s="4">
+        <v>0</v>
+      </c>
+      <c r="G365" s="4">
+        <v>0</v>
+      </c>
+      <c r="H365" s="4">
+        <v>0</v>
+      </c>
+      <c r="I365" s="4">
+        <v>0</v>
+      </c>
+      <c r="J365" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K365" s="7">
+        <v>650</v>
+      </c>
+      <c r="L365" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M365" s="4"/>
+      <c r="N365" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="O365" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15">
+      <c r="A366" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E366" s="4">
+        <v>5085</v>
+      </c>
+      <c r="F366" s="4">
+        <v>0</v>
+      </c>
+      <c r="G366" s="4">
+        <v>0</v>
+      </c>
+      <c r="H366" s="4">
+        <v>0</v>
+      </c>
+      <c r="I366" s="4">
+        <v>0</v>
+      </c>
+      <c r="J366" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K366" s="7">
+        <v>410</v>
+      </c>
+      <c r="L366" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M366" s="4"/>
+      <c r="N366" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="O366" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15">
+      <c r="A367" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E367" s="4">
+        <v>2988</v>
+      </c>
+      <c r="F367" s="4">
+        <v>0</v>
+      </c>
+      <c r="G367" s="4">
+        <v>0</v>
+      </c>
+      <c r="H367" s="4">
+        <v>0</v>
+      </c>
+      <c r="I367" s="4">
+        <v>0</v>
+      </c>
+      <c r="J367" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K367" s="7">
+        <v>0</v>
+      </c>
+      <c r="L367" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M367" s="4"/>
+      <c r="N367" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="O367" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15">
+      <c r="A368" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E368" s="4">
+        <v>4175</v>
+      </c>
+      <c r="F368" s="4">
+        <v>0</v>
+      </c>
+      <c r="G368" s="4">
+        <v>0</v>
+      </c>
+      <c r="H368" s="4">
+        <v>0</v>
+      </c>
+      <c r="I368" s="4">
+        <v>0</v>
+      </c>
+      <c r="J368" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K368" s="7">
+        <v>0</v>
+      </c>
+      <c r="L368" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M368" s="4"/>
+      <c r="N368" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="O368" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15">
+      <c r="A369" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E369" s="4">
+        <v>4999</v>
+      </c>
+      <c r="F369" s="4">
+        <v>0</v>
+      </c>
+      <c r="G369" s="4">
+        <v>0</v>
+      </c>
+      <c r="H369" s="4">
+        <v>0</v>
+      </c>
+      <c r="I369" s="4">
+        <v>0</v>
+      </c>
+      <c r="J369" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K369" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L369" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M369" s="4"/>
+      <c r="N369" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="O369" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="370" spans="1:15">
+      <c r="A370" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E370" s="4">
+        <v>3250</v>
+      </c>
+      <c r="F370" s="4">
+        <v>0</v>
+      </c>
+      <c r="G370" s="4">
+        <v>0</v>
+      </c>
+      <c r="H370" s="4">
+        <v>0</v>
+      </c>
+      <c r="I370" s="4">
+        <v>0</v>
+      </c>
+      <c r="J370" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K370" s="7">
+        <v>0</v>
+      </c>
+      <c r="L370" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M370" s="4"/>
+      <c r="N370" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="O370" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15">
+      <c r="A371" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E371" s="4">
+        <v>4845</v>
+      </c>
+      <c r="F371" s="4">
+        <v>0</v>
+      </c>
+      <c r="G371" s="4">
+        <v>0</v>
+      </c>
+      <c r="H371" s="4">
+        <v>0</v>
+      </c>
+      <c r="I371" s="4">
+        <v>0</v>
+      </c>
+      <c r="J371" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K371" s="7">
+        <v>0</v>
+      </c>
+      <c r="L371" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M371" s="4"/>
+      <c r="N371" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O371" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="372" spans="1:15">
+      <c r="A372" s="4" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E372" s="4">
+        <v>5578</v>
+      </c>
+      <c r="F372" s="4">
+        <v>0</v>
+      </c>
+      <c r="G372" s="4">
+        <v>0</v>
+      </c>
+      <c r="H372" s="4">
+        <v>0</v>
+      </c>
+      <c r="I372" s="4">
+        <v>0</v>
+      </c>
+      <c r="J372" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K372" s="7">
+        <v>400</v>
+      </c>
+      <c r="L372" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M372" s="4"/>
+      <c r="N372" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="O372" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="373" spans="1:15">
+      <c r="A373" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E373" s="4">
+        <v>4105</v>
+      </c>
+      <c r="F373" s="4">
+        <v>0</v>
+      </c>
+      <c r="G373" s="4">
+        <v>0</v>
+      </c>
+      <c r="H373" s="4">
+        <v>0</v>
+      </c>
+      <c r="I373" s="4">
+        <v>0</v>
+      </c>
+      <c r="J373" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K373" s="7">
+        <v>950</v>
+      </c>
+      <c r="L373" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M373" s="4"/>
+      <c r="N373" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O373" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="374" spans="1:15">
+      <c r="A374" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E374" s="4">
+        <v>2738</v>
+      </c>
+      <c r="F374" s="4">
+        <v>0</v>
+      </c>
+      <c r="G374" s="4">
+        <v>0</v>
+      </c>
+      <c r="H374" s="4">
+        <v>0</v>
+      </c>
+      <c r="I374" s="4">
+        <v>0</v>
+      </c>
+      <c r="J374" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K374" s="7">
+        <v>400</v>
+      </c>
+      <c r="L374" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M374" s="4"/>
+      <c r="N374" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="O374" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="375" spans="1:15">
+      <c r="A375" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E375" s="4">
+        <v>5650</v>
+      </c>
+      <c r="F375" s="4">
+        <v>0</v>
+      </c>
+      <c r="G375" s="4">
+        <v>0</v>
+      </c>
+      <c r="H375" s="4">
+        <v>0</v>
+      </c>
+      <c r="I375" s="4">
+        <v>0</v>
+      </c>
+      <c r="J375" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K375" s="7">
+        <v>410</v>
+      </c>
+      <c r="L375" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M375" s="4"/>
+      <c r="N375" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O375" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="376" spans="1:15">
+      <c r="A376" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E376" s="4">
+        <v>5771</v>
+      </c>
+      <c r="F376" s="4">
+        <v>0</v>
+      </c>
+      <c r="G376" s="4">
+        <v>0</v>
+      </c>
+      <c r="H376" s="4">
+        <v>0</v>
+      </c>
+      <c r="I376" s="4">
+        <v>0</v>
+      </c>
+      <c r="J376" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K376" s="7">
+        <v>410</v>
+      </c>
+      <c r="L376" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M376" s="4"/>
+      <c r="N376" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O376" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15">
+      <c r="A377" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E377" s="4">
+        <v>7050</v>
+      </c>
+      <c r="F377" s="4">
+        <v>0</v>
+      </c>
+      <c r="G377" s="4">
+        <v>0</v>
+      </c>
+      <c r="H377" s="4">
+        <v>0</v>
+      </c>
+      <c r="I377" s="4">
+        <v>0</v>
+      </c>
+      <c r="J377" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K377" s="7">
+        <v>410</v>
+      </c>
+      <c r="L377" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M377" s="4"/>
+      <c r="N377" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O377" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15">
+      <c r="A378" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E378" s="4">
+        <v>6786</v>
+      </c>
+      <c r="F378" s="4">
+        <v>0</v>
+      </c>
+      <c r="G378" s="4">
+        <v>0</v>
+      </c>
+      <c r="H378" s="4">
+        <v>0</v>
+      </c>
+      <c r="I378" s="4">
+        <v>0</v>
+      </c>
+      <c r="J378" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K378" s="7">
+        <v>410</v>
+      </c>
+      <c r="L378" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M378" s="4"/>
+      <c r="N378" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O378" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15">
+      <c r="A379" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E379" s="4">
+        <v>3829</v>
+      </c>
+      <c r="F379" s="4">
+        <v>0</v>
+      </c>
+      <c r="G379" s="4">
+        <v>0</v>
+      </c>
+      <c r="H379" s="4">
+        <v>0</v>
+      </c>
+      <c r="I379" s="4">
+        <v>0</v>
+      </c>
+      <c r="J379" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K379" s="7">
+        <v>0</v>
+      </c>
+      <c r="L379" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M379" s="4"/>
+      <c r="N379" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="O379" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15">
+      <c r="A380" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E380" s="4">
+        <v>2952</v>
+      </c>
+      <c r="F380" s="4">
+        <v>0</v>
+      </c>
+      <c r="G380" s="4">
+        <v>0</v>
+      </c>
+      <c r="H380" s="4">
+        <v>0</v>
+      </c>
+      <c r="I380" s="4">
+        <v>0</v>
+      </c>
+      <c r="J380" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K380" s="7">
+        <v>0</v>
+      </c>
+      <c r="L380" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M380" s="4"/>
+      <c r="N380" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="O380" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15">
+      <c r="A381" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E381" s="4">
+        <v>4845</v>
+      </c>
+      <c r="F381" s="4">
+        <v>0</v>
+      </c>
+      <c r="G381" s="4">
+        <v>0</v>
+      </c>
+      <c r="H381" s="4">
+        <v>0</v>
+      </c>
+      <c r="I381" s="4">
+        <v>0</v>
+      </c>
+      <c r="J381" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K381" s="7">
+        <v>0</v>
+      </c>
+      <c r="L381" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M381" s="4"/>
+      <c r="N381" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="O381" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="382" spans="1:15">
+      <c r="A382" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E382" s="4">
+        <v>4146</v>
+      </c>
+      <c r="F382" s="4">
+        <v>0</v>
+      </c>
+      <c r="G382" s="4">
+        <v>0</v>
+      </c>
+      <c r="H382" s="4">
+        <v>0</v>
+      </c>
+      <c r="I382" s="4">
+        <v>0</v>
+      </c>
+      <c r="J382" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K382" s="7">
+        <v>0</v>
+      </c>
+      <c r="L382" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M382" s="4"/>
+      <c r="N382" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O382" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="383" spans="1:15">
+      <c r="A383" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E383" s="4">
+        <v>4208</v>
+      </c>
+      <c r="F383" s="4">
+        <v>0</v>
+      </c>
+      <c r="G383" s="4">
+        <v>0</v>
+      </c>
+      <c r="H383" s="4">
+        <v>0</v>
+      </c>
+      <c r="I383" s="4">
+        <v>0</v>
+      </c>
+      <c r="J383" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K383" s="7">
+        <v>0</v>
+      </c>
+      <c r="L383" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M383" s="4"/>
+      <c r="N383" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O383" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15">
+      <c r="A384" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E384" s="4">
+        <v>6385</v>
+      </c>
+      <c r="F384" s="4">
+        <v>0</v>
+      </c>
+      <c r="G384" s="4">
+        <v>0</v>
+      </c>
+      <c r="H384" s="4">
+        <v>0</v>
+      </c>
+      <c r="I384" s="4">
+        <v>0</v>
+      </c>
+      <c r="J384" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K384" s="7">
+        <v>0</v>
+      </c>
+      <c r="L384" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M384" s="4"/>
+      <c r="N384" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O384" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15">
+      <c r="A385" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E385" s="4">
+        <v>4010</v>
+      </c>
+      <c r="F385" s="4">
+        <v>0</v>
+      </c>
+      <c r="G385" s="4">
+        <v>0</v>
+      </c>
+      <c r="H385" s="4">
+        <v>0</v>
+      </c>
+      <c r="I385" s="4">
+        <v>0</v>
+      </c>
+      <c r="J385" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K385" s="7">
+        <v>0</v>
+      </c>
+      <c r="L385" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M385" s="4"/>
+      <c r="N385" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O385" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="386" spans="1:15">
+      <c r="A386" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E386" s="4">
+        <v>5181</v>
+      </c>
+      <c r="F386" s="4">
+        <v>0</v>
+      </c>
+      <c r="G386" s="4">
+        <v>0</v>
+      </c>
+      <c r="H386" s="4">
+        <v>0</v>
+      </c>
+      <c r="I386" s="4">
+        <v>0</v>
+      </c>
+      <c r="J386" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K386" s="7">
+        <v>0</v>
+      </c>
+      <c r="L386" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M386" s="4"/>
+      <c r="N386" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O386" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="387" spans="1:15">
+      <c r="A387" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E387" s="4">
+        <v>4566</v>
+      </c>
+      <c r="F387" s="4">
+        <v>0</v>
+      </c>
+      <c r="G387" s="4">
+        <v>0</v>
+      </c>
+      <c r="H387" s="4">
+        <v>0</v>
+      </c>
+      <c r="I387" s="4">
+        <v>0</v>
+      </c>
+      <c r="J387" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K387" s="7">
+        <v>0</v>
+      </c>
+      <c r="L387" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M387" s="4"/>
+      <c r="N387" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O387" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="388" spans="1:15">
+      <c r="A388" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E388" s="4">
+        <v>4041</v>
+      </c>
+      <c r="F388" s="4">
+        <v>0</v>
+      </c>
+      <c r="G388" s="4">
+        <v>0</v>
+      </c>
+      <c r="H388" s="4">
+        <v>0</v>
+      </c>
+      <c r="I388" s="4">
+        <v>0</v>
+      </c>
+      <c r="J388" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K388" s="7">
+        <v>550</v>
+      </c>
+      <c r="L388" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M388" s="4"/>
+      <c r="N388" s="4" t="s">
+        <v>1260</v>
+      </c>
+      <c r="O388" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="389" spans="1:15">
+      <c r="A389" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E389" s="4">
+        <v>4154</v>
+      </c>
+      <c r="F389" s="4">
+        <v>0</v>
+      </c>
+      <c r="G389" s="4">
+        <v>0</v>
+      </c>
+      <c r="H389" s="4">
+        <v>0</v>
+      </c>
+      <c r="I389" s="4">
+        <v>0</v>
+      </c>
+      <c r="J389" s="4">
+        <v>2280</v>
+      </c>
+      <c r="K389" s="7">
+        <v>500</v>
+      </c>
+      <c r="L389" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M389" s="4"/>
+      <c r="N389" s="4" t="s">
+        <v>1260</v>
+      </c>
+      <c r="O389" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15">
+      <c r="A390" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E390" s="4">
+        <v>4114</v>
+      </c>
+      <c r="F390" s="4">
+        <v>0</v>
+      </c>
+      <c r="G390" s="4">
+        <v>0</v>
+      </c>
+      <c r="H390" s="4">
+        <v>0</v>
+      </c>
+      <c r="I390" s="4">
+        <v>0</v>
+      </c>
+      <c r="J390" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K390" s="7">
+        <v>0</v>
+      </c>
+      <c r="L390" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M390" s="4"/>
+      <c r="N390" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="O390" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15">
+      <c r="A391" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E391" s="4">
+        <v>4964</v>
+      </c>
+      <c r="F391" s="4">
+        <v>0</v>
+      </c>
+      <c r="G391" s="4">
+        <v>0</v>
+      </c>
+      <c r="H391" s="4">
+        <v>0</v>
+      </c>
+      <c r="I391" s="4">
+        <v>0</v>
+      </c>
+      <c r="J391" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K391" s="7">
+        <v>410</v>
+      </c>
+      <c r="L391" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M391" s="4"/>
+      <c r="N391" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O391" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15">
+      <c r="A392" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D392" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E392" s="4">
+        <v>2760</v>
+      </c>
+      <c r="F392" s="4">
+        <v>0</v>
+      </c>
+      <c r="G392" s="4">
+        <v>0</v>
+      </c>
+      <c r="H392" s="4">
+        <v>0</v>
+      </c>
+      <c r="I392" s="4">
+        <v>0</v>
+      </c>
+      <c r="J392" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K392" s="7">
+        <v>0</v>
+      </c>
+      <c r="L392" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M392" s="4"/>
+      <c r="N392" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="O392" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="393" spans="1:15">
+      <c r="A393" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E393" s="4">
+        <v>5082</v>
+      </c>
+      <c r="F393" s="4">
+        <v>0</v>
+      </c>
+      <c r="G393" s="4">
+        <v>0</v>
+      </c>
+      <c r="H393" s="4">
+        <v>0</v>
+      </c>
+      <c r="I393" s="4">
+        <v>0</v>
+      </c>
+      <c r="J393" s="4">
+        <v>2635</v>
+      </c>
+      <c r="K393" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L393" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M393" s="4"/>
+      <c r="N393" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="O393" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15">
+      <c r="A394" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E394" s="4">
+        <v>4105</v>
+      </c>
+      <c r="F394" s="4">
+        <v>0</v>
+      </c>
+      <c r="G394" s="4">
+        <v>0</v>
+      </c>
+      <c r="H394" s="4">
+        <v>0</v>
+      </c>
+      <c r="I394" s="4">
+        <v>0</v>
+      </c>
+      <c r="J394" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K394" s="7">
+        <v>0</v>
+      </c>
+      <c r="L394" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M394" s="4"/>
+      <c r="N394" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O394" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="395" spans="1:15">
+      <c r="A395" s="4" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E395" s="4">
+        <v>4105</v>
+      </c>
+      <c r="F395" s="4">
+        <v>0</v>
+      </c>
+      <c r="G395" s="4">
+        <v>0</v>
+      </c>
+      <c r="H395" s="4">
+        <v>0</v>
+      </c>
+      <c r="I395" s="4">
+        <v>0</v>
+      </c>
+      <c r="J395" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K395" s="7">
+        <v>0</v>
+      </c>
+      <c r="L395" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M395" s="4"/>
+      <c r="N395" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O395" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15">
+      <c r="A396" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E396" s="4">
+        <v>3971</v>
+      </c>
+      <c r="F396" s="4">
+        <v>0</v>
+      </c>
+      <c r="G396" s="4">
+        <v>0</v>
+      </c>
+      <c r="H396" s="4">
+        <v>0</v>
+      </c>
+      <c r="I396" s="4">
+        <v>0</v>
+      </c>
+      <c r="J396" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K396" s="7">
+        <v>0</v>
+      </c>
+      <c r="L396" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M396" s="4"/>
+      <c r="N396" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="O396" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15">
+      <c r="A397" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E397" s="4">
+        <v>4568</v>
+      </c>
+      <c r="F397" s="4">
+        <v>0</v>
+      </c>
+      <c r="G397" s="4">
+        <v>0</v>
+      </c>
+      <c r="H397" s="4">
+        <v>0</v>
+      </c>
+      <c r="I397" s="4">
+        <v>0</v>
+      </c>
+      <c r="J397" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K397" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L397" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M397" s="4"/>
+      <c r="N397" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O397" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15">
+      <c r="A398" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E398" s="4">
+        <v>5337</v>
+      </c>
+      <c r="F398" s="4">
+        <v>0</v>
+      </c>
+      <c r="G398" s="4">
+        <v>0</v>
+      </c>
+      <c r="H398" s="4">
+        <v>0</v>
+      </c>
+      <c r="I398" s="4">
+        <v>0</v>
+      </c>
+      <c r="J398" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K398" s="7">
+        <v>810</v>
+      </c>
+      <c r="L398" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M398" s="4"/>
+      <c r="N398" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="O398" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="399" spans="1:15">
+      <c r="A399" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E399" s="4">
+        <v>5578</v>
+      </c>
+      <c r="F399" s="4">
+        <v>0</v>
+      </c>
+      <c r="G399" s="4">
+        <v>0</v>
+      </c>
+      <c r="H399" s="4">
+        <v>0</v>
+      </c>
+      <c r="I399" s="4">
+        <v>0</v>
+      </c>
+      <c r="J399" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K399" s="7">
+        <v>810</v>
+      </c>
+      <c r="L399" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M399" s="4"/>
+      <c r="N399" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="O399" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="400" spans="1:15">
+      <c r="A400" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E400" s="4">
+        <v>4424</v>
+      </c>
+      <c r="F400" s="4">
+        <v>0</v>
+      </c>
+      <c r="G400" s="4">
+        <v>0</v>
+      </c>
+      <c r="H400" s="4">
+        <v>0</v>
+      </c>
+      <c r="I400" s="4">
+        <v>0</v>
+      </c>
+      <c r="J400" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K400" s="7">
+        <v>650</v>
+      </c>
+      <c r="L400" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M400" s="4"/>
+      <c r="N400" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="O400" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15">
+      <c r="A401" s="4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E401" s="4">
+        <v>5153</v>
+      </c>
+      <c r="F401" s="4">
+        <v>0</v>
+      </c>
+      <c r="G401" s="4">
+        <v>0</v>
+      </c>
+      <c r="H401" s="4">
+        <v>0</v>
+      </c>
+      <c r="I401" s="4">
+        <v>0</v>
+      </c>
+      <c r="J401" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K401" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L401" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M401" s="4"/>
+      <c r="N401" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="O401" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="402" spans="1:15">
+      <c r="A402" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E402" s="4">
+        <v>5781</v>
+      </c>
+      <c r="F402" s="4">
+        <v>0</v>
+      </c>
+      <c r="G402" s="4">
+        <v>0</v>
+      </c>
+      <c r="H402" s="4">
+        <v>0</v>
+      </c>
+      <c r="I402" s="4">
+        <v>0</v>
+      </c>
+      <c r="J402" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K402" s="7">
+        <v>410</v>
+      </c>
+      <c r="L402" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M402" s="4"/>
+      <c r="N402" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="O402" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15">
+      <c r="A403" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E403" s="4">
+        <v>5781</v>
+      </c>
+      <c r="F403" s="4">
+        <v>0</v>
+      </c>
+      <c r="G403" s="4">
+        <v>0</v>
+      </c>
+      <c r="H403" s="4">
+        <v>0</v>
+      </c>
+      <c r="I403" s="4">
+        <v>0</v>
+      </c>
+      <c r="J403" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K403" s="7">
+        <v>410</v>
+      </c>
+      <c r="L403" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M403" s="4"/>
+      <c r="N403" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="O403" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15">
+      <c r="A404" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E404" s="4">
+        <v>5085</v>
+      </c>
+      <c r="F404" s="4">
+        <v>0</v>
+      </c>
+      <c r="G404" s="4">
+        <v>0</v>
+      </c>
+      <c r="H404" s="4">
+        <v>0</v>
+      </c>
+      <c r="I404" s="4">
+        <v>0</v>
+      </c>
+      <c r="J404" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K404" s="7">
+        <v>210</v>
+      </c>
+      <c r="L404" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M404" s="4"/>
+      <c r="N404" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="O404" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15">
+      <c r="A405" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E405" s="4">
+        <v>4819</v>
+      </c>
+      <c r="F405" s="4">
+        <v>0</v>
+      </c>
+      <c r="G405" s="4">
+        <v>0</v>
+      </c>
+      <c r="H405" s="4">
+        <v>0</v>
+      </c>
+      <c r="I405" s="4">
+        <v>0</v>
+      </c>
+      <c r="J405" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K405" s="7">
+        <v>210</v>
+      </c>
+      <c r="L405" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M405" s="4"/>
+      <c r="N405" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="O405" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="406" spans="1:15">
+      <c r="A406" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E406" s="4">
+        <v>4105</v>
+      </c>
+      <c r="F406" s="4">
+        <v>0</v>
+      </c>
+      <c r="G406" s="4">
+        <v>0</v>
+      </c>
+      <c r="H406" s="4">
+        <v>0</v>
+      </c>
+      <c r="I406" s="4">
+        <v>0</v>
+      </c>
+      <c r="J406" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K406" s="7">
+        <v>0</v>
+      </c>
+      <c r="L406" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M406" s="4"/>
+      <c r="N406" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="O406" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="407" spans="1:15">
+      <c r="A407" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E407" s="4">
+        <v>4803</v>
+      </c>
+      <c r="F407" s="4">
+        <v>0</v>
+      </c>
+      <c r="G407" s="4">
+        <v>0</v>
+      </c>
+      <c r="H407" s="4">
+        <v>0</v>
+      </c>
+      <c r="I407" s="4">
+        <v>0</v>
+      </c>
+      <c r="J407" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K407" s="7">
+        <v>0</v>
+      </c>
+      <c r="L407" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M407" s="4"/>
+      <c r="N407" s="4" t="s">
+        <v>1305</v>
+      </c>
+      <c r="O407" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="408" spans="1:15">
+      <c r="A408" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E408" s="4">
+        <v>3764</v>
+      </c>
+      <c r="F408" s="4">
+        <v>0</v>
+      </c>
+      <c r="G408" s="4">
+        <v>0</v>
+      </c>
+      <c r="H408" s="4">
+        <v>0</v>
+      </c>
+      <c r="I408" s="4">
+        <v>0</v>
+      </c>
+      <c r="J408" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K408" s="7">
+        <v>0</v>
+      </c>
+      <c r="L408" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M408" s="4"/>
+      <c r="N408" s="4" t="s">
+        <v>1305</v>
+      </c>
+      <c r="O408" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15">
+      <c r="A409" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E409" s="4">
+        <v>3116</v>
+      </c>
+      <c r="F409" s="4">
+        <v>0</v>
+      </c>
+      <c r="G409" s="4">
+        <v>0</v>
+      </c>
+      <c r="H409" s="4">
+        <v>0</v>
+      </c>
+      <c r="I409" s="4">
+        <v>0</v>
+      </c>
+      <c r="J409" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K409" s="7">
+        <v>500</v>
+      </c>
+      <c r="L409" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M409" s="4"/>
+      <c r="N409" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="O409" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="410" spans="1:15">
+      <c r="A410" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E410" s="4">
+        <v>3688</v>
+      </c>
+      <c r="F410" s="4">
+        <v>0</v>
+      </c>
+      <c r="G410" s="4">
+        <v>0</v>
+      </c>
+      <c r="H410" s="4">
+        <v>0</v>
+      </c>
+      <c r="I410" s="4">
+        <v>0</v>
+      </c>
+      <c r="J410" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K410" s="7">
+        <v>500</v>
+      </c>
+      <c r="L410" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M410" s="4"/>
+      <c r="N410" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="O410" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="411" spans="1:15">
+      <c r="A411" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E411" s="4">
+        <v>2824</v>
+      </c>
+      <c r="F411" s="4">
+        <v>0</v>
+      </c>
+      <c r="G411" s="4">
+        <v>0</v>
+      </c>
+      <c r="H411" s="4">
+        <v>0</v>
+      </c>
+      <c r="I411" s="4">
+        <v>0</v>
+      </c>
+      <c r="J411" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K411" s="7">
+        <v>450</v>
+      </c>
+      <c r="L411" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M411" s="4"/>
+      <c r="N411" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="O411" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="412" spans="1:15">
+      <c r="A412" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E412" s="4">
+        <v>5327</v>
+      </c>
+      <c r="F412" s="4">
+        <v>0</v>
+      </c>
+      <c r="G412" s="4">
+        <v>0</v>
+      </c>
+      <c r="H412" s="4">
+        <v>0</v>
+      </c>
+      <c r="I412" s="4">
+        <v>0</v>
+      </c>
+      <c r="J412" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K412" s="7">
+        <v>450</v>
+      </c>
+      <c r="L412" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M412" s="4"/>
+      <c r="N412" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="O412" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15">
+      <c r="A413" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E413" s="4">
+        <v>5327</v>
+      </c>
+      <c r="F413" s="4">
+        <v>0</v>
+      </c>
+      <c r="G413" s="4">
+        <v>0</v>
+      </c>
+      <c r="H413" s="4">
+        <v>0</v>
+      </c>
+      <c r="I413" s="4">
+        <v>0</v>
+      </c>
+      <c r="J413" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K413" s="7">
+        <v>450</v>
+      </c>
+      <c r="L413" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M413" s="4"/>
+      <c r="N413" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="O413" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15">
+      <c r="A414" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E414" s="4">
+        <v>5670</v>
+      </c>
+      <c r="F414" s="4">
+        <v>0</v>
+      </c>
+      <c r="G414" s="4">
+        <v>0</v>
+      </c>
+      <c r="H414" s="4">
+        <v>0</v>
+      </c>
+      <c r="I414" s="4">
+        <v>0</v>
+      </c>
+      <c r="J414" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K414" s="7">
+        <v>950</v>
+      </c>
+      <c r="L414" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M414" s="4"/>
+      <c r="N414" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="O414" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="415" spans="1:15">
+      <c r="A415" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E415" s="4">
+        <v>6543</v>
+      </c>
+      <c r="F415" s="4">
+        <v>0</v>
+      </c>
+      <c r="G415" s="4">
+        <v>0</v>
+      </c>
+      <c r="H415" s="4">
+        <v>0</v>
+      </c>
+      <c r="I415" s="4">
+        <v>0</v>
+      </c>
+      <c r="J415" s="4">
+        <v>2535</v>
+      </c>
+      <c r="K415" s="7">
+        <v>450</v>
+      </c>
+      <c r="L415" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M415" s="4"/>
+      <c r="N415" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="O415" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15">
+      <c r="A416" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E416" s="4">
+        <v>5781</v>
+      </c>
+      <c r="F416" s="4">
+        <v>0</v>
+      </c>
+      <c r="G416" s="4">
+        <v>0</v>
+      </c>
+      <c r="H416" s="4">
+        <v>0</v>
+      </c>
+      <c r="I416" s="4">
+        <v>0</v>
+      </c>
+      <c r="J416" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K416" s="7">
+        <v>200</v>
+      </c>
+      <c r="L416" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M416" s="4"/>
+      <c r="N416" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O416" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="417" spans="1:15">
+      <c r="A417" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E417" s="4">
+        <v>6664</v>
+      </c>
+      <c r="F417" s="4">
+        <v>0</v>
+      </c>
+      <c r="G417" s="4">
+        <v>0</v>
+      </c>
+      <c r="H417" s="4">
+        <v>0</v>
+      </c>
+      <c r="I417" s="4">
+        <v>0</v>
+      </c>
+      <c r="J417" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K417" s="7">
+        <v>200</v>
+      </c>
+      <c r="L417" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M417" s="4"/>
+      <c r="N417" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O417" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="418" spans="1:15">
+      <c r="A418" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E418" s="4">
+        <v>6664</v>
+      </c>
+      <c r="F418" s="4">
+        <v>0</v>
+      </c>
+      <c r="G418" s="4">
+        <v>0</v>
+      </c>
+      <c r="H418" s="4">
+        <v>0</v>
+      </c>
+      <c r="I418" s="4">
+        <v>0</v>
+      </c>
+      <c r="J418" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K418" s="7">
+        <v>200</v>
+      </c>
+      <c r="L418" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M418" s="4"/>
+      <c r="N418" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O418" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="419" spans="1:15">
+      <c r="A419" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E419" s="4">
+        <v>5902</v>
+      </c>
+      <c r="F419" s="4">
+        <v>0</v>
+      </c>
+      <c r="G419" s="4">
+        <v>0</v>
+      </c>
+      <c r="H419" s="4">
+        <v>0</v>
+      </c>
+      <c r="I419" s="4">
+        <v>0</v>
+      </c>
+      <c r="J419" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K419" s="7">
+        <v>200</v>
+      </c>
+      <c r="L419" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M419" s="4"/>
+      <c r="N419" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="O419" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15">
+      <c r="A420" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E420" s="4">
+        <v>5095</v>
+      </c>
+      <c r="F420" s="4">
+        <v>0</v>
+      </c>
+      <c r="G420" s="4">
+        <v>0</v>
+      </c>
+      <c r="H420" s="4">
+        <v>0</v>
+      </c>
+      <c r="I420" s="4">
+        <v>0</v>
+      </c>
+      <c r="J420" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K420" s="7">
+        <v>0</v>
+      </c>
+      <c r="L420" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M420" s="4"/>
+      <c r="N420" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="O420" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="421" spans="1:15">
+      <c r="A421" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E421" s="4">
+        <v>7050</v>
+      </c>
+      <c r="F421" s="4">
+        <v>0</v>
+      </c>
+      <c r="G421" s="4">
+        <v>0</v>
+      </c>
+      <c r="H421" s="4">
+        <v>0</v>
+      </c>
+      <c r="I421" s="4">
+        <v>0</v>
+      </c>
+      <c r="J421" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K421" s="7">
+        <v>410</v>
+      </c>
+      <c r="L421" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="M421" s="4"/>
+      <c r="N421" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="O421" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="422" spans="1:15">
+      <c r="A422" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E422" s="4">
+        <v>5892</v>
+      </c>
+      <c r="F422" s="4">
+        <v>0</v>
+      </c>
+      <c r="G422" s="4">
+        <v>0</v>
+      </c>
+      <c r="H422" s="4">
+        <v>0</v>
+      </c>
+      <c r="I422" s="4">
+        <v>0</v>
+      </c>
+      <c r="J422" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K422" s="7">
+        <v>410</v>
+      </c>
+      <c r="L422" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M422" s="4"/>
+      <c r="N422" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="O422" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="423" spans="1:15">
+      <c r="A423" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E423" s="4">
+        <v>3116</v>
+      </c>
+      <c r="F423" s="4">
+        <v>0</v>
+      </c>
+      <c r="G423" s="4">
+        <v>0</v>
+      </c>
+      <c r="H423" s="4">
+        <v>0</v>
+      </c>
+      <c r="I423" s="4">
+        <v>0</v>
+      </c>
+      <c r="J423" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K423" s="7">
+        <v>400</v>
+      </c>
+      <c r="L423" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M423" s="4"/>
+      <c r="N423" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="O423" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="424" spans="1:15">
+      <c r="A424" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E424" s="4">
+        <v>5458</v>
+      </c>
+      <c r="F424" s="4">
+        <v>0</v>
+      </c>
+      <c r="G424" s="4">
+        <v>0</v>
+      </c>
+      <c r="H424" s="4">
+        <v>0</v>
+      </c>
+      <c r="I424" s="4">
+        <v>0</v>
+      </c>
+      <c r="J424" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K424" s="7">
+        <v>400</v>
+      </c>
+      <c r="L424" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M424" s="4"/>
+      <c r="N424" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O424" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="425" spans="1:15">
+      <c r="A425" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E425" s="4">
+        <v>4974</v>
+      </c>
+      <c r="F425" s="4">
+        <v>0</v>
+      </c>
+      <c r="G425" s="4">
+        <v>0</v>
+      </c>
+      <c r="H425" s="4">
+        <v>0</v>
+      </c>
+      <c r="I425" s="4">
+        <v>0</v>
+      </c>
+      <c r="J425" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K425" s="7">
+        <v>400</v>
+      </c>
+      <c r="L425" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M425" s="4"/>
+      <c r="N425" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O425" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="426" spans="1:15">
+      <c r="A426" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E426" s="4">
+        <v>5071</v>
+      </c>
+      <c r="F426" s="4">
+        <v>0</v>
+      </c>
+      <c r="G426" s="4">
+        <v>0</v>
+      </c>
+      <c r="H426" s="4">
+        <v>0</v>
+      </c>
+      <c r="I426" s="4">
+        <v>0</v>
+      </c>
+      <c r="J426" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K426" s="7">
+        <v>400</v>
+      </c>
+      <c r="L426" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M426" s="4"/>
+      <c r="N426" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O426" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="427" spans="1:15">
+      <c r="A427" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E427" s="4">
+        <v>5911</v>
+      </c>
+      <c r="F427" s="4">
+        <v>0</v>
+      </c>
+      <c r="G427" s="4">
+        <v>0</v>
+      </c>
+      <c r="H427" s="4">
+        <v>0</v>
+      </c>
+      <c r="I427" s="4">
+        <v>0</v>
+      </c>
+      <c r="J427" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K427" s="7">
+        <v>400</v>
+      </c>
+      <c r="L427" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="M427" s="4"/>
+      <c r="N427" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O427" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="428" spans="1:15">
+      <c r="A428" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E428" s="4">
+        <v>5192</v>
+      </c>
+      <c r="F428" s="4">
+        <v>0</v>
+      </c>
+      <c r="G428" s="4">
+        <v>0</v>
+      </c>
+      <c r="H428" s="4">
+        <v>0</v>
+      </c>
+      <c r="I428" s="4">
+        <v>0</v>
+      </c>
+      <c r="J428" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K428" s="7">
+        <v>0</v>
+      </c>
+      <c r="L428" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M428" s="4"/>
+      <c r="N428" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O428" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="429" spans="1:15">
+      <c r="A429" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E429" s="4">
+        <v>5428</v>
+      </c>
+      <c r="F429" s="4">
+        <v>0</v>
+      </c>
+      <c r="G429" s="4">
+        <v>0</v>
+      </c>
+      <c r="H429" s="4">
+        <v>0</v>
+      </c>
+      <c r="I429" s="4">
+        <v>0</v>
+      </c>
+      <c r="J429" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K429" s="7">
+        <v>400</v>
+      </c>
+      <c r="L429" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M429" s="4"/>
+      <c r="N429" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O429" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15">
+      <c r="A430" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E430" s="4">
+        <v>6654</v>
+      </c>
+      <c r="F430" s="4">
+        <v>0</v>
+      </c>
+      <c r="G430" s="4">
+        <v>0</v>
+      </c>
+      <c r="H430" s="4">
+        <v>0</v>
+      </c>
+      <c r="I430" s="4">
+        <v>0</v>
+      </c>
+      <c r="J430" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K430" s="7">
+        <v>410</v>
+      </c>
+      <c r="L430" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M430" s="4"/>
+      <c r="N430" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="O430" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="431" spans="1:15">
+      <c r="A431" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E431" s="4">
+        <v>3939</v>
+      </c>
+      <c r="F431" s="4">
+        <v>0</v>
+      </c>
+      <c r="G431" s="4">
+        <v>0</v>
+      </c>
+      <c r="H431" s="4">
+        <v>0</v>
+      </c>
+      <c r="I431" s="4">
+        <v>0</v>
+      </c>
+      <c r="J431" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K431" s="7">
+        <v>400</v>
+      </c>
+      <c r="L431" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M431" s="4"/>
+      <c r="N431" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="O431" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="432" spans="1:15">
+      <c r="A432" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E432" s="4">
+        <v>6013</v>
+      </c>
+      <c r="F432" s="4">
+        <v>0</v>
+      </c>
+      <c r="G432" s="4">
+        <v>0</v>
+      </c>
+      <c r="H432" s="4">
+        <v>0</v>
+      </c>
+      <c r="I432" s="4">
+        <v>0</v>
+      </c>
+      <c r="J432" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K432" s="7">
+        <v>410</v>
+      </c>
+      <c r="L432" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M432" s="4"/>
+      <c r="N432" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="O432" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="433" spans="1:15">
+      <c r="A433" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E433" s="4">
+        <v>5085</v>
+      </c>
+      <c r="F433" s="4">
+        <v>0</v>
+      </c>
+      <c r="G433" s="4">
+        <v>0</v>
+      </c>
+      <c r="H433" s="4">
+        <v>0</v>
+      </c>
+      <c r="I433" s="4">
+        <v>0</v>
+      </c>
+      <c r="J433" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K433" s="7">
+        <v>410</v>
+      </c>
+      <c r="L433" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M433" s="4"/>
+      <c r="N433" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="O433" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="434" spans="1:15">
+      <c r="A434" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E434" s="4">
+        <v>4424</v>
+      </c>
+      <c r="F434" s="4">
+        <v>0</v>
+      </c>
+      <c r="G434" s="4">
+        <v>0</v>
+      </c>
+      <c r="H434" s="4">
+        <v>0</v>
+      </c>
+      <c r="I434" s="4">
+        <v>0</v>
+      </c>
+      <c r="J434" s="4">
+        <v>2245</v>
+      </c>
+      <c r="K434" s="7">
+        <v>650</v>
+      </c>
+      <c r="L434" s="9" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M434" s="4"/>
+      <c r="N434" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="O434" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="435" spans="1:15">
+      <c r="A435" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E435" s="4">
+        <v>5216</v>
+      </c>
+      <c r="F435" s="4">
+        <v>0</v>
+      </c>
+      <c r="G435" s="4">
+        <v>0</v>
+      </c>
+      <c r="H435" s="4">
+        <v>0</v>
+      </c>
+      <c r="I435" s="4">
+        <v>0</v>
+      </c>
+      <c r="J435" s="4">
+        <v>2235</v>
+      </c>
+      <c r="K435" s="7">
+        <v>867</v>
+      </c>
+      <c r="L435" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M435" s="4"/>
+      <c r="N435" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="O435" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="436" spans="1:15">
+      <c r="A436" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E436" s="4">
+        <v>3971</v>
+      </c>
+      <c r="F436" s="4">
+        <v>0</v>
+      </c>
+      <c r="G436" s="4">
+        <v>0</v>
+      </c>
+      <c r="H436" s="4">
+        <v>0</v>
+      </c>
+      <c r="I436" s="4">
+        <v>0</v>
+      </c>
+      <c r="J436" s="4">
+        <v>2115</v>
+      </c>
+      <c r="K436" s="7">
+        <v>0</v>
+      </c>
+      <c r="L436" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M436" s="4"/>
+      <c r="N436" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="O436" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="437" spans="1:15">
+      <c r="A437" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E437" s="4">
+        <v>5095</v>
+      </c>
+      <c r="F437" s="4">
+        <v>0</v>
+      </c>
+      <c r="G437" s="4">
+        <v>0</v>
+      </c>
+      <c r="H437" s="4">
+        <v>0</v>
+      </c>
+      <c r="I437" s="4">
+        <v>0</v>
+      </c>
+      <c r="J437" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K437" s="7">
+        <v>200</v>
+      </c>
+      <c r="L437" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M437" s="4"/>
+      <c r="N437" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="O437" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="438" spans="1:15">
+      <c r="A438" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E438" s="4">
+        <v>4999</v>
+      </c>
+      <c r="F438" s="4">
+        <v>0</v>
+      </c>
+      <c r="G438" s="4">
+        <v>0</v>
+      </c>
+      <c r="H438" s="4">
+        <v>0</v>
+      </c>
+      <c r="I438" s="4">
+        <v>0</v>
+      </c>
+      <c r="J438" s="4">
+        <v>2415</v>
+      </c>
+      <c r="K438" s="7">
+        <v>0</v>
+      </c>
+      <c r="L438" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M438" s="4"/>
+      <c r="N438" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="O438" s="7" t="s">
+        <v>1079</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="D1:O299">
+  <autoFilter ref="D1:O438">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -10,14 +10,14 @@
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$440</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$441</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4293" uniqueCount="1369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4301" uniqueCount="1372">
   <si>
     <t>单号</t>
   </si>
@@ -1513,10 +1513,10 @@
     <t>郭显清</t>
   </si>
   <si>
-    <t>卫生健康委员会</t>
-  </si>
-  <si>
-    <t>县卫生健康委员会</t>
+    <t>卫健委</t>
+  </si>
+  <si>
+    <t>县卫健委</t>
   </si>
   <si>
     <t>[2021]第106号</t>
@@ -3535,7 +3535,7 @@
     <t>郭晓明</t>
   </si>
   <si>
-    <t>农业综合开发办公室</t>
+    <t>开发办</t>
   </si>
   <si>
     <t>[2021]退38号</t>
@@ -3571,7 +3571,7 @@
     <t>邓南放</t>
   </si>
   <si>
-    <t>人民代表大会常务委员会</t>
+    <t>人大办</t>
   </si>
   <si>
     <t>[2021]退43号</t>
@@ -3631,7 +3631,7 @@
     <t>吴慧兰</t>
   </si>
   <si>
-    <t>融媒体中心（广播电视台）</t>
+    <t>融媒体中心</t>
   </si>
   <si>
     <t>[2021]退52号</t>
@@ -4009,7 +4009,7 @@
     <t>[2021]辞30号</t>
   </si>
   <si>
-    <t xml:space="preserve">李小雪 </t>
+    <t>李小雪</t>
   </si>
   <si>
     <t>[2021]辞31号</t>
@@ -4124,6 +4124,15 @@
   </si>
   <si>
     <t>段敏</t>
+  </si>
+  <si>
+    <t>[2021]辞48号</t>
+  </si>
+  <si>
+    <t>黄翔</t>
+  </si>
+  <si>
+    <t>2021-12-01</t>
   </si>
 </sst>
 </file>
@@ -4131,11 +4140,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -4165,28 +4174,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4200,24 +4195,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4231,9 +4210,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4255,10 +4279,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4270,34 +4294,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4353,13 +4362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4371,25 +4404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4401,25 +4452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4437,31 +4488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4473,31 +4512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4509,31 +4536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4562,6 +4571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -4573,6 +4606,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4594,65 +4662,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -4667,10 +4676,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4679,133 +4688,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5198,7 +5207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T440"/>
+  <dimension ref="A1:T441"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -5207,8 +5216,8 @@
     <col min="7" max="7" width="12.625"/>
     <col min="9" max="9" width="7.625" customWidth="1"/>
     <col min="11" max="11" width="8.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="15" width="35.875" style="1" customWidth="1"/>
     <col min="16" max="16" width="28.625" style="1" customWidth="1"/>
@@ -24586,7 +24595,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="355" spans="1:15">
+    <row r="355" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>1170</v>
       </c>
@@ -24625,10 +24634,13 @@
       </c>
       <c r="M355" s="4"/>
       <c r="N355" s="4" t="s">
-        <v>1172</v>
+        <v>467</v>
       </c>
       <c r="O355" s="7" t="s">
         <v>1080</v>
+      </c>
+      <c r="P355" s="1" t="s">
+        <v>1172</v>
       </c>
     </row>
     <row r="356" spans="1:15">
@@ -28354,8 +28366,51 @@
         <v>1250</v>
       </c>
     </row>
+    <row r="441" spans="1:15">
+      <c r="A441" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E441" s="4">
+        <v>780</v>
+      </c>
+      <c r="F441" s="4">
+        <v>1575</v>
+      </c>
+      <c r="G441" s="4">
+        <v>0</v>
+      </c>
+      <c r="H441" s="4">
+        <v>0</v>
+      </c>
+      <c r="I441" s="4">
+        <v>0</v>
+      </c>
+      <c r="J441" s="4">
+        <v>2035</v>
+      </c>
+      <c r="K441" s="7"/>
+      <c r="L441" s="9" t="s">
+        <v>1371</v>
+      </c>
+      <c r="M441" s="4"/>
+      <c r="N441" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="O441" s="7" t="s">
+        <v>1250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T440">
+  <autoFilter ref="A1:T441">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -10,14 +10,14 @@
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$496</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$484</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4799" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4691" uniqueCount="1509">
   <si>
     <t>单号</t>
   </si>
@@ -2095,7 +2095,7 @@
     <t>王荣平</t>
   </si>
   <si>
-    <t>南北澳陂水利工程管理站</t>
+    <t>水利工程建设管护中心</t>
   </si>
   <si>
     <t>县南北澳陂水利工程管理站</t>
@@ -4108,18 +4108,6 @@
     <t>县文化市场综合执法大队事业干部（全拨事业）</t>
   </si>
   <si>
-    <t>[2021]行04号</t>
-  </si>
-  <si>
-    <t>肖萍</t>
-  </si>
-  <si>
-    <t>遂川县衙前镇政府事业干部</t>
-  </si>
-  <si>
-    <t>遂川县关心下一代工作委员会办公室</t>
-  </si>
-  <si>
     <t>[2021]行05号</t>
   </si>
   <si>
@@ -4132,126 +4120,21 @@
     <t>县图书馆事业干部</t>
   </si>
   <si>
-    <t>[2021]行06号</t>
-  </si>
-  <si>
-    <t>朱八生</t>
-  </si>
-  <si>
-    <t>人武部</t>
-  </si>
-  <si>
-    <t>江西省遂川县人民武装部</t>
-  </si>
-  <si>
-    <t>遂川县公安局</t>
-  </si>
-  <si>
-    <t>[2021]行07号</t>
-  </si>
-  <si>
-    <t>郭婷</t>
-  </si>
-  <si>
-    <t>珠田乡政府事业干部</t>
-  </si>
-  <si>
-    <t>县人大代表联络服务中心事业干部</t>
-  </si>
-  <si>
-    <t>[2021]行08号</t>
-  </si>
-  <si>
-    <t>包倩倩</t>
-  </si>
-  <si>
-    <t>民政局事业干部</t>
-  </si>
-  <si>
-    <t>[2021]行09号</t>
-  </si>
-  <si>
-    <t>张舟欣</t>
-  </si>
-  <si>
-    <t>西溪乡政府事业干部</t>
-  </si>
-  <si>
-    <t>县金融办事业干部（全拨事业）</t>
-  </si>
-  <si>
-    <t>[2021]行10号</t>
-  </si>
-  <si>
-    <t>骆宇</t>
-  </si>
-  <si>
-    <t>宣传部</t>
-  </si>
-  <si>
-    <t>大坑乡政府事业干部</t>
-  </si>
-  <si>
-    <t>县网信办事业干部</t>
-  </si>
-  <si>
-    <t>[2021]行11号</t>
-  </si>
-  <si>
-    <t>李晓明</t>
-  </si>
-  <si>
-    <t>县民族宗教服务中心</t>
-  </si>
-  <si>
-    <t>[2021]行12号</t>
-  </si>
-  <si>
-    <t>樊晓梅</t>
+    <t>[2021]行13号</t>
+  </si>
+  <si>
+    <t>刘毓</t>
   </si>
   <si>
     <t>会计核算中心</t>
   </si>
   <si>
-    <t>双桥乡政府事业干部</t>
-  </si>
-  <si>
-    <t>县会计核算中心事业干部</t>
-  </si>
-  <si>
-    <t>[2021]行13号</t>
-  </si>
-  <si>
-    <t>刘毓</t>
-  </si>
-  <si>
     <t>县移民扶贫办事业干部</t>
   </si>
   <si>
     <t>县会计核算中心事业干部（全拨事业）</t>
   </si>
   <si>
-    <t>[2021]行14号</t>
-  </si>
-  <si>
-    <t>杨小青</t>
-  </si>
-  <si>
-    <t>县总工会退管办事业干部</t>
-  </si>
-  <si>
-    <t>[2021]行15号</t>
-  </si>
-  <si>
-    <t>彭玉龙</t>
-  </si>
-  <si>
-    <t>汤湖镇政府事业干部</t>
-  </si>
-  <si>
-    <t>县红色文化传承中心事业干部</t>
-  </si>
-  <si>
     <t>[2021]行16号</t>
   </si>
   <si>
@@ -4280,24 +4163,6 @@
   </si>
   <si>
     <t>县委第一巡察组</t>
-  </si>
-  <si>
-    <t>[2021]行19号</t>
-  </si>
-  <si>
-    <t>黄厚杰</t>
-  </si>
-  <si>
-    <t>县博物馆事业干部（全拨事业）</t>
-  </si>
-  <si>
-    <t>[2021]行20号</t>
-  </si>
-  <si>
-    <t>郭清华</t>
-  </si>
-  <si>
-    <t>县水利局事业干部</t>
   </si>
   <si>
     <t>[2021]行21号</t>
@@ -4686,10 +4551,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
@@ -4737,22 +4602,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4765,9 +4617,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4782,22 +4640,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4843,6 +4716,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -4858,24 +4739,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4944,7 +4809,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4956,43 +4851,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5010,25 +4911,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5040,13 +4953,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5058,67 +4983,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5168,6 +5033,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -5184,16 +5064,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5209,6 +5089,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5231,37 +5122,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5273,10 +5138,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5285,34 +5150,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5324,98 +5186,101 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5500,22 +5365,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5837,7 +5693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T496"/>
+  <dimension ref="A1:T484"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -9113,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="4">
-        <v>1840</v>
+        <v>0</v>
       </c>
       <c r="G58" s="4">
-        <v>1790</v>
+        <v>0</v>
       </c>
       <c r="H58" s="4">
         <v>0</v>
@@ -9125,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="4">
-        <v>2265</v>
+        <v>0</v>
       </c>
       <c r="K58" s="15"/>
       <c r="L58" s="9" t="s">
@@ -29079,7 +28935,7 @@
       <c r="O442" s="4" t="s">
         <v>1351</v>
       </c>
-      <c r="P442" s="30" t="s">
+      <c r="P442" s="28" t="s">
         <v>1352</v>
       </c>
       <c r="Q442" s="4" t="s">
@@ -29126,7 +28982,7 @@
       <c r="O443" s="4" t="s">
         <v>1351</v>
       </c>
-      <c r="P443" s="30" t="s">
+      <c r="P443" s="28" t="s">
         <v>1356</v>
       </c>
       <c r="Q443" s="4" t="s">
@@ -29167,13 +29023,13 @@
       <c r="L444" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N444" s="30" t="s">
+      <c r="N444" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="O444" s="31" t="s">
+      <c r="O444" s="29" t="s">
         <v>1360</v>
       </c>
-      <c r="P444" s="30" t="s">
+      <c r="P444" s="28" t="s">
         <v>1361</v>
       </c>
       <c r="Q444" s="4" t="s">
@@ -29190,16 +29046,16 @@
       <c r="C445" t="s">
         <v>88</v>
       </c>
-      <c r="D445" s="28" t="s">
+      <c r="D445" s="27" t="s">
         <v>1364</v>
       </c>
-      <c r="E445" s="29">
+      <c r="E445" s="4">
         <v>1620</v>
       </c>
-      <c r="F445" s="29">
-        <v>513</v>
-      </c>
-      <c r="G445" s="29">
+      <c r="F445" s="4">
+        <v>920</v>
+      </c>
+      <c r="G445" s="4">
         <v>0</v>
       </c>
       <c r="H445" s="4">
@@ -29211,19 +29067,19 @@
       <c r="J445" s="4">
         <v>2035</v>
       </c>
-      <c r="L445" s="32" t="s">
+      <c r="L445" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N445" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="O445" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="P445" s="29" t="s">
+      <c r="N445" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="O445" s="4" t="s">
         <v>1365</v>
       </c>
-      <c r="Q445" s="29" t="s">
+      <c r="P445" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q445" s="4" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -29241,13 +29097,13 @@
         <v>1368</v>
       </c>
       <c r="E446" s="4">
+        <v>0</v>
+      </c>
+      <c r="F446" s="4">
         <v>1620</v>
       </c>
-      <c r="F446" s="4">
-        <v>920</v>
-      </c>
       <c r="G446" s="4">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="H446" s="4">
         <v>0</v>
@@ -29261,22 +29117,22 @@
       <c r="L446" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N446" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="O446" s="4" t="s">
+      <c r="N446" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="O446" s="30" t="s">
         <v>1369</v>
       </c>
-      <c r="P446" s="30" t="s">
-        <v>72</v>
+      <c r="P446" s="28" t="s">
+        <v>1370</v>
       </c>
       <c r="Q446" s="4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="447" ht="17.25" spans="1:17">
       <c r="A447" s="4" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B447" t="s">
         <v>38</v>
@@ -29284,16 +29140,16 @@
       <c r="C447" t="s">
         <v>88</v>
       </c>
-      <c r="D447" s="28" t="s">
-        <v>1372</v>
-      </c>
-      <c r="E447" s="29">
-        <v>1630</v>
-      </c>
-      <c r="F447" s="29">
-        <v>2495</v>
-      </c>
-      <c r="G447" s="29">
+      <c r="D447" s="27" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E447" s="4">
+        <v>1620</v>
+      </c>
+      <c r="F447" s="4">
+        <v>513</v>
+      </c>
+      <c r="G447" s="4">
         <v>0</v>
       </c>
       <c r="H447" s="4">
@@ -29305,19 +29161,19 @@
       <c r="J447" s="4">
         <v>2035</v>
       </c>
-      <c r="L447" s="32" t="s">
+      <c r="L447" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N447" s="25" t="s">
-        <v>1373</v>
-      </c>
-      <c r="O447" s="29" t="s">
-        <v>835</v>
-      </c>
-      <c r="P447" s="29" t="s">
+      <c r="N447" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="O447" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="P447" s="28" t="s">
         <v>1374</v>
       </c>
-      <c r="Q447" s="29" t="s">
+      <c r="Q447" s="4" t="s">
         <v>1375</v>
       </c>
     </row>
@@ -29328,17 +29184,17 @@
       <c r="B448" t="s">
         <v>38</v>
       </c>
-      <c r="C448" t="s">
-        <v>88</v>
+      <c r="C448" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D448" s="27" t="s">
         <v>1377</v>
       </c>
       <c r="E448" s="4">
-        <v>1620</v>
+        <v>780</v>
       </c>
       <c r="F448" s="4">
-        <v>692</v>
+        <v>1380</v>
       </c>
       <c r="G448" s="4">
         <v>0</v>
@@ -29349,46 +29205,49 @@
       <c r="I448" s="4">
         <v>0</v>
       </c>
-      <c r="J448" s="4">
+      <c r="J448">
         <v>2035</v>
+      </c>
+      <c r="K448" s="1">
+        <v>500</v>
       </c>
       <c r="L448" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N448" s="30" t="s">
-        <v>1218</v>
-      </c>
-      <c r="O448" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P448" s="30" t="s">
+      <c r="N448" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="O448" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P448" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q448" s="4" t="s">
         <v>1378</v>
       </c>
-      <c r="Q448" s="4" t="s">
+    </row>
+    <row r="449" ht="18" spans="1:17">
+      <c r="A449" s="4" t="s">
         <v>1379</v>
-      </c>
-    </row>
-    <row r="449" ht="17.25" spans="1:17">
-      <c r="A449" s="4" t="s">
-        <v>1380</v>
       </c>
       <c r="B449" t="s">
         <v>38</v>
       </c>
-      <c r="C449" t="s">
-        <v>88</v>
+      <c r="C449" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D449" s="27" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E449" s="4">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="F449" s="4">
-        <v>1640</v>
+        <v>1380</v>
       </c>
       <c r="G449" s="4">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H449" s="4">
         <v>0</v>
@@ -29396,90 +29255,96 @@
       <c r="I449" s="4">
         <v>0</v>
       </c>
-      <c r="J449" s="4">
+      <c r="J449">
         <v>2035</v>
+      </c>
+      <c r="K449" s="1">
+        <v>500</v>
       </c>
       <c r="L449" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N449" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="O449" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P449" s="30" t="s">
+      <c r="N449" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="O449" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P449" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q449" s="4" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="450" ht="18" spans="1:17">
+      <c r="A450" s="4" t="s">
         <v>1382</v>
-      </c>
-      <c r="Q449" s="4" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="450" ht="17.25" spans="1:17">
-      <c r="A450" s="4" t="s">
-        <v>1383</v>
       </c>
       <c r="B450" t="s">
         <v>38</v>
       </c>
-      <c r="C450" t="s">
-        <v>88</v>
+      <c r="C450" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D450" s="27" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E450" s="4">
+        <v>780</v>
+      </c>
+      <c r="F450" s="4">
+        <v>1380</v>
+      </c>
+      <c r="G450" s="4">
+        <v>0</v>
+      </c>
+      <c r="H450" s="4">
+        <v>0</v>
+      </c>
+      <c r="I450" s="4">
+        <v>0</v>
+      </c>
+      <c r="J450">
+        <v>2035</v>
+      </c>
+      <c r="K450" s="1">
+        <v>500</v>
+      </c>
+      <c r="L450" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N450" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="O450" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="P450" s="28" t="s">
         <v>1384</v>
       </c>
-      <c r="E450" s="4">
-        <v>1620</v>
-      </c>
-      <c r="F450" s="4">
-        <v>746</v>
-      </c>
-      <c r="G450" s="4">
-        <v>0</v>
-      </c>
-      <c r="H450" s="4">
-        <v>0</v>
-      </c>
-      <c r="I450" s="4">
-        <v>0</v>
-      </c>
-      <c r="J450" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L450" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N450" s="30" t="s">
-        <v>879</v>
-      </c>
-      <c r="O450" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P450" s="30" t="s">
+      <c r="Q450" s="4" t="s">
         <v>1385</v>
-      </c>
-      <c r="Q450" s="4" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="451" ht="17.25" spans="1:17">
       <c r="A451" s="4" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B451" t="s">
         <v>38</v>
       </c>
-      <c r="C451" t="s">
-        <v>88</v>
+      <c r="C451" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D451" s="27" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E451" s="4">
-        <v>1620</v>
+        <v>1260</v>
       </c>
       <c r="F451" s="4">
-        <v>600</v>
+        <v>2447</v>
       </c>
       <c r="G451" s="4">
         <v>0</v>
@@ -29490,45 +29355,48 @@
       <c r="I451" s="4">
         <v>0</v>
       </c>
-      <c r="J451" s="4">
-        <v>2035</v>
+      <c r="J451">
+        <v>2245</v>
+      </c>
+      <c r="K451" s="1">
+        <v>650</v>
       </c>
       <c r="L451" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="N451" s="30" t="s">
-        <v>920</v>
+      <c r="N451" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="O451" s="4" t="s">
-        <v>1389</v>
-      </c>
-      <c r="P451" s="30" t="s">
-        <v>1390</v>
+        <v>1177</v>
+      </c>
+      <c r="P451" s="28" t="s">
+        <v>86</v>
       </c>
       <c r="Q451" s="4" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="452" ht="17.25" spans="1:17">
       <c r="A452" s="4" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B452" t="s">
         <v>38</v>
       </c>
-      <c r="C452" t="s">
-        <v>88</v>
-      </c>
-      <c r="D452" s="28" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E452" s="29">
-        <v>1620</v>
-      </c>
-      <c r="F452" s="29">
-        <v>800</v>
-      </c>
-      <c r="G452" s="29">
+      <c r="C452" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D452" s="27" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E452" s="4">
+        <v>1260</v>
+      </c>
+      <c r="F452" s="4">
+        <v>2447</v>
+      </c>
+      <c r="G452" s="4">
         <v>0</v>
       </c>
       <c r="H452" s="4">
@@ -29537,75 +29405,81 @@
       <c r="I452" s="4">
         <v>0</v>
       </c>
-      <c r="J452" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L452" s="32" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N452" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="O452" s="29" t="s">
-        <v>1351</v>
-      </c>
-      <c r="P452" s="29" t="s">
-        <v>739</v>
-      </c>
-      <c r="Q452" s="29" t="s">
-        <v>1394</v>
+      <c r="J452">
+        <v>2245</v>
+      </c>
+      <c r="K452" s="1">
+        <v>650</v>
+      </c>
+      <c r="L452" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N452" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="O452" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="P452" s="28" t="s">
+        <v>1391</v>
+      </c>
+      <c r="Q452" s="4" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="453" ht="17.25" spans="1:17">
       <c r="A453" s="4" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B453" t="s">
         <v>38</v>
       </c>
-      <c r="C453" t="s">
-        <v>88</v>
-      </c>
-      <c r="D453" s="28" t="s">
+      <c r="C453" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D453" s="27" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E453" s="4">
+        <v>1510</v>
+      </c>
+      <c r="F453" s="4">
+        <v>3335</v>
+      </c>
+      <c r="G453" s="4">
+        <v>0</v>
+      </c>
+      <c r="H453" s="4">
+        <v>0</v>
+      </c>
+      <c r="I453" s="4">
+        <v>0</v>
+      </c>
+      <c r="J453">
+        <v>2415</v>
+      </c>
+      <c r="K453" s="1">
+        <v>1040</v>
+      </c>
+      <c r="L453" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N453" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="O453" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="P453" s="28" t="s">
+        <v>1395</v>
+      </c>
+      <c r="Q453" s="4" t="s">
         <v>1396</v>
-      </c>
-      <c r="E453" s="29">
-        <v>1620</v>
-      </c>
-      <c r="F453" s="29">
-        <v>692</v>
-      </c>
-      <c r="G453" s="29">
-        <v>0</v>
-      </c>
-      <c r="H453" s="4">
-        <v>0</v>
-      </c>
-      <c r="I453" s="4">
-        <v>0</v>
-      </c>
-      <c r="J453" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L453" s="32" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N453" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="O453" s="29" t="s">
-        <v>1397</v>
-      </c>
-      <c r="P453" s="29" t="s">
-        <v>1398</v>
-      </c>
-      <c r="Q453" s="29" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="454" ht="17.25" spans="1:17">
       <c r="A454" s="4" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B454" t="s">
         <v>38</v>
@@ -29614,16 +29488,16 @@
         <v>88</v>
       </c>
       <c r="D454" s="27" t="s">
-        <v>1401</v>
+        <v>825</v>
       </c>
       <c r="E454" s="4">
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="F454" s="4">
-        <v>1620</v>
+        <v>986</v>
       </c>
       <c r="G454" s="4">
-        <v>1610</v>
+        <v>0</v>
       </c>
       <c r="H454" s="4">
         <v>0</v>
@@ -29635,41 +29509,41 @@
         <v>2035</v>
       </c>
       <c r="L454" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N454" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="O454" s="29" t="s">
-        <v>1397</v>
-      </c>
-      <c r="P454" s="30" t="s">
-        <v>1402</v>
+        <v>1092</v>
+      </c>
+      <c r="N454" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="O454" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="P454" s="28" t="s">
+        <v>1398</v>
       </c>
       <c r="Q454" s="4" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="455" ht="17.25" spans="1:17">
       <c r="A455" s="4" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B455" t="s">
         <v>38</v>
       </c>
-      <c r="C455" t="s">
-        <v>88</v>
-      </c>
-      <c r="D455" s="28" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E455" s="29">
-        <v>1620</v>
-      </c>
-      <c r="F455" s="29">
-        <v>513</v>
-      </c>
-      <c r="G455" s="29">
+      <c r="C455" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D455" s="27" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E455" s="4">
+        <v>1260</v>
+      </c>
+      <c r="F455" s="4">
+        <v>2447</v>
+      </c>
+      <c r="G455" s="4">
         <v>0</v>
       </c>
       <c r="H455" s="4">
@@ -29678,45 +29552,48 @@
       <c r="I455" s="4">
         <v>0</v>
       </c>
-      <c r="J455" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L455" s="32" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N455" s="29" t="s">
-        <v>1218</v>
-      </c>
-      <c r="O455" s="29" t="s">
+      <c r="J455">
+        <v>2245</v>
+      </c>
+      <c r="K455" s="1">
+        <v>650</v>
+      </c>
+      <c r="L455" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N455" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="O455" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="P455" s="29" t="s">
-        <v>1378</v>
-      </c>
-      <c r="Q455" s="29" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="456" ht="17.25" spans="1:17">
+      <c r="P455" s="28" t="s">
+        <v>1402</v>
+      </c>
+      <c r="Q455" s="4" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="456" ht="18" spans="1:17">
       <c r="A456" s="4" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B456" t="s">
         <v>38</v>
       </c>
-      <c r="C456" t="s">
-        <v>88</v>
-      </c>
-      <c r="D456" s="28" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E456" s="29">
-        <v>1620</v>
-      </c>
-      <c r="F456" s="29">
-        <v>600</v>
-      </c>
-      <c r="G456" s="29">
+      <c r="C456" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D456" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="E456" s="4">
+        <v>1010</v>
+      </c>
+      <c r="F456" s="4">
+        <v>2390</v>
+      </c>
+      <c r="G456" s="4">
         <v>0</v>
       </c>
       <c r="H456" s="4">
@@ -29725,43 +29602,46 @@
       <c r="I456" s="4">
         <v>0</v>
       </c>
-      <c r="J456" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L456" s="32" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N456" s="29" t="s">
-        <v>886</v>
-      </c>
-      <c r="O456" s="29" t="s">
-        <v>1222</v>
-      </c>
-      <c r="P456" s="29" t="s">
-        <v>1409</v>
-      </c>
-      <c r="Q456" s="29" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="457" ht="17.25" spans="1:17">
+      <c r="J456">
+        <v>2115</v>
+      </c>
+      <c r="K456" s="1">
+        <v>550</v>
+      </c>
+      <c r="L456" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N456" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="O456" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="P456" s="28" t="s">
+        <v>1405</v>
+      </c>
+      <c r="Q456" s="4" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="457" ht="18" spans="1:17">
       <c r="A457" s="4" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B457" t="s">
         <v>38</v>
       </c>
-      <c r="C457" t="s">
-        <v>88</v>
+      <c r="C457" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D457" s="27" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="E457" s="4">
-        <v>1620</v>
+        <v>780</v>
       </c>
       <c r="F457" s="4">
-        <v>513</v>
+        <v>1445</v>
       </c>
       <c r="G457" s="4">
         <v>0</v>
@@ -29772,46 +29652,49 @@
       <c r="I457" s="4">
         <v>0</v>
       </c>
-      <c r="J457" s="4">
+      <c r="J457">
         <v>2035</v>
       </c>
+      <c r="K457" s="1">
+        <v>500</v>
+      </c>
       <c r="L457" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N457" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="O457" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P457" s="30" t="s">
-        <v>1413</v>
+        <v>1092</v>
+      </c>
+      <c r="N457" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="O457" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P457" s="28" t="s">
+        <v>1409</v>
       </c>
       <c r="Q457" s="4" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="458" ht="17.25" spans="1:17">
       <c r="A458" s="4" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B458" t="s">
         <v>38</v>
       </c>
-      <c r="C458" s="4" t="s">
-        <v>19</v>
+      <c r="C458" t="s">
+        <v>88</v>
       </c>
       <c r="D458" s="27" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="E458" s="4">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="F458" s="4">
-        <v>1380</v>
+        <v>1840</v>
       </c>
       <c r="G458" s="4">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H458" s="4">
         <v>0</v>
@@ -29819,31 +29702,28 @@
       <c r="I458" s="4">
         <v>0</v>
       </c>
-      <c r="J458">
+      <c r="J458" s="4">
         <v>2035</v>
       </c>
-      <c r="K458" s="1">
-        <v>500</v>
-      </c>
       <c r="L458" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N458" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="O458" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P458" s="30" t="s">
-        <v>461</v>
+        <v>1092</v>
+      </c>
+      <c r="N458" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="O458" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P458" s="28" t="s">
+        <v>1413</v>
       </c>
       <c r="Q458" s="4" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="459" ht="17.25" spans="1:17">
       <c r="A459" s="4" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="B459" t="s">
         <v>38</v>
@@ -29852,13 +29732,13 @@
         <v>19</v>
       </c>
       <c r="D459" s="27" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="E459" s="4">
-        <v>780</v>
+        <v>1170</v>
       </c>
       <c r="F459" s="4">
-        <v>1380</v>
+        <v>2897</v>
       </c>
       <c r="G459" s="4">
         <v>0</v>
@@ -29869,125 +29749,131 @@
       <c r="I459" s="4">
         <v>0</v>
       </c>
-      <c r="J459">
-        <v>2035</v>
+      <c r="J459" s="25">
+        <v>2245</v>
       </c>
       <c r="K459" s="1">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="L459" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N459" s="30" t="s">
-        <v>490</v>
+        <v>1080</v>
+      </c>
+      <c r="N459" s="28" t="s">
+        <v>90</v>
       </c>
       <c r="O459" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P459" s="30" t="s">
-        <v>491</v>
+        <v>1417</v>
+      </c>
+      <c r="P459" s="28" t="s">
+        <v>840</v>
       </c>
       <c r="Q459" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="460" ht="17.25" spans="1:17">
       <c r="A460" s="4" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B460" t="s">
         <v>38</v>
       </c>
-      <c r="C460" t="s">
-        <v>88</v>
-      </c>
-      <c r="D460" s="28" t="s">
+      <c r="C460" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D460" s="27" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E460" s="4">
+        <v>1260</v>
+      </c>
+      <c r="F460" s="4">
+        <v>2897</v>
+      </c>
+      <c r="G460" s="4">
+        <v>0</v>
+      </c>
+      <c r="H460" s="4">
+        <v>0</v>
+      </c>
+      <c r="I460" s="4">
+        <v>0</v>
+      </c>
+      <c r="J460" s="25">
+        <v>2245</v>
+      </c>
+      <c r="K460" s="1">
+        <v>650</v>
+      </c>
+      <c r="L460" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N460" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="O460" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="P460" s="28" t="s">
+        <v>1421</v>
+      </c>
+      <c r="Q460" s="4" t="s">
         <v>1422</v>
       </c>
-      <c r="E460" s="29">
-        <v>1620</v>
-      </c>
-      <c r="F460" s="29">
-        <v>554</v>
-      </c>
-      <c r="G460" s="29">
-        <v>0</v>
-      </c>
-      <c r="H460" s="4">
-        <v>0</v>
-      </c>
-      <c r="I460" s="4">
-        <v>0</v>
-      </c>
-      <c r="J460">
-        <v>2035</v>
-      </c>
-      <c r="L460" s="32" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N460" s="29" t="s">
-        <v>920</v>
-      </c>
-      <c r="O460" s="33" t="s">
-        <v>1077</v>
-      </c>
-      <c r="P460" s="29" t="s">
-        <v>1390</v>
-      </c>
-      <c r="Q460" s="29" t="s">
+    </row>
+    <row r="461" ht="17.25" spans="1:17">
+      <c r="A461" s="4" t="s">
         <v>1423</v>
-      </c>
-    </row>
-    <row r="461" ht="18" spans="1:17">
-      <c r="A461" s="4" t="s">
-        <v>1424</v>
       </c>
       <c r="B461" t="s">
         <v>38</v>
       </c>
-      <c r="C461" t="s">
-        <v>88</v>
+      <c r="C461" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D461" s="27" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E461" s="4">
+        <v>1260</v>
+      </c>
+      <c r="F461" s="4">
+        <v>2276</v>
+      </c>
+      <c r="G461" s="4">
+        <v>0</v>
+      </c>
+      <c r="H461" s="4">
+        <v>0</v>
+      </c>
+      <c r="I461" s="4">
+        <v>0</v>
+      </c>
+      <c r="J461" s="25">
+        <v>2245</v>
+      </c>
+      <c r="K461" s="1">
+        <v>650</v>
+      </c>
+      <c r="L461" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N461" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="O461" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P461" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q461" s="4" t="s">
         <v>1425</v>
       </c>
-      <c r="E461" s="4">
-        <v>1620</v>
-      </c>
-      <c r="F461" s="4">
-        <v>746</v>
-      </c>
-      <c r="G461" s="4">
-        <v>0</v>
-      </c>
-      <c r="H461" s="4">
-        <v>0</v>
-      </c>
-      <c r="I461" s="4">
-        <v>0</v>
-      </c>
-      <c r="J461">
-        <v>2035</v>
-      </c>
-      <c r="L461" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N461" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="O461" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P461" s="30" t="s">
+    </row>
+    <row r="462" ht="17.25" spans="1:17">
+      <c r="A462" s="4" t="s">
         <v>1426</v>
-      </c>
-      <c r="Q461" s="4" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="462" ht="18" spans="1:17">
-      <c r="A462" s="4" t="s">
-        <v>1427</v>
       </c>
       <c r="B462" t="s">
         <v>38</v>
@@ -29996,48 +29882,48 @@
         <v>19</v>
       </c>
       <c r="D462" s="27" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E462" s="4">
+        <v>1170</v>
+      </c>
+      <c r="F462" s="4">
+        <v>2695</v>
+      </c>
+      <c r="G462" s="4">
+        <v>0</v>
+      </c>
+      <c r="H462" s="4">
+        <v>0</v>
+      </c>
+      <c r="I462" s="4">
+        <v>0</v>
+      </c>
+      <c r="J462">
+        <v>2245</v>
+      </c>
+      <c r="K462" s="1">
+        <v>650</v>
+      </c>
+      <c r="L462" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N462" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="O462" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="P462" s="28" t="s">
         <v>1428</v>
       </c>
-      <c r="E462" s="4">
-        <v>780</v>
-      </c>
-      <c r="F462" s="4">
-        <v>1380</v>
-      </c>
-      <c r="G462" s="4">
-        <v>0</v>
-      </c>
-      <c r="H462" s="4">
-        <v>0</v>
-      </c>
-      <c r="I462" s="4">
-        <v>0</v>
-      </c>
-      <c r="J462">
-        <v>2035</v>
-      </c>
-      <c r="K462" s="1">
-        <v>500</v>
-      </c>
-      <c r="L462" s="9" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N462" s="26" t="s">
-        <v>974</v>
-      </c>
-      <c r="O462" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="P462" s="30" t="s">
+      <c r="Q462" s="4" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q462" s="4" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="463" ht="17.25" spans="1:17">
       <c r="A463" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B463" t="s">
         <v>38</v>
@@ -30046,13 +29932,13 @@
         <v>19</v>
       </c>
       <c r="D463" s="27" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E463" s="4">
-        <v>1260</v>
+        <v>1170</v>
       </c>
       <c r="F463" s="4">
-        <v>2447</v>
+        <v>2276</v>
       </c>
       <c r="G463" s="4">
         <v>0</v>
@@ -30070,16 +29956,16 @@
         <v>650</v>
       </c>
       <c r="L463" s="9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N463" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="O463" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P463" s="30" t="s">
-        <v>86</v>
+        <v>1065</v>
+      </c>
+      <c r="N463" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O463" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P463" s="28" t="s">
+        <v>1432</v>
       </c>
       <c r="Q463" s="4" t="s">
         <v>1433</v>
@@ -30099,10 +29985,10 @@
         <v>1435</v>
       </c>
       <c r="E464" s="4">
-        <v>1260</v>
+        <v>1010</v>
       </c>
       <c r="F464" s="4">
-        <v>2447</v>
+        <v>1739</v>
       </c>
       <c r="G464" s="4">
         <v>0</v>
@@ -30114,21 +30000,21 @@
         <v>0</v>
       </c>
       <c r="J464">
-        <v>2245</v>
+        <v>2115</v>
       </c>
       <c r="K464" s="1">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="L464" s="9" t="s">
-        <v>1074</v>
-      </c>
-      <c r="N464" s="30" t="s">
-        <v>490</v>
-      </c>
-      <c r="O464" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="P464" s="30" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N464" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O464" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P464" s="28" t="s">
         <v>1436</v>
       </c>
       <c r="Q464" s="4" t="s">
@@ -30149,10 +30035,10 @@
         <v>1439</v>
       </c>
       <c r="E465" s="4">
-        <v>1510</v>
+        <v>1170</v>
       </c>
       <c r="F465" s="4">
-        <v>3335</v>
+        <v>2011</v>
       </c>
       <c r="G465" s="4">
         <v>0</v>
@@ -30163,46 +30049,46 @@
       <c r="I465" s="4">
         <v>0</v>
       </c>
-      <c r="J465">
-        <v>2415</v>
+      <c r="J465" s="25">
+        <v>2245</v>
       </c>
       <c r="K465" s="1">
-        <v>1040</v>
+        <v>650</v>
       </c>
       <c r="L465" s="9" t="s">
-        <v>1085</v>
-      </c>
-      <c r="N465" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="O465" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P465" s="30" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N465" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="O465" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="P465" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q465" s="4" t="s">
         <v>1440</v>
-      </c>
-      <c r="Q465" s="4" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="466" ht="17.25" spans="1:17">
       <c r="A466" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B466" t="s">
         <v>38</v>
       </c>
-      <c r="C466" t="s">
-        <v>88</v>
+      <c r="C466" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D466" s="27" t="s">
-        <v>825</v>
+        <v>1442</v>
       </c>
       <c r="E466" s="4">
-        <v>1840</v>
+        <v>1170</v>
       </c>
       <c r="F466" s="4">
-        <v>986</v>
+        <v>2011</v>
       </c>
       <c r="G466" s="4">
         <v>0</v>
@@ -30213,28 +30099,31 @@
       <c r="I466" s="4">
         <v>0</v>
       </c>
-      <c r="J466" s="4">
-        <v>2035</v>
+      <c r="J466">
+        <v>2245</v>
+      </c>
+      <c r="K466" s="1">
+        <v>650</v>
       </c>
       <c r="L466" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N466" s="30" t="s">
-        <v>90</v>
+        <v>1065</v>
+      </c>
+      <c r="N466" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="O466" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="P466" s="30" t="s">
         <v>1443</v>
       </c>
+      <c r="P466" s="28" t="s">
+        <v>1444</v>
+      </c>
       <c r="Q466" s="4" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="467" ht="17.25" spans="1:17">
       <c r="A467" s="4" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B467" t="s">
         <v>38</v>
@@ -30243,13 +30132,13 @@
         <v>19</v>
       </c>
       <c r="D467" s="27" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="E467" s="4">
         <v>1260</v>
       </c>
       <c r="F467" s="4">
-        <v>2447</v>
+        <v>2011</v>
       </c>
       <c r="G467" s="4">
         <v>0</v>
@@ -30267,24 +30156,27 @@
         <v>650</v>
       </c>
       <c r="L467" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N467" s="25" t="s">
-        <v>171</v>
+        <v>1065</v>
+      </c>
+      <c r="M467" t="s">
+        <v>40</v>
+      </c>
+      <c r="N467" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="O467" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="P467" s="30" t="s">
-        <v>1447</v>
+        <v>1162</v>
+      </c>
+      <c r="P467" s="28" t="s">
+        <v>1448</v>
       </c>
       <c r="Q467" s="4" t="s">
-        <v>1448</v>
-      </c>
-    </row>
-    <row r="468" ht="18" spans="1:17">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="468" ht="17.25" spans="1:17">
       <c r="A468" s="4" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B468" t="s">
         <v>38</v>
@@ -30293,10 +30185,10 @@
         <v>19</v>
       </c>
       <c r="D468" s="27" t="s">
-        <v>463</v>
+        <v>1451</v>
       </c>
       <c r="E468" s="4">
-        <v>1010</v>
+        <v>1260</v>
       </c>
       <c r="F468" s="4">
         <v>2390</v>
@@ -30311,30 +30203,30 @@
         <v>0</v>
       </c>
       <c r="J468">
-        <v>2115</v>
+        <v>2245</v>
       </c>
       <c r="K468" s="1">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="L468" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N468" s="25" t="s">
-        <v>235</v>
+        <v>1065</v>
+      </c>
+      <c r="N468" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="O468" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="P468" s="30" t="s">
-        <v>1450</v>
+        <v>1162</v>
+      </c>
+      <c r="P468" s="28" t="s">
+        <v>1452</v>
       </c>
       <c r="Q468" s="4" t="s">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="469" ht="18" spans="1:17">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="469" ht="17.25" spans="1:17">
       <c r="A469" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B469" t="s">
         <v>38</v>
@@ -30343,13 +30235,13 @@
         <v>19</v>
       </c>
       <c r="D469" s="27" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="E469" s="4">
-        <v>780</v>
+        <v>1260</v>
       </c>
       <c r="F469" s="4">
-        <v>1445</v>
+        <v>2162</v>
       </c>
       <c r="G469" s="4">
         <v>0</v>
@@ -30361,48 +30253,48 @@
         <v>0</v>
       </c>
       <c r="J469">
-        <v>2035</v>
+        <v>2245</v>
       </c>
       <c r="K469" s="1">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="L469" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N469" s="26" t="s">
-        <v>974</v>
-      </c>
-      <c r="O469" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P469" s="30" t="s">
-        <v>1454</v>
+        <v>1065</v>
+      </c>
+      <c r="N469" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="O469" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="P469" s="28" t="s">
+        <v>1456</v>
       </c>
       <c r="Q469" s="4" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="470" ht="17.25" spans="1:17">
       <c r="A470" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B470" t="s">
         <v>38</v>
       </c>
-      <c r="C470" t="s">
-        <v>88</v>
+      <c r="C470" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D470" s="27" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E470" s="4">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="F470" s="4">
-        <v>1840</v>
+        <v>1907</v>
       </c>
       <c r="G470" s="4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H470" s="4">
         <v>0</v>
@@ -30410,28 +30302,31 @@
       <c r="I470" s="4">
         <v>0</v>
       </c>
-      <c r="J470" s="4">
-        <v>2035</v>
+      <c r="J470">
+        <v>2245</v>
+      </c>
+      <c r="K470" s="1">
+        <v>650</v>
       </c>
       <c r="L470" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N470" s="30" t="s">
-        <v>251</v>
+        <v>1065</v>
+      </c>
+      <c r="N470" s="28" t="s">
+        <v>105</v>
       </c>
       <c r="O470" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P470" s="30" t="s">
-        <v>1458</v>
+        <v>1460</v>
+      </c>
+      <c r="P470" s="28" t="s">
+        <v>1461</v>
       </c>
       <c r="Q470" s="4" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="471" ht="17.25" spans="1:17">
       <c r="A471" s="4" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="B471" t="s">
         <v>38</v>
@@ -30440,13 +30335,13 @@
         <v>19</v>
       </c>
       <c r="D471" s="27" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="E471" s="4">
         <v>1170</v>
       </c>
       <c r="F471" s="4">
-        <v>2897</v>
+        <v>2048</v>
       </c>
       <c r="G471" s="4">
         <v>0</v>
@@ -30457,31 +30352,31 @@
       <c r="I471" s="4">
         <v>0</v>
       </c>
-      <c r="J471" s="25">
+      <c r="J471">
         <v>2245</v>
       </c>
       <c r="K471" s="1">
         <v>650</v>
       </c>
       <c r="L471" s="9" t="s">
-        <v>1080</v>
-      </c>
-      <c r="N471" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="O471" s="25" t="s">
-        <v>1462</v>
-      </c>
-      <c r="P471" s="30" t="s">
-        <v>840</v>
+        <v>1065</v>
+      </c>
+      <c r="N471" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="O471" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="P471" s="28" t="s">
+        <v>1465</v>
       </c>
       <c r="Q471" s="4" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="472" ht="17.25" spans="1:17">
       <c r="A472" s="4" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="B472" t="s">
         <v>38</v>
@@ -30490,13 +30385,13 @@
         <v>19</v>
       </c>
       <c r="D472" s="27" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="E472" s="4">
         <v>1260</v>
       </c>
       <c r="F472" s="4">
-        <v>2897</v>
+        <v>2447</v>
       </c>
       <c r="G472" s="4">
         <v>0</v>
@@ -30507,7 +30402,7 @@
       <c r="I472" s="4">
         <v>0</v>
       </c>
-      <c r="J472" s="25">
+      <c r="J472">
         <v>2245</v>
       </c>
       <c r="K472" s="1">
@@ -30516,22 +30411,25 @@
       <c r="L472" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N472" s="30" t="s">
-        <v>42</v>
+      <c r="M472" t="s">
+        <v>40</v>
+      </c>
+      <c r="N472" s="28" t="s">
+        <v>95</v>
       </c>
       <c r="O472" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="P472" s="30" t="s">
-        <v>1466</v>
+        <v>190</v>
+      </c>
+      <c r="P472" s="28" t="s">
+        <v>97</v>
       </c>
       <c r="Q472" s="4" t="s">
-        <v>1467</v>
+        <v>190</v>
       </c>
     </row>
     <row r="473" ht="17.25" spans="1:17">
       <c r="A473" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B473" t="s">
         <v>38</v>
@@ -30540,10 +30438,10 @@
         <v>19</v>
       </c>
       <c r="D473" s="27" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E473" s="4">
-        <v>1260</v>
+        <v>1170</v>
       </c>
       <c r="F473" s="4">
         <v>2276</v>
@@ -30557,7 +30455,7 @@
       <c r="I473" s="4">
         <v>0</v>
       </c>
-      <c r="J473" s="25">
+      <c r="J473">
         <v>2245</v>
       </c>
       <c r="K473" s="1">
@@ -30566,22 +30464,22 @@
       <c r="L473" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N473" s="30" t="s">
-        <v>342</v>
+      <c r="N473" s="28" t="s">
+        <v>60</v>
       </c>
       <c r="O473" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P473" s="30" t="s">
-        <v>435</v>
+        <v>1299</v>
+      </c>
+      <c r="P473" s="28" t="s">
+        <v>1471</v>
       </c>
       <c r="Q473" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="474" ht="17.25" spans="1:17">
       <c r="A474" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B474" t="s">
         <v>38</v>
@@ -30590,13 +30488,13 @@
         <v>19</v>
       </c>
       <c r="D474" s="27" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="E474" s="4">
         <v>1170</v>
       </c>
       <c r="F474" s="4">
-        <v>2695</v>
+        <v>2390</v>
       </c>
       <c r="G474" s="4">
         <v>0</v>
@@ -30616,22 +30514,22 @@
       <c r="L474" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N474" s="30" t="s">
-        <v>228</v>
+      <c r="N474" s="28" t="s">
+        <v>77</v>
       </c>
       <c r="O474" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="P474" s="30" t="s">
-        <v>1473</v>
+        <v>1351</v>
+      </c>
+      <c r="P474" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="Q474" s="4" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="475" ht="17.25" spans="1:17">
       <c r="A475" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B475" t="s">
         <v>38</v>
@@ -30640,13 +30538,13 @@
         <v>19</v>
       </c>
       <c r="D475" s="27" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="E475" s="4">
         <v>1170</v>
       </c>
       <c r="F475" s="4">
-        <v>2276</v>
+        <v>2011</v>
       </c>
       <c r="G475" s="4">
         <v>0</v>
@@ -30666,14 +30564,14 @@
       <c r="L475" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N475" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="O475" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P475" s="30" t="s">
-        <v>1477</v>
+      <c r="N475" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="O475" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="P475" s="28" t="s">
+        <v>363</v>
       </c>
       <c r="Q475" s="4" t="s">
         <v>1478</v>
@@ -30696,7 +30594,7 @@
         <v>1010</v>
       </c>
       <c r="F476" s="4">
-        <v>1739</v>
+        <v>1571</v>
       </c>
       <c r="G476" s="4">
         <v>0</v>
@@ -30716,22 +30614,22 @@
       <c r="L476" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N476" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="O476" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P476" s="30" t="s">
-        <v>1481</v>
+      <c r="N476" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="O476" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="P476" s="28" t="s">
+        <v>102</v>
       </c>
       <c r="Q476" s="4" t="s">
-        <v>1482</v>
+        <v>860</v>
       </c>
     </row>
     <row r="477" ht="17.25" spans="1:17">
       <c r="A477" s="4" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B477" t="s">
         <v>38</v>
@@ -30740,13 +30638,13 @@
         <v>19</v>
       </c>
       <c r="D477" s="27" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="E477" s="4">
-        <v>1170</v>
+        <v>1630</v>
       </c>
       <c r="F477" s="4">
-        <v>2011</v>
+        <v>2075</v>
       </c>
       <c r="G477" s="4">
         <v>0</v>
@@ -30757,7 +30655,7 @@
       <c r="I477" s="4">
         <v>0</v>
       </c>
-      <c r="J477" s="25">
+      <c r="J477">
         <v>2245</v>
       </c>
       <c r="K477" s="1">
@@ -30766,22 +30664,22 @@
       <c r="L477" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N477" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="O477" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="P477" s="30" t="s">
-        <v>327</v>
+      <c r="N477" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="O477" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="P477" s="28" t="s">
+        <v>1483</v>
       </c>
       <c r="Q477" s="4" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="478" ht="17.25" spans="1:17">
       <c r="A478" s="4" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B478" t="s">
         <v>38</v>
@@ -30790,13 +30688,13 @@
         <v>19</v>
       </c>
       <c r="D478" s="27" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E478" s="4">
-        <v>1170</v>
+        <v>1260</v>
       </c>
       <c r="F478" s="4">
-        <v>2011</v>
+        <v>2897</v>
       </c>
       <c r="G478" s="4">
         <v>0</v>
@@ -30816,22 +30714,22 @@
       <c r="L478" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="N478" s="30" t="s">
-        <v>83</v>
+      <c r="N478" s="28" t="s">
+        <v>251</v>
       </c>
       <c r="O478" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="P478" s="28" t="s">
         <v>1488</v>
       </c>
-      <c r="P478" s="30" t="s">
+      <c r="Q478" s="4" t="s">
         <v>1489</v>
-      </c>
-      <c r="Q478" s="4" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="479" ht="17.25" spans="1:17">
       <c r="A479" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B479" t="s">
         <v>38</v>
@@ -30840,13 +30738,13 @@
         <v>19</v>
       </c>
       <c r="D479" s="27" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E479" s="4">
         <v>1260</v>
       </c>
       <c r="F479" s="4">
-        <v>2011</v>
+        <v>2115</v>
       </c>
       <c r="G479" s="4">
         <v>0</v>
@@ -30869,22 +30767,22 @@
       <c r="M479" t="s">
         <v>40</v>
       </c>
-      <c r="N479" s="30" t="s">
-        <v>24</v>
+      <c r="N479" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="O479" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P479" s="30" t="s">
+        <v>1487</v>
+      </c>
+      <c r="P479" s="28" t="s">
+        <v>1492</v>
+      </c>
+      <c r="Q479" s="4" t="s">
         <v>1493</v>
-      </c>
-      <c r="Q479" s="4" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="480" ht="17.25" spans="1:17">
       <c r="A480" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B480" t="s">
         <v>38</v>
@@ -30893,48 +30791,48 @@
         <v>19</v>
       </c>
       <c r="D480" s="27" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E480" s="4">
+        <v>1010</v>
+      </c>
+      <c r="F480" s="4">
+        <v>2219</v>
+      </c>
+      <c r="G480" s="4">
+        <v>0</v>
+      </c>
+      <c r="H480" s="4">
+        <v>0</v>
+      </c>
+      <c r="I480" s="4">
+        <v>0</v>
+      </c>
+      <c r="J480">
+        <v>2115</v>
+      </c>
+      <c r="K480" s="1">
+        <v>550</v>
+      </c>
+      <c r="L480" s="9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N480" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="O480" s="4" t="s">
         <v>1496</v>
       </c>
-      <c r="E480" s="4">
-        <v>1260</v>
-      </c>
-      <c r="F480" s="4">
-        <v>2390</v>
-      </c>
-      <c r="G480" s="4">
-        <v>0</v>
-      </c>
-      <c r="H480" s="4">
-        <v>0</v>
-      </c>
-      <c r="I480" s="4">
-        <v>0</v>
-      </c>
-      <c r="J480">
-        <v>2245</v>
-      </c>
-      <c r="K480" s="1">
-        <v>650</v>
-      </c>
-      <c r="L480" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N480" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="O480" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P480" s="30" t="s">
+      <c r="P480" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="Q480" s="4" t="s">
         <v>1497</v>
-      </c>
-      <c r="Q480" s="4" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="481" ht="17.25" spans="1:17">
       <c r="A481" s="4" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B481" t="s">
         <v>38</v>
@@ -30943,116 +30841,113 @@
         <v>19</v>
       </c>
       <c r="D481" s="27" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E481" s="4">
+        <v>1510</v>
+      </c>
+      <c r="F481" s="4">
+        <v>2822</v>
+      </c>
+      <c r="G481" s="4">
+        <v>0</v>
+      </c>
+      <c r="H481" s="4">
+        <v>0</v>
+      </c>
+      <c r="I481" s="4">
+        <v>0</v>
+      </c>
+      <c r="J481" s="25">
+        <v>2415</v>
+      </c>
+      <c r="K481" s="25">
+        <v>1040</v>
+      </c>
+      <c r="L481" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="N481" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="O481" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="P481" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q481" s="4" t="s">
         <v>1500</v>
-      </c>
-      <c r="E481" s="4">
-        <v>1260</v>
-      </c>
-      <c r="F481" s="4">
-        <v>2162</v>
-      </c>
-      <c r="G481" s="4">
-        <v>0</v>
-      </c>
-      <c r="H481" s="4">
-        <v>0</v>
-      </c>
-      <c r="I481" s="4">
-        <v>0</v>
-      </c>
-      <c r="J481">
-        <v>2245</v>
-      </c>
-      <c r="K481" s="1">
-        <v>650</v>
-      </c>
-      <c r="L481" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N481" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="O481" s="4" t="s">
-        <v>1360</v>
-      </c>
-      <c r="P481" s="30" t="s">
-        <v>1501</v>
-      </c>
-      <c r="Q481" s="4" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="482" ht="17.25" spans="1:17">
       <c r="A482" s="4" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B482" t="s">
         <v>38</v>
       </c>
-      <c r="C482" s="4" t="s">
-        <v>19</v>
+      <c r="C482" t="s">
+        <v>88</v>
       </c>
       <c r="D482" s="27" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E482" s="4">
+        <v>0</v>
+      </c>
+      <c r="F482" s="4">
+        <v>1620</v>
+      </c>
+      <c r="G482" s="4">
+        <v>986</v>
+      </c>
+      <c r="H482" s="4">
+        <v>0</v>
+      </c>
+      <c r="I482" s="4">
+        <v>0</v>
+      </c>
+      <c r="J482" s="4">
+        <v>2035</v>
+      </c>
+      <c r="L482" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="N482" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="O482" s="25" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P482" s="28" t="s">
+        <v>1503</v>
+      </c>
+      <c r="Q482" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="E482" s="4">
-        <v>1260</v>
-      </c>
-      <c r="F482" s="4">
-        <v>1907</v>
-      </c>
-      <c r="G482" s="4">
-        <v>0</v>
-      </c>
-      <c r="H482" s="4">
-        <v>0</v>
-      </c>
-      <c r="I482" s="4">
-        <v>0</v>
-      </c>
-      <c r="J482">
-        <v>2245</v>
-      </c>
-      <c r="K482" s="1">
-        <v>650</v>
-      </c>
-      <c r="L482" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N482" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="O482" s="4" t="s">
-        <v>1505</v>
-      </c>
-      <c r="P482" s="30" t="s">
-        <v>1506</v>
-      </c>
-      <c r="Q482" s="4" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="483" ht="17.25" spans="1:17">
       <c r="A483" s="4" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="B483" t="s">
         <v>38</v>
       </c>
-      <c r="C483" s="4" t="s">
-        <v>19</v>
+      <c r="C483" t="s">
+        <v>88</v>
       </c>
       <c r="D483" s="27" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="E483" s="4">
-        <v>1170</v>
+        <v>0</v>
       </c>
       <c r="F483" s="4">
-        <v>2048</v>
+        <v>1620</v>
       </c>
       <c r="G483" s="4">
-        <v>0</v>
+        <v>1274</v>
       </c>
       <c r="H483" s="4">
         <v>0</v>
@@ -31060,49 +30955,46 @@
       <c r="I483" s="4">
         <v>0</v>
       </c>
-      <c r="J483">
-        <v>2245</v>
-      </c>
-      <c r="K483" s="1">
-        <v>650</v>
+      <c r="J483" s="4">
+        <v>2035</v>
       </c>
       <c r="L483" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N483" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="O483" s="4" t="s">
-        <v>1066</v>
-      </c>
-      <c r="P483" s="30" t="s">
-        <v>1510</v>
+        <v>874</v>
+      </c>
+      <c r="N483" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="O483" s="25" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P483" s="28" t="s">
+        <v>1503</v>
       </c>
       <c r="Q483" s="4" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="484" ht="17.25" spans="1:17">
       <c r="A484" s="4" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="B484" t="s">
         <v>38</v>
       </c>
-      <c r="C484" s="4" t="s">
-        <v>19</v>
+      <c r="C484" t="s">
+        <v>88</v>
       </c>
       <c r="D484" s="27" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="E484" s="4">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="F484" s="4">
-        <v>2447</v>
+        <v>1620</v>
       </c>
       <c r="G484" s="4">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="H484" s="4">
         <v>0</v>
@@ -31110,627 +31002,27 @@
       <c r="I484" s="4">
         <v>0</v>
       </c>
-      <c r="J484">
-        <v>2245</v>
-      </c>
-      <c r="K484" s="1">
-        <v>650</v>
+      <c r="J484" s="4">
+        <v>2035</v>
       </c>
       <c r="L484" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M484" t="s">
-        <v>40</v>
-      </c>
-      <c r="N484" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="O484" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="P484" s="30" t="s">
-        <v>97</v>
+        <v>874</v>
+      </c>
+      <c r="N484" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="O484" s="25" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P484" s="28" t="s">
+        <v>1503</v>
       </c>
       <c r="Q484" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="485" ht="17.25" spans="1:17">
-      <c r="A485" s="4" t="s">
-        <v>1514</v>
-      </c>
-      <c r="B485" t="s">
-        <v>38</v>
-      </c>
-      <c r="C485" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D485" s="27" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E485" s="4">
-        <v>1170</v>
-      </c>
-      <c r="F485" s="4">
-        <v>2276</v>
-      </c>
-      <c r="G485" s="4">
-        <v>0</v>
-      </c>
-      <c r="H485" s="4">
-        <v>0</v>
-      </c>
-      <c r="I485" s="4">
-        <v>0</v>
-      </c>
-      <c r="J485">
-        <v>2245</v>
-      </c>
-      <c r="K485" s="1">
-        <v>650</v>
-      </c>
-      <c r="L485" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N485" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="O485" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="P485" s="30" t="s">
-        <v>1516</v>
-      </c>
-      <c r="Q485" s="4" t="s">
-        <v>1517</v>
-      </c>
-    </row>
-    <row r="486" ht="17.25" spans="1:17">
-      <c r="A486" s="4" t="s">
-        <v>1518</v>
-      </c>
-      <c r="B486" t="s">
-        <v>38</v>
-      </c>
-      <c r="C486" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D486" s="27" t="s">
-        <v>1519</v>
-      </c>
-      <c r="E486" s="4">
-        <v>1170</v>
-      </c>
-      <c r="F486" s="4">
-        <v>2390</v>
-      </c>
-      <c r="G486" s="4">
-        <v>0</v>
-      </c>
-      <c r="H486" s="4">
-        <v>0</v>
-      </c>
-      <c r="I486" s="4">
-        <v>0</v>
-      </c>
-      <c r="J486">
-        <v>2245</v>
-      </c>
-      <c r="K486" s="1">
-        <v>650</v>
-      </c>
-      <c r="L486" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N486" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="O486" s="4" t="s">
-        <v>1351</v>
-      </c>
-      <c r="P486" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q486" s="4" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="487" ht="17.25" spans="1:17">
-      <c r="A487" s="4" t="s">
-        <v>1521</v>
-      </c>
-      <c r="B487" t="s">
-        <v>38</v>
-      </c>
-      <c r="C487" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D487" s="27" t="s">
-        <v>1522</v>
-      </c>
-      <c r="E487" s="4">
-        <v>1170</v>
-      </c>
-      <c r="F487" s="4">
-        <v>2011</v>
-      </c>
-      <c r="G487" s="4">
-        <v>0</v>
-      </c>
-      <c r="H487" s="4">
-        <v>0</v>
-      </c>
-      <c r="I487" s="4">
-        <v>0</v>
-      </c>
-      <c r="J487">
-        <v>2245</v>
-      </c>
-      <c r="K487" s="1">
-        <v>650</v>
-      </c>
-      <c r="L487" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N487" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="O487" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P487" s="30" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q487" s="4" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="488" ht="17.25" spans="1:17">
-      <c r="A488" s="4" t="s">
-        <v>1524</v>
-      </c>
-      <c r="B488" t="s">
-        <v>38</v>
-      </c>
-      <c r="C488" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D488" s="27" t="s">
-        <v>1525</v>
-      </c>
-      <c r="E488" s="4">
-        <v>1010</v>
-      </c>
-      <c r="F488" s="4">
-        <v>1571</v>
-      </c>
-      <c r="G488" s="4">
-        <v>0</v>
-      </c>
-      <c r="H488" s="4">
-        <v>0</v>
-      </c>
-      <c r="I488" s="4">
-        <v>0</v>
-      </c>
-      <c r="J488">
-        <v>2115</v>
-      </c>
-      <c r="K488" s="1">
-        <v>550</v>
-      </c>
-      <c r="L488" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N488" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="O488" s="4" t="s">
-        <v>860</v>
-      </c>
-      <c r="P488" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q488" s="4" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="489" ht="17.25" spans="1:17">
-      <c r="A489" s="4" t="s">
-        <v>1526</v>
-      </c>
-      <c r="B489" t="s">
-        <v>38</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D489" s="27" t="s">
-        <v>1527</v>
-      </c>
-      <c r="E489" s="4">
-        <v>1630</v>
-      </c>
-      <c r="F489" s="4">
-        <v>2075</v>
-      </c>
-      <c r="G489" s="4">
-        <v>0</v>
-      </c>
-      <c r="H489" s="4">
-        <v>0</v>
-      </c>
-      <c r="I489" s="4">
-        <v>0</v>
-      </c>
-      <c r="J489">
-        <v>2245</v>
-      </c>
-      <c r="K489" s="1">
-        <v>650</v>
-      </c>
-      <c r="L489" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N489" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="O489" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P489" s="30" t="s">
-        <v>1528</v>
-      </c>
-      <c r="Q489" s="4" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="490" ht="17.25" spans="1:17">
-      <c r="A490" s="4" t="s">
-        <v>1530</v>
-      </c>
-      <c r="B490" t="s">
-        <v>38</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D490" s="27" t="s">
-        <v>1531</v>
-      </c>
-      <c r="E490" s="4">
-        <v>1260</v>
-      </c>
-      <c r="F490" s="4">
-        <v>2897</v>
-      </c>
-      <c r="G490" s="4">
-        <v>0</v>
-      </c>
-      <c r="H490" s="4">
-        <v>0</v>
-      </c>
-      <c r="I490" s="4">
-        <v>0</v>
-      </c>
-      <c r="J490">
-        <v>2245</v>
-      </c>
-      <c r="K490" s="1">
-        <v>650</v>
-      </c>
-      <c r="L490" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N490" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="O490" s="4" t="s">
-        <v>1532</v>
-      </c>
-      <c r="P490" s="30" t="s">
-        <v>1533</v>
-      </c>
-      <c r="Q490" s="4" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="491" ht="17.25" spans="1:17">
-      <c r="A491" s="4" t="s">
-        <v>1535</v>
-      </c>
-      <c r="B491" t="s">
-        <v>38</v>
-      </c>
-      <c r="C491" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D491" s="27" t="s">
-        <v>1536</v>
-      </c>
-      <c r="E491" s="4">
-        <v>1260</v>
-      </c>
-      <c r="F491" s="4">
-        <v>2115</v>
-      </c>
-      <c r="G491" s="4">
-        <v>0</v>
-      </c>
-      <c r="H491" s="4">
-        <v>0</v>
-      </c>
-      <c r="I491" s="4">
-        <v>0</v>
-      </c>
-      <c r="J491">
-        <v>2245</v>
-      </c>
-      <c r="K491" s="1">
-        <v>650</v>
-      </c>
-      <c r="L491" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M491" t="s">
-        <v>40</v>
-      </c>
-      <c r="N491" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="O491" s="4" t="s">
-        <v>1532</v>
-      </c>
-      <c r="P491" s="30" t="s">
-        <v>1537</v>
-      </c>
-      <c r="Q491" s="4" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="492" ht="17.25" spans="1:17">
-      <c r="A492" s="4" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B492" t="s">
-        <v>38</v>
-      </c>
-      <c r="C492" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D492" s="27" t="s">
-        <v>1540</v>
-      </c>
-      <c r="E492" s="4">
-        <v>1010</v>
-      </c>
-      <c r="F492" s="4">
-        <v>2219</v>
-      </c>
-      <c r="G492" s="4">
-        <v>0</v>
-      </c>
-      <c r="H492" s="4">
-        <v>0</v>
-      </c>
-      <c r="I492" s="4">
-        <v>0</v>
-      </c>
-      <c r="J492">
-        <v>2115</v>
-      </c>
-      <c r="K492" s="1">
-        <v>550</v>
-      </c>
-      <c r="L492" s="9" t="s">
-        <v>1069</v>
-      </c>
-      <c r="N492" s="30" t="s">
-        <v>644</v>
-      </c>
-      <c r="O492" s="4" t="s">
-        <v>1541</v>
-      </c>
-      <c r="P492" s="30" t="s">
-        <v>645</v>
-      </c>
-      <c r="Q492" s="4" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="493" ht="17.25" spans="1:17">
-      <c r="A493" s="4" t="s">
-        <v>1543</v>
-      </c>
-      <c r="B493" t="s">
-        <v>38</v>
-      </c>
-      <c r="C493" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D493" s="27" t="s">
-        <v>1544</v>
-      </c>
-      <c r="E493" s="4">
-        <v>1510</v>
-      </c>
-      <c r="F493" s="4">
-        <v>2822</v>
-      </c>
-      <c r="G493" s="4">
-        <v>0</v>
-      </c>
-      <c r="H493" s="4">
-        <v>0</v>
-      </c>
-      <c r="I493" s="4">
-        <v>0</v>
-      </c>
-      <c r="J493" s="25">
-        <v>2415</v>
-      </c>
-      <c r="K493" s="25">
-        <v>1040</v>
-      </c>
-      <c r="L493" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="N493" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="O493" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="P493" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q493" s="4" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="494" ht="17.25" spans="1:17">
-      <c r="A494" s="4" t="s">
-        <v>1546</v>
-      </c>
-      <c r="B494" t="s">
-        <v>38</v>
-      </c>
-      <c r="C494" t="s">
-        <v>88</v>
-      </c>
-      <c r="D494" s="27" t="s">
-        <v>1547</v>
-      </c>
-      <c r="E494" s="4">
-        <v>0</v>
-      </c>
-      <c r="F494" s="4">
-        <v>1620</v>
-      </c>
-      <c r="G494" s="4">
-        <v>986</v>
-      </c>
-      <c r="H494" s="4">
-        <v>0</v>
-      </c>
-      <c r="I494" s="4">
-        <v>0</v>
-      </c>
-      <c r="J494" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L494" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="N494" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="O494" s="25" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P494" s="30" t="s">
-        <v>1548</v>
-      </c>
-      <c r="Q494" s="4" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="495" ht="17.25" spans="1:17">
-      <c r="A495" s="4" t="s">
-        <v>1550</v>
-      </c>
-      <c r="B495" t="s">
-        <v>38</v>
-      </c>
-      <c r="C495" t="s">
-        <v>88</v>
-      </c>
-      <c r="D495" s="27" t="s">
-        <v>1551</v>
-      </c>
-      <c r="E495" s="4">
-        <v>0</v>
-      </c>
-      <c r="F495" s="4">
-        <v>1620</v>
-      </c>
-      <c r="G495" s="4">
-        <v>1274</v>
-      </c>
-      <c r="H495" s="4">
-        <v>0</v>
-      </c>
-      <c r="I495" s="4">
-        <v>0</v>
-      </c>
-      <c r="J495" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L495" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="N495" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="O495" s="25" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P495" s="30" t="s">
-        <v>1548</v>
-      </c>
-      <c r="Q495" s="4" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="496" ht="17.25" spans="1:17">
-      <c r="A496" s="4" t="s">
-        <v>1552</v>
-      </c>
-      <c r="B496" t="s">
-        <v>38</v>
-      </c>
-      <c r="C496" t="s">
-        <v>88</v>
-      </c>
-      <c r="D496" s="27" t="s">
-        <v>1553</v>
-      </c>
-      <c r="E496" s="4">
-        <v>0</v>
-      </c>
-      <c r="F496" s="4">
-        <v>1620</v>
-      </c>
-      <c r="G496" s="4">
-        <v>860</v>
-      </c>
-      <c r="H496" s="4">
-        <v>0</v>
-      </c>
-      <c r="I496" s="4">
-        <v>0</v>
-      </c>
-      <c r="J496" s="4">
-        <v>2035</v>
-      </c>
-      <c r="L496" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="N496" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="O496" s="25" t="s">
-        <v>1177</v>
-      </c>
-      <c r="P496" s="30" t="s">
-        <v>1548</v>
-      </c>
-      <c r="Q496" s="4" t="s">
-        <v>1549</v>
+        <v>1504</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T496">
+  <autoFilter ref="A1:T484">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9840"/>
+    <workbookView windowWidth="23325" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
@@ -4560,10 +4560,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
@@ -4611,16 +4611,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4633,6 +4634,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -4641,7 +4650,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4657,16 +4681,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4685,9 +4718,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4701,41 +4741,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4743,13 +4750,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4818,7 +4818,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4830,91 +4902,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4938,19 +4926,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4962,7 +4974,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4975,30 +4999,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5042,6 +5042,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -5053,32 +5071,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5098,20 +5090,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5139,6 +5128,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5147,10 +5147,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5159,133 +5159,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7689,7 +7689,7 @@
         <v>200</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>88</v>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9240"/>
+    <workbookView windowWidth="23325" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4701" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4701" uniqueCount="1511">
   <si>
     <t>单号</t>
   </si>
@@ -3044,9 +3044,6 @@
   </si>
   <si>
     <t>廖新福</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人力资源和社会保障局 </t>
   </si>
   <si>
     <t>县劳动人事争议仲裁院（全拨事业）</t>
@@ -4561,9 +4558,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
@@ -4619,16 +4616,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4642,8 +4631,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4656,8 +4646,85 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4671,76 +4738,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -4749,7 +4746,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4818,13 +4815,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4836,97 +4857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4938,13 +4869,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4968,7 +4893,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4980,25 +4953,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5046,7 +5043,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5055,7 +5052,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5075,21 +5072,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -5101,6 +5083,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5120,22 +5113,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5147,10 +5144,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5159,133 +5156,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -22674,20 +22671,20 @@
         <v>894</v>
       </c>
       <c r="O303" s="14" t="s">
-        <v>1009</v>
+        <v>316</v>
       </c>
       <c r="P303" s="7" t="s">
         <v>894</v>
       </c>
       <c r="Q303" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="R303" s="7"/>
       <c r="S303" s="7"/>
     </row>
     <row r="304" ht="14.25" spans="1:19">
       <c r="A304" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B304" t="s">
         <v>18</v>
@@ -22696,7 +22693,7 @@
         <v>88</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E304" s="24">
         <v>0</v>
@@ -22733,14 +22730,14 @@
         <v>951</v>
       </c>
       <c r="Q304" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="R304" s="7"/>
       <c r="S304" s="7"/>
     </row>
     <row r="305" ht="27.75" spans="1:19">
       <c r="A305" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B305" t="s">
         <v>18</v>
@@ -22749,7 +22746,7 @@
         <v>88</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E305" s="24">
         <v>0</v>
@@ -22780,20 +22777,20 @@
         <v>894</v>
       </c>
       <c r="O305" s="16" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="P305" s="7" t="s">
         <v>894</v>
       </c>
       <c r="Q305" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="R305" s="7"/>
       <c r="S305" s="7"/>
     </row>
     <row r="306" ht="27" spans="1:19">
       <c r="A306" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B306" t="s">
         <v>18</v>
@@ -22802,7 +22799,7 @@
         <v>88</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E306" s="24">
         <v>0</v>
@@ -22839,14 +22836,14 @@
         <v>894</v>
       </c>
       <c r="Q306" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="R306" s="7"/>
       <c r="S306" s="7"/>
     </row>
     <row r="307" spans="1:19">
       <c r="A307" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B307" t="s">
         <v>18</v>
@@ -22855,7 +22852,7 @@
         <v>88</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E307" s="24">
         <v>0</v>
@@ -22886,20 +22883,20 @@
         <v>879</v>
       </c>
       <c r="O307" s="14" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P307" s="7" t="s">
         <v>879</v>
       </c>
       <c r="Q307" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="R307" s="7"/>
       <c r="S307" s="7"/>
     </row>
     <row r="308" spans="1:19">
       <c r="A308" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>38</v>
@@ -22908,7 +22905,7 @@
         <v>19</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E308" s="24">
         <v>1260</v>
@@ -22944,17 +22941,17 @@
         <v>95</v>
       </c>
       <c r="P308" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="Q308" s="3" t="s">
         <v>1027</v>
-      </c>
-      <c r="Q308" s="3" t="s">
-        <v>1028</v>
       </c>
       <c r="R308" s="7"/>
       <c r="S308" s="7"/>
     </row>
     <row r="309" spans="1:19">
       <c r="A309" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>38</v>
@@ -22963,7 +22960,7 @@
         <v>19</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E309" s="24">
         <v>1170</v>
@@ -23002,14 +22999,14 @@
         <v>436</v>
       </c>
       <c r="Q309" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="R309" s="7"/>
       <c r="S309" s="7"/>
     </row>
     <row r="310" spans="1:19">
       <c r="A310" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>38</v>
@@ -23018,7 +23015,7 @@
         <v>19</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E310" s="24">
         <v>1010</v>
@@ -23052,7 +23049,7 @@
         <v>95</v>
       </c>
       <c r="P310" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q310" s="3" t="s">
         <v>323</v>
@@ -23062,7 +23059,7 @@
     </row>
     <row r="311" ht="27" spans="1:19">
       <c r="A311" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>38</v>
@@ -23071,7 +23068,7 @@
         <v>19</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E311" s="24">
         <v>1010</v>
@@ -23105,17 +23102,17 @@
         <v>95</v>
       </c>
       <c r="P311" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q311" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="Q311" s="3" t="s">
-        <v>1038</v>
       </c>
       <c r="R311" s="7"/>
       <c r="S311" s="7"/>
     </row>
     <row r="312" ht="27" spans="1:19">
       <c r="A312" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>38</v>
@@ -23124,7 +23121,7 @@
         <v>19</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E312" s="24">
         <v>1010</v>
@@ -23158,17 +23155,17 @@
         <v>95</v>
       </c>
       <c r="P312" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="Q312" s="3" t="s">
         <v>1041</v>
-      </c>
-      <c r="Q312" s="3" t="s">
-        <v>1042</v>
       </c>
       <c r="R312" s="7"/>
       <c r="S312" s="7"/>
     </row>
     <row r="313" ht="27" spans="1:19">
       <c r="A313" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>38</v>
@@ -23177,7 +23174,7 @@
         <v>19</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E313" s="24">
         <v>1010</v>
@@ -23211,17 +23208,17 @@
         <v>95</v>
       </c>
       <c r="P313" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Q313" s="3" t="s">
         <v>1045</v>
-      </c>
-      <c r="Q313" s="3" t="s">
-        <v>1046</v>
       </c>
       <c r="R313" s="7"/>
       <c r="S313" s="7"/>
     </row>
     <row r="314" spans="1:19">
       <c r="A314" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>38</v>
@@ -23230,7 +23227,7 @@
         <v>19</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E314" s="24">
         <v>1010</v>
@@ -23264,17 +23261,17 @@
         <v>95</v>
       </c>
       <c r="P314" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Q314" s="3" t="s">
         <v>1049</v>
-      </c>
-      <c r="Q314" s="3" t="s">
-        <v>1050</v>
       </c>
       <c r="R314" s="7"/>
       <c r="S314" s="7"/>
     </row>
     <row r="315" spans="1:19">
       <c r="A315" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>38</v>
@@ -23283,7 +23280,7 @@
         <v>19</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E315" s="24">
         <v>1010</v>
@@ -23317,17 +23314,17 @@
         <v>95</v>
       </c>
       <c r="P315" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Q315" s="3" t="s">
         <v>1053</v>
-      </c>
-      <c r="Q315" s="3" t="s">
-        <v>1054</v>
       </c>
       <c r="R315" s="7"/>
       <c r="S315" s="7"/>
     </row>
     <row r="316" spans="1:19">
       <c r="A316" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>38</v>
@@ -23336,7 +23333,7 @@
         <v>88</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E316" s="24">
         <v>0</v>
@@ -23370,17 +23367,17 @@
         <v>118</v>
       </c>
       <c r="P316" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="Q316" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="Q316" s="3" t="s">
-        <v>1058</v>
       </c>
       <c r="R316" s="7"/>
       <c r="S316" s="7"/>
     </row>
     <row r="317" spans="1:19">
       <c r="A317" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>18</v>
@@ -23389,7 +23386,7 @@
         <v>88</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E317" s="24">
         <v>0</v>
@@ -23429,7 +23426,7 @@
     </row>
     <row r="318" spans="1:19">
       <c r="A318" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B318" s="4" t="s">
         <v>18</v>
@@ -23438,7 +23435,7 @@
         <v>88</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E318" s="24">
         <v>0</v>
@@ -23478,16 +23475,16 @@
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B319" s="4" t="s">
         <v>1063</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="C319" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D319" s="4" t="s">
         <v>1064</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>1065</v>
       </c>
       <c r="E319" s="4">
         <v>5653</v>
@@ -23511,28 +23508,28 @@
         <v>0</v>
       </c>
       <c r="L319" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M319" s="4"/>
       <c r="N319" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O319" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="320" spans="1:15">
       <c r="A320" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D320" s="4" t="s">
         <v>1068</v>
-      </c>
-      <c r="B320" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D320" s="4" t="s">
-        <v>1069</v>
       </c>
       <c r="E320" s="4">
         <v>7003</v>
@@ -23556,28 +23553,28 @@
         <v>0</v>
       </c>
       <c r="L320" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M320" s="4"/>
       <c r="N320" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O320" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D321" s="4" t="s">
         <v>1071</v>
-      </c>
-      <c r="B321" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>1072</v>
       </c>
       <c r="E321" s="4">
         <v>4825</v>
@@ -23605,24 +23602,24 @@
       </c>
       <c r="M321" s="4"/>
       <c r="N321" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O321" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D322" s="4" t="s">
         <v>1073</v>
-      </c>
-      <c r="B322" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>1074</v>
       </c>
       <c r="E322" s="4">
         <v>5624</v>
@@ -23646,28 +23643,28 @@
         <v>0</v>
       </c>
       <c r="L322" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M322" s="4"/>
       <c r="N322" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O322" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D323" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C323" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D323" s="4" t="s">
-        <v>1077</v>
       </c>
       <c r="E323" s="4">
         <v>3817</v>
@@ -23691,28 +23688,28 @@
         <v>0</v>
       </c>
       <c r="L323" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M323" s="4"/>
       <c r="N323" s="4" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="O323" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="324" spans="1:15">
       <c r="A324" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D324" s="4" t="s">
         <v>1079</v>
-      </c>
-      <c r="B324" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D324" s="4" t="s">
-        <v>1080</v>
       </c>
       <c r="E324" s="4">
         <v>4845</v>
@@ -23736,28 +23733,28 @@
         <v>1040</v>
       </c>
       <c r="L324" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M324" s="4"/>
       <c r="N324" s="4" t="s">
         <v>278</v>
       </c>
       <c r="O324" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D325" s="4" t="s">
         <v>1082</v>
-      </c>
-      <c r="B325" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D325" s="4" t="s">
-        <v>1083</v>
       </c>
       <c r="E325" s="4">
         <v>3500</v>
@@ -23781,28 +23778,28 @@
         <v>0</v>
       </c>
       <c r="L325" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M325" s="4"/>
       <c r="N325" s="4" t="s">
         <v>334</v>
       </c>
       <c r="O325" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D326" s="4" t="s">
         <v>1084</v>
-      </c>
-      <c r="B326" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D326" s="4" t="s">
-        <v>1085</v>
       </c>
       <c r="E326" s="4">
         <v>5238</v>
@@ -23826,28 +23823,28 @@
         <v>0</v>
       </c>
       <c r="L326" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M326" s="4"/>
       <c r="N326" s="4" t="s">
         <v>317</v>
       </c>
       <c r="O326" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D327" s="4" t="s">
         <v>1087</v>
-      </c>
-      <c r="B327" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D327" s="4" t="s">
-        <v>1088</v>
       </c>
       <c r="E327" s="4">
         <v>4568</v>
@@ -23871,28 +23868,28 @@
         <v>650</v>
       </c>
       <c r="L327" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M327" s="4"/>
       <c r="N327" s="4" t="s">
         <v>252</v>
       </c>
       <c r="O327" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="328" spans="1:15">
       <c r="A328" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D328" s="4" t="s">
         <v>1089</v>
-      </c>
-      <c r="B328" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D328" s="4" t="s">
-        <v>1090</v>
       </c>
       <c r="E328" s="4">
         <v>4845</v>
@@ -23916,28 +23913,28 @@
         <v>1040</v>
       </c>
       <c r="L328" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M328" s="4"/>
       <c r="N328" s="4" t="s">
         <v>327</v>
       </c>
       <c r="O328" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D329" s="4" t="s">
         <v>1091</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D329" s="4" t="s">
-        <v>1092</v>
       </c>
       <c r="E329" s="4">
         <v>3377</v>
@@ -23961,28 +23958,28 @@
         <v>500</v>
       </c>
       <c r="L329" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M329" s="4"/>
       <c r="N329" s="4" t="s">
         <v>327</v>
       </c>
       <c r="O329" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D330" s="4" t="s">
         <v>1094</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>1095</v>
       </c>
       <c r="E330" s="4">
         <v>1870.4</v>
@@ -24006,28 +24003,28 @@
         <v>0</v>
       </c>
       <c r="L330" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M330" s="4"/>
       <c r="N330" s="4" t="s">
         <v>154</v>
       </c>
       <c r="O330" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D331" s="4" t="s">
         <v>1096</v>
-      </c>
-      <c r="B331" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D331" s="4" t="s">
-        <v>1097</v>
       </c>
       <c r="E331" s="4">
         <v>6095</v>
@@ -24051,28 +24048,28 @@
         <v>1040</v>
       </c>
       <c r="L331" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M331" s="4"/>
       <c r="N331" s="4" t="s">
         <v>836</v>
       </c>
       <c r="O331" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="332" spans="1:15">
       <c r="A332" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D332" s="4" t="s">
         <v>1098</v>
-      </c>
-      <c r="B332" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C332" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>1099</v>
       </c>
       <c r="E332" s="4">
         <v>5834</v>
@@ -24103,21 +24100,21 @@
         <v>836</v>
       </c>
       <c r="O332" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D333" s="4" t="s">
         <v>1100</v>
-      </c>
-      <c r="B333" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C333" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D333" s="4" t="s">
-        <v>1101</v>
       </c>
       <c r="E333" s="4">
         <v>6168</v>
@@ -24141,28 +24138,28 @@
         <v>1040</v>
       </c>
       <c r="L333" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M333" s="4"/>
       <c r="N333" s="4" t="s">
         <v>836</v>
       </c>
       <c r="O333" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D334" s="4" t="s">
         <v>1102</v>
-      </c>
-      <c r="B334" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D334" s="4" t="s">
-        <v>1103</v>
       </c>
       <c r="E334" s="4">
         <v>5380</v>
@@ -24190,24 +24187,24 @@
       </c>
       <c r="M334" s="4"/>
       <c r="N334" s="25" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="O334" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D335" s="4" t="s">
         <v>1105</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C335" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D335" s="4" t="s">
-        <v>1106</v>
       </c>
       <c r="E335" s="4">
         <v>5380</v>
@@ -24231,28 +24228,28 @@
         <v>1150</v>
       </c>
       <c r="L335" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M335" s="4"/>
       <c r="N335" s="25" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="O335" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="336" spans="1:15">
       <c r="A336" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D336" s="4" t="s">
         <v>1107</v>
-      </c>
-      <c r="B336" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C336" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D336" s="4" t="s">
-        <v>1108</v>
       </c>
       <c r="E336" s="4">
         <v>5524</v>
@@ -24276,28 +24273,28 @@
         <v>650</v>
       </c>
       <c r="L336" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M336" s="4"/>
       <c r="N336" s="25" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="O336" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D337" s="4" t="s">
         <v>1109</v>
-      </c>
-      <c r="B337" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C337" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D337" s="4" t="s">
-        <v>1110</v>
       </c>
       <c r="E337" s="4">
         <v>4568</v>
@@ -24321,28 +24318,28 @@
         <v>950</v>
       </c>
       <c r="L337" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M337" s="4"/>
       <c r="N337" s="4" t="s">
         <v>147</v>
       </c>
       <c r="O337" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D338" s="4" t="s">
         <v>1112</v>
-      </c>
-      <c r="B338" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D338" s="4" t="s">
-        <v>1113</v>
       </c>
       <c r="E338" s="4">
         <v>3466</v>
@@ -24366,28 +24363,28 @@
         <v>0</v>
       </c>
       <c r="L338" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M338" s="4"/>
       <c r="N338" s="4" t="s">
         <v>600</v>
       </c>
       <c r="O338" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="339" ht="14.25" spans="1:15">
       <c r="A339" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D339" s="4" t="s">
         <v>1114</v>
-      </c>
-      <c r="B339" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C339" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D339" s="4" t="s">
-        <v>1115</v>
       </c>
       <c r="E339" s="4">
         <v>4377</v>
@@ -24411,28 +24408,28 @@
         <v>0</v>
       </c>
       <c r="L339" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M339" s="4"/>
       <c r="N339" s="4" t="s">
         <v>600</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="340" ht="14.25" spans="1:15">
       <c r="A340" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D340" s="4" t="s">
         <v>1116</v>
-      </c>
-      <c r="B340" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D340" s="4" t="s">
-        <v>1117</v>
       </c>
       <c r="E340" s="4">
         <v>3741</v>
@@ -24456,28 +24453,28 @@
         <v>650</v>
       </c>
       <c r="L340" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M340" s="4"/>
       <c r="N340" s="16" t="s">
         <v>206</v>
       </c>
       <c r="O340" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D341" s="4" t="s">
         <v>1118</v>
-      </c>
-      <c r="B341" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C341" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D341" s="4" t="s">
-        <v>1119</v>
       </c>
       <c r="E341" s="4">
         <v>2738</v>
@@ -24501,28 +24498,28 @@
         <v>0</v>
       </c>
       <c r="L341" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M341" s="4"/>
       <c r="N341" s="25" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="O341" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D342" s="4" t="s">
         <v>1122</v>
-      </c>
-      <c r="B342" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D342" s="4" t="s">
-        <v>1123</v>
       </c>
       <c r="E342" s="4">
         <v>4278</v>
@@ -24546,28 +24543,28 @@
         <v>0</v>
       </c>
       <c r="L342" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M342" s="4"/>
       <c r="N342" s="4" t="s">
         <v>241</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D343" s="4" t="s">
         <v>1124</v>
-      </c>
-      <c r="B343" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C343" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D343" s="4" t="s">
-        <v>1125</v>
       </c>
       <c r="E343" s="4">
         <v>4424</v>
@@ -24591,28 +24588,28 @@
         <v>650</v>
       </c>
       <c r="L343" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M343" s="4"/>
       <c r="N343" s="14" t="s">
         <v>251</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="344" spans="1:15">
       <c r="A344" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D344" s="4" t="s">
         <v>1126</v>
-      </c>
-      <c r="B344" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D344" s="4" t="s">
-        <v>1127</v>
       </c>
       <c r="E344" s="4">
         <v>4568</v>
@@ -24636,28 +24633,28 @@
         <v>650</v>
       </c>
       <c r="L344" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M344" s="4"/>
       <c r="N344" s="14" t="s">
         <v>251</v>
       </c>
       <c r="O344" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D345" s="4" t="s">
         <v>1128</v>
-      </c>
-      <c r="B345" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C345" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D345" s="4" t="s">
-        <v>1129</v>
       </c>
       <c r="E345" s="4">
         <v>5495</v>
@@ -24681,28 +24678,28 @@
         <v>0</v>
       </c>
       <c r="L345" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M345" s="4"/>
       <c r="N345" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D346" s="4" t="s">
         <v>1131</v>
-      </c>
-      <c r="B346" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C346" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D346" s="4" t="s">
-        <v>1132</v>
       </c>
       <c r="E346" s="4">
         <v>8278</v>
@@ -24730,24 +24727,24 @@
       </c>
       <c r="M346" s="4"/>
       <c r="N346" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D347" s="4" t="s">
         <v>1133</v>
-      </c>
-      <c r="B347" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C347" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D347" s="4" t="s">
-        <v>1134</v>
       </c>
       <c r="E347" s="4">
         <v>3895</v>
@@ -24771,28 +24768,28 @@
         <v>400</v>
       </c>
       <c r="L347" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M347" s="4"/>
       <c r="N347" s="4" t="s">
         <v>70</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="348" spans="1:15">
       <c r="A348" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D348" s="4" t="s">
         <v>1135</v>
-      </c>
-      <c r="B348" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C348" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D348" s="4" t="s">
-        <v>1136</v>
       </c>
       <c r="E348" s="4">
         <v>4134</v>
@@ -24816,28 +24813,28 @@
         <v>0</v>
       </c>
       <c r="L348" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M348" s="4"/>
       <c r="N348" s="4" t="s">
         <v>154</v>
       </c>
       <c r="O348" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D349" s="4" t="s">
         <v>1137</v>
-      </c>
-      <c r="B349" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C349" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D349" s="4" t="s">
-        <v>1138</v>
       </c>
       <c r="E349" s="4">
         <v>3974</v>
@@ -24861,28 +24858,28 @@
         <v>0</v>
       </c>
       <c r="L349" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M349" s="4"/>
       <c r="N349" s="4" t="s">
         <v>154</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D350" s="4" t="s">
         <v>1139</v>
-      </c>
-      <c r="B350" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C350" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D350" s="4" t="s">
-        <v>1140</v>
       </c>
       <c r="E350" s="4">
         <v>4067</v>
@@ -24906,28 +24903,28 @@
         <v>650</v>
       </c>
       <c r="L350" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M350" s="4"/>
       <c r="N350" s="4" t="s">
         <v>154</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D351" s="4" t="s">
         <v>1141</v>
-      </c>
-      <c r="B351" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C351" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D351" s="4" t="s">
-        <v>1142</v>
       </c>
       <c r="E351" s="4">
         <v>2988</v>
@@ -24951,28 +24948,28 @@
         <v>0</v>
       </c>
       <c r="L351" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M351" s="4"/>
       <c r="N351" s="4" t="s">
         <v>413</v>
       </c>
       <c r="O351" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="352" spans="1:15">
       <c r="A352" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D352" s="4" t="s">
         <v>1143</v>
-      </c>
-      <c r="B352" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C352" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D352" s="4" t="s">
-        <v>1144</v>
       </c>
       <c r="E352" s="4">
         <v>4175</v>
@@ -24996,28 +24993,28 @@
         <v>0</v>
       </c>
       <c r="L352" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M352" s="4"/>
       <c r="N352" s="4" t="s">
         <v>413</v>
       </c>
       <c r="O352" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D353" s="4" t="s">
         <v>1145</v>
-      </c>
-      <c r="B353" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C353" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D353" s="4" t="s">
-        <v>1146</v>
       </c>
       <c r="E353" s="4">
         <v>4999</v>
@@ -25041,28 +25038,28 @@
         <v>1040</v>
       </c>
       <c r="L353" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M353" s="4"/>
       <c r="N353" s="4" t="s">
         <v>90</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D354" s="4" t="s">
         <v>1147</v>
-      </c>
-      <c r="B354" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C354" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D354" s="4" t="s">
-        <v>1148</v>
       </c>
       <c r="E354" s="4">
         <v>3250</v>
@@ -25086,28 +25083,28 @@
         <v>0</v>
       </c>
       <c r="L354" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M354" s="4"/>
       <c r="N354" s="4" t="s">
         <v>90</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="355" spans="1:16">
       <c r="A355" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D355" s="4" t="s">
         <v>1150</v>
-      </c>
-      <c r="B355" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C355" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D355" s="4" t="s">
-        <v>1151</v>
       </c>
       <c r="E355" s="4">
         <v>4845</v>
@@ -25131,31 +25128,31 @@
         <v>0</v>
       </c>
       <c r="L355" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M355" s="4"/>
       <c r="N355" s="4" t="s">
         <v>90</v>
       </c>
       <c r="O355" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P355" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="356" spans="1:15">
       <c r="A356" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D356" s="4" t="s">
         <v>1153</v>
-      </c>
-      <c r="B356" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D356" s="4" t="s">
-        <v>1154</v>
       </c>
       <c r="E356" s="4">
         <v>4105</v>
@@ -25179,28 +25176,28 @@
         <v>950</v>
       </c>
       <c r="L356" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M356" s="4"/>
       <c r="N356" s="4" t="s">
         <v>29</v>
       </c>
       <c r="O356" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D357" s="4" t="s">
         <v>1155</v>
-      </c>
-      <c r="B357" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C357" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D357" s="4" t="s">
-        <v>1156</v>
       </c>
       <c r="E357" s="4">
         <v>2738</v>
@@ -25224,28 +25221,28 @@
         <v>400</v>
       </c>
       <c r="L357" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M357" s="4"/>
       <c r="N357" s="4" t="s">
         <v>202</v>
       </c>
       <c r="O357" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D358" s="4" t="s">
         <v>1157</v>
-      </c>
-      <c r="B358" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D358" s="4" t="s">
-        <v>1158</v>
       </c>
       <c r="E358" s="4">
         <v>3829</v>
@@ -25269,28 +25266,28 @@
         <v>0</v>
       </c>
       <c r="L358" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M358" s="4"/>
       <c r="N358" s="4" t="s">
         <v>316</v>
       </c>
       <c r="O358" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D359" s="4" t="s">
         <v>1159</v>
-      </c>
-      <c r="B359" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C359" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D359" s="4" t="s">
-        <v>1160</v>
       </c>
       <c r="E359" s="4">
         <v>2952</v>
@@ -25314,28 +25311,28 @@
         <v>0</v>
       </c>
       <c r="L359" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M359" s="4"/>
       <c r="N359" s="4" t="s">
         <v>316</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="360" spans="1:15">
       <c r="A360" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D360" s="4" t="s">
         <v>1161</v>
-      </c>
-      <c r="B360" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D360" s="4" t="s">
-        <v>1162</v>
       </c>
       <c r="E360" s="4">
         <v>4845</v>
@@ -25359,28 +25356,28 @@
         <v>0</v>
       </c>
       <c r="L360" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M360" s="4"/>
       <c r="N360" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="O360" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D361" s="4" t="s">
         <v>1164</v>
-      </c>
-      <c r="B361" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C361" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D361" s="4" t="s">
-        <v>1165</v>
       </c>
       <c r="E361" s="4">
         <v>4146</v>
@@ -25404,28 +25401,28 @@
         <v>0</v>
       </c>
       <c r="L361" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M361" s="4"/>
       <c r="N361" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O361" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D362" s="4" t="s">
         <v>1166</v>
-      </c>
-      <c r="B362" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D362" s="4" t="s">
-        <v>1167</v>
       </c>
       <c r="E362" s="4">
         <v>4208</v>
@@ -25456,21 +25453,21 @@
         <v>242</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D363" s="4" t="s">
         <v>1168</v>
-      </c>
-      <c r="B363" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C363" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D363" s="4" t="s">
-        <v>1169</v>
       </c>
       <c r="E363" s="4">
         <v>6385</v>
@@ -25494,28 +25491,28 @@
         <v>0</v>
       </c>
       <c r="L363" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M363" s="4"/>
       <c r="N363" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="364" spans="1:15">
       <c r="A364" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D364" s="4" t="s">
         <v>1170</v>
-      </c>
-      <c r="B364" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C364" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D364" s="4" t="s">
-        <v>1171</v>
       </c>
       <c r="E364" s="4">
         <v>4010</v>
@@ -25539,28 +25536,28 @@
         <v>0</v>
       </c>
       <c r="L364" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M364" s="4"/>
       <c r="N364" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O364" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D365" s="4" t="s">
         <v>1172</v>
-      </c>
-      <c r="B365" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C365" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>1173</v>
       </c>
       <c r="E365" s="4">
         <v>5181</v>
@@ -25584,28 +25581,28 @@
         <v>0</v>
       </c>
       <c r="L365" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M365" s="4"/>
       <c r="N365" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D366" s="4" t="s">
         <v>1174</v>
-      </c>
-      <c r="B366" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C366" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D366" s="4" t="s">
-        <v>1175</v>
       </c>
       <c r="E366" s="4">
         <v>4566</v>
@@ -25629,28 +25626,28 @@
         <v>0</v>
       </c>
       <c r="L366" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M366" s="4"/>
       <c r="N366" s="4" t="s">
         <v>242</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D367" s="4" t="s">
         <v>1176</v>
-      </c>
-      <c r="B367" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C367" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D367" s="4" t="s">
-        <v>1177</v>
       </c>
       <c r="E367" s="4">
         <v>4041</v>
@@ -25674,28 +25671,28 @@
         <v>550</v>
       </c>
       <c r="L367" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M367" s="4"/>
       <c r="N367" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="368" spans="1:15">
       <c r="A368" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D368" s="4" t="s">
         <v>1179</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D368" s="4" t="s">
-        <v>1180</v>
       </c>
       <c r="E368" s="4">
         <v>4154</v>
@@ -25719,28 +25716,28 @@
         <v>500</v>
       </c>
       <c r="L368" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M368" s="4"/>
       <c r="N368" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O368" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D369" s="4" t="s">
         <v>1181</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C369" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D369" s="4" t="s">
-        <v>1182</v>
       </c>
       <c r="E369" s="4">
         <v>4114</v>
@@ -25764,28 +25761,28 @@
         <v>0</v>
       </c>
       <c r="L369" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M369" s="4"/>
       <c r="N369" s="4" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D370" s="4" t="s">
         <v>1184</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D370" s="4" t="s">
-        <v>1185</v>
       </c>
       <c r="E370" s="4">
         <v>2760</v>
@@ -25809,28 +25806,28 @@
         <v>0</v>
       </c>
       <c r="L370" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M370" s="4"/>
       <c r="N370" s="4" t="s">
         <v>413</v>
       </c>
       <c r="O370" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="371" ht="14.25" spans="1:15">
       <c r="A371" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D371" s="4" t="s">
         <v>1186</v>
-      </c>
-      <c r="B371" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C371" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D371" s="4" t="s">
-        <v>1187</v>
       </c>
       <c r="E371" s="4">
         <v>5082</v>
@@ -25854,28 +25851,28 @@
         <v>1040</v>
       </c>
       <c r="L371" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M371" s="4"/>
       <c r="N371" s="4" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="372" ht="14.25" spans="1:15">
       <c r="A372" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D372" s="4" t="s">
         <v>1189</v>
-      </c>
-      <c r="B372" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C372" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D372" s="4" t="s">
-        <v>1190</v>
       </c>
       <c r="E372" s="4">
         <v>4105</v>
@@ -25899,28 +25896,28 @@
         <v>0</v>
       </c>
       <c r="L372" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M372" s="4"/>
       <c r="N372" s="26" t="s">
         <v>975</v>
       </c>
       <c r="O372" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="373" ht="14.25" spans="1:15">
       <c r="A373" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D373" s="4" t="s">
         <v>1191</v>
-      </c>
-      <c r="B373" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C373" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D373" s="4" t="s">
-        <v>1192</v>
       </c>
       <c r="E373" s="4">
         <v>4105</v>
@@ -25944,28 +25941,28 @@
         <v>0</v>
       </c>
       <c r="L373" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M373" s="4"/>
       <c r="N373" s="26" t="s">
         <v>975</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="374" ht="14.25" spans="1:15">
       <c r="A374" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D374" s="4" t="s">
         <v>1193</v>
-      </c>
-      <c r="B374" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C374" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>1194</v>
       </c>
       <c r="E374" s="4">
         <v>3971</v>
@@ -25989,28 +25986,28 @@
         <v>0</v>
       </c>
       <c r="L374" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M374" s="4"/>
       <c r="N374" s="26" t="s">
         <v>975</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D375" s="4" t="s">
         <v>1195</v>
-      </c>
-      <c r="B375" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C375" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>1196</v>
       </c>
       <c r="E375" s="4">
         <v>4568</v>
@@ -26034,28 +26031,28 @@
         <v>1000</v>
       </c>
       <c r="L375" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M375" s="4"/>
       <c r="N375" s="4" t="s">
         <v>128</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="376" spans="1:15">
       <c r="A376" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D376" s="4" t="s">
         <v>1197</v>
-      </c>
-      <c r="B376" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C376" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D376" s="4" t="s">
-        <v>1198</v>
       </c>
       <c r="E376" s="4">
         <v>4424</v>
@@ -26079,28 +26076,28 @@
         <v>650</v>
       </c>
       <c r="L376" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M376" s="4"/>
       <c r="N376" s="4" t="s">
         <v>224</v>
       </c>
       <c r="O376" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D377" s="4" t="s">
         <v>1199</v>
-      </c>
-      <c r="B377" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C377" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D377" s="4" t="s">
-        <v>1200</v>
       </c>
       <c r="E377" s="4">
         <v>5153</v>
@@ -26124,28 +26121,28 @@
         <v>1040</v>
       </c>
       <c r="L377" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M377" s="4"/>
       <c r="N377" s="4" t="s">
         <v>224</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D378" s="4" t="s">
         <v>1201</v>
-      </c>
-      <c r="B378" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C378" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D378" s="4" t="s">
-        <v>1202</v>
       </c>
       <c r="E378" s="4">
         <v>4105</v>
@@ -26169,28 +26166,28 @@
         <v>0</v>
       </c>
       <c r="L378" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M378" s="4"/>
       <c r="N378" s="4" t="s">
         <v>491</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D379" s="4" t="s">
         <v>1203</v>
-      </c>
-      <c r="B379" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C379" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D379" s="4" t="s">
-        <v>1204</v>
       </c>
       <c r="E379" s="4">
         <v>4803</v>
@@ -26214,28 +26211,28 @@
         <v>0</v>
       </c>
       <c r="L379" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M379" s="4"/>
       <c r="N379" s="4" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="380" spans="1:15">
       <c r="A380" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D380" s="4" t="s">
         <v>1206</v>
-      </c>
-      <c r="B380" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C380" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D380" s="4" t="s">
-        <v>1207</v>
       </c>
       <c r="E380" s="4">
         <v>3764</v>
@@ -26259,28 +26256,28 @@
         <v>0</v>
       </c>
       <c r="L380" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M380" s="4"/>
       <c r="N380" s="4" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="O380" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D381" s="4" t="s">
         <v>1208</v>
-      </c>
-      <c r="B381" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C381" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D381" s="4" t="s">
-        <v>1209</v>
       </c>
       <c r="E381" s="4">
         <v>3116</v>
@@ -26304,28 +26301,28 @@
         <v>500</v>
       </c>
       <c r="L381" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M381" s="4"/>
       <c r="N381" s="4" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D382" s="4" t="s">
         <v>1211</v>
-      </c>
-      <c r="B382" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C382" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D382" s="4" t="s">
-        <v>1212</v>
       </c>
       <c r="E382" s="4">
         <v>3688</v>
@@ -26349,28 +26346,28 @@
         <v>500</v>
       </c>
       <c r="L382" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M382" s="4"/>
       <c r="N382" s="4" t="s">
         <v>944</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D383" s="4" t="s">
         <v>1213</v>
-      </c>
-      <c r="B383" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D383" s="4" t="s">
-        <v>1214</v>
       </c>
       <c r="E383" s="4">
         <v>2824</v>
@@ -26394,28 +26391,28 @@
         <v>450</v>
       </c>
       <c r="L383" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M383" s="4"/>
       <c r="N383" s="4" t="s">
         <v>124</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="384" spans="1:15">
       <c r="A384" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D384" s="4" t="s">
         <v>1215</v>
-      </c>
-      <c r="B384" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C384" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D384" s="4" t="s">
-        <v>1216</v>
       </c>
       <c r="E384" s="4">
         <v>3116</v>
@@ -26439,28 +26436,28 @@
         <v>400</v>
       </c>
       <c r="L384" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M384" s="4"/>
       <c r="N384" s="4" t="s">
         <v>41</v>
       </c>
       <c r="O384" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D385" s="4" t="s">
         <v>1217</v>
-      </c>
-      <c r="B385" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C385" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D385" s="4" t="s">
-        <v>1218</v>
       </c>
       <c r="E385" s="4">
         <v>3939</v>
@@ -26484,28 +26481,28 @@
         <v>400</v>
       </c>
       <c r="L385" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M385" s="4"/>
       <c r="N385" s="4" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="4" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E386" s="4">
         <v>4424</v>
@@ -26529,28 +26526,28 @@
         <v>650</v>
       </c>
       <c r="L386" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M386" s="4"/>
       <c r="N386" s="4" t="s">
         <v>257</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D387" s="4" t="s">
         <v>1221</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C387" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D387" s="4" t="s">
-        <v>1222</v>
       </c>
       <c r="E387" s="4">
         <v>3971</v>
@@ -26574,28 +26571,28 @@
         <v>0</v>
       </c>
       <c r="L387" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M387" s="4"/>
       <c r="N387" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="O387" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="388" spans="1:15">
       <c r="A388" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D388" s="4" t="s">
         <v>1224</v>
-      </c>
-      <c r="B388" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C388" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D388" s="4" t="s">
-        <v>1225</v>
       </c>
       <c r="E388" s="4">
         <v>4999</v>
@@ -26619,28 +26616,28 @@
         <v>0</v>
       </c>
       <c r="L388" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M388" s="4"/>
       <c r="N388" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="O388" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B389" s="4" t="s">
         <v>1227</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="C389" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D389" s="4" t="s">
         <v>1228</v>
-      </c>
-      <c r="C389" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D389" s="4" t="s">
-        <v>1229</v>
       </c>
       <c r="E389" s="4">
         <v>2595</v>
@@ -26671,21 +26668,21 @@
         <v>95</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D390" s="4" t="s">
         <v>1230</v>
-      </c>
-      <c r="B390" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C390" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D390" s="4" t="s">
-        <v>1231</v>
       </c>
       <c r="E390" s="4">
         <v>2332</v>
@@ -26707,28 +26704,28 @@
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M390" s="4"/>
       <c r="N390" s="4" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="O390" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D391" s="4" t="s">
         <v>1233</v>
-      </c>
-      <c r="B391" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C391" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D391" s="4" t="s">
-        <v>1234</v>
       </c>
       <c r="E391" s="4">
         <v>2312</v>
@@ -26750,28 +26747,28 @@
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M391" s="4"/>
       <c r="N391" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O391" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="392" spans="1:15">
       <c r="A392" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D392" s="4" t="s">
         <v>1236</v>
-      </c>
-      <c r="B392" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C392" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D392" s="4" t="s">
-        <v>1237</v>
       </c>
       <c r="E392" s="4">
         <v>2386</v>
@@ -26793,28 +26790,28 @@
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M392" s="4"/>
       <c r="N392" s="4" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="O392" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D393" s="4" t="s">
         <v>1239</v>
-      </c>
-      <c r="B393" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C393" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D393" s="4" t="s">
-        <v>1240</v>
       </c>
       <c r="E393" s="4">
         <v>2064</v>
@@ -26836,28 +26833,28 @@
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M393" s="4"/>
       <c r="N393" s="4" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D394" s="4" t="s">
         <v>1242</v>
-      </c>
-      <c r="B394" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C394" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D394" s="4" t="s">
-        <v>1243</v>
       </c>
       <c r="E394" s="4">
         <v>1946</v>
@@ -26879,28 +26876,28 @@
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M394" s="4"/>
       <c r="N394" s="4" t="s">
         <v>604</v>
       </c>
       <c r="O394" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D395" s="4" t="s">
         <v>1244</v>
-      </c>
-      <c r="B395" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D395" s="4" t="s">
-        <v>1245</v>
       </c>
       <c r="E395" s="4">
         <v>2133</v>
@@ -26922,28 +26919,28 @@
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M395" s="4"/>
       <c r="N395" s="4" t="s">
         <v>600</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="396" spans="1:15">
       <c r="A396" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D396" s="4" t="s">
         <v>1246</v>
-      </c>
-      <c r="B396" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D396" s="4" t="s">
-        <v>1247</v>
       </c>
       <c r="E396" s="4">
         <v>2500</v>
@@ -26965,28 +26962,28 @@
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M396" s="4"/>
       <c r="N396" s="4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="O396" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D397" s="4" t="s">
         <v>1249</v>
-      </c>
-      <c r="B397" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C397" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D397" s="4" t="s">
-        <v>1250</v>
       </c>
       <c r="E397" s="4">
         <v>2366</v>
@@ -27008,28 +27005,28 @@
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M397" s="4"/>
       <c r="N397" s="4" t="s">
         <v>110</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D398" s="4" t="s">
         <v>1251</v>
-      </c>
-      <c r="B398" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D398" s="4" t="s">
-        <v>1252</v>
       </c>
       <c r="E398" s="4">
         <v>2366</v>
@@ -27051,28 +27048,28 @@
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M398" s="4"/>
       <c r="N398" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D399" s="4" t="s">
         <v>1254</v>
-      </c>
-      <c r="B399" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C399" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D399" s="4" t="s">
-        <v>1255</v>
       </c>
       <c r="E399" s="4">
         <v>2286</v>
@@ -27094,28 +27091,28 @@
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M399" s="4"/>
       <c r="N399" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="400" spans="1:15">
       <c r="A400" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D400" s="4" t="s">
         <v>1256</v>
-      </c>
-      <c r="B400" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D400" s="4" t="s">
-        <v>1257</v>
       </c>
       <c r="E400" s="4">
         <v>2286</v>
@@ -27137,28 +27134,28 @@
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M400" s="4"/>
       <c r="N400" s="4" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="O400" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D401" s="4" t="s">
         <v>1258</v>
-      </c>
-      <c r="B401" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C401" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D401" s="4" t="s">
-        <v>1259</v>
       </c>
       <c r="E401" s="4">
         <v>2156</v>
@@ -27180,28 +27177,28 @@
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M401" s="4"/>
       <c r="N401" s="4" t="s">
         <v>990</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D402" s="4" t="s">
         <v>1260</v>
-      </c>
-      <c r="B402" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C402" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D402" s="4" t="s">
-        <v>1261</v>
       </c>
       <c r="E402" s="4">
         <v>2386</v>
@@ -27223,28 +27220,28 @@
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M402" s="4"/>
       <c r="N402" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D403" s="4" t="s">
         <v>1262</v>
-      </c>
-      <c r="B403" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C403" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D403" s="4" t="s">
-        <v>1263</v>
       </c>
       <c r="E403" s="4">
         <v>2312</v>
@@ -27266,28 +27263,28 @@
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M403" s="4"/>
       <c r="N403" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="404" spans="1:15">
       <c r="A404" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D404" s="4" t="s">
         <v>1264</v>
-      </c>
-      <c r="B404" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D404" s="4" t="s">
-        <v>1265</v>
       </c>
       <c r="E404" s="4">
         <v>2386</v>
@@ -27309,28 +27306,28 @@
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M404" s="4"/>
       <c r="N404" s="4" t="s">
         <v>608</v>
       </c>
       <c r="O404" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="405" spans="1:15">
       <c r="A405" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D405" s="4" t="s">
         <v>1266</v>
-      </c>
-      <c r="B405" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>1267</v>
       </c>
       <c r="E405" s="4">
         <v>2332</v>
@@ -27352,28 +27349,28 @@
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M405" s="4"/>
       <c r="N405" s="4" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O405" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D406" s="4" t="s">
         <v>1269</v>
-      </c>
-      <c r="B406" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D406" s="4" t="s">
-        <v>1270</v>
       </c>
       <c r="E406" s="4">
         <v>2332</v>
@@ -27395,28 +27392,28 @@
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M406" s="4"/>
       <c r="N406" s="4" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="407" spans="1:15">
       <c r="A407" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D407" s="4" t="s">
         <v>1271</v>
-      </c>
-      <c r="B407" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C407" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D407" s="4" t="s">
-        <v>1272</v>
       </c>
       <c r="E407" s="4">
         <v>2556</v>
@@ -27438,28 +27435,28 @@
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M407" s="4"/>
       <c r="N407" s="4" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="O407" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="408" spans="1:15">
       <c r="A408" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D408" s="4" t="s">
         <v>1274</v>
-      </c>
-      <c r="B408" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C408" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D408" s="4" t="s">
-        <v>1275</v>
       </c>
       <c r="E408" s="4">
         <v>2904</v>
@@ -27481,28 +27478,28 @@
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="M408" s="4"/>
       <c r="N408" s="4" t="s">
         <v>34</v>
       </c>
       <c r="O408" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D409" s="4" t="s">
         <v>1276</v>
-      </c>
-      <c r="B409" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C409" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D409" s="4" t="s">
-        <v>1277</v>
       </c>
       <c r="E409" s="4">
         <v>1982</v>
@@ -27524,19 +27521,19 @@
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M409" s="4"/>
       <c r="N409" s="4" t="s">
         <v>42</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B410" s="4" t="s">
         <v>18</v>
@@ -27545,7 +27542,7 @@
         <v>88</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E410" s="4">
         <v>3058</v>
@@ -27567,11 +27564,11 @@
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M410" s="4"/>
       <c r="N410" s="4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O410" s="7" t="s">
         <v>154</v>
@@ -27579,7 +27576,7 @@
     </row>
     <row r="411" spans="1:15">
       <c r="A411" s="4" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B411" s="4" t="s">
         <v>18</v>
@@ -27588,7 +27585,7 @@
         <v>88</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E411" s="4">
         <v>2266</v>
@@ -27610,19 +27607,19 @@
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M411" s="4"/>
       <c r="N411" s="4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O411" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="412" spans="1:15">
       <c r="A412" s="4" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B412" s="4" t="s">
         <v>18</v>
@@ -27631,7 +27628,7 @@
         <v>88</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E412" s="4">
         <v>2430</v>
@@ -27653,11 +27650,11 @@
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M412" s="4"/>
       <c r="N412" s="4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O412" s="7" t="s">
         <v>172</v>
@@ -27665,7 +27662,7 @@
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="4" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B413" s="4" t="s">
         <v>18</v>
@@ -27674,7 +27671,7 @@
         <v>88</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E413" s="4">
         <v>3723</v>
@@ -27696,11 +27693,11 @@
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M413" s="4"/>
       <c r="N413" s="4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O413" s="7" t="s">
         <v>172</v>
@@ -27708,7 +27705,7 @@
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="4" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B414" s="4" t="s">
         <v>18</v>
@@ -27717,7 +27714,7 @@
         <v>88</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E414" s="4">
         <v>3326</v>
@@ -27739,11 +27736,11 @@
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M414" s="4"/>
       <c r="N414" s="4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O414" s="7" t="s">
         <v>317</v>
@@ -27751,16 +27748,16 @@
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D415" s="4" t="s">
         <v>1289</v>
-      </c>
-      <c r="B415" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C415" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D415" s="4" t="s">
-        <v>1290</v>
       </c>
       <c r="E415" s="4">
         <v>1620</v>
@@ -27782,28 +27779,28 @@
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M415" s="4"/>
       <c r="N415" s="4" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="416" spans="1:15">
       <c r="A416" s="4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D416" s="4" t="s">
         <v>1292</v>
-      </c>
-      <c r="B416" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D416" s="4" t="s">
-        <v>1293</v>
       </c>
       <c r="E416" s="4">
         <v>1620</v>
@@ -27825,28 +27822,28 @@
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M416" s="4"/>
       <c r="N416" s="4" t="s">
         <v>693</v>
       </c>
       <c r="O416" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D417" s="4" t="s">
         <v>1294</v>
-      </c>
-      <c r="B417" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C417" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D417" s="4" t="s">
-        <v>1295</v>
       </c>
       <c r="E417" s="4">
         <v>1620</v>
@@ -27868,28 +27865,28 @@
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M417" s="4"/>
       <c r="N417" s="4" t="s">
         <v>898</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="418" spans="1:15">
       <c r="A418" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D418" s="4" t="s">
         <v>1296</v>
-      </c>
-      <c r="B418" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C418" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D418" s="4" t="s">
-        <v>1297</v>
       </c>
       <c r="E418" s="4">
         <v>1620</v>
@@ -27911,28 +27908,28 @@
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="M418" s="4"/>
       <c r="N418" s="4" t="s">
         <v>124</v>
       </c>
       <c r="O418" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D419" s="4" t="s">
         <v>1298</v>
-      </c>
-      <c r="B419" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C419" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D419" s="4" t="s">
-        <v>1299</v>
       </c>
       <c r="E419" s="4">
         <v>1620</v>
@@ -27954,28 +27951,28 @@
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="M419" s="4"/>
       <c r="N419" s="4" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="420" spans="1:15">
       <c r="A420" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D420" s="4" t="s">
         <v>1301</v>
-      </c>
-      <c r="B420" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C420" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D420" s="4" t="s">
-        <v>1302</v>
       </c>
       <c r="E420" s="4">
         <v>1620</v>
@@ -27997,28 +27994,28 @@
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M420" s="4"/>
       <c r="N420" s="4" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="O420" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D421" s="4" t="s">
         <v>1303</v>
-      </c>
-      <c r="B421" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C421" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D421" s="4" t="s">
-        <v>1304</v>
       </c>
       <c r="E421" s="4">
         <v>1810</v>
@@ -28040,28 +28037,28 @@
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M421" s="4"/>
       <c r="N421" s="4" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="422" spans="1:15">
       <c r="A422" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D422" s="4" t="s">
         <v>1305</v>
-      </c>
-      <c r="B422" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C422" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D422" s="4" t="s">
-        <v>1306</v>
       </c>
       <c r="E422" s="4">
         <v>1620</v>
@@ -28083,28 +28080,28 @@
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M422" s="4"/>
       <c r="N422" s="4" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="O422" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D423" s="4" t="s">
         <v>1307</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D423" s="4" t="s">
-        <v>1308</v>
       </c>
       <c r="E423" s="4">
         <v>1620</v>
@@ -28126,28 +28123,28 @@
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M423" s="4"/>
       <c r="N423" s="4" t="s">
         <v>608</v>
       </c>
       <c r="O423" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="424" spans="1:15">
       <c r="A424" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D424" s="4" t="s">
         <v>1309</v>
-      </c>
-      <c r="B424" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D424" s="4" t="s">
-        <v>1310</v>
       </c>
       <c r="E424" s="4">
         <v>1620</v>
@@ -28169,28 +28166,28 @@
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M424" s="4"/>
       <c r="N424" s="4" t="s">
         <v>608</v>
       </c>
       <c r="O424" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="425" spans="1:15">
       <c r="A425" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D425" s="4" t="s">
         <v>1311</v>
-      </c>
-      <c r="B425" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C425" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D425" s="4" t="s">
-        <v>1312</v>
       </c>
       <c r="E425" s="4">
         <v>1640</v>
@@ -28212,28 +28209,28 @@
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M425" s="4"/>
       <c r="N425" s="4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="O425" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="426" spans="1:15">
       <c r="A426" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D426" s="4" t="s">
         <v>1313</v>
-      </c>
-      <c r="B426" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C426" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D426" s="4" t="s">
-        <v>1314</v>
       </c>
       <c r="E426" s="4">
         <v>1640</v>
@@ -28255,28 +28252,28 @@
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M426" s="4"/>
       <c r="N426" s="4" t="s">
         <v>604</v>
       </c>
       <c r="O426" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D427" s="4" t="s">
         <v>1315</v>
-      </c>
-      <c r="B427" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C427" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D427" s="4" t="s">
-        <v>1316</v>
       </c>
       <c r="E427" s="4">
         <v>1510</v>
@@ -28298,28 +28295,28 @@
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M427" s="4"/>
       <c r="N427" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="428" spans="1:15">
       <c r="A428" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D428" s="4" t="s">
         <v>1318</v>
-      </c>
-      <c r="B428" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D428" s="4" t="s">
-        <v>1319</v>
       </c>
       <c r="E428" s="4">
         <v>1640</v>
@@ -28341,28 +28338,28 @@
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M428" s="4"/>
       <c r="N428" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O428" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D429" s="4" t="s">
         <v>1320</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D429" s="4" t="s">
-        <v>1321</v>
       </c>
       <c r="E429" s="4">
         <v>1810</v>
@@ -28384,28 +28381,28 @@
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M429" s="4"/>
       <c r="N429" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="430" spans="1:15">
       <c r="A430" s="4" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D430" s="4" t="s">
         <v>1322</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D430" s="4" t="s">
-        <v>1323</v>
       </c>
       <c r="E430" s="4">
         <v>1620</v>
@@ -28427,28 +28424,28 @@
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M430" s="4"/>
       <c r="N430" s="4" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D431" s="4" t="s">
         <v>1325</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D431" s="4" t="s">
-        <v>1326</v>
       </c>
       <c r="E431" s="4">
         <v>1640</v>
@@ -28470,28 +28467,28 @@
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M431" s="4"/>
       <c r="N431" s="4" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="432" spans="1:15">
       <c r="A432" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D432" s="4" t="s">
         <v>1327</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D432" s="4" t="s">
-        <v>1328</v>
       </c>
       <c r="E432" s="4">
         <v>1620</v>
@@ -28513,28 +28510,28 @@
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M432" s="4"/>
       <c r="N432" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O432" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="433" spans="1:15">
       <c r="A433" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D433" s="4" t="s">
         <v>1329</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D433" s="4" t="s">
-        <v>1330</v>
       </c>
       <c r="E433" s="4">
         <v>1640</v>
@@ -28560,24 +28557,24 @@
       </c>
       <c r="M433" s="4"/>
       <c r="N433" s="4" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="O433" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D434" s="4" t="s">
         <v>1332</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D434" s="4" t="s">
-        <v>1333</v>
       </c>
       <c r="E434" s="4">
         <v>1640</v>
@@ -28603,24 +28600,24 @@
       </c>
       <c r="M434" s="4"/>
       <c r="N434" s="4" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="O434" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D435" s="4" t="s">
         <v>1335</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D435" s="4" t="s">
-        <v>1336</v>
       </c>
       <c r="E435" s="4">
         <v>1620</v>
@@ -28646,24 +28643,24 @@
       </c>
       <c r="M435" s="4"/>
       <c r="N435" s="4" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="O435" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="436" spans="1:15">
       <c r="A436" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D436" s="4" t="s">
         <v>1337</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D436" s="4" t="s">
-        <v>1338</v>
       </c>
       <c r="E436" s="4">
         <v>1620</v>
@@ -28689,24 +28686,24 @@
       </c>
       <c r="M436" s="4"/>
       <c r="N436" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O436" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D437" s="4" t="s">
         <v>1339</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D437" s="4" t="s">
-        <v>1340</v>
       </c>
       <c r="E437" s="4">
         <v>1620</v>
@@ -28728,28 +28725,28 @@
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M437" s="4"/>
       <c r="N437" s="4" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O437" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="438" spans="1:15">
       <c r="A438" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D438" s="4" t="s">
         <v>1341</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D438" s="4" t="s">
-        <v>1342</v>
       </c>
       <c r="E438" s="4">
         <v>1640</v>
@@ -28771,28 +28768,28 @@
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M438" s="4"/>
       <c r="N438" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O438" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="439" ht="14.25" spans="1:15">
       <c r="A439" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D439" s="4" t="s">
         <v>1343</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C439" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D439" s="4" t="s">
-        <v>1344</v>
       </c>
       <c r="E439" s="4">
         <v>1620</v>
@@ -28814,28 +28811,28 @@
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M439" s="4"/>
       <c r="N439" s="4" t="s">
         <v>887</v>
       </c>
       <c r="O439" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="440" ht="14.25" spans="1:15">
       <c r="A440" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D440" s="4" t="s">
         <v>1345</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C440" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D440" s="4" t="s">
-        <v>1346</v>
       </c>
       <c r="E440" s="4">
         <v>1640</v>
@@ -28864,21 +28861,21 @@
         <v>257</v>
       </c>
       <c r="O440" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="441" spans="1:15">
       <c r="A441" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D441" s="4" t="s">
         <v>1347</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C441" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D441" s="4" t="s">
-        <v>1348</v>
       </c>
       <c r="E441" s="4">
         <v>780</v>
@@ -28900,19 +28897,19 @@
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="9" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="M441" s="4"/>
       <c r="N441" s="4" t="s">
         <v>100</v>
       </c>
       <c r="O441" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="442" ht="18" spans="1:17">
       <c r="A442" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B442" t="s">
         <v>38</v>
@@ -28921,7 +28918,7 @@
         <v>88</v>
       </c>
       <c r="D442" s="27" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E442" s="4">
         <v>1620</v>
@@ -28942,24 +28939,24 @@
         <v>2035</v>
       </c>
       <c r="L442" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N442" s="25" t="s">
         <v>334</v>
       </c>
       <c r="O442" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="P442" s="28" t="s">
         <v>1352</v>
       </c>
-      <c r="P442" s="28" t="s">
+      <c r="Q442" s="4" t="s">
         <v>1353</v>
-      </c>
-      <c r="Q442" s="4" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="443" ht="18" spans="1:17">
       <c r="A443" s="4" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B443" t="s">
         <v>38</v>
@@ -28968,7 +28965,7 @@
         <v>88</v>
       </c>
       <c r="D443" s="27" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="E443" s="4">
         <v>1620</v>
@@ -28989,24 +28986,24 @@
         <v>2035</v>
       </c>
       <c r="L443" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N443" s="26" t="s">
         <v>975</v>
       </c>
       <c r="O443" s="4" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="P443" s="28" t="s">
+        <v>1356</v>
+      </c>
+      <c r="Q443" s="4" t="s">
         <v>1357</v>
-      </c>
-      <c r="Q443" s="4" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="444" ht="17.25" spans="1:17">
       <c r="A444" s="4" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B444" t="s">
         <v>38</v>
@@ -29015,7 +29012,7 @@
         <v>88</v>
       </c>
       <c r="D444" s="27" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E444" s="4">
         <v>1620</v>
@@ -29036,24 +29033,24 @@
         <v>2035</v>
       </c>
       <c r="L444" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N444" s="28" t="s">
         <v>133</v>
       </c>
       <c r="O444" s="29" t="s">
+        <v>1360</v>
+      </c>
+      <c r="P444" s="28" t="s">
         <v>1361</v>
       </c>
-      <c r="P444" s="28" t="s">
+      <c r="Q444" s="4" t="s">
         <v>1362</v>
-      </c>
-      <c r="Q444" s="4" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="445" ht="17.25" spans="1:17">
       <c r="A445" s="4" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B445" t="s">
         <v>38</v>
@@ -29062,7 +29059,7 @@
         <v>88</v>
       </c>
       <c r="D445" s="27" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E445" s="4">
         <v>1620</v>
@@ -29083,24 +29080,24 @@
         <v>2035</v>
       </c>
       <c r="L445" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N445" s="28" t="s">
         <v>70</v>
       </c>
       <c r="O445" s="4" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="P445" s="28" t="s">
         <v>72</v>
       </c>
       <c r="Q445" s="4" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="446" ht="17.25" spans="1:17">
       <c r="A446" s="4" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B446" t="s">
         <v>38</v>
@@ -29109,7 +29106,7 @@
         <v>88</v>
       </c>
       <c r="D446" s="27" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E446" s="4">
         <v>0</v>
@@ -29130,24 +29127,24 @@
         <v>2035</v>
       </c>
       <c r="L446" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N446" s="28" t="s">
         <v>327</v>
       </c>
       <c r="O446" s="30" t="s">
+        <v>1369</v>
+      </c>
+      <c r="P446" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="P446" s="28" t="s">
+      <c r="Q446" s="4" t="s">
         <v>1371</v>
-      </c>
-      <c r="Q446" s="4" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="447" ht="17.25" spans="1:17">
       <c r="A447" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B447" t="s">
         <v>38</v>
@@ -29156,7 +29153,7 @@
         <v>88</v>
       </c>
       <c r="D447" s="27" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E447" s="4">
         <v>1620</v>
@@ -29177,24 +29174,24 @@
         <v>2035</v>
       </c>
       <c r="L447" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N447" s="28" t="s">
         <v>138</v>
       </c>
       <c r="O447" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="P447" s="28" t="s">
+        <v>1374</v>
+      </c>
+      <c r="Q447" s="4" t="s">
         <v>1375</v>
-      </c>
-      <c r="Q447" s="4" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="448" ht="17.25" spans="1:17">
       <c r="A448" s="4" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B448" t="s">
         <v>38</v>
@@ -29203,7 +29200,7 @@
         <v>19</v>
       </c>
       <c r="D448" s="27" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="E448" s="4">
         <v>780</v>
@@ -29227,7 +29224,7 @@
         <v>500</v>
       </c>
       <c r="L448" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N448" s="28" t="s">
         <v>90</v>
@@ -29239,12 +29236,12 @@
         <v>462</v>
       </c>
       <c r="Q448" s="4" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="449" ht="18" spans="1:17">
       <c r="A449" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B449" t="s">
         <v>38</v>
@@ -29253,7 +29250,7 @@
         <v>19</v>
       </c>
       <c r="D449" s="27" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E449" s="4">
         <v>780</v>
@@ -29277,7 +29274,7 @@
         <v>500</v>
       </c>
       <c r="L449" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N449" s="28" t="s">
         <v>491</v>
@@ -29289,12 +29286,12 @@
         <v>492</v>
       </c>
       <c r="Q449" s="4" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="450" ht="18" spans="1:17">
       <c r="A450" s="4" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B450" t="s">
         <v>38</v>
@@ -29303,7 +29300,7 @@
         <v>19</v>
       </c>
       <c r="D450" s="27" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E450" s="4">
         <v>780</v>
@@ -29327,7 +29324,7 @@
         <v>500</v>
       </c>
       <c r="L450" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N450" s="26" t="s">
         <v>975</v>
@@ -29336,15 +29333,15 @@
         <v>278</v>
       </c>
       <c r="P450" s="28" t="s">
+        <v>1384</v>
+      </c>
+      <c r="Q450" s="4" t="s">
         <v>1385</v>
-      </c>
-      <c r="Q450" s="4" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="451" ht="17.25" spans="1:17">
       <c r="A451" s="4" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B451" t="s">
         <v>38</v>
@@ -29353,7 +29350,7 @@
         <v>19</v>
       </c>
       <c r="D451" s="27" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E451" s="4">
         <v>1260</v>
@@ -29377,24 +29374,24 @@
         <v>650</v>
       </c>
       <c r="L451" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N451" s="28" t="s">
         <v>83</v>
       </c>
       <c r="O451" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P451" s="28" t="s">
         <v>86</v>
       </c>
       <c r="Q451" s="4" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="452" ht="17.25" spans="1:17">
       <c r="A452" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B452" t="s">
         <v>38</v>
@@ -29403,7 +29400,7 @@
         <v>19</v>
       </c>
       <c r="D452" s="27" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="E452" s="4">
         <v>1260</v>
@@ -29427,7 +29424,7 @@
         <v>650</v>
       </c>
       <c r="L452" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N452" s="28" t="s">
         <v>491</v>
@@ -29436,15 +29433,15 @@
         <v>160</v>
       </c>
       <c r="P452" s="28" t="s">
+        <v>1391</v>
+      </c>
+      <c r="Q452" s="4" t="s">
         <v>1392</v>
-      </c>
-      <c r="Q452" s="4" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="453" ht="17.25" spans="1:17">
       <c r="A453" s="4" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B453" t="s">
         <v>38</v>
@@ -29453,7 +29450,7 @@
         <v>19</v>
       </c>
       <c r="D453" s="27" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="E453" s="4">
         <v>1510</v>
@@ -29477,24 +29474,24 @@
         <v>1040</v>
       </c>
       <c r="L453" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="N453" s="25" t="s">
         <v>161</v>
       </c>
       <c r="O453" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="P453" s="28" t="s">
+        <v>1395</v>
+      </c>
+      <c r="Q453" s="4" t="s">
         <v>1396</v>
-      </c>
-      <c r="Q453" s="4" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="454" ht="17.25" spans="1:17">
       <c r="A454" s="4" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B454" t="s">
         <v>38</v>
@@ -29524,7 +29521,7 @@
         <v>2035</v>
       </c>
       <c r="L454" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N454" s="28" t="s">
         <v>90</v>
@@ -29533,15 +29530,15 @@
         <v>278</v>
       </c>
       <c r="P454" s="28" t="s">
+        <v>1398</v>
+      </c>
+      <c r="Q454" s="4" t="s">
         <v>1399</v>
-      </c>
-      <c r="Q454" s="4" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="455" ht="17.25" spans="1:17">
       <c r="A455" s="4" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B455" t="s">
         <v>38</v>
@@ -29550,7 +29547,7 @@
         <v>19</v>
       </c>
       <c r="D455" s="27" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E455" s="4">
         <v>1260</v>
@@ -29574,7 +29571,7 @@
         <v>650</v>
       </c>
       <c r="L455" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N455" s="25" t="s">
         <v>172</v>
@@ -29583,15 +29580,15 @@
         <v>465</v>
       </c>
       <c r="P455" s="28" t="s">
+        <v>1402</v>
+      </c>
+      <c r="Q455" s="4" t="s">
         <v>1403</v>
-      </c>
-      <c r="Q455" s="4" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="456" ht="18" spans="1:17">
       <c r="A456" s="4" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B456" t="s">
         <v>38</v>
@@ -29624,7 +29621,7 @@
         <v>550</v>
       </c>
       <c r="L456" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N456" s="25" t="s">
         <v>236</v>
@@ -29633,15 +29630,15 @@
         <v>465</v>
       </c>
       <c r="P456" s="28" t="s">
+        <v>1405</v>
+      </c>
+      <c r="Q456" s="4" t="s">
         <v>1406</v>
-      </c>
-      <c r="Q456" s="4" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="457" ht="18" spans="1:17">
       <c r="A457" s="4" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B457" t="s">
         <v>38</v>
@@ -29650,7 +29647,7 @@
         <v>19</v>
       </c>
       <c r="D457" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E457" s="4">
         <v>780</v>
@@ -29674,7 +29671,7 @@
         <v>500</v>
       </c>
       <c r="L457" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N457" s="26" t="s">
         <v>975</v>
@@ -29683,15 +29680,15 @@
         <v>830</v>
       </c>
       <c r="P457" s="28" t="s">
+        <v>1409</v>
+      </c>
+      <c r="Q457" s="4" t="s">
         <v>1410</v>
-      </c>
-      <c r="Q457" s="4" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="458" ht="17.25" spans="1:17">
       <c r="A458" s="4" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B458" t="s">
         <v>38</v>
@@ -29700,7 +29697,7 @@
         <v>88</v>
       </c>
       <c r="D458" s="27" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E458" s="4">
         <v>0</v>
@@ -29721,24 +29718,24 @@
         <v>2035</v>
       </c>
       <c r="L458" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N458" s="28" t="s">
         <v>252</v>
       </c>
       <c r="O458" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P458" s="28" t="s">
+        <v>1413</v>
+      </c>
+      <c r="Q458" s="4" t="s">
         <v>1414</v>
-      </c>
-      <c r="Q458" s="4" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="459" ht="17.25" spans="1:17">
       <c r="A459" s="4" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B459" t="s">
         <v>38</v>
@@ -29747,7 +29744,7 @@
         <v>19</v>
       </c>
       <c r="D459" s="27" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E459" s="4">
         <v>1170</v>
@@ -29771,24 +29768,24 @@
         <v>650</v>
       </c>
       <c r="L459" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="N459" s="28" t="s">
         <v>90</v>
       </c>
       <c r="O459" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="P459" s="28" t="s">
         <v>841</v>
       </c>
       <c r="Q459" s="4" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="460" ht="17.25" spans="1:17">
       <c r="A460" s="4" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B460" t="s">
         <v>38</v>
@@ -29797,7 +29794,7 @@
         <v>19</v>
       </c>
       <c r="D460" s="27" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E460" s="4">
         <v>1260</v>
@@ -29821,7 +29818,7 @@
         <v>650</v>
       </c>
       <c r="L460" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N460" s="28" t="s">
         <v>42</v>
@@ -29830,15 +29827,15 @@
         <v>278</v>
       </c>
       <c r="P460" s="28" t="s">
+        <v>1421</v>
+      </c>
+      <c r="Q460" s="4" t="s">
         <v>1422</v>
-      </c>
-      <c r="Q460" s="4" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="461" ht="17.25" spans="1:17">
       <c r="A461" s="4" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B461" t="s">
         <v>38</v>
@@ -29847,7 +29844,7 @@
         <v>19</v>
       </c>
       <c r="D461" s="27" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E461" s="4">
         <v>1260</v>
@@ -29871,24 +29868,24 @@
         <v>650</v>
       </c>
       <c r="L461" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N461" s="28" t="s">
         <v>343</v>
       </c>
       <c r="O461" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P461" s="28" t="s">
         <v>436</v>
       </c>
       <c r="Q461" s="4" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="462" ht="17.25" spans="1:17">
       <c r="A462" s="4" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B462" t="s">
         <v>38</v>
@@ -29897,7 +29894,7 @@
         <v>19</v>
       </c>
       <c r="D462" s="27" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E462" s="4">
         <v>1170</v>
@@ -29921,7 +29918,7 @@
         <v>650</v>
       </c>
       <c r="L462" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N462" s="28" t="s">
         <v>229</v>
@@ -29930,15 +29927,15 @@
         <v>291</v>
       </c>
       <c r="P462" s="28" t="s">
+        <v>1428</v>
+      </c>
+      <c r="Q462" s="4" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q462" s="4" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="463" ht="17.25" spans="1:17">
       <c r="A463" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B463" t="s">
         <v>38</v>
@@ -29947,7 +29944,7 @@
         <v>19</v>
       </c>
       <c r="D463" s="27" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E463" s="4">
         <v>1170</v>
@@ -29971,7 +29968,7 @@
         <v>650</v>
       </c>
       <c r="L463" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N463" s="28" t="s">
         <v>48</v>
@@ -29980,15 +29977,15 @@
         <v>830</v>
       </c>
       <c r="P463" s="28" t="s">
+        <v>1432</v>
+      </c>
+      <c r="Q463" s="4" t="s">
         <v>1433</v>
-      </c>
-      <c r="Q463" s="4" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="464" ht="17.25" spans="1:17">
       <c r="A464" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B464" t="s">
         <v>38</v>
@@ -29997,7 +29994,7 @@
         <v>19</v>
       </c>
       <c r="D464" s="27" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E464" s="4">
         <v>1010</v>
@@ -30021,7 +30018,7 @@
         <v>550</v>
       </c>
       <c r="L464" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N464" s="28" t="s">
         <v>24</v>
@@ -30030,15 +30027,15 @@
         <v>830</v>
       </c>
       <c r="P464" s="28" t="s">
+        <v>1436</v>
+      </c>
+      <c r="Q464" s="4" t="s">
         <v>1437</v>
-      </c>
-      <c r="Q464" s="4" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="465" ht="17.25" spans="1:17">
       <c r="A465" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B465" t="s">
         <v>38</v>
@@ -30047,7 +30044,7 @@
         <v>19</v>
       </c>
       <c r="D465" s="27" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E465" s="4">
         <v>1170</v>
@@ -30071,7 +30068,7 @@
         <v>650</v>
       </c>
       <c r="L465" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N465" s="28" t="s">
         <v>100</v>
@@ -30083,12 +30080,12 @@
         <v>328</v>
       </c>
       <c r="Q465" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="466" ht="17.25" spans="1:17">
       <c r="A466" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B466" t="s">
         <v>38</v>
@@ -30097,7 +30094,7 @@
         <v>19</v>
       </c>
       <c r="D466" s="27" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E466" s="4">
         <v>1170</v>
@@ -30121,24 +30118,24 @@
         <v>650</v>
       </c>
       <c r="L466" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N466" s="28" t="s">
         <v>83</v>
       </c>
       <c r="O466" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="P466" s="28" t="s">
         <v>1444</v>
       </c>
-      <c r="P466" s="28" t="s">
+      <c r="Q466" s="4" t="s">
         <v>1445</v>
-      </c>
-      <c r="Q466" s="4" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="467" ht="17.25" spans="1:17">
       <c r="A467" s="4" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B467" t="s">
         <v>38</v>
@@ -30147,7 +30144,7 @@
         <v>19</v>
       </c>
       <c r="D467" s="27" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E467" s="4">
         <v>1260</v>
@@ -30171,7 +30168,7 @@
         <v>650</v>
       </c>
       <c r="L467" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M467" t="s">
         <v>40</v>
@@ -30180,18 +30177,18 @@
         <v>24</v>
       </c>
       <c r="O467" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="P467" s="28" t="s">
+        <v>1448</v>
+      </c>
+      <c r="Q467" s="4" t="s">
         <v>1449</v>
-      </c>
-      <c r="Q467" s="4" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="468" ht="17.25" spans="1:17">
       <c r="A468" s="4" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B468" t="s">
         <v>38</v>
@@ -30200,7 +30197,7 @@
         <v>19</v>
       </c>
       <c r="D468" s="27" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E468" s="4">
         <v>1260</v>
@@ -30224,24 +30221,24 @@
         <v>650</v>
       </c>
       <c r="L468" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N468" s="28" t="s">
         <v>24</v>
       </c>
       <c r="O468" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="P468" s="28" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q468" s="4" t="s">
         <v>1453</v>
-      </c>
-      <c r="Q468" s="4" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="469" ht="17.25" spans="1:17">
       <c r="A469" s="4" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B469" t="s">
         <v>38</v>
@@ -30250,7 +30247,7 @@
         <v>19</v>
       </c>
       <c r="D469" s="27" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E469" s="4">
         <v>1260</v>
@@ -30274,24 +30271,24 @@
         <v>650</v>
       </c>
       <c r="L469" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N469" s="28" t="s">
         <v>167</v>
       </c>
       <c r="O469" s="4" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="P469" s="28" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Q469" s="4" t="s">
         <v>1457</v>
-      </c>
-      <c r="Q469" s="4" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="470" ht="17.25" spans="1:17">
       <c r="A470" s="4" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B470" t="s">
         <v>38</v>
@@ -30300,7 +30297,7 @@
         <v>19</v>
       </c>
       <c r="D470" s="27" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E470" s="4">
         <v>1260</v>
@@ -30324,24 +30321,24 @@
         <v>650</v>
       </c>
       <c r="L470" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N470" s="28" t="s">
         <v>105</v>
       </c>
       <c r="O470" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="P470" s="28" t="s">
         <v>1461</v>
       </c>
-      <c r="P470" s="28" t="s">
+      <c r="Q470" s="4" t="s">
         <v>1462</v>
-      </c>
-      <c r="Q470" s="4" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="471" ht="17.25" spans="1:17">
       <c r="A471" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B471" t="s">
         <v>38</v>
@@ -30350,7 +30347,7 @@
         <v>19</v>
       </c>
       <c r="D471" s="27" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="E471" s="4">
         <v>1170</v>
@@ -30374,24 +30371,24 @@
         <v>650</v>
       </c>
       <c r="L471" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N471" s="28" t="s">
         <v>53</v>
       </c>
       <c r="O471" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P471" s="28" t="s">
+        <v>1465</v>
+      </c>
+      <c r="Q471" s="4" t="s">
         <v>1466</v>
-      </c>
-      <c r="Q471" s="4" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="472" ht="17.25" spans="1:17">
       <c r="A472" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B472" t="s">
         <v>38</v>
@@ -30400,7 +30397,7 @@
         <v>19</v>
       </c>
       <c r="D472" s="27" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E472" s="4">
         <v>1260</v>
@@ -30424,7 +30421,7 @@
         <v>650</v>
       </c>
       <c r="L472" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M472" t="s">
         <v>40</v>
@@ -30444,7 +30441,7 @@
     </row>
     <row r="473" ht="17.25" spans="1:17">
       <c r="A473" s="4" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B473" t="s">
         <v>38</v>
@@ -30453,7 +30450,7 @@
         <v>19</v>
       </c>
       <c r="D473" s="27" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="E473" s="4">
         <v>1170</v>
@@ -30477,24 +30474,24 @@
         <v>650</v>
       </c>
       <c r="L473" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N473" s="28" t="s">
         <v>60</v>
       </c>
       <c r="O473" s="4" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="P473" s="28" t="s">
+        <v>1471</v>
+      </c>
+      <c r="Q473" s="4" t="s">
         <v>1472</v>
-      </c>
-      <c r="Q473" s="4" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="474" ht="17.25" spans="1:17">
       <c r="A474" s="4" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B474" t="s">
         <v>38</v>
@@ -30503,7 +30500,7 @@
         <v>19</v>
       </c>
       <c r="D474" s="27" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="E474" s="4">
         <v>1170</v>
@@ -30527,24 +30524,24 @@
         <v>650</v>
       </c>
       <c r="L474" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N474" s="28" t="s">
         <v>77</v>
       </c>
       <c r="O474" s="4" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="P474" s="28" t="s">
         <v>79</v>
       </c>
       <c r="Q474" s="4" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="475" ht="17.25" spans="1:17">
       <c r="A475" s="4" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B475" t="s">
         <v>38</v>
@@ -30553,7 +30550,7 @@
         <v>19</v>
       </c>
       <c r="D475" s="27" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="E475" s="4">
         <v>1170</v>
@@ -30577,24 +30574,24 @@
         <v>650</v>
       </c>
       <c r="L475" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N475" s="28" t="s">
         <v>333</v>
       </c>
       <c r="O475" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="P475" s="28" t="s">
         <v>364</v>
       </c>
       <c r="Q475" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="476" ht="17.25" spans="1:17">
       <c r="A476" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B476" t="s">
         <v>38</v>
@@ -30603,7 +30600,7 @@
         <v>19</v>
       </c>
       <c r="D476" s="27" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E476" s="4">
         <v>1010</v>
@@ -30627,7 +30624,7 @@
         <v>550</v>
       </c>
       <c r="L476" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N476" s="28" t="s">
         <v>100</v>
@@ -30644,7 +30641,7 @@
     </row>
     <row r="477" ht="17.25" spans="1:17">
       <c r="A477" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B477" t="s">
         <v>38</v>
@@ -30653,7 +30650,7 @@
         <v>19</v>
       </c>
       <c r="D477" s="27" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="E477" s="4">
         <v>1630</v>
@@ -30677,24 +30674,24 @@
         <v>650</v>
       </c>
       <c r="L477" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N477" s="28" t="s">
         <v>257</v>
       </c>
       <c r="O477" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="P477" s="28" t="s">
+        <v>1483</v>
+      </c>
+      <c r="Q477" s="4" t="s">
         <v>1484</v>
-      </c>
-      <c r="Q477" s="4" t="s">
-        <v>1485</v>
       </c>
     </row>
     <row r="478" ht="17.25" spans="1:17">
       <c r="A478" s="4" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B478" t="s">
         <v>38</v>
@@ -30703,7 +30700,7 @@
         <v>19</v>
       </c>
       <c r="D478" s="27" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E478" s="4">
         <v>1260</v>
@@ -30727,24 +30724,24 @@
         <v>650</v>
       </c>
       <c r="L478" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N478" s="28" t="s">
         <v>252</v>
       </c>
       <c r="O478" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="P478" s="28" t="s">
         <v>1488</v>
       </c>
-      <c r="P478" s="28" t="s">
+      <c r="Q478" s="4" t="s">
         <v>1489</v>
-      </c>
-      <c r="Q478" s="4" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="479" ht="17.25" spans="1:17">
       <c r="A479" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B479" t="s">
         <v>38</v>
@@ -30753,7 +30750,7 @@
         <v>19</v>
       </c>
       <c r="D479" s="27" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E479" s="4">
         <v>1260</v>
@@ -30777,7 +30774,7 @@
         <v>650</v>
       </c>
       <c r="L479" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M479" t="s">
         <v>40</v>
@@ -30786,18 +30783,18 @@
         <v>128</v>
       </c>
       <c r="O479" s="4" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="P479" s="28" t="s">
+        <v>1492</v>
+      </c>
+      <c r="Q479" s="4" t="s">
         <v>1493</v>
-      </c>
-      <c r="Q479" s="4" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="480" ht="17.25" spans="1:17">
       <c r="A480" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B480" t="s">
         <v>38</v>
@@ -30806,7 +30803,7 @@
         <v>19</v>
       </c>
       <c r="D480" s="27" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E480" s="4">
         <v>1010</v>
@@ -30830,24 +30827,24 @@
         <v>550</v>
       </c>
       <c r="L480" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="N480" s="28" t="s">
         <v>645</v>
       </c>
       <c r="O480" s="4" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P480" s="28" t="s">
         <v>646</v>
       </c>
       <c r="Q480" s="4" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="481" ht="17.25" spans="1:17">
       <c r="A481" s="4" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B481" t="s">
         <v>38</v>
@@ -30856,7 +30853,7 @@
         <v>19</v>
       </c>
       <c r="D481" s="27" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E481" s="4">
         <v>1510</v>
@@ -30886,18 +30883,18 @@
         <v>252</v>
       </c>
       <c r="O481" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="P481" s="28" t="s">
         <v>252</v>
       </c>
       <c r="Q481" s="4" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="482" ht="17.25" spans="1:17">
       <c r="A482" s="4" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B482" t="s">
         <v>38</v>
@@ -30906,7 +30903,7 @@
         <v>88</v>
       </c>
       <c r="D482" s="27" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E482" s="4">
         <v>0</v>
@@ -30933,18 +30930,18 @@
         <v>252</v>
       </c>
       <c r="O482" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P482" s="28" t="s">
+        <v>1503</v>
+      </c>
+      <c r="Q482" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="Q482" s="4" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="483" ht="17.25" spans="1:17">
       <c r="A483" s="4" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B483" t="s">
         <v>38</v>
@@ -30953,7 +30950,7 @@
         <v>88</v>
       </c>
       <c r="D483" s="27" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="E483" s="4">
         <v>0</v>
@@ -30980,18 +30977,18 @@
         <v>252</v>
       </c>
       <c r="O483" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P483" s="28" t="s">
+        <v>1503</v>
+      </c>
+      <c r="Q483" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="Q483" s="4" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="484" ht="17.25" spans="1:17">
       <c r="A484" s="4" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B484" t="s">
         <v>38</v>
@@ -31000,7 +30997,7 @@
         <v>88</v>
       </c>
       <c r="D484" s="27" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E484" s="4">
         <v>0</v>
@@ -31027,27 +31024,27 @@
         <v>252</v>
       </c>
       <c r="O484" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="P484" s="28" t="s">
+        <v>1503</v>
+      </c>
+      <c r="Q484" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="Q484" s="4" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="485" ht="17.25" spans="1:17">
       <c r="A485" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D485" s="27" t="s">
         <v>1510</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D485" s="27" t="s">
-        <v>1511</v>
       </c>
       <c r="E485" s="4">
         <v>0</v>
@@ -31068,13 +31065,13 @@
         <v>2035</v>
       </c>
       <c r="L485" s="9" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="N485" s="25" t="s">
         <v>202</v>
       </c>
       <c r="O485" s="25" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9840"/>
+    <workbookView windowWidth="23325" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$504</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4701" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4874" uniqueCount="1571">
   <si>
     <t>单号</t>
   </si>
@@ -4550,6 +4550,186 @@
   </si>
   <si>
     <t>冯小华</t>
+  </si>
+  <si>
+    <t>[2021]第316号</t>
+  </si>
+  <si>
+    <t>王先平</t>
+  </si>
+  <si>
+    <t>2021年医学定向毕业生</t>
+  </si>
+  <si>
+    <t>左安中心卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第317号</t>
+  </si>
+  <si>
+    <t>康炜</t>
+  </si>
+  <si>
+    <t>高坪卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第318号</t>
+  </si>
+  <si>
+    <t>肖清华</t>
+  </si>
+  <si>
+    <t>大汾中心卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第319号</t>
+  </si>
+  <si>
+    <t>郭威</t>
+  </si>
+  <si>
+    <t>南江卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第320号</t>
+  </si>
+  <si>
+    <t>康若茜</t>
+  </si>
+  <si>
+    <t>衙前中心卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第321号</t>
+  </si>
+  <si>
+    <t>肖林</t>
+  </si>
+  <si>
+    <t>堆子前中心卫生院（差额事业）</t>
+  </si>
+  <si>
+    <t>[2021]第322号</t>
+  </si>
+  <si>
+    <t>郭涌</t>
+  </si>
+  <si>
+    <t>县交通运输局事业干部</t>
+  </si>
+  <si>
+    <t>[2021]第323号</t>
+  </si>
+  <si>
+    <t>林晓琴</t>
+  </si>
+  <si>
+    <t>[2021]第324号</t>
+  </si>
+  <si>
+    <t>[2021]第325号</t>
+  </si>
+  <si>
+    <t>林春燕</t>
+  </si>
+  <si>
+    <t>调出单位：泉江镇党委委员、纪委书记、监察办主任</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇党委副书记、政法委员</t>
+  </si>
+  <si>
+    <t>[2021]第326号</t>
+  </si>
+  <si>
+    <t>朱显河</t>
+  </si>
+  <si>
+    <t>调出单位：枚江镇党委副书记、政法委员</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇人大主席</t>
+  </si>
+  <si>
+    <t>[2021]第327号</t>
+  </si>
+  <si>
+    <t>陈大洋</t>
+  </si>
+  <si>
+    <t>调出单位：五斗江乡党委委员、副乡长</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇党委委员、纪委书记、监察办主任</t>
+  </si>
+  <si>
+    <t>[2021]第328号</t>
+  </si>
+  <si>
+    <t>张小安</t>
+  </si>
+  <si>
+    <t>调出单位：高坪镇政府</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇政府</t>
+  </si>
+  <si>
+    <t>[2021]第329号</t>
+  </si>
+  <si>
+    <t>彭伟</t>
+  </si>
+  <si>
+    <t>调出单位：双桥乡人大副主席</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇政府副镇长</t>
+  </si>
+  <si>
+    <t>[2021]第330号</t>
+  </si>
+  <si>
+    <t>调出单位：左安镇人大副主席</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇党委委员、组织员</t>
+  </si>
+  <si>
+    <t>[2021]第331号</t>
+  </si>
+  <si>
+    <t>冯德明</t>
+  </si>
+  <si>
+    <t>调出单位：雩田镇党委副书记、镇长</t>
+  </si>
+  <si>
+    <t>调入单位：堆子前镇党委书记</t>
+  </si>
+  <si>
+    <t>[2021]第332号</t>
+  </si>
+  <si>
+    <t>古小亮</t>
+  </si>
+  <si>
+    <t>县乡村振兴局</t>
+  </si>
+  <si>
+    <t>县发改委</t>
+  </si>
+  <si>
+    <t>[2021]第333号</t>
+  </si>
+  <si>
+    <t>肖远云</t>
+  </si>
+  <si>
+    <t>[2021]第334号</t>
+  </si>
+  <si>
+    <t>郭华生</t>
   </si>
 </sst>
 </file>
@@ -4557,11 +4737,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4610,9 +4790,53 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4623,24 +4847,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4654,39 +4863,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4708,21 +4905,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -4730,9 +4918,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4744,15 +4931,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4815,7 +4995,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4827,31 +5055,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4869,19 +5091,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4893,25 +5133,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4923,79 +5175,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5041,18 +5227,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5072,6 +5251,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -5083,32 +5271,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5131,6 +5293,30 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -5144,10 +5330,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5156,137 +5342,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5378,6 +5564,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5699,7 +5894,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T485"/>
+  <dimension ref="A1:T504"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -31076,8 +31271,934 @@
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>
     </row>
+    <row r="486" ht="17.25" spans="1:17">
+      <c r="A486" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B486" t="s">
+        <v>18</v>
+      </c>
+      <c r="C486" t="s">
+        <v>88</v>
+      </c>
+      <c r="D486" s="27" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E486">
+        <v>0</v>
+      </c>
+      <c r="F486">
+        <v>0</v>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486">
+        <v>1780</v>
+      </c>
+      <c r="I486" s="4">
+        <v>0</v>
+      </c>
+      <c r="J486">
+        <v>1895</v>
+      </c>
+      <c r="L486" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N486" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O486" s="32" t="s">
+        <v>1323</v>
+      </c>
+      <c r="P486" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q486" s="32" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="487" ht="17.25" spans="1:17">
+      <c r="A487" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B487" t="s">
+        <v>18</v>
+      </c>
+      <c r="C487" t="s">
+        <v>88</v>
+      </c>
+      <c r="D487" s="27" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E487">
+        <v>0</v>
+      </c>
+      <c r="F487">
+        <v>0</v>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487">
+        <v>1780</v>
+      </c>
+      <c r="I487" s="4">
+        <v>0</v>
+      </c>
+      <c r="J487">
+        <v>1895</v>
+      </c>
+      <c r="L487" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N487" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O487" s="32" t="s">
+        <v>1252</v>
+      </c>
+      <c r="P487" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q487" s="32" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="488" ht="17.25" spans="1:17">
+      <c r="A488" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B488" t="s">
+        <v>18</v>
+      </c>
+      <c r="C488" t="s">
+        <v>88</v>
+      </c>
+      <c r="D488" s="27" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E488">
+        <v>0</v>
+      </c>
+      <c r="F488">
+        <v>0</v>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488">
+        <v>1780</v>
+      </c>
+      <c r="I488" s="4">
+        <v>0</v>
+      </c>
+      <c r="J488">
+        <v>1895</v>
+      </c>
+      <c r="L488" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N488" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O488" s="32" t="s">
+        <v>1316</v>
+      </c>
+      <c r="P488" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q488" s="32" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="489" ht="17.25" spans="1:17">
+      <c r="A489" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B489" t="s">
+        <v>18</v>
+      </c>
+      <c r="C489" t="s">
+        <v>88</v>
+      </c>
+      <c r="D489" s="27" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E489">
+        <v>0</v>
+      </c>
+      <c r="F489">
+        <v>0</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489">
+        <v>1780</v>
+      </c>
+      <c r="I489" s="4">
+        <v>0</v>
+      </c>
+      <c r="J489">
+        <v>1895</v>
+      </c>
+      <c r="L489" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N489" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O489" s="32" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P489" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q489" s="32" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="490" ht="17.25" spans="1:17">
+      <c r="A490" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B490" t="s">
+        <v>18</v>
+      </c>
+      <c r="C490" t="s">
+        <v>88</v>
+      </c>
+      <c r="D490" s="27" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E490">
+        <v>0</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+      <c r="H490">
+        <v>1780</v>
+      </c>
+      <c r="I490" s="4">
+        <v>0</v>
+      </c>
+      <c r="J490">
+        <v>1895</v>
+      </c>
+      <c r="L490" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N490" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O490" s="32" t="s">
+        <v>1272</v>
+      </c>
+      <c r="P490" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q490" s="32" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="491" ht="17.25" spans="1:17">
+      <c r="A491" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B491" t="s">
+        <v>18</v>
+      </c>
+      <c r="C491" t="s">
+        <v>88</v>
+      </c>
+      <c r="D491" s="27" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E491">
+        <v>0</v>
+      </c>
+      <c r="F491">
+        <v>0</v>
+      </c>
+      <c r="G491">
+        <v>0</v>
+      </c>
+      <c r="H491">
+        <v>1780</v>
+      </c>
+      <c r="I491" s="4">
+        <v>0</v>
+      </c>
+      <c r="J491">
+        <v>1895</v>
+      </c>
+      <c r="L491" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N491" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O491" s="32" t="s">
+        <v>1234</v>
+      </c>
+      <c r="P491" s="32" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Q491" s="32" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="492" ht="17.25" spans="1:17">
+      <c r="A492" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B492" t="s">
+        <v>38</v>
+      </c>
+      <c r="C492" t="s">
+        <v>88</v>
+      </c>
+      <c r="D492" s="31" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E492">
+        <v>0</v>
+      </c>
+      <c r="F492">
+        <v>0</v>
+      </c>
+      <c r="G492">
+        <v>0</v>
+      </c>
+      <c r="H492">
+        <v>0</v>
+      </c>
+      <c r="I492" s="4">
+        <v>0</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
+      <c r="L492" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="N492" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="O492" s="33" t="s">
+        <v>998</v>
+      </c>
+      <c r="P492" s="32" t="s">
+        <v>1532</v>
+      </c>
+      <c r="Q492" s="32" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="493" ht="17.25" spans="1:17">
+      <c r="A493" s="4" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B493" t="s">
+        <v>38</v>
+      </c>
+      <c r="C493" t="s">
+        <v>88</v>
+      </c>
+      <c r="D493" s="31" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E493">
+        <v>0</v>
+      </c>
+      <c r="F493">
+        <v>0</v>
+      </c>
+      <c r="G493">
+        <v>0</v>
+      </c>
+      <c r="H493">
+        <v>0</v>
+      </c>
+      <c r="I493" s="4">
+        <v>0</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
+      <c r="L493" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="N493" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="O493" s="33" t="s">
+        <v>998</v>
+      </c>
+      <c r="P493" s="32" t="s">
+        <v>1532</v>
+      </c>
+      <c r="Q493" s="32" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="494" ht="17.25" spans="1:17">
+      <c r="A494" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B494" t="s">
+        <v>38</v>
+      </c>
+      <c r="C494" t="s">
+        <v>88</v>
+      </c>
+      <c r="D494" s="31" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E494">
+        <v>0</v>
+      </c>
+      <c r="F494">
+        <v>0</v>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+      <c r="H494">
+        <v>0</v>
+      </c>
+      <c r="I494" s="4">
+        <v>0</v>
+      </c>
+      <c r="J494">
+        <v>0</v>
+      </c>
+      <c r="L494" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="N494" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="O494" s="33" t="s">
+        <v>998</v>
+      </c>
+      <c r="P494" s="32" t="s">
+        <v>1532</v>
+      </c>
+      <c r="Q494" s="32" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="495" ht="17.25" spans="1:17">
+      <c r="A495" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B495" t="s">
+        <v>38</v>
+      </c>
+      <c r="C495" t="s">
+        <v>19</v>
+      </c>
+      <c r="D495" s="31" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E495">
+        <v>1010</v>
+      </c>
+      <c r="F495">
+        <v>2276</v>
+      </c>
+      <c r="G495">
+        <v>0</v>
+      </c>
+      <c r="H495">
+        <v>0</v>
+      </c>
+      <c r="I495" s="4">
+        <v>0</v>
+      </c>
+      <c r="J495">
+        <v>2245</v>
+      </c>
+      <c r="K495" s="1">
+        <v>650</v>
+      </c>
+      <c r="L495" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N495" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O495" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P495" s="32" t="s">
+        <v>1538</v>
+      </c>
+      <c r="Q495" s="32" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="496" ht="17.25" spans="1:17">
+      <c r="A496" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B496" t="s">
+        <v>38</v>
+      </c>
+      <c r="C496" t="s">
+        <v>19</v>
+      </c>
+      <c r="D496" s="31" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E496">
+        <v>1010</v>
+      </c>
+      <c r="F496">
+        <v>2219</v>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+      <c r="H496">
+        <v>0</v>
+      </c>
+      <c r="I496" s="4">
+        <v>0</v>
+      </c>
+      <c r="J496">
+        <v>2245</v>
+      </c>
+      <c r="K496" s="1">
+        <v>650</v>
+      </c>
+      <c r="L496" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N496" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="O496" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P496" s="32" t="s">
+        <v>1542</v>
+      </c>
+      <c r="Q496" s="32" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="497" ht="17.25" spans="1:17">
+      <c r="A497" s="4" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B497" t="s">
+        <v>38</v>
+      </c>
+      <c r="C497" t="s">
+        <v>19</v>
+      </c>
+      <c r="D497" s="31" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E497">
+        <v>1010</v>
+      </c>
+      <c r="F497">
+        <v>2115</v>
+      </c>
+      <c r="G497">
+        <v>0</v>
+      </c>
+      <c r="H497">
+        <v>0</v>
+      </c>
+      <c r="I497" s="4">
+        <v>0</v>
+      </c>
+      <c r="J497">
+        <v>2115</v>
+      </c>
+      <c r="K497" s="1">
+        <v>550</v>
+      </c>
+      <c r="L497" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N497" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="O497" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P497" s="32" t="s">
+        <v>1546</v>
+      </c>
+      <c r="Q497" s="32" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="498" ht="17.25" spans="1:17">
+      <c r="A498" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B498" t="s">
+        <v>38</v>
+      </c>
+      <c r="C498" t="s">
+        <v>19</v>
+      </c>
+      <c r="D498" s="31" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E498">
+        <v>1010</v>
+      </c>
+      <c r="F498">
+        <v>1544</v>
+      </c>
+      <c r="G498">
+        <v>0</v>
+      </c>
+      <c r="H498">
+        <v>0</v>
+      </c>
+      <c r="I498" s="4">
+        <v>0</v>
+      </c>
+      <c r="J498">
+        <v>2115</v>
+      </c>
+      <c r="K498" s="1">
+        <v>550</v>
+      </c>
+      <c r="L498" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N498" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="O498" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P498" s="32" t="s">
+        <v>1550</v>
+      </c>
+      <c r="Q498" s="32" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="499" ht="17.25" spans="1:17">
+      <c r="A499" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B499" t="s">
+        <v>38</v>
+      </c>
+      <c r="C499" t="s">
+        <v>19</v>
+      </c>
+      <c r="D499" s="31" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E499">
+        <v>1010</v>
+      </c>
+      <c r="F499">
+        <v>1487</v>
+      </c>
+      <c r="G499">
+        <v>0</v>
+      </c>
+      <c r="H499">
+        <v>0</v>
+      </c>
+      <c r="I499" s="4">
+        <v>0</v>
+      </c>
+      <c r="J499">
+        <v>2115</v>
+      </c>
+      <c r="K499" s="1">
+        <v>550</v>
+      </c>
+      <c r="L499" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N499" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="O499" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P499" s="32" t="s">
+        <v>1554</v>
+      </c>
+      <c r="Q499" s="32" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="500" ht="17.25" spans="1:17">
+      <c r="A500" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B500" t="s">
+        <v>38</v>
+      </c>
+      <c r="C500" t="s">
+        <v>19</v>
+      </c>
+      <c r="D500" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="E500">
+        <v>1010</v>
+      </c>
+      <c r="F500">
+        <v>1776</v>
+      </c>
+      <c r="G500">
+        <v>0</v>
+      </c>
+      <c r="H500">
+        <v>0</v>
+      </c>
+      <c r="I500" s="4">
+        <v>0</v>
+      </c>
+      <c r="J500">
+        <v>2115</v>
+      </c>
+      <c r="K500" s="1">
+        <v>550</v>
+      </c>
+      <c r="L500" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N500" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="O500" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P500" s="32" t="s">
+        <v>1557</v>
+      </c>
+      <c r="Q500" s="32" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="501" ht="17.25" spans="1:17">
+      <c r="A501" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B501" t="s">
+        <v>38</v>
+      </c>
+      <c r="C501" t="s">
+        <v>19</v>
+      </c>
+      <c r="D501" s="31" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E501">
+        <v>1260</v>
+      </c>
+      <c r="F501">
+        <v>2276</v>
+      </c>
+      <c r="G501">
+        <v>0</v>
+      </c>
+      <c r="H501">
+        <v>0</v>
+      </c>
+      <c r="I501" s="4">
+        <v>0</v>
+      </c>
+      <c r="J501">
+        <v>2245</v>
+      </c>
+      <c r="L501" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M501" t="s">
+        <v>159</v>
+      </c>
+      <c r="N501" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="O501" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="P501" s="32" t="s">
+        <v>1561</v>
+      </c>
+      <c r="Q501" s="32" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="502" ht="17.25" spans="1:17">
+      <c r="A502" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B502" t="s">
+        <v>38</v>
+      </c>
+      <c r="C502" t="s">
+        <v>19</v>
+      </c>
+      <c r="D502" s="31" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E502">
+        <v>1260</v>
+      </c>
+      <c r="F502">
+        <v>2695</v>
+      </c>
+      <c r="G502">
+        <v>0</v>
+      </c>
+      <c r="H502">
+        <v>0</v>
+      </c>
+      <c r="I502" s="4">
+        <v>0</v>
+      </c>
+      <c r="J502">
+        <v>2245</v>
+      </c>
+      <c r="K502" s="1">
+        <v>650</v>
+      </c>
+      <c r="L502" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="N502" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="O502" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="P502" s="32" t="s">
+        <v>1565</v>
+      </c>
+      <c r="Q502" s="32" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="503" ht="17.25" spans="1:17">
+      <c r="A503" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B503" t="s">
+        <v>38</v>
+      </c>
+      <c r="C503" t="s">
+        <v>19</v>
+      </c>
+      <c r="D503" s="31" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E503">
+        <v>1260</v>
+      </c>
+      <c r="F503">
+        <v>2323</v>
+      </c>
+      <c r="G503">
+        <v>0</v>
+      </c>
+      <c r="H503">
+        <v>0</v>
+      </c>
+      <c r="I503" s="4">
+        <v>0</v>
+      </c>
+      <c r="J503">
+        <v>2245</v>
+      </c>
+      <c r="K503" s="1">
+        <v>650</v>
+      </c>
+      <c r="L503" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="N503" s="32" t="s">
+        <v>975</v>
+      </c>
+      <c r="O503" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="P503" s="32" t="s">
+        <v>1384</v>
+      </c>
+      <c r="Q503" s="32" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="504" ht="17.25" spans="1:17">
+      <c r="A504" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B504" t="s">
+        <v>38</v>
+      </c>
+      <c r="C504" t="s">
+        <v>19</v>
+      </c>
+      <c r="D504" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E504">
+        <v>1260</v>
+      </c>
+      <c r="F504">
+        <v>2571</v>
+      </c>
+      <c r="G504">
+        <v>0</v>
+      </c>
+      <c r="H504">
+        <v>0</v>
+      </c>
+      <c r="I504" s="4">
+        <v>0</v>
+      </c>
+      <c r="J504">
+        <v>2245</v>
+      </c>
+      <c r="K504" s="1">
+        <v>650</v>
+      </c>
+      <c r="L504" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M504" t="s">
+        <v>40</v>
+      </c>
+      <c r="N504" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="O504" s="32" t="s">
+        <v>975</v>
+      </c>
+      <c r="P504" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q504" s="32" t="s">
+        <v>1384</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T485">
+  <autoFilter ref="A1:T504">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4910" uniqueCount="1592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="1595">
   <si>
     <t>单号</t>
   </si>
@@ -4793,6 +4793,15 @@
   </si>
   <si>
     <t>黄坑卫生院（差额拨款）</t>
+  </si>
+  <si>
+    <t>[2021]第339号</t>
+  </si>
+  <si>
+    <t>吕子文</t>
+  </si>
+  <si>
+    <t>赣州市赣县沙地卫生院</t>
   </si>
 </sst>
 </file>
@@ -4801,8 +4810,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
@@ -4851,8 +4860,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4866,30 +4876,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4903,19 +4890,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4935,8 +4927,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4952,28 +4983,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5064,31 +5073,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5100,31 +5085,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5142,7 +5109,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5154,13 +5145,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5172,19 +5199,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5196,13 +5211,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5214,25 +5241,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5244,7 +5253,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5289,45 +5298,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -5355,7 +5325,46 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5393,10 +5402,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5405,133 +5414,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5954,7 +5963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T508"/>
+  <dimension ref="A1:T509"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -32445,6 +32454,53 @@
         <v>1591</v>
       </c>
     </row>
+    <row r="509" ht="17.25" spans="1:17">
+      <c r="A509" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B509" t="s">
+        <v>18</v>
+      </c>
+      <c r="C509" t="s">
+        <v>88</v>
+      </c>
+      <c r="D509" s="31" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E509">
+        <v>0</v>
+      </c>
+      <c r="F509">
+        <v>1620</v>
+      </c>
+      <c r="G509">
+        <v>646</v>
+      </c>
+      <c r="H509">
+        <v>0</v>
+      </c>
+      <c r="I509">
+        <v>0</v>
+      </c>
+      <c r="J509">
+        <v>2035</v>
+      </c>
+      <c r="L509" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="N509" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="O509" s="32" t="s">
+        <v>602</v>
+      </c>
+      <c r="P509" s="32" t="s">
+        <v>1594</v>
+      </c>
+      <c r="Q509" s="32" t="s">
+        <v>602</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T508">
     <extLst/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9840"/>
+    <workbookView windowWidth="23325" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$509</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="1595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="1613">
   <si>
     <t>单号</t>
   </si>
@@ -4802,6 +4802,60 @@
   </si>
   <si>
     <t>赣州市赣县沙地卫生院</t>
+  </si>
+  <si>
+    <t>[2021]第-3号</t>
+  </si>
+  <si>
+    <t>[2021]第-4号</t>
+  </si>
+  <si>
+    <t>王晓华</t>
+  </si>
+  <si>
+    <t>[2021]第-5号</t>
+  </si>
+  <si>
+    <t>李小平</t>
+  </si>
+  <si>
+    <t>去年未预算</t>
+  </si>
+  <si>
+    <t>[2021]第-6号</t>
+  </si>
+  <si>
+    <t>黄颖</t>
+  </si>
+  <si>
+    <t>2020-11-01</t>
+  </si>
+  <si>
+    <t>2020年事业单位公开招考</t>
+  </si>
+  <si>
+    <t>环卫所</t>
+  </si>
+  <si>
+    <t>[2021]第-7号</t>
+  </si>
+  <si>
+    <t>钟颖</t>
+  </si>
+  <si>
+    <t>[2021]第-8号</t>
+  </si>
+  <si>
+    <t>梁巍</t>
+  </si>
+  <si>
+    <t>[2021]第-9号</t>
+  </si>
+  <si>
+    <t>[2021]第-10号</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
   </si>
 </sst>
 </file>
@@ -4809,10 +4863,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
@@ -4860,9 +4914,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4875,16 +4935,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4894,28 +4954,6 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4935,15 +4973,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4957,8 +4997,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4966,15 +5013,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4982,7 +5030,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4996,9 +5044,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5073,13 +5127,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5097,19 +5169,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5127,7 +5193,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5139,13 +5211,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5157,13 +5223,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5181,79 +5289,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5314,9 +5368,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5386,11 +5442,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5402,10 +5456,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5414,133 +5468,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5963,7 +6017,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T509"/>
+  <dimension ref="A1:T517"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -8585,7 +8639,9 @@
       <c r="J46" s="4">
         <v>2265</v>
       </c>
-      <c r="K46" s="15"/>
+      <c r="K46" s="15">
+        <v>650</v>
+      </c>
       <c r="L46" s="9" t="s">
         <v>237</v>
       </c>
@@ -32501,8 +32557,336 @@
         <v>602</v>
       </c>
     </row>
+    <row r="510" spans="1:15">
+      <c r="A510" s="4" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B510" t="s">
+        <v>38</v>
+      </c>
+      <c r="C510" t="s">
+        <v>88</v>
+      </c>
+      <c r="D510" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E510">
+        <v>0</v>
+      </c>
+      <c r="F510">
+        <v>1620</v>
+      </c>
+      <c r="G510">
+        <v>860</v>
+      </c>
+      <c r="H510">
+        <v>0</v>
+      </c>
+      <c r="I510">
+        <v>0</v>
+      </c>
+      <c r="J510">
+        <v>2035</v>
+      </c>
+      <c r="L510" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N510" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="O510" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15">
+      <c r="A511" s="4" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B511" t="s">
+        <v>38</v>
+      </c>
+      <c r="C511" t="s">
+        <v>88</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E511">
+        <v>0</v>
+      </c>
+      <c r="F511">
+        <v>1620</v>
+      </c>
+      <c r="G511">
+        <v>1274</v>
+      </c>
+      <c r="H511">
+        <v>0</v>
+      </c>
+      <c r="I511">
+        <v>0</v>
+      </c>
+      <c r="J511">
+        <v>2035</v>
+      </c>
+      <c r="L511" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N511" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O511" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15">
+      <c r="A512" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B512" t="s">
+        <v>38</v>
+      </c>
+      <c r="C512" t="s">
+        <v>88</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E512">
+        <v>0</v>
+      </c>
+      <c r="F512">
+        <v>1620</v>
+      </c>
+      <c r="G512">
+        <v>920</v>
+      </c>
+      <c r="H512">
+        <v>0</v>
+      </c>
+      <c r="I512">
+        <v>0</v>
+      </c>
+      <c r="J512">
+        <v>2035</v>
+      </c>
+      <c r="L512" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N512" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O512" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="513" spans="1:15">
+      <c r="A513" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B513" t="s">
+        <v>18</v>
+      </c>
+      <c r="C513" t="s">
+        <v>88</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E513">
+        <v>0</v>
+      </c>
+      <c r="F513">
+        <v>0</v>
+      </c>
+      <c r="G513">
+        <v>0</v>
+      </c>
+      <c r="H513">
+        <v>1780</v>
+      </c>
+      <c r="I513">
+        <v>0</v>
+      </c>
+      <c r="J513">
+        <v>1895</v>
+      </c>
+      <c r="L513" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="N513" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O513" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15">
+      <c r="A514" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B514" t="s">
+        <v>38</v>
+      </c>
+      <c r="C514" t="s">
+        <v>88</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E514">
+        <v>0</v>
+      </c>
+      <c r="F514">
+        <v>0</v>
+      </c>
+      <c r="G514">
+        <v>0</v>
+      </c>
+      <c r="H514">
+        <v>1660</v>
+      </c>
+      <c r="I514">
+        <v>0</v>
+      </c>
+      <c r="J514">
+        <v>1895</v>
+      </c>
+      <c r="L514" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="N514" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O514" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15">
+      <c r="A515" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B515" t="s">
+        <v>38</v>
+      </c>
+      <c r="C515" t="s">
+        <v>88</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E515">
+        <v>0</v>
+      </c>
+      <c r="F515">
+        <v>1620</v>
+      </c>
+      <c r="G515">
+        <v>472</v>
+      </c>
+      <c r="H515">
+        <v>0</v>
+      </c>
+      <c r="I515">
+        <v>0</v>
+      </c>
+      <c r="J515">
+        <v>2035</v>
+      </c>
+      <c r="L515" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N515" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="O515" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15">
+      <c r="A516" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B516" t="s">
+        <v>18</v>
+      </c>
+      <c r="C516" t="s">
+        <v>88</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E516">
+        <v>0</v>
+      </c>
+      <c r="F516">
+        <v>0</v>
+      </c>
+      <c r="G516">
+        <v>0</v>
+      </c>
+      <c r="H516">
+        <v>1660</v>
+      </c>
+      <c r="I516">
+        <v>0</v>
+      </c>
+      <c r="J516">
+        <v>2035</v>
+      </c>
+      <c r="L516" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="N516" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O516" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15">
+      <c r="A517" s="4" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B517" t="s">
+        <v>38</v>
+      </c>
+      <c r="C517" t="s">
+        <v>88</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E517">
+        <v>0</v>
+      </c>
+      <c r="F517">
+        <v>1620</v>
+      </c>
+      <c r="G517">
+        <v>1346</v>
+      </c>
+      <c r="H517">
+        <v>0</v>
+      </c>
+      <c r="I517">
+        <v>0</v>
+      </c>
+      <c r="J517">
+        <v>2035</v>
+      </c>
+      <c r="L517" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="N517" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="O517" s="1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T508">
+  <autoFilter ref="A1:T509">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9240"/>
+    <workbookView windowWidth="23325" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$518</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="1613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4989" uniqueCount="1617">
   <si>
     <t>单号</t>
   </si>
@@ -4856,6 +4856,18 @@
   </si>
   <si>
     <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>[2021]空06号</t>
+  </si>
+  <si>
+    <t>彭玄保</t>
+  </si>
+  <si>
+    <t>[2021]第340号</t>
+  </si>
+  <si>
+    <t>李益平</t>
   </si>
 </sst>
 </file>
@@ -4863,11 +4875,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4915,69 +4927,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4997,8 +4956,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5012,8 +4986,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5030,7 +5041,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5038,7 +5049,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5051,8 +5062,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5127,13 +5139,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5151,13 +5175,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5169,7 +5193,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5181,19 +5217,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5205,13 +5229,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5223,7 +5265,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5247,25 +5295,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5277,19 +5307,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5302,12 +5320,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5368,17 +5380,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -5401,11 +5402,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5425,17 +5432,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5448,6 +5449,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5456,10 +5468,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5468,133 +5480,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6017,7 +6029,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T517"/>
+  <dimension ref="A1:T519"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -25586,7 +25598,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="9" t="s">
-        <v>1115</v>
+        <v>1074</v>
       </c>
       <c r="M358" s="4"/>
       <c r="N358" s="4" t="s">
@@ -25631,7 +25643,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="9" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="M359" s="4"/>
       <c r="N359" s="4" t="s">
@@ -32885,8 +32897,90 @@
         <v>1001</v>
       </c>
     </row>
+    <row r="518" spans="1:15">
+      <c r="A518" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E518">
+        <v>0</v>
+      </c>
+      <c r="F518">
+        <v>1500</v>
+      </c>
+      <c r="G518">
+        <v>990</v>
+      </c>
+      <c r="H518">
+        <v>0</v>
+      </c>
+      <c r="I518">
+        <v>0</v>
+      </c>
+      <c r="J518">
+        <v>2035</v>
+      </c>
+      <c r="L518" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N518" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="O518" s="1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15">
+      <c r="A519" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E519">
+        <v>0</v>
+      </c>
+      <c r="F519">
+        <v>1500</v>
+      </c>
+      <c r="G519">
+        <v>620</v>
+      </c>
+      <c r="H519">
+        <v>0</v>
+      </c>
+      <c r="I519">
+        <v>0</v>
+      </c>
+      <c r="J519">
+        <v>2035</v>
+      </c>
+      <c r="L519" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N519" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="O519" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T509">
+  <autoFilter ref="A1:T518">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -10,14 +10,14 @@
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$518</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$522</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4989" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5010" uniqueCount="1624">
   <si>
     <t>单号</t>
   </si>
@@ -4868,6 +4868,27 @@
   </si>
   <si>
     <t>李益平</t>
+  </si>
+  <si>
+    <t>[2021]辞49号</t>
+  </si>
+  <si>
+    <t>刘玲</t>
+  </si>
+  <si>
+    <t>[2021]辞50号</t>
+  </si>
+  <si>
+    <t>郭瑞丰</t>
+  </si>
+  <si>
+    <t>[2021]第341号</t>
+  </si>
+  <si>
+    <t>郭铃华</t>
+  </si>
+  <si>
+    <t>2021年事业单位选调考试</t>
   </si>
 </sst>
 </file>
@@ -4875,11 +4896,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4933,8 +4954,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4942,7 +4971,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4956,16 +4992,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4979,29 +5023,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5009,47 +5032,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5064,9 +5054,40 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5145,7 +5166,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5157,19 +5226,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5181,19 +5244,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5211,7 +5280,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5235,24 +5304,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5265,49 +5316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5319,7 +5334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5363,21 +5384,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -5387,17 +5393,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5418,25 +5435,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5452,11 +5460,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5468,10 +5489,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5480,133 +5501,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6028,8 +6049,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T519"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <dimension ref="A1:T522"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -6108,7 +6129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:19">
+    <row r="2" ht="14.25" hidden="1" spans="1:19">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -6167,7 +6188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:19">
+    <row r="3" ht="14.25" hidden="1" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -6226,7 +6247,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:19">
+    <row r="4" ht="14.25" hidden="1" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
@@ -6285,7 +6306,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:19">
+    <row r="5" ht="14.25" hidden="1" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>37</v>
       </c>
@@ -6342,7 +6363,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:19">
+    <row r="6" ht="14.25" hidden="1" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -6401,7 +6422,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:19">
+    <row r="7" ht="14.25" hidden="1" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
@@ -6460,7 +6481,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:19">
+    <row r="8" ht="14.25" hidden="1" spans="1:19">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -6519,7 +6540,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:19">
+    <row r="9" ht="14.25" hidden="1" spans="1:19">
       <c r="A9" s="4" t="s">
         <v>63</v>
       </c>
@@ -6578,7 +6599,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:19">
+    <row r="10" ht="14.25" hidden="1" spans="1:19">
       <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
@@ -6635,7 +6656,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:19">
+    <row r="11" ht="14.25" hidden="1" spans="1:19">
       <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
@@ -6694,7 +6715,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:19">
+    <row r="12" ht="14.25" hidden="1" spans="1:19">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -6751,7 +6772,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:19">
+    <row r="13" ht="14.25" hidden="1" spans="1:19">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -6806,7 +6827,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:19">
+    <row r="14" ht="14.25" hidden="1" spans="1:19">
       <c r="A14" s="4" t="s">
         <v>93</v>
       </c>
@@ -6865,7 +6886,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:19">
+    <row r="15" ht="14.25" hidden="1" spans="1:19">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -6924,7 +6945,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:19">
+    <row r="16" ht="14.25" hidden="1" spans="1:19">
       <c r="A16" s="4" t="s">
         <v>103</v>
       </c>
@@ -6983,7 +7004,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:19">
+    <row r="17" ht="14.25" hidden="1" spans="1:19">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -7038,7 +7059,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:19">
+    <row r="18" ht="14.25" hidden="1" spans="1:19">
       <c r="A18" s="4" t="s">
         <v>113</v>
       </c>
@@ -7097,7 +7118,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:20">
+    <row r="19" ht="14.25" hidden="1" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
@@ -7158,7 +7179,7 @@
         <v>87662.6773333333</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:19">
+    <row r="20" ht="14.25" hidden="1" spans="1:19">
       <c r="A20" s="4" t="s">
         <v>122</v>
       </c>
@@ -7215,7 +7236,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:20">
+    <row r="21" ht="14.25" hidden="1" spans="1:20">
       <c r="A21" s="4" t="s">
         <v>125</v>
       </c>
@@ -7276,7 +7297,7 @@
         <v>53992.6</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:19">
+    <row r="22" ht="14.25" hidden="1" spans="1:19">
       <c r="A22" s="4" t="s">
         <v>131</v>
       </c>
@@ -7331,7 +7352,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="1:19">
+    <row r="23" ht="14.25" hidden="1" spans="1:19">
       <c r="A23" s="4" t="s">
         <v>137</v>
       </c>
@@ -7386,7 +7407,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:19">
+    <row r="24" ht="14.25" hidden="1" spans="1:19">
       <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
@@ -7441,7 +7462,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:19">
+    <row r="25" ht="14.25" hidden="1" spans="1:19">
       <c r="A25" s="4" t="s">
         <v>146</v>
       </c>
@@ -7500,7 +7521,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" ht="14.25" spans="1:19">
+    <row r="26" ht="14.25" hidden="1" spans="1:19">
       <c r="A26" s="4" t="s">
         <v>150</v>
       </c>
@@ -7557,7 +7578,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="1:19">
+    <row r="27" ht="14.25" hidden="1" spans="1:19">
       <c r="A27" s="4" t="s">
         <v>157</v>
       </c>
@@ -7614,7 +7635,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" ht="14.25" spans="1:19">
+    <row r="28" ht="14.25" hidden="1" spans="1:19">
       <c r="A28" s="4" t="s">
         <v>165</v>
       </c>
@@ -7673,7 +7694,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:19">
+    <row r="29" ht="14.25" hidden="1" spans="1:19">
       <c r="A29" s="4" t="s">
         <v>171</v>
       </c>
@@ -7730,7 +7751,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:19">
+    <row r="30" ht="14.25" hidden="1" spans="1:19">
       <c r="A30" s="4" t="s">
         <v>176</v>
       </c>
@@ -7787,7 +7808,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="1:19">
+    <row r="31" ht="14.25" hidden="1" spans="1:19">
       <c r="A31" s="4" t="s">
         <v>180</v>
       </c>
@@ -7844,7 +7865,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:19">
+    <row r="32" ht="14.25" hidden="1" spans="1:19">
       <c r="A32" s="4" t="s">
         <v>185</v>
       </c>
@@ -7899,7 +7920,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="1:19">
+    <row r="33" ht="27" hidden="1" spans="1:19">
       <c r="A33" s="4" t="s">
         <v>190</v>
       </c>
@@ -7956,7 +7977,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" ht="27" spans="1:19">
+    <row r="34" ht="27" hidden="1" spans="1:19">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -8011,7 +8032,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="1:19">
+    <row r="35" ht="14.25" hidden="1" spans="1:19">
       <c r="A35" s="4" t="s">
         <v>201</v>
       </c>
@@ -8066,7 +8087,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="1:19">
+    <row r="36" ht="14.25" hidden="1" spans="1:19">
       <c r="A36" s="4" t="s">
         <v>207</v>
       </c>
@@ -8121,7 +8142,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" ht="14.25" spans="1:19">
+    <row r="37" ht="14.25" hidden="1" spans="1:19">
       <c r="A37" s="4" t="s">
         <v>211</v>
       </c>
@@ -8176,7 +8197,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" ht="14.25" spans="1:19">
+    <row r="38" ht="14.25" hidden="1" spans="1:19">
       <c r="A38" s="4" t="s">
         <v>215</v>
       </c>
@@ -8233,7 +8254,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" ht="14.25" spans="1:19">
+    <row r="39" ht="14.25" hidden="1" spans="1:19">
       <c r="A39" s="4" t="s">
         <v>219</v>
       </c>
@@ -8288,7 +8309,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" ht="27" spans="1:19">
+    <row r="40" ht="27" hidden="1" spans="1:19">
       <c r="A40" s="4" t="s">
         <v>224</v>
       </c>
@@ -8343,7 +8364,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" ht="14.25" spans="1:19">
+    <row r="41" ht="14.25" hidden="1" spans="1:19">
       <c r="A41" s="4" t="s">
         <v>229</v>
       </c>
@@ -8400,7 +8421,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" ht="14.25" spans="1:19">
+    <row r="42" ht="14.25" hidden="1" spans="1:19">
       <c r="A42" s="4" t="s">
         <v>235</v>
       </c>
@@ -8455,7 +8476,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" ht="14.25" spans="1:19">
+    <row r="43" ht="14.25" hidden="1" spans="1:19">
       <c r="A43" s="4" t="s">
         <v>241</v>
       </c>
@@ -8510,7 +8531,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" ht="14.25" spans="1:19">
+    <row r="44" ht="14.25" hidden="1" spans="1:19">
       <c r="A44" s="4" t="s">
         <v>247</v>
       </c>
@@ -8565,7 +8586,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="45" ht="14.25" spans="1:19">
+    <row r="45" ht="15" spans="1:19">
       <c r="A45" s="4" t="s">
         <v>251</v>
       </c>
@@ -8620,7 +8641,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="46" ht="27" spans="1:19">
+    <row r="46" ht="27" hidden="1" spans="1:19">
       <c r="A46" s="4" t="s">
         <v>257</v>
       </c>
@@ -8677,7 +8698,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" ht="14.25" spans="1:19">
+    <row r="47" ht="14.25" hidden="1" spans="1:19">
       <c r="A47" s="4" t="s">
         <v>262</v>
       </c>
@@ -8732,7 +8753,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" ht="14.25" spans="1:19">
+    <row r="48" ht="14.25" hidden="1" spans="1:19">
       <c r="A48" s="4" t="s">
         <v>266</v>
       </c>
@@ -8787,7 +8808,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" ht="27" spans="1:19">
+    <row r="49" ht="27" hidden="1" spans="1:19">
       <c r="A49" s="4" t="s">
         <v>270</v>
       </c>
@@ -8844,7 +8865,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="14.25" spans="1:19">
+    <row r="50" ht="14.25" hidden="1" spans="1:19">
       <c r="A50" s="4" t="s">
         <v>278</v>
       </c>
@@ -8899,7 +8920,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" ht="14.25" spans="1:19">
+    <row r="51" ht="14.25" hidden="1" spans="1:19">
       <c r="A51" s="4" t="s">
         <v>283</v>
       </c>
@@ -8956,7 +8977,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" ht="27.75" spans="1:19">
+    <row r="52" ht="27.75" hidden="1" spans="1:19">
       <c r="A52" s="4" t="s">
         <v>286</v>
       </c>
@@ -9013,7 +9034,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="53" ht="15" spans="1:19">
+    <row r="53" ht="15" hidden="1" spans="1:19">
       <c r="A53" s="4" t="s">
         <v>291</v>
       </c>
@@ -9068,7 +9089,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="1:19">
+    <row r="54" ht="14.25" hidden="1" spans="1:19">
       <c r="A54" s="4" t="s">
         <v>297</v>
       </c>
@@ -9125,7 +9146,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" ht="14.25" spans="1:19">
+    <row r="55" ht="14.25" hidden="1" spans="1:19">
       <c r="A55" s="4" t="s">
         <v>304</v>
       </c>
@@ -9180,7 +9201,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" ht="14.25" spans="1:19">
+    <row r="56" ht="14.25" hidden="1" spans="1:19">
       <c r="A56" s="4" t="s">
         <v>308</v>
       </c>
@@ -9237,7 +9258,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="1:19">
+    <row r="57" ht="14.25" hidden="1" spans="1:19">
       <c r="A57" s="4" t="s">
         <v>312</v>
       </c>
@@ -9296,7 +9317,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="58" ht="27" spans="1:19">
+    <row r="58" ht="27" hidden="1" spans="1:19">
       <c r="A58" s="4" t="s">
         <v>316</v>
       </c>
@@ -9351,7 +9372,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:19">
+    <row r="59" ht="14.25" hidden="1" spans="1:19">
       <c r="A59" s="4" t="s">
         <v>322</v>
       </c>
@@ -9408,7 +9429,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="60" ht="14.25" spans="1:19">
+    <row r="60" ht="14.25" hidden="1" spans="1:19">
       <c r="A60" s="4" t="s">
         <v>327</v>
       </c>
@@ -9465,7 +9486,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" ht="14.25" spans="1:19">
+    <row r="61" ht="14.25" hidden="1" spans="1:19">
       <c r="A61" s="4" t="s">
         <v>333</v>
       </c>
@@ -9522,7 +9543,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" ht="14.25" spans="1:19">
+    <row r="62" ht="14.25" hidden="1" spans="1:19">
       <c r="A62" s="5" t="s">
         <v>339</v>
       </c>
@@ -9577,7 +9598,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" ht="27" spans="1:19">
+    <row r="63" ht="27" hidden="1" spans="1:19">
       <c r="A63" s="4" t="s">
         <v>343</v>
       </c>
@@ -9634,7 +9655,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="64" ht="27" spans="1:19">
+    <row r="64" ht="27" hidden="1" spans="1:19">
       <c r="A64" s="4" t="s">
         <v>348</v>
       </c>
@@ -9691,7 +9712,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="65" ht="14.25" spans="1:19">
+    <row r="65" ht="14.25" hidden="1" spans="1:19">
       <c r="A65" s="4" t="s">
         <v>352</v>
       </c>
@@ -9748,7 +9769,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="66" ht="14.25" spans="1:19">
+    <row r="66" ht="14.25" hidden="1" spans="1:19">
       <c r="A66" s="4" t="s">
         <v>356</v>
       </c>
@@ -9805,7 +9826,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="67" ht="14.25" spans="1:19">
+    <row r="67" ht="14.25" hidden="1" spans="1:19">
       <c r="A67" s="4" t="s">
         <v>360</v>
       </c>
@@ -9862,7 +9883,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" ht="14.25" spans="1:19">
+    <row r="68" ht="14.25" hidden="1" spans="1:19">
       <c r="A68" s="4" t="s">
         <v>364</v>
       </c>
@@ -9919,7 +9940,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="69" ht="27" spans="1:19">
+    <row r="69" ht="27" hidden="1" spans="1:19">
       <c r="A69" s="4" t="s">
         <v>367</v>
       </c>
@@ -9976,7 +9997,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="70" ht="14.25" spans="1:19">
+    <row r="70" ht="14.25" hidden="1" spans="1:19">
       <c r="A70" s="4" t="s">
         <v>371</v>
       </c>
@@ -10033,7 +10054,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" ht="14.25" spans="1:19">
+    <row r="71" ht="14.25" hidden="1" spans="1:19">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -10090,7 +10111,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" ht="14.25" spans="1:19">
+    <row r="72" ht="14.25" hidden="1" spans="1:19">
       <c r="A72" s="4" t="s">
         <v>378</v>
       </c>
@@ -10147,7 +10168,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" ht="27" spans="1:19">
+    <row r="73" ht="27" hidden="1" spans="1:19">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10204,7 +10225,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74" ht="27" spans="1:19">
+    <row r="74" ht="27" hidden="1" spans="1:19">
       <c r="A74" s="4" t="s">
         <v>385</v>
       </c>
@@ -10261,7 +10282,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" ht="14.25" spans="1:19">
+    <row r="75" ht="14.25" hidden="1" spans="1:19">
       <c r="A75" s="4" t="s">
         <v>389</v>
       </c>
@@ -10318,7 +10339,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="76" ht="27" spans="1:19">
+    <row r="76" ht="27" hidden="1" spans="1:19">
       <c r="A76" s="4" t="s">
         <v>393</v>
       </c>
@@ -10375,7 +10396,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" ht="14.25" spans="1:19">
+    <row r="77" ht="14.25" hidden="1" spans="1:19">
       <c r="A77" s="4" t="s">
         <v>397</v>
       </c>
@@ -10434,7 +10455,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" ht="27" spans="1:19">
+    <row r="78" ht="27" hidden="1" spans="1:19">
       <c r="A78" s="4" t="s">
         <v>401</v>
       </c>
@@ -10491,7 +10512,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" ht="14.25" spans="1:19">
+    <row r="79" ht="14.25" hidden="1" spans="1:19">
       <c r="A79" s="4" t="s">
         <v>405</v>
       </c>
@@ -10548,7 +10569,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="80" ht="14.25" spans="1:19">
+    <row r="80" ht="14.25" hidden="1" spans="1:19">
       <c r="A80" s="4" t="s">
         <v>409</v>
       </c>
@@ -10605,7 +10626,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="81" ht="14.25" spans="1:19">
+    <row r="81" ht="14.25" hidden="1" spans="1:19">
       <c r="A81" s="4" t="s">
         <v>413</v>
       </c>
@@ -10662,7 +10683,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="82" ht="14.25" spans="1:19">
+    <row r="82" ht="14.25" hidden="1" spans="1:19">
       <c r="A82" s="4" t="s">
         <v>418</v>
       </c>
@@ -10719,7 +10740,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="83" ht="14.25" spans="1:19">
+    <row r="83" ht="14.25" hidden="1" spans="1:19">
       <c r="A83" s="4" t="s">
         <v>422</v>
       </c>
@@ -10776,7 +10797,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="84" ht="14.25" spans="1:19">
+    <row r="84" ht="14.25" hidden="1" spans="1:19">
       <c r="A84" s="4" t="s">
         <v>426</v>
       </c>
@@ -10833,7 +10854,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="85" ht="27" spans="1:19">
+    <row r="85" ht="27" hidden="1" spans="1:19">
       <c r="A85" s="4" t="s">
         <v>429</v>
       </c>
@@ -10890,7 +10911,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="86" ht="27" spans="1:19">
+    <row r="86" ht="27" hidden="1" spans="1:19">
       <c r="A86" s="4" t="s">
         <v>433</v>
       </c>
@@ -10947,7 +10968,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="87" ht="14.25" spans="1:19">
+    <row r="87" ht="14.25" hidden="1" spans="1:19">
       <c r="A87" s="4" t="s">
         <v>436</v>
       </c>
@@ -11004,7 +11025,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="88" ht="14.25" spans="1:19">
+    <row r="88" ht="14.25" hidden="1" spans="1:19">
       <c r="A88" s="4" t="s">
         <v>440</v>
       </c>
@@ -11061,7 +11082,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="89" ht="14.25" spans="1:19">
+    <row r="89" ht="14.25" hidden="1" spans="1:19">
       <c r="A89" s="4" t="s">
         <v>444</v>
       </c>
@@ -11118,7 +11139,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90" ht="27" spans="1:19">
+    <row r="90" ht="27" hidden="1" spans="1:19">
       <c r="A90" s="4" t="s">
         <v>448</v>
       </c>
@@ -11175,7 +11196,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="91" ht="14.25" spans="1:19">
+    <row r="91" ht="14.25" hidden="1" spans="1:19">
       <c r="A91" s="4" t="s">
         <v>452</v>
       </c>
@@ -11232,7 +11253,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" ht="14.25" spans="1:19">
+    <row r="92" ht="14.25" hidden="1" spans="1:19">
       <c r="A92" s="4" t="s">
         <v>454</v>
       </c>
@@ -11289,7 +11310,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" ht="14.25" spans="1:19">
+    <row r="93" ht="14.25" hidden="1" spans="1:19">
       <c r="A93" s="4" t="s">
         <v>456</v>
       </c>
@@ -11346,7 +11367,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" ht="14.25" spans="1:19">
+    <row r="94" ht="14.25" hidden="1" spans="1:19">
       <c r="A94" s="4" t="s">
         <v>458</v>
       </c>
@@ -11403,7 +11424,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" ht="14.25" spans="1:19">
+    <row r="95" ht="14.25" hidden="1" spans="1:19">
       <c r="A95" s="4" t="s">
         <v>461</v>
       </c>
@@ -11460,7 +11481,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="96" ht="14.25" spans="1:19">
+    <row r="96" ht="14.25" hidden="1" spans="1:19">
       <c r="A96" s="4" t="s">
         <v>465</v>
       </c>
@@ -11517,7 +11538,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="97" ht="14.25" spans="1:19">
+    <row r="97" ht="14.25" hidden="1" spans="1:19">
       <c r="A97" s="4" t="s">
         <v>469</v>
       </c>
@@ -11574,7 +11595,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" ht="14.25" spans="1:19">
+    <row r="98" ht="14.25" hidden="1" spans="1:19">
       <c r="A98" s="4" t="s">
         <v>474</v>
       </c>
@@ -11631,7 +11652,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" ht="14.25" spans="1:19">
+    <row r="99" ht="14.25" hidden="1" spans="1:19">
       <c r="A99" s="4" t="s">
         <v>476</v>
       </c>
@@ -11688,7 +11709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" ht="14.25" spans="1:19">
+    <row r="100" ht="14.25" hidden="1" spans="1:19">
       <c r="A100" s="4" t="s">
         <v>479</v>
       </c>
@@ -11745,7 +11766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" ht="14.25" spans="1:19">
+    <row r="101" ht="14.25" hidden="1" spans="1:19">
       <c r="A101" s="4" t="s">
         <v>481</v>
       </c>
@@ -11802,7 +11823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" ht="14.25" spans="1:19">
+    <row r="102" ht="14.25" hidden="1" spans="1:19">
       <c r="A102" s="4" t="s">
         <v>483</v>
       </c>
@@ -11859,7 +11880,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" ht="14.25" spans="1:19">
+    <row r="103" ht="14.25" hidden="1" spans="1:19">
       <c r="A103" s="4" t="s">
         <v>485</v>
       </c>
@@ -11916,7 +11937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" ht="14.25" spans="1:19">
+    <row r="104" ht="14.25" hidden="1" spans="1:19">
       <c r="A104" s="4" t="s">
         <v>487</v>
       </c>
@@ -11973,7 +11994,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" ht="14.25" spans="1:19">
+    <row r="105" ht="14.25" hidden="1" spans="1:19">
       <c r="A105" s="4" t="s">
         <v>489</v>
       </c>
@@ -12030,7 +12051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" ht="14.25" spans="1:19">
+    <row r="106" ht="14.25" hidden="1" spans="1:19">
       <c r="A106" s="4" t="s">
         <v>491</v>
       </c>
@@ -12087,7 +12108,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="107" ht="14.25" spans="1:19">
+    <row r="107" ht="14.25" hidden="1" spans="1:19">
       <c r="A107" s="4" t="s">
         <v>495</v>
       </c>
@@ -12144,7 +12165,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="108" ht="14.25" spans="1:19">
+    <row r="108" ht="14.25" hidden="1" spans="1:19">
       <c r="A108" s="4" t="s">
         <v>497</v>
       </c>
@@ -12199,7 +12220,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="109" ht="14.25" spans="1:19">
+    <row r="109" ht="14.25" hidden="1" spans="1:19">
       <c r="A109" s="4" t="s">
         <v>502</v>
       </c>
@@ -12256,7 +12277,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="110" ht="14.25" spans="1:19">
+    <row r="110" ht="14.25" hidden="1" spans="1:19">
       <c r="A110" s="4" t="s">
         <v>504</v>
       </c>
@@ -12313,7 +12334,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" ht="14.25" spans="1:19">
+    <row r="111" ht="14.25" hidden="1" spans="1:19">
       <c r="A111" s="4" t="s">
         <v>506</v>
       </c>
@@ -12370,7 +12391,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="112" ht="14.25" spans="1:19">
+    <row r="112" ht="14.25" hidden="1" spans="1:19">
       <c r="A112" s="4" t="s">
         <v>508</v>
       </c>
@@ -12427,7 +12448,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="113" ht="14.25" spans="1:19">
+    <row r="113" ht="14.25" hidden="1" spans="1:19">
       <c r="A113" s="4" t="s">
         <v>510</v>
       </c>
@@ -12484,7 +12505,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" ht="27" spans="1:19">
+    <row r="114" ht="27" hidden="1" spans="1:19">
       <c r="A114" s="4" t="s">
         <v>513</v>
       </c>
@@ -12541,7 +12562,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="115" ht="27" spans="1:19">
+    <row r="115" ht="27" hidden="1" spans="1:19">
       <c r="A115" s="4" t="s">
         <v>517</v>
       </c>
@@ -12598,7 +12619,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="116" ht="27" spans="1:19">
+    <row r="116" ht="27" hidden="1" spans="1:19">
       <c r="A116" s="4" t="s">
         <v>520</v>
       </c>
@@ -12655,7 +12676,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="117" ht="14.25" spans="1:19">
+    <row r="117" ht="14.25" hidden="1" spans="1:19">
       <c r="A117" s="4" t="s">
         <v>523</v>
       </c>
@@ -12710,7 +12731,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="118" ht="14.25" spans="1:19">
+    <row r="118" ht="14.25" hidden="1" spans="1:19">
       <c r="A118" s="4" t="s">
         <v>528</v>
       </c>
@@ -12767,7 +12788,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" ht="14.25" spans="1:19">
+    <row r="119" ht="14.25" hidden="1" spans="1:19">
       <c r="A119" s="4" t="s">
         <v>530</v>
       </c>
@@ -12824,7 +12845,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" ht="14.25" spans="1:19">
+    <row r="120" ht="14.25" hidden="1" spans="1:19">
       <c r="A120" s="4" t="s">
         <v>532</v>
       </c>
@@ -12881,7 +12902,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121" ht="14.25" spans="1:19">
+    <row r="121" ht="14.25" hidden="1" spans="1:19">
       <c r="A121" s="4" t="s">
         <v>534</v>
       </c>
@@ -12938,7 +12959,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="122" ht="14.25" spans="1:19">
+    <row r="122" ht="14.25" hidden="1" spans="1:19">
       <c r="A122" s="4" t="s">
         <v>536</v>
       </c>
@@ -12995,7 +13016,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" ht="14.25" spans="1:19">
+    <row r="123" ht="14.25" hidden="1" spans="1:19">
       <c r="A123" s="4" t="s">
         <v>539</v>
       </c>
@@ -13052,7 +13073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" ht="14.25" spans="1:19">
+    <row r="124" ht="14.25" hidden="1" spans="1:19">
       <c r="A124" s="4" t="s">
         <v>542</v>
       </c>
@@ -13109,7 +13130,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" ht="14.25" spans="1:19">
+    <row r="125" ht="14.25" hidden="1" spans="1:19">
       <c r="A125" s="4" t="s">
         <v>544</v>
       </c>
@@ -13166,7 +13187,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" ht="14.25" spans="1:19">
+    <row r="126" ht="14.25" hidden="1" spans="1:19">
       <c r="A126" s="4" t="s">
         <v>546</v>
       </c>
@@ -13223,7 +13244,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="127" ht="14.25" spans="1:19">
+    <row r="127" ht="14.25" hidden="1" spans="1:19">
       <c r="A127" s="4" t="s">
         <v>551</v>
       </c>
@@ -13280,7 +13301,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="128" ht="14.25" spans="1:19">
+    <row r="128" ht="14.25" hidden="1" spans="1:19">
       <c r="A128" s="4" t="s">
         <v>553</v>
       </c>
@@ -13337,7 +13358,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="129" ht="14.25" spans="1:19">
+    <row r="129" ht="14.25" hidden="1" spans="1:19">
       <c r="A129" s="4" t="s">
         <v>556</v>
       </c>
@@ -13392,7 +13413,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" ht="14.25" spans="1:19">
+    <row r="130" ht="14.25" hidden="1" spans="1:19">
       <c r="A130" s="4" t="s">
         <v>560</v>
       </c>
@@ -13447,7 +13468,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="131" ht="14.25" spans="1:19">
+    <row r="131" ht="14.25" hidden="1" spans="1:19">
       <c r="A131" s="4" t="s">
         <v>562</v>
       </c>
@@ -13502,7 +13523,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="132" ht="14.25" spans="1:19">
+    <row r="132" ht="14.25" hidden="1" spans="1:19">
       <c r="A132" s="4" t="s">
         <v>564</v>
       </c>
@@ -13557,7 +13578,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="133" ht="14.25" spans="1:19">
+    <row r="133" ht="14.25" hidden="1" spans="1:19">
       <c r="A133" s="4" t="s">
         <v>566</v>
       </c>
@@ -13612,7 +13633,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="134" ht="14.25" spans="1:19">
+    <row r="134" ht="14.25" hidden="1" spans="1:19">
       <c r="A134" s="4" t="s">
         <v>568</v>
       </c>
@@ -13667,7 +13688,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="135" ht="14.25" spans="1:19">
+    <row r="135" ht="14.25" hidden="1" spans="1:19">
       <c r="A135" s="4" t="s">
         <v>572</v>
       </c>
@@ -13722,7 +13743,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="136" ht="14.25" spans="1:19">
+    <row r="136" ht="14.25" hidden="1" spans="1:19">
       <c r="A136" s="4" t="s">
         <v>574</v>
       </c>
@@ -13777,7 +13798,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="137" ht="14.25" spans="1:19">
+    <row r="137" ht="14.25" hidden="1" spans="1:19">
       <c r="A137" s="4" t="s">
         <v>576</v>
       </c>
@@ -13832,7 +13853,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="138" ht="14.25" spans="1:19">
+    <row r="138" ht="14.25" hidden="1" spans="1:19">
       <c r="A138" s="4" t="s">
         <v>578</v>
       </c>
@@ -13887,7 +13908,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="139" ht="14.25" spans="1:19">
+    <row r="139" ht="14.25" hidden="1" spans="1:19">
       <c r="A139" s="4" t="s">
         <v>580</v>
       </c>
@@ -13942,7 +13963,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="140" ht="14.25" spans="1:19">
+    <row r="140" ht="14.25" hidden="1" spans="1:19">
       <c r="A140" s="4" t="s">
         <v>582</v>
       </c>
@@ -13999,7 +14020,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="141" ht="14.25" spans="1:19">
+    <row r="141" ht="14.25" hidden="1" spans="1:19">
       <c r="A141" s="4" t="s">
         <v>585</v>
       </c>
@@ -14056,7 +14077,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="142" ht="14.25" spans="1:19">
+    <row r="142" ht="14.25" hidden="1" spans="1:19">
       <c r="A142" s="4" t="s">
         <v>587</v>
       </c>
@@ -14113,7 +14134,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="143" ht="14.25" spans="1:19">
+    <row r="143" ht="14.25" hidden="1" spans="1:19">
       <c r="A143" s="4" t="s">
         <v>589</v>
       </c>
@@ -14172,7 +14193,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="144" ht="14.25" spans="1:19">
+    <row r="144" ht="14.25" hidden="1" spans="1:19">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
@@ -14229,7 +14250,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="145" ht="27" spans="1:19">
+    <row r="145" ht="27" hidden="1" spans="1:19">
       <c r="A145" s="4" t="s">
         <v>594</v>
       </c>
@@ -14284,7 +14305,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" ht="14.25" spans="1:19">
+    <row r="146" ht="14.25" hidden="1" spans="1:19">
       <c r="A146" s="4" t="s">
         <v>595</v>
       </c>
@@ -14339,7 +14360,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="147" ht="14.25" spans="1:19">
+    <row r="147" ht="14.25" hidden="1" spans="1:19">
       <c r="A147" s="4" t="s">
         <v>599</v>
       </c>
@@ -14392,7 +14413,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" ht="14.25" spans="1:19">
+    <row r="148" ht="14.25" hidden="1" spans="1:19">
       <c r="A148" s="4" t="s">
         <v>605</v>
       </c>
@@ -14445,7 +14466,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="149" ht="14.25" spans="1:19">
+    <row r="149" ht="14.25" hidden="1" spans="1:19">
       <c r="A149" s="4" t="s">
         <v>609</v>
       </c>
@@ -14498,7 +14519,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="150" ht="14.25" spans="1:19">
+    <row r="150" ht="14.25" hidden="1" spans="1:19">
       <c r="A150" s="4" t="s">
         <v>613</v>
       </c>
@@ -14557,7 +14578,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="151" ht="14.25" spans="1:19">
+    <row r="151" ht="14.25" hidden="1" spans="1:19">
       <c r="A151" s="4" t="s">
         <v>615</v>
       </c>
@@ -14614,7 +14635,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="152" ht="14.25" spans="1:19">
+    <row r="152" ht="14.25" hidden="1" spans="1:19">
       <c r="A152" s="4" t="s">
         <v>617</v>
       </c>
@@ -14671,7 +14692,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" ht="14.25" spans="1:19">
+    <row r="153" ht="14.25" hidden="1" spans="1:19">
       <c r="A153" s="4" t="s">
         <v>619</v>
       </c>
@@ -14728,7 +14749,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="154" ht="14.25" spans="1:19">
+    <row r="154" ht="14.25" hidden="1" spans="1:19">
       <c r="A154" s="4" t="s">
         <v>621</v>
       </c>
@@ -14785,7 +14806,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="155" ht="27" spans="1:19">
+    <row r="155" ht="27" hidden="1" spans="1:19">
       <c r="A155" s="4" t="s">
         <v>624</v>
       </c>
@@ -14842,7 +14863,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" ht="27" spans="1:19">
+    <row r="156" ht="27" hidden="1" spans="1:19">
       <c r="A156" s="4" t="s">
         <v>628</v>
       </c>
@@ -14899,7 +14920,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="157" ht="14.25" spans="1:19">
+    <row r="157" ht="14.25" hidden="1" spans="1:19">
       <c r="A157" s="4" t="s">
         <v>630</v>
       </c>
@@ -14956,7 +14977,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" ht="14.25" spans="1:19">
+    <row r="158" ht="14.25" hidden="1" spans="1:19">
       <c r="A158" s="4" t="s">
         <v>632</v>
       </c>
@@ -15013,7 +15034,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" ht="14.25" spans="1:19">
+    <row r="159" ht="14.25" hidden="1" spans="1:19">
       <c r="A159" s="4" t="s">
         <v>634</v>
       </c>
@@ -15070,7 +15091,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" ht="14.25" spans="1:19">
+    <row r="160" ht="14.25" hidden="1" spans="1:19">
       <c r="A160" s="4" t="s">
         <v>636</v>
       </c>
@@ -15127,7 +15148,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" ht="14.25" spans="1:19">
+    <row r="161" ht="14.25" hidden="1" spans="1:19">
       <c r="A161" s="4" t="s">
         <v>638</v>
       </c>
@@ -15184,7 +15205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" ht="14.25" spans="1:19">
+    <row r="162" ht="14.25" hidden="1" spans="1:19">
       <c r="A162" s="4" t="s">
         <v>640</v>
       </c>
@@ -15241,7 +15262,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="163" ht="14.25" spans="1:19">
+    <row r="163" ht="14.25" hidden="1" spans="1:19">
       <c r="A163" s="4" t="s">
         <v>642</v>
       </c>
@@ -15298,7 +15319,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="164" ht="14.25" spans="1:19">
+    <row r="164" ht="14.25" hidden="1" spans="1:19">
       <c r="A164" s="4" t="s">
         <v>644</v>
       </c>
@@ -15355,7 +15376,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="165" ht="14.25" spans="1:19">
+    <row r="165" ht="14.25" hidden="1" spans="1:19">
       <c r="A165" s="4" t="s">
         <v>646</v>
       </c>
@@ -15412,7 +15433,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="166" ht="14.25" spans="1:19">
+    <row r="166" ht="14.25" hidden="1" spans="1:19">
       <c r="A166" s="4" t="s">
         <v>651</v>
       </c>
@@ -15469,7 +15490,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="167" ht="14.25" spans="1:19">
+    <row r="167" ht="14.25" hidden="1" spans="1:19">
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
@@ -15526,7 +15547,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="168" ht="14.25" spans="1:19">
+    <row r="168" ht="14.25" hidden="1" spans="1:19">
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
@@ -15583,7 +15604,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="169" ht="14.25" spans="1:19">
+    <row r="169" ht="14.25" hidden="1" spans="1:19">
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
@@ -15640,7 +15661,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="170" ht="14.25" spans="1:19">
+    <row r="170" ht="14.25" hidden="1" spans="1:19">
       <c r="A170" s="4" t="s">
         <v>659</v>
       </c>
@@ -15697,7 +15718,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="171" ht="14.25" spans="1:19">
+    <row r="171" ht="14.25" hidden="1" spans="1:19">
       <c r="A171" s="4" t="s">
         <v>661</v>
       </c>
@@ -15754,7 +15775,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="172" ht="14.25" spans="1:19">
+    <row r="172" ht="14.25" hidden="1" spans="1:19">
       <c r="A172" s="4" t="s">
         <v>663</v>
       </c>
@@ -15811,7 +15832,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="173" ht="14.25" spans="1:19">
+    <row r="173" ht="14.25" hidden="1" spans="1:19">
       <c r="A173" s="4" t="s">
         <v>665</v>
       </c>
@@ -15868,7 +15889,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="174" ht="14.25" spans="1:19">
+    <row r="174" ht="14.25" hidden="1" spans="1:19">
       <c r="A174" s="4" t="s">
         <v>667</v>
       </c>
@@ -15925,7 +15946,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" ht="14.25" spans="1:19">
+    <row r="175" ht="14.25" hidden="1" spans="1:19">
       <c r="A175" s="4" t="s">
         <v>669</v>
       </c>
@@ -15982,7 +16003,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="176" ht="14.25" spans="1:19">
+    <row r="176" ht="14.25" hidden="1" spans="1:19">
       <c r="A176" s="4" t="s">
         <v>671</v>
       </c>
@@ -16039,7 +16060,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="177" ht="14.25" spans="1:19">
+    <row r="177" ht="14.25" hidden="1" spans="1:19">
       <c r="A177" s="4" t="s">
         <v>673</v>
       </c>
@@ -16096,7 +16117,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="178" ht="14.25" spans="1:19">
+    <row r="178" ht="14.25" hidden="1" spans="1:19">
       <c r="A178" s="4" t="s">
         <v>677</v>
       </c>
@@ -16153,7 +16174,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="179" ht="14.25" spans="1:19">
+    <row r="179" ht="14.25" hidden="1" spans="1:19">
       <c r="A179" s="4" t="s">
         <v>679</v>
       </c>
@@ -16210,7 +16231,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" ht="14.25" spans="1:19">
+    <row r="180" ht="14.25" hidden="1" spans="1:19">
       <c r="A180" s="4" t="s">
         <v>681</v>
       </c>
@@ -16267,7 +16288,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" ht="14.25" spans="1:19">
+    <row r="181" ht="14.25" hidden="1" spans="1:19">
       <c r="A181" s="4" t="s">
         <v>683</v>
       </c>
@@ -16324,7 +16345,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" ht="14.25" spans="1:19">
+    <row r="182" ht="14.25" hidden="1" spans="1:19">
       <c r="A182" s="4" t="s">
         <v>685</v>
       </c>
@@ -16381,7 +16402,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" ht="14.25" spans="1:19">
+    <row r="183" ht="14.25" hidden="1" spans="1:19">
       <c r="A183" s="4" t="s">
         <v>687</v>
       </c>
@@ -16438,7 +16459,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" ht="14.25" spans="1:19">
+    <row r="184" ht="14.25" hidden="1" spans="1:19">
       <c r="A184" s="4" t="s">
         <v>690</v>
       </c>
@@ -16495,7 +16516,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" ht="14.25" spans="1:19">
+    <row r="185" ht="14.25" hidden="1" spans="1:19">
       <c r="A185" s="4" t="s">
         <v>692</v>
       </c>
@@ -16552,7 +16573,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" ht="14.25" spans="1:19">
+    <row r="186" ht="14.25" hidden="1" spans="1:19">
       <c r="A186" s="4" t="s">
         <v>694</v>
       </c>
@@ -16607,7 +16628,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="187" ht="14.25" spans="1:19">
+    <row r="187" ht="14.25" hidden="1" spans="1:19">
       <c r="A187" s="4" t="s">
         <v>698</v>
       </c>
@@ -16664,7 +16685,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" ht="14.25" spans="1:19">
+    <row r="188" ht="14.25" hidden="1" spans="1:19">
       <c r="A188" s="4" t="s">
         <v>700</v>
       </c>
@@ -16721,7 +16742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" ht="14.25" spans="1:19">
+    <row r="189" ht="14.25" hidden="1" spans="1:19">
       <c r="A189" s="4" t="s">
         <v>702</v>
       </c>
@@ -16780,7 +16801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" ht="14.25" spans="1:19">
+    <row r="190" ht="14.25" hidden="1" spans="1:19">
       <c r="A190" s="4" t="s">
         <v>706</v>
       </c>
@@ -16835,7 +16856,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" ht="14.25" spans="1:19">
+    <row r="191" ht="14.25" hidden="1" spans="1:19">
       <c r="A191" s="4" t="s">
         <v>708</v>
       </c>
@@ -16894,7 +16915,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" ht="14.25" spans="1:19">
+    <row r="192" ht="14.25" hidden="1" spans="1:19">
       <c r="A192" s="4" t="s">
         <v>710</v>
       </c>
@@ -16953,7 +16974,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="193" ht="14.25" spans="1:19">
+    <row r="193" ht="14.25" hidden="1" spans="1:19">
       <c r="A193" s="4" t="s">
         <v>714</v>
       </c>
@@ -17012,7 +17033,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="194" ht="14.25" spans="1:19">
+    <row r="194" ht="14.25" hidden="1" spans="1:19">
       <c r="A194" s="4" t="s">
         <v>717</v>
       </c>
@@ -17071,7 +17092,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="195" ht="14.25" spans="1:19">
+    <row r="195" ht="14.25" hidden="1" spans="1:19">
       <c r="A195" s="4" t="s">
         <v>719</v>
       </c>
@@ -17130,7 +17151,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="196" ht="14.25" spans="1:19">
+    <row r="196" ht="14.25" hidden="1" spans="1:19">
       <c r="A196" s="4" t="s">
         <v>722</v>
       </c>
@@ -17187,7 +17208,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="197" ht="14.25" spans="1:19">
+    <row r="197" ht="14.25" hidden="1" spans="1:19">
       <c r="A197" s="4" t="s">
         <v>723</v>
       </c>
@@ -17244,7 +17265,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="198" ht="14.25" spans="1:19">
+    <row r="198" ht="14.25" hidden="1" spans="1:19">
       <c r="A198" s="4" t="s">
         <v>725</v>
       </c>
@@ -17301,7 +17322,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="199" ht="27" spans="1:19">
+    <row r="199" ht="27" hidden="1" spans="1:19">
       <c r="A199" s="4" t="s">
         <v>727</v>
       </c>
@@ -17358,7 +17379,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="200" ht="14.25" spans="1:19">
+    <row r="200" ht="14.25" hidden="1" spans="1:19">
       <c r="A200" s="4" t="s">
         <v>731</v>
       </c>
@@ -17415,7 +17436,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="201" ht="14.25" spans="1:19">
+    <row r="201" ht="14.25" hidden="1" spans="1:19">
       <c r="A201" s="4" t="s">
         <v>735</v>
       </c>
@@ -17472,7 +17493,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="202" ht="14.25" spans="1:19">
+    <row r="202" ht="14.25" hidden="1" spans="1:19">
       <c r="A202" s="4" t="s">
         <v>738</v>
       </c>
@@ -17529,7 +17550,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="203" ht="14.25" spans="1:19">
+    <row r="203" ht="14.25" hidden="1" spans="1:19">
       <c r="A203" s="4" t="s">
         <v>740</v>
       </c>
@@ -17586,7 +17607,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="204" ht="14.25" spans="1:19">
+    <row r="204" ht="14.25" hidden="1" spans="1:19">
       <c r="A204" s="4" t="s">
         <v>742</v>
       </c>
@@ -17643,7 +17664,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="205" ht="14.25" spans="1:19">
+    <row r="205" ht="14.25" hidden="1" spans="1:19">
       <c r="A205" s="4" t="s">
         <v>745</v>
       </c>
@@ -17702,7 +17723,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" ht="14.25" spans="1:19">
+    <row r="206" ht="14.25" hidden="1" spans="1:19">
       <c r="A206" s="4" t="s">
         <v>749</v>
       </c>
@@ -17759,7 +17780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" ht="14.25" spans="1:19">
+    <row r="207" ht="14.25" hidden="1" spans="1:19">
       <c r="A207" s="4" t="s">
         <v>751</v>
       </c>
@@ -17816,7 +17837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" ht="14.25" spans="1:19">
+    <row r="208" ht="14.25" hidden="1" spans="1:19">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -17873,7 +17894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" ht="14.25" spans="1:19">
+    <row r="209" ht="14.25" hidden="1" spans="1:19">
       <c r="A209" s="4" t="s">
         <v>755</v>
       </c>
@@ -17928,7 +17949,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" ht="14.25" spans="1:19">
+    <row r="210" ht="14.25" hidden="1" spans="1:19">
       <c r="A210" s="4" t="s">
         <v>757</v>
       </c>
@@ -17985,7 +18006,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" ht="14.25" spans="1:19">
+    <row r="211" ht="14.25" hidden="1" spans="1:19">
       <c r="A211" s="4" t="s">
         <v>759</v>
       </c>
@@ -18042,7 +18063,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="212" ht="14.25" spans="1:19">
+    <row r="212" ht="14.25" hidden="1" spans="1:19">
       <c r="A212" s="4" t="s">
         <v>761</v>
       </c>
@@ -18099,7 +18120,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="213" ht="14.25" spans="1:19">
+    <row r="213" ht="14.25" hidden="1" spans="1:19">
       <c r="A213" s="4" t="s">
         <v>763</v>
       </c>
@@ -18156,7 +18177,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="214" ht="14.25" spans="1:19">
+    <row r="214" ht="14.25" hidden="1" spans="1:19">
       <c r="A214" s="4" t="s">
         <v>765</v>
       </c>
@@ -18213,7 +18234,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="215" ht="14.25" spans="1:19">
+    <row r="215" ht="14.25" hidden="1" spans="1:19">
       <c r="A215" s="4" t="s">
         <v>768</v>
       </c>
@@ -18270,7 +18291,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="216" ht="14.25" spans="1:19">
+    <row r="216" ht="14.25" hidden="1" spans="1:19">
       <c r="A216" s="4" t="s">
         <v>770</v>
       </c>
@@ -18329,7 +18350,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="217" ht="14.25" spans="1:19">
+    <row r="217" ht="14.25" hidden="1" spans="1:19">
       <c r="A217" s="4" t="s">
         <v>773</v>
       </c>
@@ -18386,7 +18407,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="218" ht="14.25" spans="1:19">
+    <row r="218" ht="14.25" hidden="1" spans="1:19">
       <c r="A218" s="4" t="s">
         <v>775</v>
       </c>
@@ -18443,7 +18464,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="219" ht="27" spans="1:19">
+    <row r="219" ht="27" hidden="1" spans="1:19">
       <c r="A219" s="4" t="s">
         <v>777</v>
       </c>
@@ -18498,7 +18519,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="220" ht="27" spans="1:19">
+    <row r="220" ht="27" hidden="1" spans="1:19">
       <c r="A220" s="4" t="s">
         <v>781</v>
       </c>
@@ -18553,7 +18574,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="221" ht="27" spans="1:19">
+    <row r="221" ht="27" hidden="1" spans="1:19">
       <c r="A221" s="4" t="s">
         <v>783</v>
       </c>
@@ -18608,7 +18629,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="222" ht="27" spans="1:19">
+    <row r="222" ht="27" hidden="1" spans="1:19">
       <c r="A222" s="4" t="s">
         <v>785</v>
       </c>
@@ -18663,7 +18684,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="223" ht="27" spans="1:19">
+    <row r="223" ht="27" hidden="1" spans="1:19">
       <c r="A223" s="4" t="s">
         <v>787</v>
       </c>
@@ -18718,7 +18739,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="224" ht="27" spans="1:19">
+    <row r="224" ht="27" hidden="1" spans="1:19">
       <c r="A224" s="4" t="s">
         <v>789</v>
       </c>
@@ -18773,7 +18794,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="225" ht="14.25" spans="1:19">
+    <row r="225" ht="14.25" hidden="1" spans="1:19">
       <c r="A225" s="4" t="s">
         <v>791</v>
       </c>
@@ -18830,7 +18851,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="226" ht="14.25" spans="1:19">
+    <row r="226" ht="14.25" hidden="1" spans="1:19">
       <c r="A226" s="4" t="s">
         <v>793</v>
       </c>
@@ -18887,7 +18908,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="227" ht="14.25" spans="1:19">
+    <row r="227" ht="14.25" hidden="1" spans="1:19">
       <c r="A227" s="4" t="s">
         <v>794</v>
       </c>
@@ -18944,7 +18965,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="228" ht="14.25" spans="1:19">
+    <row r="228" ht="14.25" hidden="1" spans="1:19">
       <c r="A228" s="4" t="s">
         <v>796</v>
       </c>
@@ -19001,7 +19022,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" ht="14.25" spans="1:19">
+    <row r="229" ht="14.25" hidden="1" spans="1:19">
       <c r="A229" s="4" t="s">
         <v>798</v>
       </c>
@@ -19058,7 +19079,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="230" ht="14.25" spans="1:19">
+    <row r="230" ht="14.25" hidden="1" spans="1:19">
       <c r="A230" s="4" t="s">
         <v>800</v>
       </c>
@@ -19115,7 +19136,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="231" ht="14.25" spans="1:19">
+    <row r="231" ht="14.25" hidden="1" spans="1:19">
       <c r="A231" s="4" t="s">
         <v>802</v>
       </c>
@@ -19172,7 +19193,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="232" ht="14.25" spans="1:19">
+    <row r="232" ht="14.25" hidden="1" spans="1:19">
       <c r="A232" s="4" t="s">
         <v>804</v>
       </c>
@@ -19229,7 +19250,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="233" ht="14.25" spans="1:19">
+    <row r="233" ht="14.25" hidden="1" spans="1:19">
       <c r="A233" s="4" t="s">
         <v>806</v>
       </c>
@@ -19286,7 +19307,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" ht="14.25" spans="1:19">
+    <row r="234" ht="14.25" hidden="1" spans="1:19">
       <c r="A234" s="4" t="s">
         <v>808</v>
       </c>
@@ -19343,7 +19364,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="235" ht="14.25" spans="1:19">
+    <row r="235" ht="14.25" hidden="1" spans="1:19">
       <c r="A235" s="4" t="s">
         <v>810</v>
       </c>
@@ -19400,7 +19421,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="236" ht="27" spans="1:19">
+    <row r="236" ht="27" hidden="1" spans="1:19">
       <c r="A236" s="4" t="s">
         <v>812</v>
       </c>
@@ -19455,7 +19476,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="237" ht="27" spans="1:19">
+    <row r="237" ht="27" hidden="1" spans="1:19">
       <c r="A237" s="4" t="s">
         <v>817</v>
       </c>
@@ -19510,7 +19531,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="238" ht="27" spans="1:19">
+    <row r="238" ht="27" hidden="1" spans="1:19">
       <c r="A238" s="4" t="s">
         <v>819</v>
       </c>
@@ -19565,7 +19586,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="239" ht="14.25" spans="1:19">
+    <row r="239" ht="14.25" hidden="1" spans="1:19">
       <c r="A239" s="4" t="s">
         <v>821</v>
       </c>
@@ -19620,7 +19641,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="240" ht="14.25" spans="1:19">
+    <row r="240" ht="14.25" hidden="1" spans="1:19">
       <c r="A240" s="4" t="s">
         <v>825</v>
       </c>
@@ -19677,7 +19698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" ht="14.25" spans="1:19">
+    <row r="241" ht="14.25" hidden="1" spans="1:19">
       <c r="A241" s="4" t="s">
         <v>827</v>
       </c>
@@ -19734,7 +19755,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" ht="14.25" spans="1:19">
+    <row r="242" ht="14.25" hidden="1" spans="1:19">
       <c r="A242" s="4" t="s">
         <v>829</v>
       </c>
@@ -19791,7 +19812,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="243" ht="14.25" spans="1:19">
+    <row r="243" ht="14.25" hidden="1" spans="1:19">
       <c r="A243" s="4" t="s">
         <v>832</v>
       </c>
@@ -19848,7 +19869,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" ht="14.25" spans="1:19">
+    <row r="244" ht="14.25" hidden="1" spans="1:19">
       <c r="A244" s="4" t="s">
         <v>836</v>
       </c>
@@ -19905,7 +19926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="245" ht="14.25" spans="1:19">
+    <row r="245" ht="14.25" hidden="1" spans="1:19">
       <c r="A245" s="4" t="s">
         <v>838</v>
       </c>
@@ -19962,7 +19983,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="246" ht="14.25" spans="1:19">
+    <row r="246" ht="14.25" hidden="1" spans="1:19">
       <c r="A246" s="4" t="s">
         <v>842</v>
       </c>
@@ -20017,7 +20038,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="247" ht="14.25" spans="1:19">
+    <row r="247" ht="14.25" hidden="1" spans="1:19">
       <c r="A247" s="4" t="s">
         <v>846</v>
       </c>
@@ -20072,7 +20093,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" ht="14.25" spans="1:19">
+    <row r="248" ht="14.25" hidden="1" spans="1:19">
       <c r="A248" s="4" t="s">
         <v>849</v>
       </c>
@@ -20127,7 +20148,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" ht="14.25" spans="1:19">
+    <row r="249" ht="14.25" hidden="1" spans="1:19">
       <c r="A249" s="4" t="s">
         <v>851</v>
       </c>
@@ -20182,7 +20203,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" ht="14.25" spans="1:19">
+    <row r="250" ht="14.25" hidden="1" spans="1:19">
       <c r="A250" s="4" t="s">
         <v>853</v>
       </c>
@@ -20237,7 +20258,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" ht="14.25" spans="1:19">
+    <row r="251" ht="14.25" hidden="1" spans="1:19">
       <c r="A251" s="4" t="s">
         <v>855</v>
       </c>
@@ -20294,7 +20315,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="252" ht="14.25" spans="1:19">
+    <row r="252" ht="14.25" hidden="1" spans="1:19">
       <c r="A252" s="4" t="s">
         <v>857</v>
       </c>
@@ -20351,7 +20372,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="253" ht="14.25" spans="1:19">
+    <row r="253" ht="14.25" hidden="1" spans="1:19">
       <c r="A253" s="4" t="s">
         <v>859</v>
       </c>
@@ -20408,7 +20429,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="254" ht="14.25" spans="1:19">
+    <row r="254" ht="14.25" hidden="1" spans="1:19">
       <c r="A254" s="4" t="s">
         <v>861</v>
       </c>
@@ -20465,7 +20486,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="255" ht="14.25" spans="1:19">
+    <row r="255" ht="14.25" hidden="1" spans="1:19">
       <c r="A255" s="4" t="s">
         <v>863</v>
       </c>
@@ -20524,7 +20545,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="256" ht="14.25" spans="1:19">
+    <row r="256" ht="14.25" hidden="1" spans="1:19">
       <c r="A256" s="4" t="s">
         <v>866</v>
       </c>
@@ -20581,7 +20602,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="257" ht="15" spans="1:19">
+    <row r="257" ht="15" hidden="1" spans="1:19">
       <c r="A257" s="4" t="s">
         <v>868</v>
       </c>
@@ -20752,7 +20773,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="260" ht="14.25" spans="1:19">
+    <row r="260" ht="14.25" hidden="1" spans="1:19">
       <c r="A260" s="4" t="s">
         <v>877</v>
       </c>
@@ -20803,7 +20824,7 @@
       <c r="R260" s="7"/>
       <c r="S260" s="7"/>
     </row>
-    <row r="261" ht="14.25" spans="1:19">
+    <row r="261" ht="14.25" hidden="1" spans="1:19">
       <c r="A261" s="4" t="s">
         <v>881</v>
       </c>
@@ -20854,7 +20875,7 @@
       <c r="R261" s="7"/>
       <c r="S261" s="7"/>
     </row>
-    <row r="262" ht="14.25" spans="1:19">
+    <row r="262" ht="14.25" hidden="1" spans="1:19">
       <c r="A262" s="4" t="s">
         <v>886</v>
       </c>
@@ -20905,7 +20926,7 @@
       <c r="R262" s="7"/>
       <c r="S262" s="7"/>
     </row>
-    <row r="263" ht="14.25" spans="1:19">
+    <row r="263" ht="14.25" hidden="1" spans="1:19">
       <c r="A263" s="4" t="s">
         <v>889</v>
       </c>
@@ -20956,7 +20977,7 @@
       <c r="R263" s="7"/>
       <c r="S263" s="7"/>
     </row>
-    <row r="264" ht="14.25" spans="1:19">
+    <row r="264" ht="14.25" hidden="1" spans="1:19">
       <c r="A264" s="4" t="s">
         <v>893</v>
       </c>
@@ -21007,7 +21028,7 @@
       <c r="R264" s="7"/>
       <c r="S264" s="7"/>
     </row>
-    <row r="265" ht="14.25" spans="1:19">
+    <row r="265" ht="14.25" hidden="1" spans="1:19">
       <c r="A265" s="4" t="s">
         <v>896</v>
       </c>
@@ -21058,7 +21079,7 @@
       <c r="R265" s="7"/>
       <c r="S265" s="7"/>
     </row>
-    <row r="266" ht="14.25" spans="1:19">
+    <row r="266" ht="14.25" hidden="1" spans="1:19">
       <c r="A266" s="4" t="s">
         <v>900</v>
       </c>
@@ -21109,7 +21130,7 @@
       <c r="R266" s="7"/>
       <c r="S266" s="7"/>
     </row>
-    <row r="267" ht="14.25" spans="1:19">
+    <row r="267" ht="14.25" hidden="1" spans="1:19">
       <c r="A267" s="4" t="s">
         <v>904</v>
       </c>
@@ -21160,7 +21181,7 @@
       <c r="R267" s="7"/>
       <c r="S267" s="7"/>
     </row>
-    <row r="268" ht="14.25" spans="1:19">
+    <row r="268" ht="14.25" hidden="1" spans="1:19">
       <c r="A268" s="4" t="s">
         <v>907</v>
       </c>
@@ -21211,7 +21232,7 @@
       <c r="R268" s="7"/>
       <c r="S268" s="7"/>
     </row>
-    <row r="269" ht="14.25" spans="1:19">
+    <row r="269" ht="14.25" hidden="1" spans="1:19">
       <c r="A269" s="4" t="s">
         <v>909</v>
       </c>
@@ -21262,7 +21283,7 @@
       <c r="R269" s="7"/>
       <c r="S269" s="7"/>
     </row>
-    <row r="270" ht="14.25" spans="1:19">
+    <row r="270" ht="14.25" hidden="1" spans="1:19">
       <c r="A270" s="4" t="s">
         <v>912</v>
       </c>
@@ -21313,7 +21334,7 @@
       <c r="R270" s="7"/>
       <c r="S270" s="7"/>
     </row>
-    <row r="271" ht="14.25" spans="1:19">
+    <row r="271" ht="14.25" hidden="1" spans="1:19">
       <c r="A271" s="4" t="s">
         <v>914</v>
       </c>
@@ -21366,7 +21387,7 @@
       <c r="R271" s="7"/>
       <c r="S271" s="7"/>
     </row>
-    <row r="272" ht="14.25" spans="1:19">
+    <row r="272" ht="14.25" hidden="1" spans="1:19">
       <c r="A272" s="4" t="s">
         <v>918</v>
       </c>
@@ -21419,7 +21440,7 @@
       <c r="R272" s="7"/>
       <c r="S272" s="7"/>
     </row>
-    <row r="273" ht="14.25" spans="1:19">
+    <row r="273" ht="14.25" hidden="1" spans="1:19">
       <c r="A273" s="4" t="s">
         <v>920</v>
       </c>
@@ -21472,7 +21493,7 @@
       <c r="R273" s="7"/>
       <c r="S273" s="7"/>
     </row>
-    <row r="274" ht="14.25" spans="1:19">
+    <row r="274" ht="14.25" hidden="1" spans="1:19">
       <c r="A274" s="4" t="s">
         <v>923</v>
       </c>
@@ -21523,7 +21544,7 @@
       <c r="R274" s="7"/>
       <c r="S274" s="7"/>
     </row>
-    <row r="275" ht="14.25" spans="1:19">
+    <row r="275" ht="14.25" hidden="1" spans="1:19">
       <c r="A275" s="4" t="s">
         <v>927</v>
       </c>
@@ -21574,7 +21595,7 @@
       <c r="R275" s="7"/>
       <c r="S275" s="7"/>
     </row>
-    <row r="276" ht="14.25" spans="1:19">
+    <row r="276" ht="14.25" hidden="1" spans="1:19">
       <c r="A276" s="4" t="s">
         <v>930</v>
       </c>
@@ -21625,7 +21646,7 @@
       <c r="R276" s="7"/>
       <c r="S276" s="7"/>
     </row>
-    <row r="277" ht="14.25" spans="1:19">
+    <row r="277" ht="14.25" hidden="1" spans="1:19">
       <c r="A277" s="4" t="s">
         <v>932</v>
       </c>
@@ -21676,7 +21697,7 @@
       <c r="R277" s="7"/>
       <c r="S277" s="7"/>
     </row>
-    <row r="278" ht="14.25" spans="1:19">
+    <row r="278" ht="14.25" hidden="1" spans="1:19">
       <c r="A278" s="4" t="s">
         <v>935</v>
       </c>
@@ -21727,7 +21748,7 @@
       <c r="R278" s="7"/>
       <c r="S278" s="7"/>
     </row>
-    <row r="279" ht="14.25" spans="1:19">
+    <row r="279" ht="14.25" hidden="1" spans="1:19">
       <c r="A279" s="4" t="s">
         <v>937</v>
       </c>
@@ -21780,7 +21801,7 @@
       <c r="R279" s="7"/>
       <c r="S279" s="7"/>
     </row>
-    <row r="280" ht="14.25" spans="1:19">
+    <row r="280" ht="14.25" hidden="1" spans="1:19">
       <c r="A280" s="4" t="s">
         <v>940</v>
       </c>
@@ -21833,7 +21854,7 @@
       <c r="R280" s="7"/>
       <c r="S280" s="7"/>
     </row>
-    <row r="281" ht="14.25" spans="1:19">
+    <row r="281" ht="14.25" hidden="1" spans="1:19">
       <c r="A281" s="4" t="s">
         <v>943</v>
       </c>
@@ -21884,7 +21905,7 @@
       <c r="R281" s="7"/>
       <c r="S281" s="7"/>
     </row>
-    <row r="282" ht="14.25" spans="1:19">
+    <row r="282" ht="14.25" hidden="1" spans="1:19">
       <c r="A282" s="4" t="s">
         <v>946</v>
       </c>
@@ -21935,7 +21956,7 @@
       <c r="R282" s="7"/>
       <c r="S282" s="7"/>
     </row>
-    <row r="283" ht="14.25" spans="1:19">
+    <row r="283" ht="14.25" hidden="1" spans="1:19">
       <c r="A283" s="4" t="s">
         <v>950</v>
       </c>
@@ -21986,7 +22007,7 @@
       <c r="R283" s="7"/>
       <c r="S283" s="7"/>
     </row>
-    <row r="284" ht="14.25" spans="1:19">
+    <row r="284" ht="14.25" hidden="1" spans="1:19">
       <c r="A284" s="4" t="s">
         <v>953</v>
       </c>
@@ -22037,7 +22058,7 @@
       <c r="R284" s="7"/>
       <c r="S284" s="7"/>
     </row>
-    <row r="285" ht="14.25" spans="1:19">
+    <row r="285" ht="14.25" hidden="1" spans="1:19">
       <c r="A285" s="4" t="s">
         <v>937</v>
       </c>
@@ -22088,7 +22109,7 @@
       <c r="R285" s="7"/>
       <c r="S285" s="7"/>
     </row>
-    <row r="286" ht="14.25" spans="1:19">
+    <row r="286" ht="14.25" hidden="1" spans="1:19">
       <c r="A286" s="4" t="s">
         <v>940</v>
       </c>
@@ -22139,7 +22160,7 @@
       <c r="R286" s="7"/>
       <c r="S286" s="7"/>
     </row>
-    <row r="287" ht="14.25" spans="1:19">
+    <row r="287" ht="14.25" hidden="1" spans="1:19">
       <c r="A287" s="4" t="s">
         <v>959</v>
       </c>
@@ -22190,7 +22211,7 @@
       <c r="R287" s="7"/>
       <c r="S287" s="7"/>
     </row>
-    <row r="288" ht="14.25" spans="1:19">
+    <row r="288" ht="14.25" hidden="1" spans="1:19">
       <c r="A288" s="4" t="s">
         <v>963</v>
       </c>
@@ -22241,7 +22262,7 @@
       <c r="R288" s="7"/>
       <c r="S288" s="7"/>
     </row>
-    <row r="289" ht="14.25" spans="1:19">
+    <row r="289" ht="14.25" hidden="1" spans="1:19">
       <c r="A289" s="4" t="s">
         <v>965</v>
       </c>
@@ -22292,7 +22313,7 @@
       <c r="R289" s="7"/>
       <c r="S289" s="7"/>
     </row>
-    <row r="290" ht="14.25" spans="1:19">
+    <row r="290" ht="14.25" hidden="1" spans="1:19">
       <c r="A290" s="4" t="s">
         <v>967</v>
       </c>
@@ -22343,7 +22364,7 @@
       <c r="R290" s="7"/>
       <c r="S290" s="7"/>
     </row>
-    <row r="291" ht="14.25" spans="1:19">
+    <row r="291" ht="14.25" hidden="1" spans="1:19">
       <c r="A291" s="4" t="s">
         <v>969</v>
       </c>
@@ -22394,7 +22415,7 @@
       <c r="R291" s="7"/>
       <c r="S291" s="7"/>
     </row>
-    <row r="292" ht="27" spans="1:19">
+    <row r="292" ht="27" hidden="1" spans="1:19">
       <c r="A292" s="4" t="s">
         <v>973</v>
       </c>
@@ -22445,7 +22466,7 @@
       <c r="R292" s="7"/>
       <c r="S292" s="7"/>
     </row>
-    <row r="293" ht="14.25" spans="1:19">
+    <row r="293" ht="14.25" hidden="1" spans="1:19">
       <c r="A293" s="4" t="s">
         <v>977</v>
       </c>
@@ -22496,7 +22517,7 @@
       <c r="R293" s="7"/>
       <c r="S293" s="7"/>
     </row>
-    <row r="294" ht="14.25" spans="1:19">
+    <row r="294" ht="14.25" hidden="1" spans="1:19">
       <c r="A294" s="4" t="s">
         <v>981</v>
       </c>
@@ -22547,7 +22568,7 @@
       <c r="R294" s="7"/>
       <c r="S294" s="7"/>
     </row>
-    <row r="295" ht="14.25" spans="1:19">
+    <row r="295" ht="14.25" hidden="1" spans="1:19">
       <c r="A295" s="4" t="s">
         <v>984</v>
       </c>
@@ -22598,7 +22619,7 @@
       <c r="R295" s="7"/>
       <c r="S295" s="7"/>
     </row>
-    <row r="296" ht="14.25" spans="1:19">
+    <row r="296" ht="14.25" hidden="1" spans="1:19">
       <c r="A296" s="4" t="s">
         <v>987</v>
       </c>
@@ -22649,7 +22670,7 @@
       <c r="R296" s="7"/>
       <c r="S296" s="7"/>
     </row>
-    <row r="297" ht="14.25" spans="1:19">
+    <row r="297" ht="14.25" hidden="1" spans="1:19">
       <c r="A297" s="4" t="s">
         <v>990</v>
       </c>
@@ -22700,7 +22721,7 @@
       <c r="R297" s="7"/>
       <c r="S297" s="7"/>
     </row>
-    <row r="298" ht="14.25" spans="1:19">
+    <row r="298" ht="14.25" hidden="1" spans="1:19">
       <c r="A298" s="4" t="s">
         <v>992</v>
       </c>
@@ -22751,7 +22772,7 @@
       <c r="R298" s="7"/>
       <c r="S298" s="7"/>
     </row>
-    <row r="299" ht="14.25" spans="1:19">
+    <row r="299" ht="14.25" hidden="1" spans="1:19">
       <c r="A299" s="4" t="s">
         <v>996</v>
       </c>
@@ -22802,7 +22823,7 @@
       <c r="R299" s="7"/>
       <c r="S299" s="7"/>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" hidden="1" spans="1:19">
       <c r="A300" s="4" t="s">
         <v>999</v>
       </c>
@@ -22908,7 +22929,7 @@
       <c r="R301" s="7"/>
       <c r="S301" s="7"/>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" hidden="1" spans="1:19">
       <c r="A302" s="4" t="s">
         <v>1008</v>
       </c>
@@ -22961,7 +22982,7 @@
       <c r="R302" s="7"/>
       <c r="S302" s="7"/>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" hidden="1" spans="1:19">
       <c r="A303" s="4" t="s">
         <v>1011</v>
       </c>
@@ -23014,7 +23035,7 @@
       <c r="R303" s="7"/>
       <c r="S303" s="7"/>
     </row>
-    <row r="304" ht="14.25" spans="1:19">
+    <row r="304" ht="14.25" hidden="1" spans="1:19">
       <c r="A304" s="4" t="s">
         <v>1014</v>
       </c>
@@ -23067,7 +23088,7 @@
       <c r="R304" s="7"/>
       <c r="S304" s="7"/>
     </row>
-    <row r="305" ht="27.75" spans="1:19">
+    <row r="305" ht="27.75" hidden="1" spans="1:19">
       <c r="A305" s="4" t="s">
         <v>1017</v>
       </c>
@@ -23120,7 +23141,7 @@
       <c r="R305" s="7"/>
       <c r="S305" s="7"/>
     </row>
-    <row r="306" ht="27" spans="1:19">
+    <row r="306" ht="27" hidden="1" spans="1:19">
       <c r="A306" s="4" t="s">
         <v>1021</v>
       </c>
@@ -23173,7 +23194,7 @@
       <c r="R306" s="7"/>
       <c r="S306" s="7"/>
     </row>
-    <row r="307" spans="1:19">
+    <row r="307" hidden="1" spans="1:19">
       <c r="A307" s="4" t="s">
         <v>1024</v>
       </c>
@@ -23226,7 +23247,7 @@
       <c r="R307" s="7"/>
       <c r="S307" s="7"/>
     </row>
-    <row r="308" spans="1:19">
+    <row r="308" hidden="1" spans="1:19">
       <c r="A308" s="4" t="s">
         <v>1028</v>
       </c>
@@ -23281,7 +23302,7 @@
       <c r="R308" s="7"/>
       <c r="S308" s="7"/>
     </row>
-    <row r="309" spans="1:19">
+    <row r="309" hidden="1" spans="1:19">
       <c r="A309" s="4" t="s">
         <v>1032</v>
       </c>
@@ -23336,7 +23357,7 @@
       <c r="R309" s="7"/>
       <c r="S309" s="7"/>
     </row>
-    <row r="310" spans="1:19">
+    <row r="310" hidden="1" spans="1:19">
       <c r="A310" s="4" t="s">
         <v>1035</v>
       </c>
@@ -23389,7 +23410,7 @@
       <c r="R310" s="7"/>
       <c r="S310" s="7"/>
     </row>
-    <row r="311" ht="27" spans="1:19">
+    <row r="311" ht="27" hidden="1" spans="1:19">
       <c r="A311" s="4" t="s">
         <v>1038</v>
       </c>
@@ -23442,7 +23463,7 @@
       <c r="R311" s="7"/>
       <c r="S311" s="7"/>
     </row>
-    <row r="312" ht="27" spans="1:19">
+    <row r="312" ht="27" hidden="1" spans="1:19">
       <c r="A312" s="4" t="s">
         <v>1042</v>
       </c>
@@ -23495,7 +23516,7 @@
       <c r="R312" s="7"/>
       <c r="S312" s="7"/>
     </row>
-    <row r="313" ht="27" spans="1:19">
+    <row r="313" ht="27" hidden="1" spans="1:19">
       <c r="A313" s="4" t="s">
         <v>1046</v>
       </c>
@@ -23548,7 +23569,7 @@
       <c r="R313" s="7"/>
       <c r="S313" s="7"/>
     </row>
-    <row r="314" spans="1:19">
+    <row r="314" hidden="1" spans="1:19">
       <c r="A314" s="4" t="s">
         <v>1050</v>
       </c>
@@ -23601,7 +23622,7 @@
       <c r="R314" s="7"/>
       <c r="S314" s="7"/>
     </row>
-    <row r="315" spans="1:19">
+    <row r="315" hidden="1" spans="1:19">
       <c r="A315" s="4" t="s">
         <v>1054</v>
       </c>
@@ -23654,7 +23675,7 @@
       <c r="R315" s="7"/>
       <c r="S315" s="7"/>
     </row>
-    <row r="316" spans="1:19">
+    <row r="316" hidden="1" spans="1:19">
       <c r="A316" s="4" t="s">
         <v>1058</v>
       </c>
@@ -23707,7 +23728,7 @@
       <c r="R316" s="7"/>
       <c r="S316" s="7"/>
     </row>
-    <row r="317" spans="1:19">
+    <row r="317" hidden="1" spans="1:19">
       <c r="A317" s="4" t="s">
         <v>1062</v>
       </c>
@@ -23756,7 +23777,7 @@
       <c r="R317" s="7"/>
       <c r="S317" s="7"/>
     </row>
-    <row r="318" spans="1:19">
+    <row r="318" hidden="1" spans="1:19">
       <c r="A318" s="4" t="s">
         <v>1065</v>
       </c>
@@ -23805,7 +23826,7 @@
       <c r="R318" s="7"/>
       <c r="S318" s="7"/>
     </row>
-    <row r="319" spans="1:15">
+    <row r="319" hidden="1" spans="1:15">
       <c r="A319" s="4" t="s">
         <v>1067</v>
       </c>
@@ -23850,7 +23871,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="320" spans="1:15">
+    <row r="320" hidden="1" spans="1:15">
       <c r="A320" s="4" t="s">
         <v>1072</v>
       </c>
@@ -23895,7 +23916,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="321" spans="1:15">
+    <row r="321" hidden="1" spans="1:15">
       <c r="A321" s="4" t="s">
         <v>1075</v>
       </c>
@@ -23940,7 +23961,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="322" spans="1:15">
+    <row r="322" hidden="1" spans="1:15">
       <c r="A322" s="4" t="s">
         <v>1077</v>
       </c>
@@ -23985,7 +24006,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="323" spans="1:15">
+    <row r="323" hidden="1" spans="1:15">
       <c r="A323" s="4" t="s">
         <v>1080</v>
       </c>
@@ -24030,7 +24051,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="324" spans="1:15">
+    <row r="324" hidden="1" spans="1:15">
       <c r="A324" s="4" t="s">
         <v>1083</v>
       </c>
@@ -24075,7 +24096,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="325" spans="1:15">
+    <row r="325" hidden="1" spans="1:15">
       <c r="A325" s="4" t="s">
         <v>1086</v>
       </c>
@@ -24120,7 +24141,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="326" spans="1:15">
+    <row r="326" hidden="1" spans="1:15">
       <c r="A326" s="4" t="s">
         <v>1088</v>
       </c>
@@ -24165,7 +24186,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="327" spans="1:15">
+    <row r="327" hidden="1" spans="1:15">
       <c r="A327" s="4" t="s">
         <v>1091</v>
       </c>
@@ -24210,7 +24231,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="328" spans="1:15">
+    <row r="328" hidden="1" spans="1:15">
       <c r="A328" s="4" t="s">
         <v>1093</v>
       </c>
@@ -24255,7 +24276,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="329" spans="1:15">
+    <row r="329" hidden="1" spans="1:15">
       <c r="A329" s="4" t="s">
         <v>1095</v>
       </c>
@@ -24300,7 +24321,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="330" spans="1:15">
+    <row r="330" hidden="1" spans="1:15">
       <c r="A330" s="4" t="s">
         <v>1098</v>
       </c>
@@ -24345,7 +24366,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="331" spans="1:15">
+    <row r="331" hidden="1" spans="1:15">
       <c r="A331" s="4" t="s">
         <v>1100</v>
       </c>
@@ -24390,7 +24411,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="332" spans="1:15">
+    <row r="332" hidden="1" spans="1:15">
       <c r="A332" s="4" t="s">
         <v>1102</v>
       </c>
@@ -24435,7 +24456,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="333" spans="1:15">
+    <row r="333" hidden="1" spans="1:15">
       <c r="A333" s="4" t="s">
         <v>1104</v>
       </c>
@@ -24480,7 +24501,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="334" spans="1:15">
+    <row r="334" hidden="1" spans="1:15">
       <c r="A334" s="4" t="s">
         <v>1106</v>
       </c>
@@ -24525,7 +24546,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="335" spans="1:15">
+    <row r="335" hidden="1" spans="1:15">
       <c r="A335" s="4" t="s">
         <v>1109</v>
       </c>
@@ -24570,7 +24591,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="336" spans="1:15">
+    <row r="336" hidden="1" spans="1:15">
       <c r="A336" s="4" t="s">
         <v>1111</v>
       </c>
@@ -24615,7 +24636,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" hidden="1" spans="1:15">
       <c r="A337" s="4" t="s">
         <v>1113</v>
       </c>
@@ -24660,7 +24681,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="338" spans="1:15">
+    <row r="338" hidden="1" spans="1:15">
       <c r="A338" s="4" t="s">
         <v>1116</v>
       </c>
@@ -24705,7 +24726,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="339" ht="14.25" spans="1:15">
+    <row r="339" ht="14.25" hidden="1" spans="1:15">
       <c r="A339" s="4" t="s">
         <v>1118</v>
       </c>
@@ -24750,7 +24771,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="340" ht="14.25" spans="1:15">
+    <row r="340" ht="14.25" hidden="1" spans="1:15">
       <c r="A340" s="4" t="s">
         <v>1120</v>
       </c>
@@ -24795,7 +24816,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="341" spans="1:15">
+    <row r="341" hidden="1" spans="1:15">
       <c r="A341" s="4" t="s">
         <v>1122</v>
       </c>
@@ -24840,7 +24861,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="342" spans="1:15">
+    <row r="342" hidden="1" spans="1:15">
       <c r="A342" s="4" t="s">
         <v>1126</v>
       </c>
@@ -24975,7 +24996,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="345" spans="1:15">
+    <row r="345" hidden="1" spans="1:15">
       <c r="A345" s="4" t="s">
         <v>1132</v>
       </c>
@@ -25020,7 +25041,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="346" spans="1:15">
+    <row r="346" hidden="1" spans="1:15">
       <c r="A346" s="4" t="s">
         <v>1135</v>
       </c>
@@ -25065,7 +25086,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="347" spans="1:15">
+    <row r="347" hidden="1" spans="1:15">
       <c r="A347" s="4" t="s">
         <v>1137</v>
       </c>
@@ -25110,7 +25131,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="348" spans="1:15">
+    <row r="348" hidden="1" spans="1:15">
       <c r="A348" s="4" t="s">
         <v>1139</v>
       </c>
@@ -25155,7 +25176,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="349" spans="1:15">
+    <row r="349" hidden="1" spans="1:15">
       <c r="A349" s="4" t="s">
         <v>1141</v>
       </c>
@@ -25200,7 +25221,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="350" spans="1:15">
+    <row r="350" hidden="1" spans="1:15">
       <c r="A350" s="4" t="s">
         <v>1143</v>
       </c>
@@ -25245,7 +25266,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="351" spans="1:15">
+    <row r="351" hidden="1" spans="1:15">
       <c r="A351" s="4" t="s">
         <v>1145</v>
       </c>
@@ -25290,7 +25311,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="352" spans="1:15">
+    <row r="352" hidden="1" spans="1:15">
       <c r="A352" s="4" t="s">
         <v>1147</v>
       </c>
@@ -25335,7 +25356,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="353" spans="1:15">
+    <row r="353" hidden="1" spans="1:15">
       <c r="A353" s="4" t="s">
         <v>1149</v>
       </c>
@@ -25380,7 +25401,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="354" spans="1:15">
+    <row r="354" hidden="1" spans="1:15">
       <c r="A354" s="4" t="s">
         <v>1151</v>
       </c>
@@ -25425,7 +25446,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" hidden="1" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>1154</v>
       </c>
@@ -25473,7 +25494,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="356" spans="1:15">
+    <row r="356" hidden="1" spans="1:15">
       <c r="A356" s="4" t="s">
         <v>1157</v>
       </c>
@@ -25518,7 +25539,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="357" spans="1:15">
+    <row r="357" hidden="1" spans="1:15">
       <c r="A357" s="4" t="s">
         <v>1159</v>
       </c>
@@ -25563,7 +25584,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="358" spans="1:15">
+    <row r="358" hidden="1" spans="1:15">
       <c r="A358" s="4" t="s">
         <v>1161</v>
       </c>
@@ -25608,7 +25629,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="359" spans="1:15">
+    <row r="359" hidden="1" spans="1:15">
       <c r="A359" s="4" t="s">
         <v>1163</v>
       </c>
@@ -25653,7 +25674,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="360" spans="1:15">
+    <row r="360" hidden="1" spans="1:15">
       <c r="A360" s="4" t="s">
         <v>1165</v>
       </c>
@@ -25698,7 +25719,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="361" spans="1:15">
+    <row r="361" hidden="1" spans="1:15">
       <c r="A361" s="4" t="s">
         <v>1168</v>
       </c>
@@ -25743,7 +25764,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="362" spans="1:15">
+    <row r="362" hidden="1" spans="1:15">
       <c r="A362" s="4" t="s">
         <v>1170</v>
       </c>
@@ -25788,7 +25809,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="363" spans="1:15">
+    <row r="363" hidden="1" spans="1:15">
       <c r="A363" s="4" t="s">
         <v>1172</v>
       </c>
@@ -25833,7 +25854,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="364" spans="1:15">
+    <row r="364" hidden="1" spans="1:15">
       <c r="A364" s="4" t="s">
         <v>1174</v>
       </c>
@@ -25878,7 +25899,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="365" spans="1:15">
+    <row r="365" hidden="1" spans="1:15">
       <c r="A365" s="4" t="s">
         <v>1176</v>
       </c>
@@ -25923,7 +25944,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="366" spans="1:15">
+    <row r="366" hidden="1" spans="1:15">
       <c r="A366" s="4" t="s">
         <v>1178</v>
       </c>
@@ -25968,7 +25989,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="367" spans="1:15">
+    <row r="367" hidden="1" spans="1:15">
       <c r="A367" s="4" t="s">
         <v>1180</v>
       </c>
@@ -26013,7 +26034,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="368" spans="1:15">
+    <row r="368" hidden="1" spans="1:15">
       <c r="A368" s="4" t="s">
         <v>1183</v>
       </c>
@@ -26058,7 +26079,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="369" spans="1:15">
+    <row r="369" hidden="1" spans="1:15">
       <c r="A369" s="4" t="s">
         <v>1185</v>
       </c>
@@ -26103,7 +26124,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="370" spans="1:15">
+    <row r="370" hidden="1" spans="1:15">
       <c r="A370" s="4" t="s">
         <v>1188</v>
       </c>
@@ -26148,7 +26169,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="371" ht="14.25" spans="1:15">
+    <row r="371" ht="14.25" hidden="1" spans="1:15">
       <c r="A371" s="4" t="s">
         <v>1190</v>
       </c>
@@ -26193,7 +26214,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="372" ht="14.25" spans="1:15">
+    <row r="372" ht="14.25" hidden="1" spans="1:15">
       <c r="A372" s="4" t="s">
         <v>1193</v>
       </c>
@@ -26238,7 +26259,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="373" ht="14.25" spans="1:15">
+    <row r="373" ht="14.25" hidden="1" spans="1:15">
       <c r="A373" s="4" t="s">
         <v>1195</v>
       </c>
@@ -26283,7 +26304,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="374" ht="14.25" spans="1:15">
+    <row r="374" ht="14.25" hidden="1" spans="1:15">
       <c r="A374" s="4" t="s">
         <v>1197</v>
       </c>
@@ -26328,7 +26349,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="375" spans="1:15">
+    <row r="375" hidden="1" spans="1:15">
       <c r="A375" s="4" t="s">
         <v>1199</v>
       </c>
@@ -26373,7 +26394,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="376" spans="1:15">
+    <row r="376" hidden="1" spans="1:15">
       <c r="A376" s="4" t="s">
         <v>1201</v>
       </c>
@@ -26418,7 +26439,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="377" spans="1:15">
+    <row r="377" hidden="1" spans="1:15">
       <c r="A377" s="4" t="s">
         <v>1203</v>
       </c>
@@ -26463,7 +26484,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="378" spans="1:15">
+    <row r="378" hidden="1" spans="1:15">
       <c r="A378" s="4" t="s">
         <v>1205</v>
       </c>
@@ -26508,7 +26529,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="379" spans="1:15">
+    <row r="379" hidden="1" spans="1:15">
       <c r="A379" s="4" t="s">
         <v>1207</v>
       </c>
@@ -26553,7 +26574,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="380" spans="1:15">
+    <row r="380" hidden="1" spans="1:15">
       <c r="A380" s="4" t="s">
         <v>1210</v>
       </c>
@@ -26598,7 +26619,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="381" spans="1:15">
+    <row r="381" hidden="1" spans="1:15">
       <c r="A381" s="4" t="s">
         <v>1212</v>
       </c>
@@ -26643,7 +26664,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="382" spans="1:15">
+    <row r="382" hidden="1" spans="1:15">
       <c r="A382" s="4" t="s">
         <v>1215</v>
       </c>
@@ -26688,7 +26709,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="383" spans="1:15">
+    <row r="383" hidden="1" spans="1:15">
       <c r="A383" s="4" t="s">
         <v>1217</v>
       </c>
@@ -26733,7 +26754,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="384" spans="1:15">
+    <row r="384" hidden="1" spans="1:15">
       <c r="A384" s="4" t="s">
         <v>1219</v>
       </c>
@@ -26778,7 +26799,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="385" spans="1:15">
+    <row r="385" hidden="1" spans="1:15">
       <c r="A385" s="4" t="s">
         <v>1221</v>
       </c>
@@ -26823,7 +26844,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="386" spans="1:15">
+    <row r="386" hidden="1" spans="1:15">
       <c r="A386" s="4" t="s">
         <v>1224</v>
       </c>
@@ -26868,7 +26889,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="387" spans="1:15">
+    <row r="387" hidden="1" spans="1:15">
       <c r="A387" s="4" t="s">
         <v>1225</v>
       </c>
@@ -26913,7 +26934,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="388" spans="1:15">
+    <row r="388" hidden="1" spans="1:15">
       <c r="A388" s="4" t="s">
         <v>1228</v>
       </c>
@@ -26958,7 +26979,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="389" spans="1:15">
+    <row r="389" hidden="1" spans="1:15">
       <c r="A389" s="4" t="s">
         <v>1231</v>
       </c>
@@ -27003,7 +27024,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="390" spans="1:15">
+    <row r="390" hidden="1" spans="1:15">
       <c r="A390" s="4" t="s">
         <v>1234</v>
       </c>
@@ -27046,7 +27067,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="391" spans="1:15">
+    <row r="391" hidden="1" spans="1:15">
       <c r="A391" s="4" t="s">
         <v>1237</v>
       </c>
@@ -27089,7 +27110,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="392" spans="1:15">
+    <row r="392" hidden="1" spans="1:15">
       <c r="A392" s="4" t="s">
         <v>1240</v>
       </c>
@@ -27132,7 +27153,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="393" spans="1:15">
+    <row r="393" hidden="1" spans="1:15">
       <c r="A393" s="4" t="s">
         <v>1243</v>
       </c>
@@ -27175,7 +27196,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" spans="1:15">
+    <row r="394" hidden="1" spans="1:15">
       <c r="A394" s="4" t="s">
         <v>1246</v>
       </c>
@@ -27218,7 +27239,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="395" spans="1:15">
+    <row r="395" hidden="1" spans="1:15">
       <c r="A395" s="4" t="s">
         <v>1248</v>
       </c>
@@ -27261,7 +27282,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="396" spans="1:15">
+    <row r="396" hidden="1" spans="1:15">
       <c r="A396" s="4" t="s">
         <v>1250</v>
       </c>
@@ -27304,7 +27325,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="397" spans="1:15">
+    <row r="397" hidden="1" spans="1:15">
       <c r="A397" s="4" t="s">
         <v>1253</v>
       </c>
@@ -27347,7 +27368,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="398" spans="1:15">
+    <row r="398" hidden="1" spans="1:15">
       <c r="A398" s="4" t="s">
         <v>1255</v>
       </c>
@@ -27390,7 +27411,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="399" spans="1:15">
+    <row r="399" hidden="1" spans="1:15">
       <c r="A399" s="4" t="s">
         <v>1258</v>
       </c>
@@ -27433,7 +27454,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="400" spans="1:15">
+    <row r="400" hidden="1" spans="1:15">
       <c r="A400" s="4" t="s">
         <v>1260</v>
       </c>
@@ -27476,7 +27497,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="401" spans="1:15">
+    <row r="401" hidden="1" spans="1:15">
       <c r="A401" s="4" t="s">
         <v>1262</v>
       </c>
@@ -27519,7 +27540,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="402" spans="1:15">
+    <row r="402" hidden="1" spans="1:15">
       <c r="A402" s="4" t="s">
         <v>1264</v>
       </c>
@@ -27562,7 +27583,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="403" spans="1:15">
+    <row r="403" hidden="1" spans="1:15">
       <c r="A403" s="4" t="s">
         <v>1266</v>
       </c>
@@ -27605,7 +27626,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="404" spans="1:15">
+    <row r="404" hidden="1" spans="1:15">
       <c r="A404" s="4" t="s">
         <v>1268</v>
       </c>
@@ -27648,7 +27669,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="405" spans="1:15">
+    <row r="405" hidden="1" spans="1:15">
       <c r="A405" s="4" t="s">
         <v>1270</v>
       </c>
@@ -27691,7 +27712,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="406" spans="1:15">
+    <row r="406" hidden="1" spans="1:15">
       <c r="A406" s="4" t="s">
         <v>1273</v>
       </c>
@@ -27734,7 +27755,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="407" spans="1:15">
+    <row r="407" hidden="1" spans="1:15">
       <c r="A407" s="4" t="s">
         <v>1275</v>
       </c>
@@ -27777,7 +27798,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="408" spans="1:15">
+    <row r="408" hidden="1" spans="1:15">
       <c r="A408" s="4" t="s">
         <v>1278</v>
       </c>
@@ -27820,7 +27841,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="409" spans="1:15">
+    <row r="409" hidden="1" spans="1:15">
       <c r="A409" s="4" t="s">
         <v>1280</v>
       </c>
@@ -27863,7 +27884,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" hidden="1" spans="1:15">
       <c r="A410" s="4" t="s">
         <v>1282</v>
       </c>
@@ -27906,7 +27927,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="411" spans="1:15">
+    <row r="411" hidden="1" spans="1:15">
       <c r="A411" s="4" t="s">
         <v>1285</v>
       </c>
@@ -27949,7 +27970,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="412" spans="1:15">
+    <row r="412" hidden="1" spans="1:15">
       <c r="A412" s="4" t="s">
         <v>1287</v>
       </c>
@@ -27992,7 +28013,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="413" spans="1:15">
+    <row r="413" hidden="1" spans="1:15">
       <c r="A413" s="4" t="s">
         <v>1289</v>
       </c>
@@ -28035,7 +28056,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" spans="1:15">
+    <row r="414" hidden="1" spans="1:15">
       <c r="A414" s="4" t="s">
         <v>1291</v>
       </c>
@@ -28078,7 +28099,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="415" spans="1:15">
+    <row r="415" hidden="1" spans="1:15">
       <c r="A415" s="4" t="s">
         <v>1293</v>
       </c>
@@ -28121,7 +28142,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="416" spans="1:15">
+    <row r="416" hidden="1" spans="1:15">
       <c r="A416" s="4" t="s">
         <v>1296</v>
       </c>
@@ -28164,7 +28185,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="417" spans="1:15">
+    <row r="417" hidden="1" spans="1:15">
       <c r="A417" s="4" t="s">
         <v>1298</v>
       </c>
@@ -28207,7 +28228,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="418" spans="1:15">
+    <row r="418" hidden="1" spans="1:15">
       <c r="A418" s="4" t="s">
         <v>1300</v>
       </c>
@@ -28250,7 +28271,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="419" spans="1:15">
+    <row r="419" hidden="1" spans="1:15">
       <c r="A419" s="4" t="s">
         <v>1302</v>
       </c>
@@ -28293,7 +28314,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="420" spans="1:15">
+    <row r="420" hidden="1" spans="1:15">
       <c r="A420" s="4" t="s">
         <v>1305</v>
       </c>
@@ -28336,7 +28357,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="421" spans="1:15">
+    <row r="421" hidden="1" spans="1:15">
       <c r="A421" s="4" t="s">
         <v>1307</v>
       </c>
@@ -28379,7 +28400,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" hidden="1" spans="1:15">
       <c r="A422" s="4" t="s">
         <v>1309</v>
       </c>
@@ -28422,7 +28443,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" hidden="1" spans="1:15">
       <c r="A423" s="4" t="s">
         <v>1311</v>
       </c>
@@ -28465,7 +28486,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" hidden="1" spans="1:15">
       <c r="A424" s="4" t="s">
         <v>1313</v>
       </c>
@@ -28508,7 +28529,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" hidden="1" spans="1:15">
       <c r="A425" s="4" t="s">
         <v>1315</v>
       </c>
@@ -28551,7 +28572,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" hidden="1" spans="1:15">
       <c r="A426" s="4" t="s">
         <v>1317</v>
       </c>
@@ -28594,7 +28615,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" hidden="1" spans="1:15">
       <c r="A427" s="4" t="s">
         <v>1319</v>
       </c>
@@ -28637,7 +28658,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" hidden="1" spans="1:15">
       <c r="A428" s="4" t="s">
         <v>1322</v>
       </c>
@@ -28680,7 +28701,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" hidden="1" spans="1:15">
       <c r="A429" s="4" t="s">
         <v>1324</v>
       </c>
@@ -28723,7 +28744,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" hidden="1" spans="1:15">
       <c r="A430" s="4" t="s">
         <v>1326</v>
       </c>
@@ -28766,7 +28787,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" hidden="1" spans="1:15">
       <c r="A431" s="4" t="s">
         <v>1329</v>
       </c>
@@ -28809,7 +28830,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" hidden="1" spans="1:15">
       <c r="A432" s="4" t="s">
         <v>1331</v>
       </c>
@@ -28852,7 +28873,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" hidden="1" spans="1:15">
       <c r="A433" s="4" t="s">
         <v>1333</v>
       </c>
@@ -28895,7 +28916,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" hidden="1" spans="1:15">
       <c r="A434" s="4" t="s">
         <v>1336</v>
       </c>
@@ -28938,7 +28959,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" hidden="1" spans="1:15">
       <c r="A435" s="4" t="s">
         <v>1339</v>
       </c>
@@ -28981,7 +29002,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" hidden="1" spans="1:15">
       <c r="A436" s="4" t="s">
         <v>1341</v>
       </c>
@@ -29024,7 +29045,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" hidden="1" spans="1:15">
       <c r="A437" s="4" t="s">
         <v>1343</v>
       </c>
@@ -29067,7 +29088,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" hidden="1" spans="1:15">
       <c r="A438" s="4" t="s">
         <v>1345</v>
       </c>
@@ -29110,7 +29131,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="439" ht="14.25" spans="1:15">
+    <row r="439" ht="14.25" hidden="1" spans="1:15">
       <c r="A439" s="4" t="s">
         <v>1347</v>
       </c>
@@ -29153,7 +29174,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="440" ht="14.25" spans="1:15">
+    <row r="440" ht="14.25" hidden="1" spans="1:15">
       <c r="A440" s="4" t="s">
         <v>1349</v>
       </c>
@@ -29196,7 +29217,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" hidden="1" spans="1:15">
       <c r="A441" s="4" t="s">
         <v>1351</v>
       </c>
@@ -29239,7 +29260,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="442" ht="18" spans="1:17">
+    <row r="442" ht="18" hidden="1" spans="1:17">
       <c r="A442" s="4" t="s">
         <v>1354</v>
       </c>
@@ -29286,7 +29307,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="443" ht="18" spans="1:17">
+    <row r="443" ht="18" hidden="1" spans="1:17">
       <c r="A443" s="4" t="s">
         <v>1359</v>
       </c>
@@ -29333,7 +29354,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="444" ht="17.25" spans="1:17">
+    <row r="444" ht="17.25" hidden="1" spans="1:17">
       <c r="A444" s="4" t="s">
         <v>1363</v>
       </c>
@@ -29380,7 +29401,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="445" ht="17.25" spans="1:17">
+    <row r="445" ht="17.25" hidden="1" spans="1:17">
       <c r="A445" s="4" t="s">
         <v>1368</v>
       </c>
@@ -29427,7 +29448,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="446" ht="17.25" spans="1:17">
+    <row r="446" ht="17.25" hidden="1" spans="1:17">
       <c r="A446" s="4" t="s">
         <v>1372</v>
       </c>
@@ -29474,7 +29495,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="447" ht="17.25" spans="1:17">
+    <row r="447" ht="17.25" hidden="1" spans="1:17">
       <c r="A447" s="4" t="s">
         <v>1377</v>
       </c>
@@ -29521,7 +29542,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="448" ht="17.25" spans="1:17">
+    <row r="448" ht="17.25" hidden="1" spans="1:17">
       <c r="A448" s="4" t="s">
         <v>1381</v>
       </c>
@@ -29571,7 +29592,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="449" ht="18" spans="1:17">
+    <row r="449" ht="18" hidden="1" spans="1:17">
       <c r="A449" s="4" t="s">
         <v>1384</v>
       </c>
@@ -29621,7 +29642,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="450" ht="18" spans="1:17">
+    <row r="450" ht="18" hidden="1" spans="1:17">
       <c r="A450" s="4" t="s">
         <v>1387</v>
       </c>
@@ -29671,7 +29692,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="451" ht="17.25" spans="1:17">
+    <row r="451" ht="17.25" hidden="1" spans="1:17">
       <c r="A451" s="4" t="s">
         <v>1391</v>
       </c>
@@ -29721,7 +29742,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="452" ht="17.25" spans="1:17">
+    <row r="452" ht="17.25" hidden="1" spans="1:17">
       <c r="A452" s="4" t="s">
         <v>1394</v>
       </c>
@@ -29771,7 +29792,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="453" ht="17.25" spans="1:17">
+    <row r="453" ht="17.25" hidden="1" spans="1:17">
       <c r="A453" s="4" t="s">
         <v>1398</v>
       </c>
@@ -29821,7 +29842,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="454" ht="17.25" spans="1:17">
+    <row r="454" ht="17.25" hidden="1" spans="1:17">
       <c r="A454" s="4" t="s">
         <v>1402</v>
       </c>
@@ -29868,7 +29889,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="455" ht="17.25" spans="1:17">
+    <row r="455" ht="17.25" hidden="1" spans="1:17">
       <c r="A455" s="4" t="s">
         <v>1405</v>
       </c>
@@ -29918,7 +29939,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="456" ht="18" spans="1:17">
+    <row r="456" ht="18" hidden="1" spans="1:17">
       <c r="A456" s="4" t="s">
         <v>1409</v>
       </c>
@@ -29968,7 +29989,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="457" ht="18" spans="1:17">
+    <row r="457" ht="18" hidden="1" spans="1:17">
       <c r="A457" s="4" t="s">
         <v>1412</v>
       </c>
@@ -30018,7 +30039,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="458" ht="17.25" spans="1:17">
+    <row r="458" ht="17.25" hidden="1" spans="1:17">
       <c r="A458" s="4" t="s">
         <v>1416</v>
       </c>
@@ -30065,7 +30086,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="459" ht="17.25" spans="1:17">
+    <row r="459" ht="17.25" hidden="1" spans="1:17">
       <c r="A459" s="4" t="s">
         <v>1420</v>
       </c>
@@ -30115,7 +30136,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="460" ht="17.25" spans="1:17">
+    <row r="460" ht="17.25" hidden="1" spans="1:17">
       <c r="A460" s="4" t="s">
         <v>1424</v>
       </c>
@@ -30165,7 +30186,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="461" ht="17.25" spans="1:17">
+    <row r="461" ht="17.25" hidden="1" spans="1:17">
       <c r="A461" s="4" t="s">
         <v>1428</v>
       </c>
@@ -30215,7 +30236,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="462" ht="17.25" spans="1:17">
+    <row r="462" ht="17.25" hidden="1" spans="1:17">
       <c r="A462" s="4" t="s">
         <v>1431</v>
       </c>
@@ -30265,7 +30286,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="463" ht="17.25" spans="1:17">
+    <row r="463" ht="17.25" hidden="1" spans="1:17">
       <c r="A463" s="4" t="s">
         <v>1435</v>
       </c>
@@ -30315,7 +30336,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="464" ht="17.25" spans="1:17">
+    <row r="464" ht="17.25" hidden="1" spans="1:17">
       <c r="A464" s="4" t="s">
         <v>1439</v>
       </c>
@@ -30365,7 +30386,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="465" ht="17.25" spans="1:17">
+    <row r="465" ht="17.25" hidden="1" spans="1:17">
       <c r="A465" s="4" t="s">
         <v>1443</v>
       </c>
@@ -30415,7 +30436,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="466" ht="17.25" spans="1:17">
+    <row r="466" ht="17.25" hidden="1" spans="1:17">
       <c r="A466" s="4" t="s">
         <v>1446</v>
       </c>
@@ -30465,7 +30486,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="467" ht="17.25" spans="1:17">
+    <row r="467" ht="17.25" hidden="1" spans="1:17">
       <c r="A467" s="4" t="s">
         <v>1451</v>
       </c>
@@ -30518,7 +30539,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="468" ht="17.25" spans="1:17">
+    <row r="468" ht="17.25" hidden="1" spans="1:17">
       <c r="A468" s="4" t="s">
         <v>1455</v>
       </c>
@@ -30568,7 +30589,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="469" ht="17.25" spans="1:17">
+    <row r="469" ht="17.25" hidden="1" spans="1:17">
       <c r="A469" s="4" t="s">
         <v>1459</v>
       </c>
@@ -30618,7 +30639,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="470" ht="17.25" spans="1:17">
+    <row r="470" ht="17.25" hidden="1" spans="1:17">
       <c r="A470" s="4" t="s">
         <v>1463</v>
       </c>
@@ -30668,7 +30689,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="471" ht="17.25" spans="1:17">
+    <row r="471" ht="17.25" hidden="1" spans="1:17">
       <c r="A471" s="4" t="s">
         <v>1468</v>
       </c>
@@ -30718,7 +30739,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="472" ht="17.25" spans="1:17">
+    <row r="472" ht="17.25" hidden="1" spans="1:17">
       <c r="A472" s="4" t="s">
         <v>1472</v>
       </c>
@@ -30771,7 +30792,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="473" ht="17.25" spans="1:17">
+    <row r="473" ht="17.25" hidden="1" spans="1:17">
       <c r="A473" s="4" t="s">
         <v>1474</v>
       </c>
@@ -30821,7 +30842,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="474" ht="17.25" spans="1:17">
+    <row r="474" ht="17.25" hidden="1" spans="1:17">
       <c r="A474" s="4" t="s">
         <v>1478</v>
       </c>
@@ -30871,7 +30892,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="475" ht="17.25" spans="1:17">
+    <row r="475" ht="17.25" hidden="1" spans="1:17">
       <c r="A475" s="4" t="s">
         <v>1481</v>
       </c>
@@ -30921,7 +30942,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="476" ht="17.25" spans="1:17">
+    <row r="476" ht="17.25" hidden="1" spans="1:17">
       <c r="A476" s="4" t="s">
         <v>1484</v>
       </c>
@@ -30971,7 +30992,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="477" ht="17.25" spans="1:17">
+    <row r="477" ht="17.25" hidden="1" spans="1:17">
       <c r="A477" s="4" t="s">
         <v>1486</v>
       </c>
@@ -31021,7 +31042,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="478" ht="17.25" spans="1:17">
+    <row r="478" ht="17.25" hidden="1" spans="1:17">
       <c r="A478" s="4" t="s">
         <v>1490</v>
       </c>
@@ -31071,7 +31092,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="479" ht="17.25" spans="1:17">
+    <row r="479" ht="17.25" hidden="1" spans="1:17">
       <c r="A479" s="4" t="s">
         <v>1495</v>
       </c>
@@ -31124,7 +31145,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="480" ht="17.25" spans="1:17">
+    <row r="480" ht="17.25" hidden="1" spans="1:17">
       <c r="A480" s="4" t="s">
         <v>1499</v>
       </c>
@@ -31174,7 +31195,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="481" ht="17.25" spans="1:17">
+    <row r="481" ht="17.25" hidden="1" spans="1:17">
       <c r="A481" s="4" t="s">
         <v>1503</v>
       </c>
@@ -31224,7 +31245,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="482" ht="17.25" spans="1:17">
+    <row r="482" ht="17.25" hidden="1" spans="1:17">
       <c r="A482" s="4" t="s">
         <v>1506</v>
       </c>
@@ -31271,7 +31292,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="483" ht="17.25" spans="1:17">
+    <row r="483" ht="17.25" hidden="1" spans="1:17">
       <c r="A483" s="4" t="s">
         <v>1510</v>
       </c>
@@ -31318,7 +31339,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="484" ht="17.25" spans="1:17">
+    <row r="484" ht="17.25" hidden="1" spans="1:17">
       <c r="A484" s="4" t="s">
         <v>1512</v>
       </c>
@@ -31365,7 +31386,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="485" ht="17.25" spans="1:17">
+    <row r="485" ht="17.25" hidden="1" spans="1:17">
       <c r="A485" s="4" t="s">
         <v>1514</v>
       </c>
@@ -31408,7 +31429,7 @@
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>
     </row>
-    <row r="486" ht="17.25" spans="1:17">
+    <row r="486" ht="17.25" hidden="1" spans="1:17">
       <c r="A486" s="4" t="s">
         <v>1516</v>
       </c>
@@ -31455,7 +31476,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="487" ht="17.25" spans="1:17">
+    <row r="487" ht="17.25" hidden="1" spans="1:17">
       <c r="A487" s="4" t="s">
         <v>1520</v>
       </c>
@@ -31502,7 +31523,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="488" ht="17.25" spans="1:17">
+    <row r="488" ht="17.25" hidden="1" spans="1:17">
       <c r="A488" s="4" t="s">
         <v>1523</v>
       </c>
@@ -31549,7 +31570,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="489" ht="17.25" spans="1:17">
+    <row r="489" ht="17.25" hidden="1" spans="1:17">
       <c r="A489" s="4" t="s">
         <v>1526</v>
       </c>
@@ -31596,7 +31617,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="490" ht="17.25" spans="1:17">
+    <row r="490" ht="17.25" hidden="1" spans="1:17">
       <c r="A490" s="4" t="s">
         <v>1529</v>
       </c>
@@ -31643,7 +31664,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="491" ht="17.25" spans="1:17">
+    <row r="491" ht="17.25" hidden="1" spans="1:17">
       <c r="A491" s="4" t="s">
         <v>1532</v>
       </c>
@@ -31831,7 +31852,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="495" ht="17.25" spans="1:17">
+    <row r="495" ht="17.25" hidden="1" spans="1:17">
       <c r="A495" s="4" t="s">
         <v>1541</v>
       </c>
@@ -31881,7 +31902,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="496" ht="17.25" spans="1:17">
+    <row r="496" ht="17.25" hidden="1" spans="1:17">
       <c r="A496" s="4" t="s">
         <v>1545</v>
       </c>
@@ -31931,7 +31952,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="497" ht="17.25" spans="1:17">
+    <row r="497" ht="17.25" hidden="1" spans="1:17">
       <c r="A497" s="4" t="s">
         <v>1549</v>
       </c>
@@ -31981,7 +32002,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="498" ht="17.25" spans="1:17">
+    <row r="498" ht="17.25" hidden="1" spans="1:17">
       <c r="A498" s="4" t="s">
         <v>1553</v>
       </c>
@@ -32031,7 +32052,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="499" ht="17.25" spans="1:17">
+    <row r="499" ht="17.25" hidden="1" spans="1:17">
       <c r="A499" s="4" t="s">
         <v>1557</v>
       </c>
@@ -32081,7 +32102,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="500" ht="17.25" spans="1:17">
+    <row r="500" ht="17.25" hidden="1" spans="1:17">
       <c r="A500" s="4" t="s">
         <v>1561</v>
       </c>
@@ -32131,7 +32152,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="501" ht="17.25" spans="1:17">
+    <row r="501" ht="17.25" hidden="1" spans="1:17">
       <c r="A501" s="4" t="s">
         <v>1564</v>
       </c>
@@ -32181,7 +32202,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="502" ht="17.25" spans="1:17">
+    <row r="502" ht="17.25" hidden="1" spans="1:17">
       <c r="A502" s="4" t="s">
         <v>1568</v>
       </c>
@@ -32231,7 +32252,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="503" ht="17.25" spans="1:17">
+    <row r="503" ht="17.25" hidden="1" spans="1:17">
       <c r="A503" s="4" t="s">
         <v>1572</v>
       </c>
@@ -32281,7 +32302,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="504" ht="17.25" spans="1:17">
+    <row r="504" ht="17.25" hidden="1" spans="1:17">
       <c r="A504" s="4" t="s">
         <v>1574</v>
       </c>
@@ -32334,7 +32355,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="505" ht="17.25" spans="1:17">
+    <row r="505" ht="17.25" hidden="1" spans="1:17">
       <c r="A505" s="4" t="s">
         <v>1576</v>
       </c>
@@ -32381,7 +32402,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="506" ht="17.25" spans="1:17">
+    <row r="506" ht="17.25" hidden="1" spans="1:17">
       <c r="A506" s="4" t="s">
         <v>1580</v>
       </c>
@@ -32428,7 +32449,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="507" ht="17.25" spans="1:17">
+    <row r="507" ht="17.25" hidden="1" spans="1:17">
       <c r="A507" s="4" t="s">
         <v>1584</v>
       </c>
@@ -32475,7 +32496,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="508" ht="17.25" spans="1:17">
+    <row r="508" ht="17.25" hidden="1" spans="1:17">
       <c r="A508" s="4" t="s">
         <v>1588</v>
       </c>
@@ -32522,7 +32543,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="509" ht="17.25" spans="1:17">
+    <row r="509" ht="17.25" hidden="1" spans="1:17">
       <c r="A509" s="4" t="s">
         <v>1592</v>
       </c>
@@ -32569,7 +32590,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="510" spans="1:15">
+    <row r="510" hidden="1" spans="1:15">
       <c r="A510" s="4" t="s">
         <v>1595</v>
       </c>
@@ -32610,7 +32631,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="511" spans="1:15">
+    <row r="511" hidden="1" spans="1:15">
       <c r="A511" s="4" t="s">
         <v>1596</v>
       </c>
@@ -32651,7 +32672,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="512" spans="1:15">
+    <row r="512" hidden="1" spans="1:15">
       <c r="A512" s="4" t="s">
         <v>1598</v>
       </c>
@@ -32692,7 +32713,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="513" spans="1:15">
+    <row r="513" hidden="1" spans="1:15">
       <c r="A513" s="4" t="s">
         <v>1601</v>
       </c>
@@ -32733,7 +32754,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="514" spans="1:15">
+    <row r="514" hidden="1" spans="1:15">
       <c r="A514" s="4" t="s">
         <v>1606</v>
       </c>
@@ -32774,7 +32795,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="515" spans="1:15">
+    <row r="515" hidden="1" spans="1:15">
       <c r="A515" s="4" t="s">
         <v>1608</v>
       </c>
@@ -32815,7 +32836,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="516" spans="1:15">
+    <row r="516" hidden="1" spans="1:15">
       <c r="A516" s="4" t="s">
         <v>1610</v>
       </c>
@@ -32856,7 +32877,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="517" spans="1:15">
+    <row r="517" hidden="1" spans="1:15">
       <c r="A517" s="4" t="s">
         <v>1611</v>
       </c>
@@ -32897,7 +32918,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="518" spans="1:15">
+    <row r="518" hidden="1" spans="1:15">
       <c r="A518" t="s">
         <v>1613</v>
       </c>
@@ -32938,7 +32959,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="519" spans="1:15">
+    <row r="519" hidden="1" spans="1:15">
       <c r="A519" s="4" t="s">
         <v>1615</v>
       </c>
@@ -32979,8 +33000,137 @@
         <v>1019</v>
       </c>
     </row>
+    <row r="520" hidden="1" spans="1:15">
+      <c r="A520" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D520" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E520">
+        <v>1510</v>
+      </c>
+      <c r="F520">
+        <v>692</v>
+      </c>
+      <c r="G520" s="4">
+        <v>0</v>
+      </c>
+      <c r="H520" s="4">
+        <v>0</v>
+      </c>
+      <c r="I520" s="4">
+        <v>0</v>
+      </c>
+      <c r="J520" s="4">
+        <v>2035</v>
+      </c>
+      <c r="L520" s="9" t="s">
+        <v>1353</v>
+      </c>
+      <c r="N520" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="O520" s="7" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="521" hidden="1" spans="1:15">
+      <c r="A521" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E521">
+        <v>1640</v>
+      </c>
+      <c r="F521">
+        <v>692</v>
+      </c>
+      <c r="G521" s="4">
+        <v>0</v>
+      </c>
+      <c r="H521" s="4">
+        <v>0</v>
+      </c>
+      <c r="I521" s="4">
+        <v>0</v>
+      </c>
+      <c r="J521" s="4">
+        <v>2035</v>
+      </c>
+      <c r="L521" s="9" t="s">
+        <v>1353</v>
+      </c>
+      <c r="N521" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="O521" s="7" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="522" hidden="1" spans="1:15">
+      <c r="A522" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B522" t="s">
+        <v>18</v>
+      </c>
+      <c r="C522" t="s">
+        <v>88</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E522">
+        <v>1620</v>
+      </c>
+      <c r="F522">
+        <v>1200</v>
+      </c>
+      <c r="G522" s="4">
+        <v>0</v>
+      </c>
+      <c r="H522" s="4">
+        <v>0</v>
+      </c>
+      <c r="I522" s="4">
+        <v>0</v>
+      </c>
+      <c r="J522">
+        <v>2035</v>
+      </c>
+      <c r="L522" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N522" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="O522" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T518">
+  <autoFilter ref="A1:T522">
+    <filterColumn colId="13">
+      <customFilters>
+        <customFilter operator="equal" val="交通运输局"/>
+        <customFilter operator="equal" val="交通运输事业发展中心"/>
+      </customFilters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -10,14 +10,14 @@
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$522</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$524</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5010" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1628">
   <si>
     <t>单号</t>
   </si>
@@ -4882,13 +4882,25 @@
     <t>郭瑞丰</t>
   </si>
   <si>
+    <t>[2021]第-11号</t>
+  </si>
+  <si>
+    <t>郭铃华</t>
+  </si>
+  <si>
+    <t>2021年事业单位选调考试</t>
+  </si>
+  <si>
     <t>[2021]第341号</t>
   </si>
   <si>
-    <t>郭铃华</t>
-  </si>
-  <si>
-    <t>2021年事业单位选调考试</t>
+    <t>黄逸博</t>
+  </si>
+  <si>
+    <t>左安事业</t>
+  </si>
+  <si>
+    <t>[2021]空07号</t>
   </si>
 </sst>
 </file>
@@ -4898,9 +4910,9 @@
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4948,7 +4960,97 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4962,30 +5064,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5000,28 +5080,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -5030,23 +5088,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5054,40 +5097,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5160,25 +5172,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5190,13 +5220,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5208,79 +5250,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5298,19 +5268,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5328,6 +5322,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5340,7 +5340,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5387,18 +5399,55 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -5434,50 +5483,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5489,10 +5501,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5501,133 +5513,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6049,8 +6061,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
-  <dimension ref="A1:T522"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:T524"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -6129,7 +6141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="14.25" hidden="1" spans="1:19">
+    <row r="2" ht="14.25" spans="1:19">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -6188,7 +6200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="14.25" hidden="1" spans="1:19">
+    <row r="3" ht="14.25" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -6247,7 +6259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="14.25" hidden="1" spans="1:19">
+    <row r="4" ht="14.25" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
@@ -6306,7 +6318,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="14.25" hidden="1" spans="1:19">
+    <row r="5" ht="14.25" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>37</v>
       </c>
@@ -6363,7 +6375,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="14.25" hidden="1" spans="1:19">
+    <row r="6" ht="14.25" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -6422,7 +6434,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="14.25" hidden="1" spans="1:19">
+    <row r="7" ht="14.25" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
@@ -6481,7 +6493,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="14.25" hidden="1" spans="1:19">
+    <row r="8" ht="14.25" spans="1:19">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -6540,7 +6552,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="14.25" hidden="1" spans="1:19">
+    <row r="9" ht="14.25" spans="1:19">
       <c r="A9" s="4" t="s">
         <v>63</v>
       </c>
@@ -6599,7 +6611,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" ht="14.25" hidden="1" spans="1:19">
+    <row r="10" ht="14.25" spans="1:19">
       <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
@@ -6656,7 +6668,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" ht="14.25" hidden="1" spans="1:19">
+    <row r="11" ht="14.25" spans="1:19">
       <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
@@ -6715,7 +6727,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="14.25" hidden="1" spans="1:19">
+    <row r="12" ht="14.25" spans="1:19">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -6772,7 +6784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" ht="14.25" hidden="1" spans="1:19">
+    <row r="13" ht="14.25" spans="1:19">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -6827,7 +6839,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" ht="14.25" hidden="1" spans="1:19">
+    <row r="14" ht="14.25" spans="1:19">
       <c r="A14" s="4" t="s">
         <v>93</v>
       </c>
@@ -6886,7 +6898,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" ht="14.25" hidden="1" spans="1:19">
+    <row r="15" ht="14.25" spans="1:19">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -6945,7 +6957,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" ht="14.25" hidden="1" spans="1:19">
+    <row r="16" ht="14.25" spans="1:19">
       <c r="A16" s="4" t="s">
         <v>103</v>
       </c>
@@ -7004,7 +7016,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" ht="14.25" hidden="1" spans="1:19">
+    <row r="17" ht="14.25" spans="1:19">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -7059,7 +7071,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" ht="14.25" hidden="1" spans="1:19">
+    <row r="18" ht="14.25" spans="1:19">
       <c r="A18" s="4" t="s">
         <v>113</v>
       </c>
@@ -7118,7 +7130,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" ht="14.25" hidden="1" spans="1:20">
+    <row r="19" ht="14.25" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
@@ -7179,7 +7191,7 @@
         <v>87662.6773333333</v>
       </c>
     </row>
-    <row r="20" ht="14.25" hidden="1" spans="1:19">
+    <row r="20" ht="14.25" spans="1:19">
       <c r="A20" s="4" t="s">
         <v>122</v>
       </c>
@@ -7236,7 +7248,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" ht="14.25" hidden="1" spans="1:20">
+    <row r="21" ht="14.25" spans="1:20">
       <c r="A21" s="4" t="s">
         <v>125</v>
       </c>
@@ -7297,7 +7309,7 @@
         <v>53992.6</v>
       </c>
     </row>
-    <row r="22" ht="14.25" hidden="1" spans="1:19">
+    <row r="22" ht="14.25" spans="1:19">
       <c r="A22" s="4" t="s">
         <v>131</v>
       </c>
@@ -7352,7 +7364,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" ht="14.25" hidden="1" spans="1:19">
+    <row r="23" ht="14.25" spans="1:19">
       <c r="A23" s="4" t="s">
         <v>137</v>
       </c>
@@ -7407,7 +7419,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="14.25" hidden="1" spans="1:19">
+    <row r="24" ht="14.25" spans="1:19">
       <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
@@ -7462,7 +7474,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" ht="14.25" hidden="1" spans="1:19">
+    <row r="25" ht="14.25" spans="1:19">
       <c r="A25" s="4" t="s">
         <v>146</v>
       </c>
@@ -7521,7 +7533,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" ht="14.25" hidden="1" spans="1:19">
+    <row r="26" ht="14.25" spans="1:19">
       <c r="A26" s="4" t="s">
         <v>150</v>
       </c>
@@ -7578,7 +7590,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" ht="14.25" hidden="1" spans="1:19">
+    <row r="27" ht="14.25" spans="1:19">
       <c r="A27" s="4" t="s">
         <v>157</v>
       </c>
@@ -7635,7 +7647,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" ht="14.25" hidden="1" spans="1:19">
+    <row r="28" ht="14.25" spans="1:19">
       <c r="A28" s="4" t="s">
         <v>165</v>
       </c>
@@ -7694,7 +7706,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" ht="14.25" hidden="1" spans="1:19">
+    <row r="29" ht="14.25" spans="1:19">
       <c r="A29" s="4" t="s">
         <v>171</v>
       </c>
@@ -7751,7 +7763,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="14.25" hidden="1" spans="1:19">
+    <row r="30" ht="14.25" spans="1:19">
       <c r="A30" s="4" t="s">
         <v>176</v>
       </c>
@@ -7808,7 +7820,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" ht="14.25" hidden="1" spans="1:19">
+    <row r="31" ht="14.25" spans="1:19">
       <c r="A31" s="4" t="s">
         <v>180</v>
       </c>
@@ -7865,7 +7877,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" ht="14.25" hidden="1" spans="1:19">
+    <row r="32" ht="14.25" spans="1:19">
       <c r="A32" s="4" t="s">
         <v>185</v>
       </c>
@@ -7920,7 +7932,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" ht="27" hidden="1" spans="1:19">
+    <row r="33" ht="27" spans="1:19">
       <c r="A33" s="4" t="s">
         <v>190</v>
       </c>
@@ -7977,7 +7989,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" ht="27" hidden="1" spans="1:19">
+    <row r="34" ht="27" spans="1:19">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -8032,7 +8044,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" ht="14.25" hidden="1" spans="1:19">
+    <row r="35" ht="14.25" spans="1:19">
       <c r="A35" s="4" t="s">
         <v>201</v>
       </c>
@@ -8087,7 +8099,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" ht="14.25" hidden="1" spans="1:19">
+    <row r="36" ht="14.25" spans="1:19">
       <c r="A36" s="4" t="s">
         <v>207</v>
       </c>
@@ -8142,7 +8154,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" ht="14.25" hidden="1" spans="1:19">
+    <row r="37" ht="14.25" spans="1:19">
       <c r="A37" s="4" t="s">
         <v>211</v>
       </c>
@@ -8197,7 +8209,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" ht="14.25" hidden="1" spans="1:19">
+    <row r="38" ht="14.25" spans="1:19">
       <c r="A38" s="4" t="s">
         <v>215</v>
       </c>
@@ -8254,7 +8266,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" ht="14.25" hidden="1" spans="1:19">
+    <row r="39" ht="14.25" spans="1:19">
       <c r="A39" s="4" t="s">
         <v>219</v>
       </c>
@@ -8309,7 +8321,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" ht="27" hidden="1" spans="1:19">
+    <row r="40" ht="27" spans="1:19">
       <c r="A40" s="4" t="s">
         <v>224</v>
       </c>
@@ -8364,7 +8376,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" ht="14.25" hidden="1" spans="1:19">
+    <row r="41" ht="14.25" spans="1:19">
       <c r="A41" s="4" t="s">
         <v>229</v>
       </c>
@@ -8421,7 +8433,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" ht="14.25" hidden="1" spans="1:19">
+    <row r="42" ht="14.25" spans="1:19">
       <c r="A42" s="4" t="s">
         <v>235</v>
       </c>
@@ -8476,7 +8488,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" ht="14.25" hidden="1" spans="1:19">
+    <row r="43" ht="14.25" spans="1:19">
       <c r="A43" s="4" t="s">
         <v>241</v>
       </c>
@@ -8531,7 +8543,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" ht="14.25" hidden="1" spans="1:19">
+    <row r="44" ht="14.25" spans="1:19">
       <c r="A44" s="4" t="s">
         <v>247</v>
       </c>
@@ -8586,7 +8598,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="45" ht="15" spans="1:19">
+    <row r="45" ht="14.25" spans="1:19">
       <c r="A45" s="4" t="s">
         <v>251</v>
       </c>
@@ -8641,7 +8653,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="46" ht="27" hidden="1" spans="1:19">
+    <row r="46" ht="27" spans="1:19">
       <c r="A46" s="4" t="s">
         <v>257</v>
       </c>
@@ -8698,7 +8710,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" ht="14.25" hidden="1" spans="1:19">
+    <row r="47" ht="14.25" spans="1:19">
       <c r="A47" s="4" t="s">
         <v>262</v>
       </c>
@@ -8753,7 +8765,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" ht="14.25" hidden="1" spans="1:19">
+    <row r="48" ht="14.25" spans="1:19">
       <c r="A48" s="4" t="s">
         <v>266</v>
       </c>
@@ -8808,7 +8820,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" ht="27" hidden="1" spans="1:19">
+    <row r="49" ht="27" spans="1:19">
       <c r="A49" s="4" t="s">
         <v>270</v>
       </c>
@@ -8865,7 +8877,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="14.25" hidden="1" spans="1:19">
+    <row r="50" ht="14.25" spans="1:19">
       <c r="A50" s="4" t="s">
         <v>278</v>
       </c>
@@ -8920,7 +8932,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" ht="14.25" hidden="1" spans="1:19">
+    <row r="51" ht="14.25" spans="1:19">
       <c r="A51" s="4" t="s">
         <v>283</v>
       </c>
@@ -8977,7 +8989,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" ht="27.75" hidden="1" spans="1:19">
+    <row r="52" ht="27.75" spans="1:19">
       <c r="A52" s="4" t="s">
         <v>286</v>
       </c>
@@ -9034,7 +9046,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="53" ht="15" hidden="1" spans="1:19">
+    <row r="53" ht="15" spans="1:19">
       <c r="A53" s="4" t="s">
         <v>291</v>
       </c>
@@ -9089,7 +9101,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="54" ht="14.25" hidden="1" spans="1:19">
+    <row r="54" ht="14.25" spans="1:19">
       <c r="A54" s="4" t="s">
         <v>297</v>
       </c>
@@ -9146,7 +9158,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" ht="14.25" hidden="1" spans="1:19">
+    <row r="55" ht="14.25" spans="1:19">
       <c r="A55" s="4" t="s">
         <v>304</v>
       </c>
@@ -9201,7 +9213,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" ht="14.25" hidden="1" spans="1:19">
+    <row r="56" ht="14.25" spans="1:19">
       <c r="A56" s="4" t="s">
         <v>308</v>
       </c>
@@ -9258,7 +9270,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="57" ht="14.25" hidden="1" spans="1:19">
+    <row r="57" ht="14.25" spans="1:19">
       <c r="A57" s="4" t="s">
         <v>312</v>
       </c>
@@ -9317,7 +9329,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="58" ht="27" hidden="1" spans="1:19">
+    <row r="58" ht="27" spans="1:19">
       <c r="A58" s="4" t="s">
         <v>316</v>
       </c>
@@ -9372,7 +9384,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" ht="14.25" hidden="1" spans="1:19">
+    <row r="59" ht="14.25" spans="1:19">
       <c r="A59" s="4" t="s">
         <v>322</v>
       </c>
@@ -9429,7 +9441,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="60" ht="14.25" hidden="1" spans="1:19">
+    <row r="60" ht="14.25" spans="1:19">
       <c r="A60" s="4" t="s">
         <v>327</v>
       </c>
@@ -9486,7 +9498,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" ht="14.25" hidden="1" spans="1:19">
+    <row r="61" ht="14.25" spans="1:19">
       <c r="A61" s="4" t="s">
         <v>333</v>
       </c>
@@ -9543,7 +9555,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" ht="14.25" hidden="1" spans="1:19">
+    <row r="62" ht="14.25" spans="1:19">
       <c r="A62" s="5" t="s">
         <v>339</v>
       </c>
@@ -9598,7 +9610,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" ht="27" hidden="1" spans="1:19">
+    <row r="63" ht="27" spans="1:19">
       <c r="A63" s="4" t="s">
         <v>343</v>
       </c>
@@ -9655,7 +9667,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="64" ht="27" hidden="1" spans="1:19">
+    <row r="64" ht="27" spans="1:19">
       <c r="A64" s="4" t="s">
         <v>348</v>
       </c>
@@ -9712,7 +9724,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="65" ht="14.25" hidden="1" spans="1:19">
+    <row r="65" ht="14.25" spans="1:19">
       <c r="A65" s="4" t="s">
         <v>352</v>
       </c>
@@ -9769,7 +9781,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="66" ht="14.25" hidden="1" spans="1:19">
+    <row r="66" ht="14.25" spans="1:19">
       <c r="A66" s="4" t="s">
         <v>356</v>
       </c>
@@ -9826,7 +9838,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="67" ht="14.25" hidden="1" spans="1:19">
+    <row r="67" ht="14.25" spans="1:19">
       <c r="A67" s="4" t="s">
         <v>360</v>
       </c>
@@ -9883,7 +9895,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" ht="14.25" hidden="1" spans="1:19">
+    <row r="68" ht="14.25" spans="1:19">
       <c r="A68" s="4" t="s">
         <v>364</v>
       </c>
@@ -9940,7 +9952,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="69" ht="27" hidden="1" spans="1:19">
+    <row r="69" ht="27" spans="1:19">
       <c r="A69" s="4" t="s">
         <v>367</v>
       </c>
@@ -9997,7 +10009,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="70" ht="14.25" hidden="1" spans="1:19">
+    <row r="70" ht="14.25" spans="1:19">
       <c r="A70" s="4" t="s">
         <v>371</v>
       </c>
@@ -10054,7 +10066,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" ht="14.25" hidden="1" spans="1:19">
+    <row r="71" ht="14.25" spans="1:19">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -10111,7 +10123,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" ht="14.25" hidden="1" spans="1:19">
+    <row r="72" ht="14.25" spans="1:19">
       <c r="A72" s="4" t="s">
         <v>378</v>
       </c>
@@ -10168,7 +10180,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" ht="27" hidden="1" spans="1:19">
+    <row r="73" ht="27" spans="1:19">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10225,7 +10237,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74" ht="27" hidden="1" spans="1:19">
+    <row r="74" ht="27" spans="1:19">
       <c r="A74" s="4" t="s">
         <v>385</v>
       </c>
@@ -10282,7 +10294,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" ht="14.25" hidden="1" spans="1:19">
+    <row r="75" ht="14.25" spans="1:19">
       <c r="A75" s="4" t="s">
         <v>389</v>
       </c>
@@ -10339,7 +10351,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="76" ht="27" hidden="1" spans="1:19">
+    <row r="76" ht="27" spans="1:19">
       <c r="A76" s="4" t="s">
         <v>393</v>
       </c>
@@ -10396,7 +10408,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" ht="14.25" hidden="1" spans="1:19">
+    <row r="77" ht="14.25" spans="1:19">
       <c r="A77" s="4" t="s">
         <v>397</v>
       </c>
@@ -10455,7 +10467,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" ht="27" hidden="1" spans="1:19">
+    <row r="78" ht="27" spans="1:19">
       <c r="A78" s="4" t="s">
         <v>401</v>
       </c>
@@ -10512,7 +10524,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" ht="14.25" hidden="1" spans="1:19">
+    <row r="79" ht="14.25" spans="1:19">
       <c r="A79" s="4" t="s">
         <v>405</v>
       </c>
@@ -10569,7 +10581,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="80" ht="14.25" hidden="1" spans="1:19">
+    <row r="80" ht="14.25" spans="1:19">
       <c r="A80" s="4" t="s">
         <v>409</v>
       </c>
@@ -10626,7 +10638,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="81" ht="14.25" hidden="1" spans="1:19">
+    <row r="81" ht="14.25" spans="1:19">
       <c r="A81" s="4" t="s">
         <v>413</v>
       </c>
@@ -10683,7 +10695,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="82" ht="14.25" hidden="1" spans="1:19">
+    <row r="82" ht="14.25" spans="1:19">
       <c r="A82" s="4" t="s">
         <v>418</v>
       </c>
@@ -10740,7 +10752,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="83" ht="14.25" hidden="1" spans="1:19">
+    <row r="83" ht="14.25" spans="1:19">
       <c r="A83" s="4" t="s">
         <v>422</v>
       </c>
@@ -10797,7 +10809,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="84" ht="14.25" hidden="1" spans="1:19">
+    <row r="84" ht="14.25" spans="1:19">
       <c r="A84" s="4" t="s">
         <v>426</v>
       </c>
@@ -10854,7 +10866,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="85" ht="27" hidden="1" spans="1:19">
+    <row r="85" ht="27" spans="1:19">
       <c r="A85" s="4" t="s">
         <v>429</v>
       </c>
@@ -10911,7 +10923,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="86" ht="27" hidden="1" spans="1:19">
+    <row r="86" ht="27" spans="1:19">
       <c r="A86" s="4" t="s">
         <v>433</v>
       </c>
@@ -10968,7 +10980,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="87" ht="14.25" hidden="1" spans="1:19">
+    <row r="87" ht="14.25" spans="1:19">
       <c r="A87" s="4" t="s">
         <v>436</v>
       </c>
@@ -11025,7 +11037,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="88" ht="14.25" hidden="1" spans="1:19">
+    <row r="88" ht="14.25" spans="1:19">
       <c r="A88" s="4" t="s">
         <v>440</v>
       </c>
@@ -11082,7 +11094,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="89" ht="14.25" hidden="1" spans="1:19">
+    <row r="89" ht="14.25" spans="1:19">
       <c r="A89" s="4" t="s">
         <v>444</v>
       </c>
@@ -11139,7 +11151,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90" ht="27" hidden="1" spans="1:19">
+    <row r="90" ht="27" spans="1:19">
       <c r="A90" s="4" t="s">
         <v>448</v>
       </c>
@@ -11196,7 +11208,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="91" ht="14.25" hidden="1" spans="1:19">
+    <row r="91" ht="14.25" spans="1:19">
       <c r="A91" s="4" t="s">
         <v>452</v>
       </c>
@@ -11253,7 +11265,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" ht="14.25" hidden="1" spans="1:19">
+    <row r="92" ht="14.25" spans="1:19">
       <c r="A92" s="4" t="s">
         <v>454</v>
       </c>
@@ -11310,7 +11322,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" ht="14.25" hidden="1" spans="1:19">
+    <row r="93" ht="14.25" spans="1:19">
       <c r="A93" s="4" t="s">
         <v>456</v>
       </c>
@@ -11367,7 +11379,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" ht="14.25" hidden="1" spans="1:19">
+    <row r="94" ht="14.25" spans="1:19">
       <c r="A94" s="4" t="s">
         <v>458</v>
       </c>
@@ -11424,7 +11436,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" ht="14.25" hidden="1" spans="1:19">
+    <row r="95" ht="14.25" spans="1:19">
       <c r="A95" s="4" t="s">
         <v>461</v>
       </c>
@@ -11481,7 +11493,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="96" ht="14.25" hidden="1" spans="1:19">
+    <row r="96" ht="14.25" spans="1:19">
       <c r="A96" s="4" t="s">
         <v>465</v>
       </c>
@@ -11538,7 +11550,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="97" ht="14.25" hidden="1" spans="1:19">
+    <row r="97" ht="14.25" spans="1:19">
       <c r="A97" s="4" t="s">
         <v>469</v>
       </c>
@@ -11595,7 +11607,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" ht="14.25" hidden="1" spans="1:19">
+    <row r="98" ht="14.25" spans="1:19">
       <c r="A98" s="4" t="s">
         <v>474</v>
       </c>
@@ -11652,7 +11664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" ht="14.25" hidden="1" spans="1:19">
+    <row r="99" ht="14.25" spans="1:19">
       <c r="A99" s="4" t="s">
         <v>476</v>
       </c>
@@ -11709,7 +11721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" ht="14.25" hidden="1" spans="1:19">
+    <row r="100" ht="14.25" spans="1:19">
       <c r="A100" s="4" t="s">
         <v>479</v>
       </c>
@@ -11766,7 +11778,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" ht="14.25" hidden="1" spans="1:19">
+    <row r="101" ht="14.25" spans="1:19">
       <c r="A101" s="4" t="s">
         <v>481</v>
       </c>
@@ -11823,7 +11835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" ht="14.25" hidden="1" spans="1:19">
+    <row r="102" ht="14.25" spans="1:19">
       <c r="A102" s="4" t="s">
         <v>483</v>
       </c>
@@ -11880,7 +11892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" ht="14.25" hidden="1" spans="1:19">
+    <row r="103" ht="14.25" spans="1:19">
       <c r="A103" s="4" t="s">
         <v>485</v>
       </c>
@@ -11937,7 +11949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" ht="14.25" hidden="1" spans="1:19">
+    <row r="104" ht="14.25" spans="1:19">
       <c r="A104" s="4" t="s">
         <v>487</v>
       </c>
@@ -11994,7 +12006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" ht="14.25" hidden="1" spans="1:19">
+    <row r="105" ht="14.25" spans="1:19">
       <c r="A105" s="4" t="s">
         <v>489</v>
       </c>
@@ -12051,7 +12063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" ht="14.25" hidden="1" spans="1:19">
+    <row r="106" ht="14.25" spans="1:19">
       <c r="A106" s="4" t="s">
         <v>491</v>
       </c>
@@ -12108,7 +12120,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="107" ht="14.25" hidden="1" spans="1:19">
+    <row r="107" ht="14.25" spans="1:19">
       <c r="A107" s="4" t="s">
         <v>495</v>
       </c>
@@ -12165,7 +12177,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="108" ht="14.25" hidden="1" spans="1:19">
+    <row r="108" ht="14.25" spans="1:19">
       <c r="A108" s="4" t="s">
         <v>497</v>
       </c>
@@ -12220,7 +12232,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="109" ht="14.25" hidden="1" spans="1:19">
+    <row r="109" ht="14.25" spans="1:19">
       <c r="A109" s="4" t="s">
         <v>502</v>
       </c>
@@ -12277,7 +12289,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="110" ht="14.25" hidden="1" spans="1:19">
+    <row r="110" ht="14.25" spans="1:19">
       <c r="A110" s="4" t="s">
         <v>504</v>
       </c>
@@ -12334,7 +12346,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" ht="14.25" hidden="1" spans="1:19">
+    <row r="111" ht="14.25" spans="1:19">
       <c r="A111" s="4" t="s">
         <v>506</v>
       </c>
@@ -12391,7 +12403,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="112" ht="14.25" hidden="1" spans="1:19">
+    <row r="112" ht="14.25" spans="1:19">
       <c r="A112" s="4" t="s">
         <v>508</v>
       </c>
@@ -12448,7 +12460,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="113" ht="14.25" hidden="1" spans="1:19">
+    <row r="113" ht="14.25" spans="1:19">
       <c r="A113" s="4" t="s">
         <v>510</v>
       </c>
@@ -12505,7 +12517,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" ht="27" hidden="1" spans="1:19">
+    <row r="114" ht="27" spans="1:19">
       <c r="A114" s="4" t="s">
         <v>513</v>
       </c>
@@ -12562,7 +12574,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="115" ht="27" hidden="1" spans="1:19">
+    <row r="115" ht="27" spans="1:19">
       <c r="A115" s="4" t="s">
         <v>517</v>
       </c>
@@ -12619,7 +12631,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="116" ht="27" hidden="1" spans="1:19">
+    <row r="116" ht="27" spans="1:19">
       <c r="A116" s="4" t="s">
         <v>520</v>
       </c>
@@ -12676,7 +12688,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="117" ht="14.25" hidden="1" spans="1:19">
+    <row r="117" ht="14.25" spans="1:19">
       <c r="A117" s="4" t="s">
         <v>523</v>
       </c>
@@ -12731,7 +12743,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="118" ht="14.25" hidden="1" spans="1:19">
+    <row r="118" ht="14.25" spans="1:19">
       <c r="A118" s="4" t="s">
         <v>528</v>
       </c>
@@ -12788,7 +12800,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" ht="14.25" hidden="1" spans="1:19">
+    <row r="119" ht="14.25" spans="1:19">
       <c r="A119" s="4" t="s">
         <v>530</v>
       </c>
@@ -12845,7 +12857,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" ht="14.25" hidden="1" spans="1:19">
+    <row r="120" ht="14.25" spans="1:19">
       <c r="A120" s="4" t="s">
         <v>532</v>
       </c>
@@ -12902,7 +12914,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121" ht="14.25" hidden="1" spans="1:19">
+    <row r="121" ht="14.25" spans="1:19">
       <c r="A121" s="4" t="s">
         <v>534</v>
       </c>
@@ -12959,7 +12971,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="122" ht="14.25" hidden="1" spans="1:19">
+    <row r="122" ht="14.25" spans="1:19">
       <c r="A122" s="4" t="s">
         <v>536</v>
       </c>
@@ -13016,7 +13028,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" ht="14.25" hidden="1" spans="1:19">
+    <row r="123" ht="14.25" spans="1:19">
       <c r="A123" s="4" t="s">
         <v>539</v>
       </c>
@@ -13073,7 +13085,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" ht="14.25" hidden="1" spans="1:19">
+    <row r="124" ht="14.25" spans="1:19">
       <c r="A124" s="4" t="s">
         <v>542</v>
       </c>
@@ -13130,7 +13142,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" ht="14.25" hidden="1" spans="1:19">
+    <row r="125" ht="14.25" spans="1:19">
       <c r="A125" s="4" t="s">
         <v>544</v>
       </c>
@@ -13187,7 +13199,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" ht="14.25" hidden="1" spans="1:19">
+    <row r="126" ht="14.25" spans="1:19">
       <c r="A126" s="4" t="s">
         <v>546</v>
       </c>
@@ -13244,7 +13256,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="127" ht="14.25" hidden="1" spans="1:19">
+    <row r="127" ht="14.25" spans="1:19">
       <c r="A127" s="4" t="s">
         <v>551</v>
       </c>
@@ -13301,7 +13313,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="128" ht="14.25" hidden="1" spans="1:19">
+    <row r="128" ht="14.25" spans="1:19">
       <c r="A128" s="4" t="s">
         <v>553</v>
       </c>
@@ -13358,7 +13370,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="129" ht="14.25" hidden="1" spans="1:19">
+    <row r="129" ht="14.25" spans="1:19">
       <c r="A129" s="4" t="s">
         <v>556</v>
       </c>
@@ -13413,7 +13425,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" ht="14.25" hidden="1" spans="1:19">
+    <row r="130" ht="14.25" spans="1:19">
       <c r="A130" s="4" t="s">
         <v>560</v>
       </c>
@@ -13468,7 +13480,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="131" ht="14.25" hidden="1" spans="1:19">
+    <row r="131" ht="14.25" spans="1:19">
       <c r="A131" s="4" t="s">
         <v>562</v>
       </c>
@@ -13523,7 +13535,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="132" ht="14.25" hidden="1" spans="1:19">
+    <row r="132" ht="14.25" spans="1:19">
       <c r="A132" s="4" t="s">
         <v>564</v>
       </c>
@@ -13578,7 +13590,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="133" ht="14.25" hidden="1" spans="1:19">
+    <row r="133" ht="14.25" spans="1:19">
       <c r="A133" s="4" t="s">
         <v>566</v>
       </c>
@@ -13633,7 +13645,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="134" ht="14.25" hidden="1" spans="1:19">
+    <row r="134" ht="14.25" spans="1:19">
       <c r="A134" s="4" t="s">
         <v>568</v>
       </c>
@@ -13688,7 +13700,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="135" ht="14.25" hidden="1" spans="1:19">
+    <row r="135" ht="14.25" spans="1:19">
       <c r="A135" s="4" t="s">
         <v>572</v>
       </c>
@@ -13743,7 +13755,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="136" ht="14.25" hidden="1" spans="1:19">
+    <row r="136" ht="14.25" spans="1:19">
       <c r="A136" s="4" t="s">
         <v>574</v>
       </c>
@@ -13798,7 +13810,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="137" ht="14.25" hidden="1" spans="1:19">
+    <row r="137" ht="14.25" spans="1:19">
       <c r="A137" s="4" t="s">
         <v>576</v>
       </c>
@@ -13853,7 +13865,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="138" ht="14.25" hidden="1" spans="1:19">
+    <row r="138" ht="14.25" spans="1:19">
       <c r="A138" s="4" t="s">
         <v>578</v>
       </c>
@@ -13908,7 +13920,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="139" ht="14.25" hidden="1" spans="1:19">
+    <row r="139" ht="14.25" spans="1:19">
       <c r="A139" s="4" t="s">
         <v>580</v>
       </c>
@@ -13963,7 +13975,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="140" ht="14.25" hidden="1" spans="1:19">
+    <row r="140" ht="14.25" spans="1:19">
       <c r="A140" s="4" t="s">
         <v>582</v>
       </c>
@@ -14020,7 +14032,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="141" ht="14.25" hidden="1" spans="1:19">
+    <row r="141" ht="14.25" spans="1:19">
       <c r="A141" s="4" t="s">
         <v>585</v>
       </c>
@@ -14077,7 +14089,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="142" ht="14.25" hidden="1" spans="1:19">
+    <row r="142" ht="14.25" spans="1:19">
       <c r="A142" s="4" t="s">
         <v>587</v>
       </c>
@@ -14134,7 +14146,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="143" ht="14.25" hidden="1" spans="1:19">
+    <row r="143" ht="14.25" spans="1:19">
       <c r="A143" s="4" t="s">
         <v>589</v>
       </c>
@@ -14193,7 +14205,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="144" ht="14.25" hidden="1" spans="1:19">
+    <row r="144" ht="14.25" spans="1:19">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
@@ -14250,7 +14262,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="145" ht="27" hidden="1" spans="1:19">
+    <row r="145" ht="27" spans="1:19">
       <c r="A145" s="4" t="s">
         <v>594</v>
       </c>
@@ -14305,7 +14317,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" ht="14.25" hidden="1" spans="1:19">
+    <row r="146" ht="14.25" spans="1:19">
       <c r="A146" s="4" t="s">
         <v>595</v>
       </c>
@@ -14360,7 +14372,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="147" ht="14.25" hidden="1" spans="1:19">
+    <row r="147" ht="14.25" spans="1:19">
       <c r="A147" s="4" t="s">
         <v>599</v>
       </c>
@@ -14413,7 +14425,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" ht="14.25" hidden="1" spans="1:19">
+    <row r="148" ht="14.25" spans="1:19">
       <c r="A148" s="4" t="s">
         <v>605</v>
       </c>
@@ -14466,7 +14478,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="149" ht="14.25" hidden="1" spans="1:19">
+    <row r="149" ht="14.25" spans="1:19">
       <c r="A149" s="4" t="s">
         <v>609</v>
       </c>
@@ -14519,7 +14531,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="150" ht="14.25" hidden="1" spans="1:19">
+    <row r="150" ht="14.25" spans="1:19">
       <c r="A150" s="4" t="s">
         <v>613</v>
       </c>
@@ -14578,7 +14590,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="151" ht="14.25" hidden="1" spans="1:19">
+    <row r="151" ht="14.25" spans="1:19">
       <c r="A151" s="4" t="s">
         <v>615</v>
       </c>
@@ -14635,7 +14647,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="152" ht="14.25" hidden="1" spans="1:19">
+    <row r="152" ht="14.25" spans="1:19">
       <c r="A152" s="4" t="s">
         <v>617</v>
       </c>
@@ -14692,7 +14704,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" ht="14.25" hidden="1" spans="1:19">
+    <row r="153" ht="14.25" spans="1:19">
       <c r="A153" s="4" t="s">
         <v>619</v>
       </c>
@@ -14749,7 +14761,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="154" ht="14.25" hidden="1" spans="1:19">
+    <row r="154" ht="14.25" spans="1:19">
       <c r="A154" s="4" t="s">
         <v>621</v>
       </c>
@@ -14806,7 +14818,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="155" ht="27" hidden="1" spans="1:19">
+    <row r="155" ht="27" spans="1:19">
       <c r="A155" s="4" t="s">
         <v>624</v>
       </c>
@@ -14863,7 +14875,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" ht="27" hidden="1" spans="1:19">
+    <row r="156" ht="27" spans="1:19">
       <c r="A156" s="4" t="s">
         <v>628</v>
       </c>
@@ -14920,7 +14932,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="157" ht="14.25" hidden="1" spans="1:19">
+    <row r="157" ht="14.25" spans="1:19">
       <c r="A157" s="4" t="s">
         <v>630</v>
       </c>
@@ -14977,7 +14989,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" ht="14.25" hidden="1" spans="1:19">
+    <row r="158" ht="14.25" spans="1:19">
       <c r="A158" s="4" t="s">
         <v>632</v>
       </c>
@@ -15034,7 +15046,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" ht="14.25" hidden="1" spans="1:19">
+    <row r="159" ht="14.25" spans="1:19">
       <c r="A159" s="4" t="s">
         <v>634</v>
       </c>
@@ -15091,7 +15103,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" ht="14.25" hidden="1" spans="1:19">
+    <row r="160" ht="14.25" spans="1:19">
       <c r="A160" s="4" t="s">
         <v>636</v>
       </c>
@@ -15148,7 +15160,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" ht="14.25" hidden="1" spans="1:19">
+    <row r="161" ht="14.25" spans="1:19">
       <c r="A161" s="4" t="s">
         <v>638</v>
       </c>
@@ -15205,7 +15217,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" ht="14.25" hidden="1" spans="1:19">
+    <row r="162" ht="14.25" spans="1:19">
       <c r="A162" s="4" t="s">
         <v>640</v>
       </c>
@@ -15262,7 +15274,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="163" ht="14.25" hidden="1" spans="1:19">
+    <row r="163" ht="14.25" spans="1:19">
       <c r="A163" s="4" t="s">
         <v>642</v>
       </c>
@@ -15319,7 +15331,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="164" ht="14.25" hidden="1" spans="1:19">
+    <row r="164" ht="14.25" spans="1:19">
       <c r="A164" s="4" t="s">
         <v>644</v>
       </c>
@@ -15376,7 +15388,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="165" ht="14.25" hidden="1" spans="1:19">
+    <row r="165" ht="14.25" spans="1:19">
       <c r="A165" s="4" t="s">
         <v>646</v>
       </c>
@@ -15433,7 +15445,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="166" ht="14.25" hidden="1" spans="1:19">
+    <row r="166" ht="14.25" spans="1:19">
       <c r="A166" s="4" t="s">
         <v>651</v>
       </c>
@@ -15490,7 +15502,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="167" ht="14.25" hidden="1" spans="1:19">
+    <row r="167" ht="14.25" spans="1:19">
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
@@ -15547,7 +15559,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="168" ht="14.25" hidden="1" spans="1:19">
+    <row r="168" ht="14.25" spans="1:19">
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
@@ -15604,7 +15616,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="169" ht="14.25" hidden="1" spans="1:19">
+    <row r="169" ht="14.25" spans="1:19">
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
@@ -15661,7 +15673,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="170" ht="14.25" hidden="1" spans="1:19">
+    <row r="170" ht="14.25" spans="1:19">
       <c r="A170" s="4" t="s">
         <v>659</v>
       </c>
@@ -15718,7 +15730,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="171" ht="14.25" hidden="1" spans="1:19">
+    <row r="171" ht="14.25" spans="1:19">
       <c r="A171" s="4" t="s">
         <v>661</v>
       </c>
@@ -15775,7 +15787,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="172" ht="14.25" hidden="1" spans="1:19">
+    <row r="172" ht="14.25" spans="1:19">
       <c r="A172" s="4" t="s">
         <v>663</v>
       </c>
@@ -15832,7 +15844,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="173" ht="14.25" hidden="1" spans="1:19">
+    <row r="173" ht="14.25" spans="1:19">
       <c r="A173" s="4" t="s">
         <v>665</v>
       </c>
@@ -15889,7 +15901,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="174" ht="14.25" hidden="1" spans="1:19">
+    <row r="174" ht="14.25" spans="1:19">
       <c r="A174" s="4" t="s">
         <v>667</v>
       </c>
@@ -15946,7 +15958,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" ht="14.25" hidden="1" spans="1:19">
+    <row r="175" ht="14.25" spans="1:19">
       <c r="A175" s="4" t="s">
         <v>669</v>
       </c>
@@ -16003,7 +16015,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="176" ht="14.25" hidden="1" spans="1:19">
+    <row r="176" ht="14.25" spans="1:19">
       <c r="A176" s="4" t="s">
         <v>671</v>
       </c>
@@ -16060,7 +16072,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="177" ht="14.25" hidden="1" spans="1:19">
+    <row r="177" ht="14.25" spans="1:19">
       <c r="A177" s="4" t="s">
         <v>673</v>
       </c>
@@ -16117,7 +16129,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="178" ht="14.25" hidden="1" spans="1:19">
+    <row r="178" ht="14.25" spans="1:19">
       <c r="A178" s="4" t="s">
         <v>677</v>
       </c>
@@ -16174,7 +16186,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="179" ht="14.25" hidden="1" spans="1:19">
+    <row r="179" ht="14.25" spans="1:19">
       <c r="A179" s="4" t="s">
         <v>679</v>
       </c>
@@ -16231,7 +16243,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" ht="14.25" hidden="1" spans="1:19">
+    <row r="180" ht="14.25" spans="1:19">
       <c r="A180" s="4" t="s">
         <v>681</v>
       </c>
@@ -16288,7 +16300,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" ht="14.25" hidden="1" spans="1:19">
+    <row r="181" ht="14.25" spans="1:19">
       <c r="A181" s="4" t="s">
         <v>683</v>
       </c>
@@ -16345,7 +16357,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" ht="14.25" hidden="1" spans="1:19">
+    <row r="182" ht="14.25" spans="1:19">
       <c r="A182" s="4" t="s">
         <v>685</v>
       </c>
@@ -16402,7 +16414,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" ht="14.25" hidden="1" spans="1:19">
+    <row r="183" ht="14.25" spans="1:19">
       <c r="A183" s="4" t="s">
         <v>687</v>
       </c>
@@ -16459,7 +16471,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" ht="14.25" hidden="1" spans="1:19">
+    <row r="184" ht="14.25" spans="1:19">
       <c r="A184" s="4" t="s">
         <v>690</v>
       </c>
@@ -16516,7 +16528,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" ht="14.25" hidden="1" spans="1:19">
+    <row r="185" ht="14.25" spans="1:19">
       <c r="A185" s="4" t="s">
         <v>692</v>
       </c>
@@ -16573,7 +16585,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" ht="14.25" hidden="1" spans="1:19">
+    <row r="186" ht="14.25" spans="1:19">
       <c r="A186" s="4" t="s">
         <v>694</v>
       </c>
@@ -16628,7 +16640,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="187" ht="14.25" hidden="1" spans="1:19">
+    <row r="187" ht="14.25" spans="1:19">
       <c r="A187" s="4" t="s">
         <v>698</v>
       </c>
@@ -16685,7 +16697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" ht="14.25" hidden="1" spans="1:19">
+    <row r="188" ht="14.25" spans="1:19">
       <c r="A188" s="4" t="s">
         <v>700</v>
       </c>
@@ -16742,7 +16754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" ht="14.25" hidden="1" spans="1:19">
+    <row r="189" ht="14.25" spans="1:19">
       <c r="A189" s="4" t="s">
         <v>702</v>
       </c>
@@ -16801,7 +16813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" ht="14.25" hidden="1" spans="1:19">
+    <row r="190" ht="14.25" spans="1:19">
       <c r="A190" s="4" t="s">
         <v>706</v>
       </c>
@@ -16856,7 +16868,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" ht="14.25" hidden="1" spans="1:19">
+    <row r="191" ht="14.25" spans="1:19">
       <c r="A191" s="4" t="s">
         <v>708</v>
       </c>
@@ -16915,7 +16927,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" ht="14.25" hidden="1" spans="1:19">
+    <row r="192" ht="14.25" spans="1:19">
       <c r="A192" s="4" t="s">
         <v>710</v>
       </c>
@@ -16974,7 +16986,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="193" ht="14.25" hidden="1" spans="1:19">
+    <row r="193" ht="14.25" spans="1:19">
       <c r="A193" s="4" t="s">
         <v>714</v>
       </c>
@@ -17033,7 +17045,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="194" ht="14.25" hidden="1" spans="1:19">
+    <row r="194" ht="14.25" spans="1:19">
       <c r="A194" s="4" t="s">
         <v>717</v>
       </c>
@@ -17092,7 +17104,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="195" ht="14.25" hidden="1" spans="1:19">
+    <row r="195" ht="14.25" spans="1:19">
       <c r="A195" s="4" t="s">
         <v>719</v>
       </c>
@@ -17151,7 +17163,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="196" ht="14.25" hidden="1" spans="1:19">
+    <row r="196" ht="14.25" spans="1:19">
       <c r="A196" s="4" t="s">
         <v>722</v>
       </c>
@@ -17208,7 +17220,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="197" ht="14.25" hidden="1" spans="1:19">
+    <row r="197" ht="14.25" spans="1:19">
       <c r="A197" s="4" t="s">
         <v>723</v>
       </c>
@@ -17265,7 +17277,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="198" ht="14.25" hidden="1" spans="1:19">
+    <row r="198" ht="14.25" spans="1:19">
       <c r="A198" s="4" t="s">
         <v>725</v>
       </c>
@@ -17322,7 +17334,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="199" ht="27" hidden="1" spans="1:19">
+    <row r="199" ht="27" spans="1:19">
       <c r="A199" s="4" t="s">
         <v>727</v>
       </c>
@@ -17379,7 +17391,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="200" ht="14.25" hidden="1" spans="1:19">
+    <row r="200" ht="14.25" spans="1:19">
       <c r="A200" s="4" t="s">
         <v>731</v>
       </c>
@@ -17436,7 +17448,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="201" ht="14.25" hidden="1" spans="1:19">
+    <row r="201" ht="14.25" spans="1:19">
       <c r="A201" s="4" t="s">
         <v>735</v>
       </c>
@@ -17493,7 +17505,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="202" ht="14.25" hidden="1" spans="1:19">
+    <row r="202" ht="14.25" spans="1:19">
       <c r="A202" s="4" t="s">
         <v>738</v>
       </c>
@@ -17550,7 +17562,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="203" ht="14.25" hidden="1" spans="1:19">
+    <row r="203" ht="14.25" spans="1:19">
       <c r="A203" s="4" t="s">
         <v>740</v>
       </c>
@@ -17607,7 +17619,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="204" ht="14.25" hidden="1" spans="1:19">
+    <row r="204" ht="14.25" spans="1:19">
       <c r="A204" s="4" t="s">
         <v>742</v>
       </c>
@@ -17664,7 +17676,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="205" ht="14.25" hidden="1" spans="1:19">
+    <row r="205" ht="14.25" spans="1:19">
       <c r="A205" s="4" t="s">
         <v>745</v>
       </c>
@@ -17723,7 +17735,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" ht="14.25" hidden="1" spans="1:19">
+    <row r="206" ht="14.25" spans="1:19">
       <c r="A206" s="4" t="s">
         <v>749</v>
       </c>
@@ -17780,7 +17792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" ht="14.25" hidden="1" spans="1:19">
+    <row r="207" ht="14.25" spans="1:19">
       <c r="A207" s="4" t="s">
         <v>751</v>
       </c>
@@ -17837,7 +17849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" ht="14.25" hidden="1" spans="1:19">
+    <row r="208" ht="14.25" spans="1:19">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -17894,7 +17906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" ht="14.25" hidden="1" spans="1:19">
+    <row r="209" ht="14.25" spans="1:19">
       <c r="A209" s="4" t="s">
         <v>755</v>
       </c>
@@ -17949,7 +17961,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" ht="14.25" hidden="1" spans="1:19">
+    <row r="210" ht="14.25" spans="1:19">
       <c r="A210" s="4" t="s">
         <v>757</v>
       </c>
@@ -18006,7 +18018,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" ht="14.25" hidden="1" spans="1:19">
+    <row r="211" ht="14.25" spans="1:19">
       <c r="A211" s="4" t="s">
         <v>759</v>
       </c>
@@ -18063,7 +18075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="212" ht="14.25" hidden="1" spans="1:19">
+    <row r="212" ht="14.25" spans="1:19">
       <c r="A212" s="4" t="s">
         <v>761</v>
       </c>
@@ -18120,7 +18132,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="213" ht="14.25" hidden="1" spans="1:19">
+    <row r="213" ht="14.25" spans="1:19">
       <c r="A213" s="4" t="s">
         <v>763</v>
       </c>
@@ -18177,7 +18189,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="214" ht="14.25" hidden="1" spans="1:19">
+    <row r="214" ht="14.25" spans="1:19">
       <c r="A214" s="4" t="s">
         <v>765</v>
       </c>
@@ -18234,7 +18246,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="215" ht="14.25" hidden="1" spans="1:19">
+    <row r="215" ht="14.25" spans="1:19">
       <c r="A215" s="4" t="s">
         <v>768</v>
       </c>
@@ -18291,7 +18303,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="216" ht="14.25" hidden="1" spans="1:19">
+    <row r="216" ht="14.25" spans="1:19">
       <c r="A216" s="4" t="s">
         <v>770</v>
       </c>
@@ -18350,7 +18362,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="217" ht="14.25" hidden="1" spans="1:19">
+    <row r="217" ht="14.25" spans="1:19">
       <c r="A217" s="4" t="s">
         <v>773</v>
       </c>
@@ -18407,7 +18419,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="218" ht="14.25" hidden="1" spans="1:19">
+    <row r="218" ht="14.25" spans="1:19">
       <c r="A218" s="4" t="s">
         <v>775</v>
       </c>
@@ -18464,7 +18476,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="219" ht="27" hidden="1" spans="1:19">
+    <row r="219" ht="27" spans="1:19">
       <c r="A219" s="4" t="s">
         <v>777</v>
       </c>
@@ -18519,7 +18531,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="220" ht="27" hidden="1" spans="1:19">
+    <row r="220" ht="27" spans="1:19">
       <c r="A220" s="4" t="s">
         <v>781</v>
       </c>
@@ -18574,7 +18586,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="221" ht="27" hidden="1" spans="1:19">
+    <row r="221" ht="27" spans="1:19">
       <c r="A221" s="4" t="s">
         <v>783</v>
       </c>
@@ -18629,7 +18641,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="222" ht="27" hidden="1" spans="1:19">
+    <row r="222" ht="27" spans="1:19">
       <c r="A222" s="4" t="s">
         <v>785</v>
       </c>
@@ -18684,7 +18696,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="223" ht="27" hidden="1" spans="1:19">
+    <row r="223" ht="27" spans="1:19">
       <c r="A223" s="4" t="s">
         <v>787</v>
       </c>
@@ -18739,7 +18751,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="224" ht="27" hidden="1" spans="1:19">
+    <row r="224" ht="27" spans="1:19">
       <c r="A224" s="4" t="s">
         <v>789</v>
       </c>
@@ -18794,7 +18806,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="225" ht="14.25" hidden="1" spans="1:19">
+    <row r="225" ht="14.25" spans="1:19">
       <c r="A225" s="4" t="s">
         <v>791</v>
       </c>
@@ -18851,7 +18863,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="226" ht="14.25" hidden="1" spans="1:19">
+    <row r="226" ht="14.25" spans="1:19">
       <c r="A226" s="4" t="s">
         <v>793</v>
       </c>
@@ -18908,7 +18920,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="227" ht="14.25" hidden="1" spans="1:19">
+    <row r="227" ht="14.25" spans="1:19">
       <c r="A227" s="4" t="s">
         <v>794</v>
       </c>
@@ -18965,7 +18977,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="228" ht="14.25" hidden="1" spans="1:19">
+    <row r="228" ht="14.25" spans="1:19">
       <c r="A228" s="4" t="s">
         <v>796</v>
       </c>
@@ -19022,7 +19034,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" ht="14.25" hidden="1" spans="1:19">
+    <row r="229" ht="14.25" spans="1:19">
       <c r="A229" s="4" t="s">
         <v>798</v>
       </c>
@@ -19079,7 +19091,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="230" ht="14.25" hidden="1" spans="1:19">
+    <row r="230" ht="14.25" spans="1:19">
       <c r="A230" s="4" t="s">
         <v>800</v>
       </c>
@@ -19136,7 +19148,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="231" ht="14.25" hidden="1" spans="1:19">
+    <row r="231" ht="14.25" spans="1:19">
       <c r="A231" s="4" t="s">
         <v>802</v>
       </c>
@@ -19193,7 +19205,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="232" ht="14.25" hidden="1" spans="1:19">
+    <row r="232" ht="14.25" spans="1:19">
       <c r="A232" s="4" t="s">
         <v>804</v>
       </c>
@@ -19250,7 +19262,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="233" ht="14.25" hidden="1" spans="1:19">
+    <row r="233" ht="14.25" spans="1:19">
       <c r="A233" s="4" t="s">
         <v>806</v>
       </c>
@@ -19307,7 +19319,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" ht="14.25" hidden="1" spans="1:19">
+    <row r="234" ht="14.25" spans="1:19">
       <c r="A234" s="4" t="s">
         <v>808</v>
       </c>
@@ -19364,7 +19376,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="235" ht="14.25" hidden="1" spans="1:19">
+    <row r="235" ht="14.25" spans="1:19">
       <c r="A235" s="4" t="s">
         <v>810</v>
       </c>
@@ -19421,7 +19433,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="236" ht="27" hidden="1" spans="1:19">
+    <row r="236" ht="27" spans="1:19">
       <c r="A236" s="4" t="s">
         <v>812</v>
       </c>
@@ -19476,7 +19488,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="237" ht="27" hidden="1" spans="1:19">
+    <row r="237" ht="27" spans="1:19">
       <c r="A237" s="4" t="s">
         <v>817</v>
       </c>
@@ -19531,7 +19543,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="238" ht="27" hidden="1" spans="1:19">
+    <row r="238" ht="27" spans="1:19">
       <c r="A238" s="4" t="s">
         <v>819</v>
       </c>
@@ -19586,7 +19598,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="239" ht="14.25" hidden="1" spans="1:19">
+    <row r="239" ht="14.25" spans="1:19">
       <c r="A239" s="4" t="s">
         <v>821</v>
       </c>
@@ -19641,7 +19653,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="240" ht="14.25" hidden="1" spans="1:19">
+    <row r="240" ht="14.25" spans="1:19">
       <c r="A240" s="4" t="s">
         <v>825</v>
       </c>
@@ -19698,7 +19710,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" ht="14.25" hidden="1" spans="1:19">
+    <row r="241" ht="14.25" spans="1:19">
       <c r="A241" s="4" t="s">
         <v>827</v>
       </c>
@@ -19755,7 +19767,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" ht="14.25" hidden="1" spans="1:19">
+    <row r="242" ht="14.25" spans="1:19">
       <c r="A242" s="4" t="s">
         <v>829</v>
       </c>
@@ -19812,7 +19824,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="243" ht="14.25" hidden="1" spans="1:19">
+    <row r="243" ht="14.25" spans="1:19">
       <c r="A243" s="4" t="s">
         <v>832</v>
       </c>
@@ -19869,7 +19881,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" ht="14.25" hidden="1" spans="1:19">
+    <row r="244" ht="14.25" spans="1:19">
       <c r="A244" s="4" t="s">
         <v>836</v>
       </c>
@@ -19926,7 +19938,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="245" ht="14.25" hidden="1" spans="1:19">
+    <row r="245" ht="14.25" spans="1:19">
       <c r="A245" s="4" t="s">
         <v>838</v>
       </c>
@@ -19983,7 +19995,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="246" ht="14.25" hidden="1" spans="1:19">
+    <row r="246" ht="14.25" spans="1:19">
       <c r="A246" s="4" t="s">
         <v>842</v>
       </c>
@@ -20038,7 +20050,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="247" ht="14.25" hidden="1" spans="1:19">
+    <row r="247" ht="14.25" spans="1:19">
       <c r="A247" s="4" t="s">
         <v>846</v>
       </c>
@@ -20093,7 +20105,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" ht="14.25" hidden="1" spans="1:19">
+    <row r="248" ht="14.25" spans="1:19">
       <c r="A248" s="4" t="s">
         <v>849</v>
       </c>
@@ -20148,7 +20160,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" ht="14.25" hidden="1" spans="1:19">
+    <row r="249" ht="14.25" spans="1:19">
       <c r="A249" s="4" t="s">
         <v>851</v>
       </c>
@@ -20203,7 +20215,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" ht="14.25" hidden="1" spans="1:19">
+    <row r="250" ht="14.25" spans="1:19">
       <c r="A250" s="4" t="s">
         <v>853</v>
       </c>
@@ -20258,7 +20270,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" ht="14.25" hidden="1" spans="1:19">
+    <row r="251" ht="14.25" spans="1:19">
       <c r="A251" s="4" t="s">
         <v>855</v>
       </c>
@@ -20315,7 +20327,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="252" ht="14.25" hidden="1" spans="1:19">
+    <row r="252" ht="14.25" spans="1:19">
       <c r="A252" s="4" t="s">
         <v>857</v>
       </c>
@@ -20372,7 +20384,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="253" ht="14.25" hidden="1" spans="1:19">
+    <row r="253" ht="14.25" spans="1:19">
       <c r="A253" s="4" t="s">
         <v>859</v>
       </c>
@@ -20429,7 +20441,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="254" ht="14.25" hidden="1" spans="1:19">
+    <row r="254" ht="14.25" spans="1:19">
       <c r="A254" s="4" t="s">
         <v>861</v>
       </c>
@@ -20486,7 +20498,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="255" ht="14.25" hidden="1" spans="1:19">
+    <row r="255" ht="14.25" spans="1:19">
       <c r="A255" s="4" t="s">
         <v>863</v>
       </c>
@@ -20545,7 +20557,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="256" ht="14.25" hidden="1" spans="1:19">
+    <row r="256" ht="14.25" spans="1:19">
       <c r="A256" s="4" t="s">
         <v>866</v>
       </c>
@@ -20602,7 +20614,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="257" ht="15" hidden="1" spans="1:19">
+    <row r="257" ht="15" spans="1:19">
       <c r="A257" s="4" t="s">
         <v>868</v>
       </c>
@@ -20773,7 +20785,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="260" ht="14.25" hidden="1" spans="1:19">
+    <row r="260" ht="14.25" spans="1:19">
       <c r="A260" s="4" t="s">
         <v>877</v>
       </c>
@@ -20824,7 +20836,7 @@
       <c r="R260" s="7"/>
       <c r="S260" s="7"/>
     </row>
-    <row r="261" ht="14.25" hidden="1" spans="1:19">
+    <row r="261" ht="14.25" spans="1:19">
       <c r="A261" s="4" t="s">
         <v>881</v>
       </c>
@@ -20875,7 +20887,7 @@
       <c r="R261" s="7"/>
       <c r="S261" s="7"/>
     </row>
-    <row r="262" ht="14.25" hidden="1" spans="1:19">
+    <row r="262" ht="14.25" spans="1:19">
       <c r="A262" s="4" t="s">
         <v>886</v>
       </c>
@@ -20926,7 +20938,7 @@
       <c r="R262" s="7"/>
       <c r="S262" s="7"/>
     </row>
-    <row r="263" ht="14.25" hidden="1" spans="1:19">
+    <row r="263" ht="14.25" spans="1:19">
       <c r="A263" s="4" t="s">
         <v>889</v>
       </c>
@@ -20977,7 +20989,7 @@
       <c r="R263" s="7"/>
       <c r="S263" s="7"/>
     </row>
-    <row r="264" ht="14.25" hidden="1" spans="1:19">
+    <row r="264" ht="14.25" spans="1:19">
       <c r="A264" s="4" t="s">
         <v>893</v>
       </c>
@@ -21028,7 +21040,7 @@
       <c r="R264" s="7"/>
       <c r="S264" s="7"/>
     </row>
-    <row r="265" ht="14.25" hidden="1" spans="1:19">
+    <row r="265" ht="14.25" spans="1:19">
       <c r="A265" s="4" t="s">
         <v>896</v>
       </c>
@@ -21079,7 +21091,7 @@
       <c r="R265" s="7"/>
       <c r="S265" s="7"/>
     </row>
-    <row r="266" ht="14.25" hidden="1" spans="1:19">
+    <row r="266" ht="14.25" spans="1:19">
       <c r="A266" s="4" t="s">
         <v>900</v>
       </c>
@@ -21130,7 +21142,7 @@
       <c r="R266" s="7"/>
       <c r="S266" s="7"/>
     </row>
-    <row r="267" ht="14.25" hidden="1" spans="1:19">
+    <row r="267" ht="14.25" spans="1:19">
       <c r="A267" s="4" t="s">
         <v>904</v>
       </c>
@@ -21181,7 +21193,7 @@
       <c r="R267" s="7"/>
       <c r="S267" s="7"/>
     </row>
-    <row r="268" ht="14.25" hidden="1" spans="1:19">
+    <row r="268" ht="14.25" spans="1:19">
       <c r="A268" s="4" t="s">
         <v>907</v>
       </c>
@@ -21232,7 +21244,7 @@
       <c r="R268" s="7"/>
       <c r="S268" s="7"/>
     </row>
-    <row r="269" ht="14.25" hidden="1" spans="1:19">
+    <row r="269" ht="14.25" spans="1:19">
       <c r="A269" s="4" t="s">
         <v>909</v>
       </c>
@@ -21283,7 +21295,7 @@
       <c r="R269" s="7"/>
       <c r="S269" s="7"/>
     </row>
-    <row r="270" ht="14.25" hidden="1" spans="1:19">
+    <row r="270" ht="14.25" spans="1:19">
       <c r="A270" s="4" t="s">
         <v>912</v>
       </c>
@@ -21334,7 +21346,7 @@
       <c r="R270" s="7"/>
       <c r="S270" s="7"/>
     </row>
-    <row r="271" ht="14.25" hidden="1" spans="1:19">
+    <row r="271" ht="14.25" spans="1:19">
       <c r="A271" s="4" t="s">
         <v>914</v>
       </c>
@@ -21387,7 +21399,7 @@
       <c r="R271" s="7"/>
       <c r="S271" s="7"/>
     </row>
-    <row r="272" ht="14.25" hidden="1" spans="1:19">
+    <row r="272" ht="14.25" spans="1:19">
       <c r="A272" s="4" t="s">
         <v>918</v>
       </c>
@@ -21440,7 +21452,7 @@
       <c r="R272" s="7"/>
       <c r="S272" s="7"/>
     </row>
-    <row r="273" ht="14.25" hidden="1" spans="1:19">
+    <row r="273" ht="14.25" spans="1:19">
       <c r="A273" s="4" t="s">
         <v>920</v>
       </c>
@@ -21493,7 +21505,7 @@
       <c r="R273" s="7"/>
       <c r="S273" s="7"/>
     </row>
-    <row r="274" ht="14.25" hidden="1" spans="1:19">
+    <row r="274" ht="14.25" spans="1:19">
       <c r="A274" s="4" t="s">
         <v>923</v>
       </c>
@@ -21544,7 +21556,7 @@
       <c r="R274" s="7"/>
       <c r="S274" s="7"/>
     </row>
-    <row r="275" ht="14.25" hidden="1" spans="1:19">
+    <row r="275" ht="14.25" spans="1:19">
       <c r="A275" s="4" t="s">
         <v>927</v>
       </c>
@@ -21595,7 +21607,7 @@
       <c r="R275" s="7"/>
       <c r="S275" s="7"/>
     </row>
-    <row r="276" ht="14.25" hidden="1" spans="1:19">
+    <row r="276" ht="14.25" spans="1:19">
       <c r="A276" s="4" t="s">
         <v>930</v>
       </c>
@@ -21646,7 +21658,7 @@
       <c r="R276" s="7"/>
       <c r="S276" s="7"/>
     </row>
-    <row r="277" ht="14.25" hidden="1" spans="1:19">
+    <row r="277" ht="14.25" spans="1:19">
       <c r="A277" s="4" t="s">
         <v>932</v>
       </c>
@@ -21697,7 +21709,7 @@
       <c r="R277" s="7"/>
       <c r="S277" s="7"/>
     </row>
-    <row r="278" ht="14.25" hidden="1" spans="1:19">
+    <row r="278" ht="14.25" spans="1:19">
       <c r="A278" s="4" t="s">
         <v>935</v>
       </c>
@@ -21748,7 +21760,7 @@
       <c r="R278" s="7"/>
       <c r="S278" s="7"/>
     </row>
-    <row r="279" ht="14.25" hidden="1" spans="1:19">
+    <row r="279" ht="14.25" spans="1:19">
       <c r="A279" s="4" t="s">
         <v>937</v>
       </c>
@@ -21801,7 +21813,7 @@
       <c r="R279" s="7"/>
       <c r="S279" s="7"/>
     </row>
-    <row r="280" ht="14.25" hidden="1" spans="1:19">
+    <row r="280" ht="14.25" spans="1:19">
       <c r="A280" s="4" t="s">
         <v>940</v>
       </c>
@@ -21854,7 +21866,7 @@
       <c r="R280" s="7"/>
       <c r="S280" s="7"/>
     </row>
-    <row r="281" ht="14.25" hidden="1" spans="1:19">
+    <row r="281" ht="14.25" spans="1:19">
       <c r="A281" s="4" t="s">
         <v>943</v>
       </c>
@@ -21905,7 +21917,7 @@
       <c r="R281" s="7"/>
       <c r="S281" s="7"/>
     </row>
-    <row r="282" ht="14.25" hidden="1" spans="1:19">
+    <row r="282" ht="14.25" spans="1:19">
       <c r="A282" s="4" t="s">
         <v>946</v>
       </c>
@@ -21956,7 +21968,7 @@
       <c r="R282" s="7"/>
       <c r="S282" s="7"/>
     </row>
-    <row r="283" ht="14.25" hidden="1" spans="1:19">
+    <row r="283" ht="14.25" spans="1:19">
       <c r="A283" s="4" t="s">
         <v>950</v>
       </c>
@@ -22007,7 +22019,7 @@
       <c r="R283" s="7"/>
       <c r="S283" s="7"/>
     </row>
-    <row r="284" ht="14.25" hidden="1" spans="1:19">
+    <row r="284" ht="14.25" spans="1:19">
       <c r="A284" s="4" t="s">
         <v>953</v>
       </c>
@@ -22058,7 +22070,7 @@
       <c r="R284" s="7"/>
       <c r="S284" s="7"/>
     </row>
-    <row r="285" ht="14.25" hidden="1" spans="1:19">
+    <row r="285" ht="14.25" spans="1:19">
       <c r="A285" s="4" t="s">
         <v>937</v>
       </c>
@@ -22109,7 +22121,7 @@
       <c r="R285" s="7"/>
       <c r="S285" s="7"/>
     </row>
-    <row r="286" ht="14.25" hidden="1" spans="1:19">
+    <row r="286" ht="14.25" spans="1:19">
       <c r="A286" s="4" t="s">
         <v>940</v>
       </c>
@@ -22160,7 +22172,7 @@
       <c r="R286" s="7"/>
       <c r="S286" s="7"/>
     </row>
-    <row r="287" ht="14.25" hidden="1" spans="1:19">
+    <row r="287" ht="14.25" spans="1:19">
       <c r="A287" s="4" t="s">
         <v>959</v>
       </c>
@@ -22211,7 +22223,7 @@
       <c r="R287" s="7"/>
       <c r="S287" s="7"/>
     </row>
-    <row r="288" ht="14.25" hidden="1" spans="1:19">
+    <row r="288" ht="14.25" spans="1:19">
       <c r="A288" s="4" t="s">
         <v>963</v>
       </c>
@@ -22262,7 +22274,7 @@
       <c r="R288" s="7"/>
       <c r="S288" s="7"/>
     </row>
-    <row r="289" ht="14.25" hidden="1" spans="1:19">
+    <row r="289" ht="14.25" spans="1:19">
       <c r="A289" s="4" t="s">
         <v>965</v>
       </c>
@@ -22313,7 +22325,7 @@
       <c r="R289" s="7"/>
       <c r="S289" s="7"/>
     </row>
-    <row r="290" ht="14.25" hidden="1" spans="1:19">
+    <row r="290" ht="14.25" spans="1:19">
       <c r="A290" s="4" t="s">
         <v>967</v>
       </c>
@@ -22364,7 +22376,7 @@
       <c r="R290" s="7"/>
       <c r="S290" s="7"/>
     </row>
-    <row r="291" ht="14.25" hidden="1" spans="1:19">
+    <row r="291" ht="14.25" spans="1:19">
       <c r="A291" s="4" t="s">
         <v>969</v>
       </c>
@@ -22415,7 +22427,7 @@
       <c r="R291" s="7"/>
       <c r="S291" s="7"/>
     </row>
-    <row r="292" ht="27" hidden="1" spans="1:19">
+    <row r="292" ht="27" spans="1:19">
       <c r="A292" s="4" t="s">
         <v>973</v>
       </c>
@@ -22466,7 +22478,7 @@
       <c r="R292" s="7"/>
       <c r="S292" s="7"/>
     </row>
-    <row r="293" ht="14.25" hidden="1" spans="1:19">
+    <row r="293" ht="14.25" spans="1:19">
       <c r="A293" s="4" t="s">
         <v>977</v>
       </c>
@@ -22517,7 +22529,7 @@
       <c r="R293" s="7"/>
       <c r="S293" s="7"/>
     </row>
-    <row r="294" ht="14.25" hidden="1" spans="1:19">
+    <row r="294" ht="14.25" spans="1:19">
       <c r="A294" s="4" t="s">
         <v>981</v>
       </c>
@@ -22568,7 +22580,7 @@
       <c r="R294" s="7"/>
       <c r="S294" s="7"/>
     </row>
-    <row r="295" ht="14.25" hidden="1" spans="1:19">
+    <row r="295" ht="14.25" spans="1:19">
       <c r="A295" s="4" t="s">
         <v>984</v>
       </c>
@@ -22619,7 +22631,7 @@
       <c r="R295" s="7"/>
       <c r="S295" s="7"/>
     </row>
-    <row r="296" ht="14.25" hidden="1" spans="1:19">
+    <row r="296" ht="14.25" spans="1:19">
       <c r="A296" s="4" t="s">
         <v>987</v>
       </c>
@@ -22670,7 +22682,7 @@
       <c r="R296" s="7"/>
       <c r="S296" s="7"/>
     </row>
-    <row r="297" ht="14.25" hidden="1" spans="1:19">
+    <row r="297" ht="14.25" spans="1:19">
       <c r="A297" s="4" t="s">
         <v>990</v>
       </c>
@@ -22721,7 +22733,7 @@
       <c r="R297" s="7"/>
       <c r="S297" s="7"/>
     </row>
-    <row r="298" ht="14.25" hidden="1" spans="1:19">
+    <row r="298" ht="14.25" spans="1:19">
       <c r="A298" s="4" t="s">
         <v>992</v>
       </c>
@@ -22772,7 +22784,7 @@
       <c r="R298" s="7"/>
       <c r="S298" s="7"/>
     </row>
-    <row r="299" ht="14.25" hidden="1" spans="1:19">
+    <row r="299" ht="14.25" spans="1:19">
       <c r="A299" s="4" t="s">
         <v>996</v>
       </c>
@@ -22823,7 +22835,7 @@
       <c r="R299" s="7"/>
       <c r="S299" s="7"/>
     </row>
-    <row r="300" hidden="1" spans="1:19">
+    <row r="300" spans="1:19">
       <c r="A300" s="4" t="s">
         <v>999</v>
       </c>
@@ -22929,7 +22941,7 @@
       <c r="R301" s="7"/>
       <c r="S301" s="7"/>
     </row>
-    <row r="302" hidden="1" spans="1:19">
+    <row r="302" spans="1:19">
       <c r="A302" s="4" t="s">
         <v>1008</v>
       </c>
@@ -22982,7 +22994,7 @@
       <c r="R302" s="7"/>
       <c r="S302" s="7"/>
     </row>
-    <row r="303" hidden="1" spans="1:19">
+    <row r="303" spans="1:19">
       <c r="A303" s="4" t="s">
         <v>1011</v>
       </c>
@@ -23035,7 +23047,7 @@
       <c r="R303" s="7"/>
       <c r="S303" s="7"/>
     </row>
-    <row r="304" ht="14.25" hidden="1" spans="1:19">
+    <row r="304" ht="14.25" spans="1:19">
       <c r="A304" s="4" t="s">
         <v>1014</v>
       </c>
@@ -23088,7 +23100,7 @@
       <c r="R304" s="7"/>
       <c r="S304" s="7"/>
     </row>
-    <row r="305" ht="27.75" hidden="1" spans="1:19">
+    <row r="305" ht="27.75" spans="1:19">
       <c r="A305" s="4" t="s">
         <v>1017</v>
       </c>
@@ -23141,7 +23153,7 @@
       <c r="R305" s="7"/>
       <c r="S305" s="7"/>
     </row>
-    <row r="306" ht="27" hidden="1" spans="1:19">
+    <row r="306" ht="27" spans="1:19">
       <c r="A306" s="4" t="s">
         <v>1021</v>
       </c>
@@ -23194,7 +23206,7 @@
       <c r="R306" s="7"/>
       <c r="S306" s="7"/>
     </row>
-    <row r="307" hidden="1" spans="1:19">
+    <row r="307" spans="1:19">
       <c r="A307" s="4" t="s">
         <v>1024</v>
       </c>
@@ -23247,7 +23259,7 @@
       <c r="R307" s="7"/>
       <c r="S307" s="7"/>
     </row>
-    <row r="308" hidden="1" spans="1:19">
+    <row r="308" spans="1:19">
       <c r="A308" s="4" t="s">
         <v>1028</v>
       </c>
@@ -23302,7 +23314,7 @@
       <c r="R308" s="7"/>
       <c r="S308" s="7"/>
     </row>
-    <row r="309" hidden="1" spans="1:19">
+    <row r="309" spans="1:19">
       <c r="A309" s="4" t="s">
         <v>1032</v>
       </c>
@@ -23357,7 +23369,7 @@
       <c r="R309" s="7"/>
       <c r="S309" s="7"/>
     </row>
-    <row r="310" hidden="1" spans="1:19">
+    <row r="310" spans="1:19">
       <c r="A310" s="4" t="s">
         <v>1035</v>
       </c>
@@ -23410,7 +23422,7 @@
       <c r="R310" s="7"/>
       <c r="S310" s="7"/>
     </row>
-    <row r="311" ht="27" hidden="1" spans="1:19">
+    <row r="311" ht="27" spans="1:19">
       <c r="A311" s="4" t="s">
         <v>1038</v>
       </c>
@@ -23463,7 +23475,7 @@
       <c r="R311" s="7"/>
       <c r="S311" s="7"/>
     </row>
-    <row r="312" ht="27" hidden="1" spans="1:19">
+    <row r="312" ht="27" spans="1:19">
       <c r="A312" s="4" t="s">
         <v>1042</v>
       </c>
@@ -23516,7 +23528,7 @@
       <c r="R312" s="7"/>
       <c r="S312" s="7"/>
     </row>
-    <row r="313" ht="27" hidden="1" spans="1:19">
+    <row r="313" ht="27" spans="1:19">
       <c r="A313" s="4" t="s">
         <v>1046</v>
       </c>
@@ -23569,7 +23581,7 @@
       <c r="R313" s="7"/>
       <c r="S313" s="7"/>
     </row>
-    <row r="314" hidden="1" spans="1:19">
+    <row r="314" spans="1:19">
       <c r="A314" s="4" t="s">
         <v>1050</v>
       </c>
@@ -23622,7 +23634,7 @@
       <c r="R314" s="7"/>
       <c r="S314" s="7"/>
     </row>
-    <row r="315" hidden="1" spans="1:19">
+    <row r="315" spans="1:19">
       <c r="A315" s="4" t="s">
         <v>1054</v>
       </c>
@@ -23675,7 +23687,7 @@
       <c r="R315" s="7"/>
       <c r="S315" s="7"/>
     </row>
-    <row r="316" hidden="1" spans="1:19">
+    <row r="316" spans="1:19">
       <c r="A316" s="4" t="s">
         <v>1058</v>
       </c>
@@ -23728,7 +23740,7 @@
       <c r="R316" s="7"/>
       <c r="S316" s="7"/>
     </row>
-    <row r="317" hidden="1" spans="1:19">
+    <row r="317" spans="1:19">
       <c r="A317" s="4" t="s">
         <v>1062</v>
       </c>
@@ -23777,7 +23789,7 @@
       <c r="R317" s="7"/>
       <c r="S317" s="7"/>
     </row>
-    <row r="318" hidden="1" spans="1:19">
+    <row r="318" spans="1:19">
       <c r="A318" s="4" t="s">
         <v>1065</v>
       </c>
@@ -23826,7 +23838,7 @@
       <c r="R318" s="7"/>
       <c r="S318" s="7"/>
     </row>
-    <row r="319" hidden="1" spans="1:15">
+    <row r="319" spans="1:15">
       <c r="A319" s="4" t="s">
         <v>1067</v>
       </c>
@@ -23871,7 +23883,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:15">
+    <row r="320" spans="1:15">
       <c r="A320" s="4" t="s">
         <v>1072</v>
       </c>
@@ -23916,7 +23928,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:15">
+    <row r="321" spans="1:15">
       <c r="A321" s="4" t="s">
         <v>1075</v>
       </c>
@@ -23961,7 +23973,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:15">
+    <row r="322" spans="1:15">
       <c r="A322" s="4" t="s">
         <v>1077</v>
       </c>
@@ -24006,7 +24018,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:15">
+    <row r="323" spans="1:15">
       <c r="A323" s="4" t="s">
         <v>1080</v>
       </c>
@@ -24051,7 +24063,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:15">
+    <row r="324" spans="1:15">
       <c r="A324" s="4" t="s">
         <v>1083</v>
       </c>
@@ -24096,7 +24108,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:15">
+    <row r="325" spans="1:15">
       <c r="A325" s="4" t="s">
         <v>1086</v>
       </c>
@@ -24141,7 +24153,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:15">
+    <row r="326" spans="1:15">
       <c r="A326" s="4" t="s">
         <v>1088</v>
       </c>
@@ -24186,7 +24198,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:15">
+    <row r="327" spans="1:15">
       <c r="A327" s="4" t="s">
         <v>1091</v>
       </c>
@@ -24231,7 +24243,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:15">
+    <row r="328" spans="1:15">
       <c r="A328" s="4" t="s">
         <v>1093</v>
       </c>
@@ -24276,7 +24288,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:15">
+    <row r="329" spans="1:15">
       <c r="A329" s="4" t="s">
         <v>1095</v>
       </c>
@@ -24321,7 +24333,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:15">
+    <row r="330" spans="1:15">
       <c r="A330" s="4" t="s">
         <v>1098</v>
       </c>
@@ -24366,7 +24378,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:15">
+    <row r="331" spans="1:15">
       <c r="A331" s="4" t="s">
         <v>1100</v>
       </c>
@@ -24411,7 +24423,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:15">
+    <row r="332" spans="1:15">
       <c r="A332" s="4" t="s">
         <v>1102</v>
       </c>
@@ -24456,7 +24468,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:15">
+    <row r="333" spans="1:15">
       <c r="A333" s="4" t="s">
         <v>1104</v>
       </c>
@@ -24501,7 +24513,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:15">
+    <row r="334" spans="1:15">
       <c r="A334" s="4" t="s">
         <v>1106</v>
       </c>
@@ -24546,7 +24558,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:15">
+    <row r="335" spans="1:15">
       <c r="A335" s="4" t="s">
         <v>1109</v>
       </c>
@@ -24591,7 +24603,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:15">
+    <row r="336" spans="1:15">
       <c r="A336" s="4" t="s">
         <v>1111</v>
       </c>
@@ -24636,7 +24648,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:15">
+    <row r="337" spans="1:15">
       <c r="A337" s="4" t="s">
         <v>1113</v>
       </c>
@@ -24681,7 +24693,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:15">
+    <row r="338" spans="1:15">
       <c r="A338" s="4" t="s">
         <v>1116</v>
       </c>
@@ -24726,7 +24738,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="339" ht="14.25" hidden="1" spans="1:15">
+    <row r="339" ht="14.25" spans="1:15">
       <c r="A339" s="4" t="s">
         <v>1118</v>
       </c>
@@ -24771,7 +24783,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="340" ht="14.25" hidden="1" spans="1:15">
+    <row r="340" ht="14.25" spans="1:15">
       <c r="A340" s="4" t="s">
         <v>1120</v>
       </c>
@@ -24816,7 +24828,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:15">
+    <row r="341" spans="1:15">
       <c r="A341" s="4" t="s">
         <v>1122</v>
       </c>
@@ -24861,7 +24873,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:15">
+    <row r="342" spans="1:15">
       <c r="A342" s="4" t="s">
         <v>1126</v>
       </c>
@@ -24996,7 +25008,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:15">
+    <row r="345" spans="1:15">
       <c r="A345" s="4" t="s">
         <v>1132</v>
       </c>
@@ -25041,7 +25053,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="346" hidden="1" spans="1:15">
+    <row r="346" spans="1:15">
       <c r="A346" s="4" t="s">
         <v>1135</v>
       </c>
@@ -25086,7 +25098,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:15">
+    <row r="347" spans="1:15">
       <c r="A347" s="4" t="s">
         <v>1137</v>
       </c>
@@ -25131,7 +25143,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:15">
+    <row r="348" spans="1:15">
       <c r="A348" s="4" t="s">
         <v>1139</v>
       </c>
@@ -25176,7 +25188,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:15">
+    <row r="349" spans="1:15">
       <c r="A349" s="4" t="s">
         <v>1141</v>
       </c>
@@ -25221,7 +25233,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:15">
+    <row r="350" spans="1:15">
       <c r="A350" s="4" t="s">
         <v>1143</v>
       </c>
@@ -25266,7 +25278,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:15">
+    <row r="351" spans="1:15">
       <c r="A351" s="4" t="s">
         <v>1145</v>
       </c>
@@ -25311,7 +25323,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:15">
+    <row r="352" spans="1:15">
       <c r="A352" s="4" t="s">
         <v>1147</v>
       </c>
@@ -25356,7 +25368,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:15">
+    <row r="353" spans="1:15">
       <c r="A353" s="4" t="s">
         <v>1149</v>
       </c>
@@ -25401,7 +25413,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:15">
+    <row r="354" spans="1:15">
       <c r="A354" s="4" t="s">
         <v>1151</v>
       </c>
@@ -25446,7 +25458,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:16">
+    <row r="355" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>1154</v>
       </c>
@@ -25494,7 +25506,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:15">
+    <row r="356" spans="1:15">
       <c r="A356" s="4" t="s">
         <v>1157</v>
       </c>
@@ -25539,7 +25551,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:15">
+    <row r="357" spans="1:15">
       <c r="A357" s="4" t="s">
         <v>1159</v>
       </c>
@@ -25584,7 +25596,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:15">
+    <row r="358" spans="1:15">
       <c r="A358" s="4" t="s">
         <v>1161</v>
       </c>
@@ -25629,7 +25641,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:15">
+    <row r="359" spans="1:15">
       <c r="A359" s="4" t="s">
         <v>1163</v>
       </c>
@@ -25674,7 +25686,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:15">
+    <row r="360" spans="1:15">
       <c r="A360" s="4" t="s">
         <v>1165</v>
       </c>
@@ -25719,7 +25731,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:15">
+    <row r="361" spans="1:15">
       <c r="A361" s="4" t="s">
         <v>1168</v>
       </c>
@@ -25764,7 +25776,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:15">
+    <row r="362" spans="1:15">
       <c r="A362" s="4" t="s">
         <v>1170</v>
       </c>
@@ -25809,7 +25821,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:15">
+    <row r="363" spans="1:15">
       <c r="A363" s="4" t="s">
         <v>1172</v>
       </c>
@@ -25854,7 +25866,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:15">
+    <row r="364" spans="1:15">
       <c r="A364" s="4" t="s">
         <v>1174</v>
       </c>
@@ -25899,7 +25911,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:15">
+    <row r="365" spans="1:15">
       <c r="A365" s="4" t="s">
         <v>1176</v>
       </c>
@@ -25944,7 +25956,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:15">
+    <row r="366" spans="1:15">
       <c r="A366" s="4" t="s">
         <v>1178</v>
       </c>
@@ -25989,7 +26001,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:15">
+    <row r="367" spans="1:15">
       <c r="A367" s="4" t="s">
         <v>1180</v>
       </c>
@@ -26034,7 +26046,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:15">
+    <row r="368" spans="1:15">
       <c r="A368" s="4" t="s">
         <v>1183</v>
       </c>
@@ -26079,7 +26091,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:15">
+    <row r="369" spans="1:15">
       <c r="A369" s="4" t="s">
         <v>1185</v>
       </c>
@@ -26124,7 +26136,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:15">
+    <row r="370" spans="1:15">
       <c r="A370" s="4" t="s">
         <v>1188</v>
       </c>
@@ -26169,7 +26181,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="371" ht="14.25" hidden="1" spans="1:15">
+    <row r="371" ht="14.25" spans="1:15">
       <c r="A371" s="4" t="s">
         <v>1190</v>
       </c>
@@ -26214,7 +26226,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="372" ht="14.25" hidden="1" spans="1:15">
+    <row r="372" ht="14.25" spans="1:15">
       <c r="A372" s="4" t="s">
         <v>1193</v>
       </c>
@@ -26259,7 +26271,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="373" ht="14.25" hidden="1" spans="1:15">
+    <row r="373" ht="14.25" spans="1:15">
       <c r="A373" s="4" t="s">
         <v>1195</v>
       </c>
@@ -26304,7 +26316,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="374" ht="14.25" hidden="1" spans="1:15">
+    <row r="374" ht="14.25" spans="1:15">
       <c r="A374" s="4" t="s">
         <v>1197</v>
       </c>
@@ -26349,7 +26361,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:15">
+    <row r="375" spans="1:15">
       <c r="A375" s="4" t="s">
         <v>1199</v>
       </c>
@@ -26394,7 +26406,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:15">
+    <row r="376" spans="1:15">
       <c r="A376" s="4" t="s">
         <v>1201</v>
       </c>
@@ -26439,7 +26451,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:15">
+    <row r="377" spans="1:15">
       <c r="A377" s="4" t="s">
         <v>1203</v>
       </c>
@@ -26484,7 +26496,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:15">
+    <row r="378" spans="1:15">
       <c r="A378" s="4" t="s">
         <v>1205</v>
       </c>
@@ -26529,7 +26541,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:15">
+    <row r="379" spans="1:15">
       <c r="A379" s="4" t="s">
         <v>1207</v>
       </c>
@@ -26574,7 +26586,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:15">
+    <row r="380" spans="1:15">
       <c r="A380" s="4" t="s">
         <v>1210</v>
       </c>
@@ -26619,7 +26631,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:15">
+    <row r="381" spans="1:15">
       <c r="A381" s="4" t="s">
         <v>1212</v>
       </c>
@@ -26664,7 +26676,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:15">
+    <row r="382" spans="1:15">
       <c r="A382" s="4" t="s">
         <v>1215</v>
       </c>
@@ -26709,7 +26721,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:15">
+    <row r="383" spans="1:15">
       <c r="A383" s="4" t="s">
         <v>1217</v>
       </c>
@@ -26754,7 +26766,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:15">
+    <row r="384" spans="1:15">
       <c r="A384" s="4" t="s">
         <v>1219</v>
       </c>
@@ -26799,7 +26811,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:15">
+    <row r="385" spans="1:15">
       <c r="A385" s="4" t="s">
         <v>1221</v>
       </c>
@@ -26844,7 +26856,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:15">
+    <row r="386" spans="1:15">
       <c r="A386" s="4" t="s">
         <v>1224</v>
       </c>
@@ -26889,7 +26901,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:15">
+    <row r="387" spans="1:15">
       <c r="A387" s="4" t="s">
         <v>1225</v>
       </c>
@@ -26934,7 +26946,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:15">
+    <row r="388" spans="1:15">
       <c r="A388" s="4" t="s">
         <v>1228</v>
       </c>
@@ -26979,7 +26991,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:15">
+    <row r="389" spans="1:15">
       <c r="A389" s="4" t="s">
         <v>1231</v>
       </c>
@@ -27024,7 +27036,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:15">
+    <row r="390" spans="1:15">
       <c r="A390" s="4" t="s">
         <v>1234</v>
       </c>
@@ -27067,7 +27079,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:15">
+    <row r="391" spans="1:15">
       <c r="A391" s="4" t="s">
         <v>1237</v>
       </c>
@@ -27110,7 +27122,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:15">
+    <row r="392" spans="1:15">
       <c r="A392" s="4" t="s">
         <v>1240</v>
       </c>
@@ -27153,7 +27165,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:15">
+    <row r="393" spans="1:15">
       <c r="A393" s="4" t="s">
         <v>1243</v>
       </c>
@@ -27196,7 +27208,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:15">
+    <row r="394" spans="1:15">
       <c r="A394" s="4" t="s">
         <v>1246</v>
       </c>
@@ -27239,7 +27251,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:15">
+    <row r="395" spans="1:15">
       <c r="A395" s="4" t="s">
         <v>1248</v>
       </c>
@@ -27282,7 +27294,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:15">
+    <row r="396" spans="1:15">
       <c r="A396" s="4" t="s">
         <v>1250</v>
       </c>
@@ -27325,7 +27337,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:15">
+    <row r="397" spans="1:15">
       <c r="A397" s="4" t="s">
         <v>1253</v>
       </c>
@@ -27368,7 +27380,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:15">
+    <row r="398" spans="1:15">
       <c r="A398" s="4" t="s">
         <v>1255</v>
       </c>
@@ -27411,7 +27423,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:15">
+    <row r="399" spans="1:15">
       <c r="A399" s="4" t="s">
         <v>1258</v>
       </c>
@@ -27454,7 +27466,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:15">
+    <row r="400" spans="1:15">
       <c r="A400" s="4" t="s">
         <v>1260</v>
       </c>
@@ -27497,7 +27509,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:15">
+    <row r="401" spans="1:15">
       <c r="A401" s="4" t="s">
         <v>1262</v>
       </c>
@@ -27540,7 +27552,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:15">
+    <row r="402" spans="1:15">
       <c r="A402" s="4" t="s">
         <v>1264</v>
       </c>
@@ -27583,7 +27595,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:15">
+    <row r="403" spans="1:15">
       <c r="A403" s="4" t="s">
         <v>1266</v>
       </c>
@@ -27626,7 +27638,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:15">
+    <row r="404" spans="1:15">
       <c r="A404" s="4" t="s">
         <v>1268</v>
       </c>
@@ -27669,7 +27681,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:15">
+    <row r="405" spans="1:15">
       <c r="A405" s="4" t="s">
         <v>1270</v>
       </c>
@@ -27712,7 +27724,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:15">
+    <row r="406" spans="1:15">
       <c r="A406" s="4" t="s">
         <v>1273</v>
       </c>
@@ -27755,7 +27767,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:15">
+    <row r="407" spans="1:15">
       <c r="A407" s="4" t="s">
         <v>1275</v>
       </c>
@@ -27798,7 +27810,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:15">
+    <row r="408" spans="1:15">
       <c r="A408" s="4" t="s">
         <v>1278</v>
       </c>
@@ -27841,7 +27853,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:15">
+    <row r="409" spans="1:15">
       <c r="A409" s="4" t="s">
         <v>1280</v>
       </c>
@@ -27884,7 +27896,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:15">
+    <row r="410" spans="1:15">
       <c r="A410" s="4" t="s">
         <v>1282</v>
       </c>
@@ -27927,7 +27939,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:15">
+    <row r="411" spans="1:15">
       <c r="A411" s="4" t="s">
         <v>1285</v>
       </c>
@@ -27970,7 +27982,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:15">
+    <row r="412" spans="1:15">
       <c r="A412" s="4" t="s">
         <v>1287</v>
       </c>
@@ -28013,7 +28025,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:15">
+    <row r="413" spans="1:15">
       <c r="A413" s="4" t="s">
         <v>1289</v>
       </c>
@@ -28056,7 +28068,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:15">
+    <row r="414" spans="1:15">
       <c r="A414" s="4" t="s">
         <v>1291</v>
       </c>
@@ -28099,7 +28111,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:15">
+    <row r="415" spans="1:15">
       <c r="A415" s="4" t="s">
         <v>1293</v>
       </c>
@@ -28142,7 +28154,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:15">
+    <row r="416" spans="1:15">
       <c r="A416" s="4" t="s">
         <v>1296</v>
       </c>
@@ -28185,7 +28197,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:15">
+    <row r="417" spans="1:15">
       <c r="A417" s="4" t="s">
         <v>1298</v>
       </c>
@@ -28228,7 +28240,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:15">
+    <row r="418" spans="1:15">
       <c r="A418" s="4" t="s">
         <v>1300</v>
       </c>
@@ -28271,7 +28283,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:15">
+    <row r="419" spans="1:15">
       <c r="A419" s="4" t="s">
         <v>1302</v>
       </c>
@@ -28314,7 +28326,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:15">
+    <row r="420" spans="1:15">
       <c r="A420" s="4" t="s">
         <v>1305</v>
       </c>
@@ -28357,7 +28369,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:15">
+    <row r="421" spans="1:15">
       <c r="A421" s="4" t="s">
         <v>1307</v>
       </c>
@@ -28400,7 +28412,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:15">
+    <row r="422" spans="1:15">
       <c r="A422" s="4" t="s">
         <v>1309</v>
       </c>
@@ -28443,7 +28455,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:15">
+    <row r="423" spans="1:15">
       <c r="A423" s="4" t="s">
         <v>1311</v>
       </c>
@@ -28486,7 +28498,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:15">
+    <row r="424" spans="1:15">
       <c r="A424" s="4" t="s">
         <v>1313</v>
       </c>
@@ -28529,7 +28541,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:15">
+    <row r="425" spans="1:15">
       <c r="A425" s="4" t="s">
         <v>1315</v>
       </c>
@@ -28572,7 +28584,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:15">
+    <row r="426" spans="1:15">
       <c r="A426" s="4" t="s">
         <v>1317</v>
       </c>
@@ -28615,7 +28627,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:15">
+    <row r="427" spans="1:15">
       <c r="A427" s="4" t="s">
         <v>1319</v>
       </c>
@@ -28658,7 +28670,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:15">
+    <row r="428" spans="1:15">
       <c r="A428" s="4" t="s">
         <v>1322</v>
       </c>
@@ -28701,7 +28713,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:15">
+    <row r="429" spans="1:15">
       <c r="A429" s="4" t="s">
         <v>1324</v>
       </c>
@@ -28744,7 +28756,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:15">
+    <row r="430" spans="1:15">
       <c r="A430" s="4" t="s">
         <v>1326</v>
       </c>
@@ -28787,7 +28799,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:15">
+    <row r="431" spans="1:15">
       <c r="A431" s="4" t="s">
         <v>1329</v>
       </c>
@@ -28830,7 +28842,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:15">
+    <row r="432" spans="1:15">
       <c r="A432" s="4" t="s">
         <v>1331</v>
       </c>
@@ -28873,7 +28885,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:15">
+    <row r="433" spans="1:15">
       <c r="A433" s="4" t="s">
         <v>1333</v>
       </c>
@@ -28916,7 +28928,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:15">
+    <row r="434" spans="1:15">
       <c r="A434" s="4" t="s">
         <v>1336</v>
       </c>
@@ -28959,7 +28971,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:15">
+    <row r="435" spans="1:15">
       <c r="A435" s="4" t="s">
         <v>1339</v>
       </c>
@@ -29002,7 +29014,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:15">
+    <row r="436" spans="1:15">
       <c r="A436" s="4" t="s">
         <v>1341</v>
       </c>
@@ -29045,7 +29057,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:15">
+    <row r="437" spans="1:15">
       <c r="A437" s="4" t="s">
         <v>1343</v>
       </c>
@@ -29088,7 +29100,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:15">
+    <row r="438" spans="1:15">
       <c r="A438" s="4" t="s">
         <v>1345</v>
       </c>
@@ -29131,7 +29143,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="439" ht="14.25" hidden="1" spans="1:15">
+    <row r="439" ht="14.25" spans="1:15">
       <c r="A439" s="4" t="s">
         <v>1347</v>
       </c>
@@ -29174,7 +29186,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="440" ht="14.25" hidden="1" spans="1:15">
+    <row r="440" ht="14.25" spans="1:15">
       <c r="A440" s="4" t="s">
         <v>1349</v>
       </c>
@@ -29217,7 +29229,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:15">
+    <row r="441" spans="1:15">
       <c r="A441" s="4" t="s">
         <v>1351</v>
       </c>
@@ -29260,7 +29272,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="442" ht="18" hidden="1" spans="1:17">
+    <row r="442" ht="18" spans="1:17">
       <c r="A442" s="4" t="s">
         <v>1354</v>
       </c>
@@ -29307,7 +29319,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="443" ht="18" hidden="1" spans="1:17">
+    <row r="443" ht="18" spans="1:17">
       <c r="A443" s="4" t="s">
         <v>1359</v>
       </c>
@@ -29354,7 +29366,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="444" ht="17.25" hidden="1" spans="1:17">
+    <row r="444" ht="17.25" spans="1:17">
       <c r="A444" s="4" t="s">
         <v>1363</v>
       </c>
@@ -29401,7 +29413,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="445" ht="17.25" hidden="1" spans="1:17">
+    <row r="445" ht="17.25" spans="1:17">
       <c r="A445" s="4" t="s">
         <v>1368</v>
       </c>
@@ -29448,7 +29460,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="446" ht="17.25" hidden="1" spans="1:17">
+    <row r="446" ht="17.25" spans="1:17">
       <c r="A446" s="4" t="s">
         <v>1372</v>
       </c>
@@ -29495,7 +29507,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="447" ht="17.25" hidden="1" spans="1:17">
+    <row r="447" ht="17.25" spans="1:17">
       <c r="A447" s="4" t="s">
         <v>1377</v>
       </c>
@@ -29542,7 +29554,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="448" ht="17.25" hidden="1" spans="1:17">
+    <row r="448" ht="17.25" spans="1:17">
       <c r="A448" s="4" t="s">
         <v>1381</v>
       </c>
@@ -29592,7 +29604,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="449" ht="18" hidden="1" spans="1:17">
+    <row r="449" ht="18" spans="1:17">
       <c r="A449" s="4" t="s">
         <v>1384</v>
       </c>
@@ -29642,7 +29654,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="450" ht="18" hidden="1" spans="1:17">
+    <row r="450" ht="18" spans="1:17">
       <c r="A450" s="4" t="s">
         <v>1387</v>
       </c>
@@ -29692,7 +29704,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="451" ht="17.25" hidden="1" spans="1:17">
+    <row r="451" ht="17.25" spans="1:17">
       <c r="A451" s="4" t="s">
         <v>1391</v>
       </c>
@@ -29742,7 +29754,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="452" ht="17.25" hidden="1" spans="1:17">
+    <row r="452" ht="17.25" spans="1:17">
       <c r="A452" s="4" t="s">
         <v>1394</v>
       </c>
@@ -29792,7 +29804,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="453" ht="17.25" hidden="1" spans="1:17">
+    <row r="453" ht="17.25" spans="1:17">
       <c r="A453" s="4" t="s">
         <v>1398</v>
       </c>
@@ -29842,7 +29854,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="454" ht="17.25" hidden="1" spans="1:17">
+    <row r="454" ht="17.25" spans="1:17">
       <c r="A454" s="4" t="s">
         <v>1402</v>
       </c>
@@ -29889,7 +29901,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="455" ht="17.25" hidden="1" spans="1:17">
+    <row r="455" ht="17.25" spans="1:17">
       <c r="A455" s="4" t="s">
         <v>1405</v>
       </c>
@@ -29939,7 +29951,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="456" ht="18" hidden="1" spans="1:17">
+    <row r="456" ht="18" spans="1:17">
       <c r="A456" s="4" t="s">
         <v>1409</v>
       </c>
@@ -29989,7 +30001,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="457" ht="18" hidden="1" spans="1:17">
+    <row r="457" ht="18" spans="1:17">
       <c r="A457" s="4" t="s">
         <v>1412</v>
       </c>
@@ -30039,7 +30051,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="458" ht="17.25" hidden="1" spans="1:17">
+    <row r="458" ht="17.25" spans="1:17">
       <c r="A458" s="4" t="s">
         <v>1416</v>
       </c>
@@ -30086,7 +30098,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="459" ht="17.25" hidden="1" spans="1:17">
+    <row r="459" ht="17.25" spans="1:17">
       <c r="A459" s="4" t="s">
         <v>1420</v>
       </c>
@@ -30136,7 +30148,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="460" ht="17.25" hidden="1" spans="1:17">
+    <row r="460" ht="17.25" spans="1:17">
       <c r="A460" s="4" t="s">
         <v>1424</v>
       </c>
@@ -30186,7 +30198,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="461" ht="17.25" hidden="1" spans="1:17">
+    <row r="461" ht="17.25" spans="1:17">
       <c r="A461" s="4" t="s">
         <v>1428</v>
       </c>
@@ -30236,7 +30248,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="462" ht="17.25" hidden="1" spans="1:17">
+    <row r="462" ht="17.25" spans="1:17">
       <c r="A462" s="4" t="s">
         <v>1431</v>
       </c>
@@ -30286,7 +30298,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="463" ht="17.25" hidden="1" spans="1:17">
+    <row r="463" ht="17.25" spans="1:17">
       <c r="A463" s="4" t="s">
         <v>1435</v>
       </c>
@@ -30336,7 +30348,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="464" ht="17.25" hidden="1" spans="1:17">
+    <row r="464" ht="17.25" spans="1:17">
       <c r="A464" s="4" t="s">
         <v>1439</v>
       </c>
@@ -30386,7 +30398,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="465" ht="17.25" hidden="1" spans="1:17">
+    <row r="465" ht="17.25" spans="1:17">
       <c r="A465" s="4" t="s">
         <v>1443</v>
       </c>
@@ -30436,7 +30448,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="466" ht="17.25" hidden="1" spans="1:17">
+    <row r="466" ht="17.25" spans="1:17">
       <c r="A466" s="4" t="s">
         <v>1446</v>
       </c>
@@ -30486,7 +30498,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="467" ht="17.25" hidden="1" spans="1:17">
+    <row r="467" ht="17.25" spans="1:17">
       <c r="A467" s="4" t="s">
         <v>1451</v>
       </c>
@@ -30539,7 +30551,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="468" ht="17.25" hidden="1" spans="1:17">
+    <row r="468" ht="17.25" spans="1:17">
       <c r="A468" s="4" t="s">
         <v>1455</v>
       </c>
@@ -30589,7 +30601,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="469" ht="17.25" hidden="1" spans="1:17">
+    <row r="469" ht="17.25" spans="1:17">
       <c r="A469" s="4" t="s">
         <v>1459</v>
       </c>
@@ -30639,7 +30651,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="470" ht="17.25" hidden="1" spans="1:17">
+    <row r="470" ht="17.25" spans="1:17">
       <c r="A470" s="4" t="s">
         <v>1463</v>
       </c>
@@ -30689,7 +30701,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="471" ht="17.25" hidden="1" spans="1:17">
+    <row r="471" ht="17.25" spans="1:17">
       <c r="A471" s="4" t="s">
         <v>1468</v>
       </c>
@@ -30739,7 +30751,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="472" ht="17.25" hidden="1" spans="1:17">
+    <row r="472" ht="17.25" spans="1:17">
       <c r="A472" s="4" t="s">
         <v>1472</v>
       </c>
@@ -30792,7 +30804,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="473" ht="17.25" hidden="1" spans="1:17">
+    <row r="473" ht="17.25" spans="1:17">
       <c r="A473" s="4" t="s">
         <v>1474</v>
       </c>
@@ -30842,7 +30854,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="474" ht="17.25" hidden="1" spans="1:17">
+    <row r="474" ht="17.25" spans="1:17">
       <c r="A474" s="4" t="s">
         <v>1478</v>
       </c>
@@ -30892,7 +30904,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="475" ht="17.25" hidden="1" spans="1:17">
+    <row r="475" ht="17.25" spans="1:17">
       <c r="A475" s="4" t="s">
         <v>1481</v>
       </c>
@@ -30942,7 +30954,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="476" ht="17.25" hidden="1" spans="1:17">
+    <row r="476" ht="17.25" spans="1:17">
       <c r="A476" s="4" t="s">
         <v>1484</v>
       </c>
@@ -30992,7 +31004,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="477" ht="17.25" hidden="1" spans="1:17">
+    <row r="477" ht="17.25" spans="1:17">
       <c r="A477" s="4" t="s">
         <v>1486</v>
       </c>
@@ -31042,7 +31054,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="478" ht="17.25" hidden="1" spans="1:17">
+    <row r="478" ht="17.25" spans="1:17">
       <c r="A478" s="4" t="s">
         <v>1490</v>
       </c>
@@ -31092,7 +31104,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="479" ht="17.25" hidden="1" spans="1:17">
+    <row r="479" ht="17.25" spans="1:17">
       <c r="A479" s="4" t="s">
         <v>1495</v>
       </c>
@@ -31145,7 +31157,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="480" ht="17.25" hidden="1" spans="1:17">
+    <row r="480" ht="17.25" spans="1:17">
       <c r="A480" s="4" t="s">
         <v>1499</v>
       </c>
@@ -31195,7 +31207,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="481" ht="17.25" hidden="1" spans="1:17">
+    <row r="481" ht="17.25" spans="1:17">
       <c r="A481" s="4" t="s">
         <v>1503</v>
       </c>
@@ -31245,7 +31257,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="482" ht="17.25" hidden="1" spans="1:17">
+    <row r="482" ht="17.25" spans="1:17">
       <c r="A482" s="4" t="s">
         <v>1506</v>
       </c>
@@ -31292,7 +31304,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="483" ht="17.25" hidden="1" spans="1:17">
+    <row r="483" ht="17.25" spans="1:17">
       <c r="A483" s="4" t="s">
         <v>1510</v>
       </c>
@@ -31339,7 +31351,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="484" ht="17.25" hidden="1" spans="1:17">
+    <row r="484" ht="17.25" spans="1:17">
       <c r="A484" s="4" t="s">
         <v>1512</v>
       </c>
@@ -31386,7 +31398,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="485" ht="17.25" hidden="1" spans="1:17">
+    <row r="485" ht="17.25" spans="1:17">
       <c r="A485" s="4" t="s">
         <v>1514</v>
       </c>
@@ -31429,7 +31441,7 @@
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>
     </row>
-    <row r="486" ht="17.25" hidden="1" spans="1:17">
+    <row r="486" ht="17.25" spans="1:17">
       <c r="A486" s="4" t="s">
         <v>1516</v>
       </c>
@@ -31476,7 +31488,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="487" ht="17.25" hidden="1" spans="1:17">
+    <row r="487" ht="17.25" spans="1:17">
       <c r="A487" s="4" t="s">
         <v>1520</v>
       </c>
@@ -31523,7 +31535,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="488" ht="17.25" hidden="1" spans="1:17">
+    <row r="488" ht="17.25" spans="1:17">
       <c r="A488" s="4" t="s">
         <v>1523</v>
       </c>
@@ -31570,7 +31582,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="489" ht="17.25" hidden="1" spans="1:17">
+    <row r="489" ht="17.25" spans="1:17">
       <c r="A489" s="4" t="s">
         <v>1526</v>
       </c>
@@ -31617,7 +31629,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="490" ht="17.25" hidden="1" spans="1:17">
+    <row r="490" ht="17.25" spans="1:17">
       <c r="A490" s="4" t="s">
         <v>1529</v>
       </c>
@@ -31664,7 +31676,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="491" ht="17.25" hidden="1" spans="1:17">
+    <row r="491" ht="17.25" spans="1:17">
       <c r="A491" s="4" t="s">
         <v>1532</v>
       </c>
@@ -31852,7 +31864,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="495" ht="17.25" hidden="1" spans="1:17">
+    <row r="495" ht="17.25" spans="1:17">
       <c r="A495" s="4" t="s">
         <v>1541</v>
       </c>
@@ -31902,7 +31914,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="496" ht="17.25" hidden="1" spans="1:17">
+    <row r="496" ht="17.25" spans="1:17">
       <c r="A496" s="4" t="s">
         <v>1545</v>
       </c>
@@ -31952,7 +31964,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="497" ht="17.25" hidden="1" spans="1:17">
+    <row r="497" ht="17.25" spans="1:17">
       <c r="A497" s="4" t="s">
         <v>1549</v>
       </c>
@@ -32002,7 +32014,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="498" ht="17.25" hidden="1" spans="1:17">
+    <row r="498" ht="17.25" spans="1:17">
       <c r="A498" s="4" t="s">
         <v>1553</v>
       </c>
@@ -32052,7 +32064,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="499" ht="17.25" hidden="1" spans="1:17">
+    <row r="499" ht="17.25" spans="1:17">
       <c r="A499" s="4" t="s">
         <v>1557</v>
       </c>
@@ -32102,7 +32114,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="500" ht="17.25" hidden="1" spans="1:17">
+    <row r="500" ht="17.25" spans="1:17">
       <c r="A500" s="4" t="s">
         <v>1561</v>
       </c>
@@ -32152,7 +32164,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="501" ht="17.25" hidden="1" spans="1:17">
+    <row r="501" ht="17.25" spans="1:17">
       <c r="A501" s="4" t="s">
         <v>1564</v>
       </c>
@@ -32202,7 +32214,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="502" ht="17.25" hidden="1" spans="1:17">
+    <row r="502" ht="17.25" spans="1:17">
       <c r="A502" s="4" t="s">
         <v>1568</v>
       </c>
@@ -32252,7 +32264,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="503" ht="17.25" hidden="1" spans="1:17">
+    <row r="503" ht="17.25" spans="1:17">
       <c r="A503" s="4" t="s">
         <v>1572</v>
       </c>
@@ -32302,7 +32314,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="504" ht="17.25" hidden="1" spans="1:17">
+    <row r="504" ht="17.25" spans="1:17">
       <c r="A504" s="4" t="s">
         <v>1574</v>
       </c>
@@ -32355,7 +32367,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="505" ht="17.25" hidden="1" spans="1:17">
+    <row r="505" ht="17.25" spans="1:17">
       <c r="A505" s="4" t="s">
         <v>1576</v>
       </c>
@@ -32402,7 +32414,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="506" ht="17.25" hidden="1" spans="1:17">
+    <row r="506" ht="17.25" spans="1:17">
       <c r="A506" s="4" t="s">
         <v>1580</v>
       </c>
@@ -32449,7 +32461,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="507" ht="17.25" hidden="1" spans="1:17">
+    <row r="507" ht="17.25" spans="1:17">
       <c r="A507" s="4" t="s">
         <v>1584</v>
       </c>
@@ -32496,7 +32508,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="508" ht="17.25" hidden="1" spans="1:17">
+    <row r="508" ht="17.25" spans="1:17">
       <c r="A508" s="4" t="s">
         <v>1588</v>
       </c>
@@ -32543,7 +32555,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="509" ht="17.25" hidden="1" spans="1:17">
+    <row r="509" ht="17.25" spans="1:17">
       <c r="A509" s="4" t="s">
         <v>1592</v>
       </c>
@@ -32590,7 +32602,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="510" hidden="1" spans="1:15">
+    <row r="510" spans="1:15">
       <c r="A510" s="4" t="s">
         <v>1595</v>
       </c>
@@ -32631,7 +32643,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="511" hidden="1" spans="1:15">
+    <row r="511" spans="1:15">
       <c r="A511" s="4" t="s">
         <v>1596</v>
       </c>
@@ -32672,7 +32684,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="512" hidden="1" spans="1:15">
+    <row r="512" spans="1:15">
       <c r="A512" s="4" t="s">
         <v>1598</v>
       </c>
@@ -32713,7 +32725,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="513" hidden="1" spans="1:15">
+    <row r="513" spans="1:15">
       <c r="A513" s="4" t="s">
         <v>1601</v>
       </c>
@@ -32754,7 +32766,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="514" hidden="1" spans="1:15">
+    <row r="514" spans="1:15">
       <c r="A514" s="4" t="s">
         <v>1606</v>
       </c>
@@ -32795,7 +32807,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="515" hidden="1" spans="1:15">
+    <row r="515" spans="1:15">
       <c r="A515" s="4" t="s">
         <v>1608</v>
       </c>
@@ -32836,7 +32848,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="516" hidden="1" spans="1:15">
+    <row r="516" spans="1:15">
       <c r="A516" s="4" t="s">
         <v>1610</v>
       </c>
@@ -32877,7 +32889,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="517" hidden="1" spans="1:15">
+    <row r="517" spans="1:15">
       <c r="A517" s="4" t="s">
         <v>1611</v>
       </c>
@@ -32918,7 +32930,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="518" hidden="1" spans="1:15">
+    <row r="518" spans="1:15">
       <c r="A518" t="s">
         <v>1613</v>
       </c>
@@ -32959,7 +32971,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="519" hidden="1" spans="1:15">
+    <row r="519" spans="1:15">
       <c r="A519" s="4" t="s">
         <v>1615</v>
       </c>
@@ -33000,7 +33012,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="520" hidden="1" spans="1:15">
+    <row r="520" spans="1:15">
       <c r="A520" t="s">
         <v>1617</v>
       </c>
@@ -33041,7 +33053,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="521" hidden="1" spans="1:15">
+    <row r="521" spans="1:15">
       <c r="A521" t="s">
         <v>1619</v>
       </c>
@@ -33082,7 +33094,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="522" hidden="1" spans="1:15">
+    <row r="522" spans="1:15">
       <c r="A522" s="4" t="s">
         <v>1621</v>
       </c>
@@ -33123,14 +33135,90 @@
         <v>173</v>
       </c>
     </row>
+    <row r="523" spans="1:15">
+      <c r="A523" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B523" t="s">
+        <v>18</v>
+      </c>
+      <c r="C523" t="s">
+        <v>88</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E523">
+        <v>0</v>
+      </c>
+      <c r="F523">
+        <v>1510</v>
+      </c>
+      <c r="G523">
+        <v>436</v>
+      </c>
+      <c r="H523" s="4">
+        <v>0</v>
+      </c>
+      <c r="I523" s="4">
+        <v>0</v>
+      </c>
+      <c r="J523">
+        <v>2035</v>
+      </c>
+      <c r="L523" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N523" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="O523" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15">
+      <c r="A524" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B524" t="s">
+        <v>18</v>
+      </c>
+      <c r="C524" t="s">
+        <v>88</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E524">
+        <v>0</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524">
+        <v>3723</v>
+      </c>
+      <c r="H524">
+        <v>0</v>
+      </c>
+      <c r="I524">
+        <v>0</v>
+      </c>
+      <c r="J524">
+        <v>2035</v>
+      </c>
+      <c r="L524" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="N524" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="O524" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T522">
-    <filterColumn colId="13">
-      <customFilters>
-        <customFilter operator="equal" val="交通运输局"/>
-        <customFilter operator="equal" val="交通运输事业发展中心"/>
-      </customFilters>
-    </filterColumn>
+  <autoFilter ref="A1:T524">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1630">
   <si>
     <t>单号</t>
   </si>
@@ -4888,7 +4888,7 @@
     <t>郭铃华</t>
   </si>
   <si>
-    <t>2021年事业单位选调考试</t>
+    <t>2020年事业单位选调考试</t>
   </si>
   <si>
     <t>[2021]第341号</t>
@@ -4900,7 +4900,13 @@
     <t>左安事业</t>
   </si>
   <si>
-    <t>[2021]空07号</t>
+    <t>[2021]第-12号</t>
+  </si>
+  <si>
+    <t>林远盛</t>
+  </si>
+  <si>
+    <t>泉江镇事业</t>
   </si>
 </sst>
 </file>
@@ -4908,11 +4914,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4960,14 +4966,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4988,58 +5055,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -5048,24 +5063,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5080,14 +5079,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -5097,7 +5088,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5172,25 +5178,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5202,25 +5190,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5232,7 +5226,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5244,7 +5250,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5268,13 +5274,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5286,7 +5286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5298,13 +5304,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5316,43 +5334,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5399,17 +5405,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5447,8 +5459,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5463,21 +5484,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -5501,10 +5507,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5513,16 +5519,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5531,115 +5537,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5795,6 +5801,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6061,7 +6076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
   <dimension ref="A1:T524"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -6141,7 +6156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:19">
+    <row r="2" ht="14.25" hidden="1" spans="1:19">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -6200,7 +6215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:19">
+    <row r="3" ht="14.25" hidden="1" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -6259,7 +6274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:19">
+    <row r="4" ht="14.25" hidden="1" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
@@ -6318,7 +6333,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:19">
+    <row r="5" ht="14.25" hidden="1" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>37</v>
       </c>
@@ -6375,7 +6390,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:19">
+    <row r="6" ht="14.25" hidden="1" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -6434,7 +6449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:19">
+    <row r="7" ht="14.25" hidden="1" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
@@ -6493,7 +6508,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:19">
+    <row r="8" ht="14.25" hidden="1" spans="1:19">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -6552,7 +6567,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:19">
+    <row r="9" ht="14.25" hidden="1" spans="1:19">
       <c r="A9" s="4" t="s">
         <v>63</v>
       </c>
@@ -6611,7 +6626,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:19">
+    <row r="10" ht="14.25" hidden="1" spans="1:19">
       <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
@@ -6668,7 +6683,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:19">
+    <row r="11" ht="14.25" hidden="1" spans="1:19">
       <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
@@ -6727,7 +6742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:19">
+    <row r="12" ht="14.25" hidden="1" spans="1:19">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -6784,7 +6799,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:19">
+    <row r="13" ht="14.25" hidden="1" spans="1:19">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -6839,7 +6854,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:19">
+    <row r="14" ht="14.25" hidden="1" spans="1:19">
       <c r="A14" s="4" t="s">
         <v>93</v>
       </c>
@@ -6898,7 +6913,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:19">
+    <row r="15" ht="14.25" hidden="1" spans="1:19">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -6957,7 +6972,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:19">
+    <row r="16" ht="14.25" hidden="1" spans="1:19">
       <c r="A16" s="4" t="s">
         <v>103</v>
       </c>
@@ -7016,7 +7031,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:19">
+    <row r="17" ht="14.25" hidden="1" spans="1:19">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -7071,7 +7086,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:19">
+    <row r="18" ht="14.25" hidden="1" spans="1:19">
       <c r="A18" s="4" t="s">
         <v>113</v>
       </c>
@@ -7130,7 +7145,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:20">
+    <row r="19" ht="14.25" hidden="1" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
@@ -7191,7 +7206,7 @@
         <v>87662.6773333333</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:19">
+    <row r="20" ht="14.25" hidden="1" spans="1:19">
       <c r="A20" s="4" t="s">
         <v>122</v>
       </c>
@@ -7248,7 +7263,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:20">
+    <row r="21" ht="14.25" hidden="1" spans="1:20">
       <c r="A21" s="4" t="s">
         <v>125</v>
       </c>
@@ -7309,7 +7324,7 @@
         <v>53992.6</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:19">
+    <row r="22" ht="14.25" hidden="1" spans="1:19">
       <c r="A22" s="4" t="s">
         <v>131</v>
       </c>
@@ -7364,7 +7379,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="1:19">
+    <row r="23" ht="14.25" hidden="1" spans="1:19">
       <c r="A23" s="4" t="s">
         <v>137</v>
       </c>
@@ -7419,7 +7434,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:19">
+    <row r="24" ht="14.25" hidden="1" spans="1:19">
       <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
@@ -7474,7 +7489,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:19">
+    <row r="25" ht="14.25" hidden="1" spans="1:19">
       <c r="A25" s="4" t="s">
         <v>146</v>
       </c>
@@ -7533,7 +7548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" ht="14.25" spans="1:19">
+    <row r="26" ht="14.25" hidden="1" spans="1:19">
       <c r="A26" s="4" t="s">
         <v>150</v>
       </c>
@@ -7590,7 +7605,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="1:19">
+    <row r="27" ht="14.25" hidden="1" spans="1:19">
       <c r="A27" s="4" t="s">
         <v>157</v>
       </c>
@@ -7647,7 +7662,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" ht="14.25" spans="1:19">
+    <row r="28" ht="14.25" hidden="1" spans="1:19">
       <c r="A28" s="4" t="s">
         <v>165</v>
       </c>
@@ -7706,7 +7721,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:19">
+    <row r="29" ht="14.25" hidden="1" spans="1:19">
       <c r="A29" s="4" t="s">
         <v>171</v>
       </c>
@@ -7763,7 +7778,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:19">
+    <row r="30" ht="14.25" hidden="1" spans="1:19">
       <c r="A30" s="4" t="s">
         <v>176</v>
       </c>
@@ -7820,7 +7835,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="1:19">
+    <row r="31" ht="14.25" hidden="1" spans="1:19">
       <c r="A31" s="4" t="s">
         <v>180</v>
       </c>
@@ -7877,7 +7892,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:19">
+    <row r="32" ht="14.25" hidden="1" spans="1:19">
       <c r="A32" s="4" t="s">
         <v>185</v>
       </c>
@@ -7932,7 +7947,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="1:19">
+    <row r="33" ht="27" hidden="1" spans="1:19">
       <c r="A33" s="4" t="s">
         <v>190</v>
       </c>
@@ -7989,7 +8004,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" ht="27" spans="1:19">
+    <row r="34" ht="27" hidden="1" spans="1:19">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -8044,7 +8059,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="1:19">
+    <row r="35" ht="14.25" hidden="1" spans="1:19">
       <c r="A35" s="4" t="s">
         <v>201</v>
       </c>
@@ -8099,7 +8114,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="1:19">
+    <row r="36" ht="14.25" hidden="1" spans="1:19">
       <c r="A36" s="4" t="s">
         <v>207</v>
       </c>
@@ -8154,7 +8169,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" ht="14.25" spans="1:19">
+    <row r="37" ht="14.25" hidden="1" spans="1:19">
       <c r="A37" s="4" t="s">
         <v>211</v>
       </c>
@@ -8209,7 +8224,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" ht="14.25" spans="1:19">
+    <row r="38" ht="14.25" hidden="1" spans="1:19">
       <c r="A38" s="4" t="s">
         <v>215</v>
       </c>
@@ -8266,7 +8281,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" ht="14.25" spans="1:19">
+    <row r="39" ht="14.25" hidden="1" spans="1:19">
       <c r="A39" s="4" t="s">
         <v>219</v>
       </c>
@@ -8321,7 +8336,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" ht="27" spans="1:19">
+    <row r="40" ht="27" hidden="1" spans="1:19">
       <c r="A40" s="4" t="s">
         <v>224</v>
       </c>
@@ -8376,7 +8391,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" ht="14.25" spans="1:19">
+    <row r="41" ht="14.25" hidden="1" spans="1:19">
       <c r="A41" s="4" t="s">
         <v>229</v>
       </c>
@@ -8433,7 +8448,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" ht="14.25" spans="1:19">
+    <row r="42" ht="14.25" hidden="1" spans="1:19">
       <c r="A42" s="4" t="s">
         <v>235</v>
       </c>
@@ -8488,7 +8503,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" ht="14.25" spans="1:19">
+    <row r="43" ht="14.25" hidden="1" spans="1:19">
       <c r="A43" s="4" t="s">
         <v>241</v>
       </c>
@@ -8543,7 +8558,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" ht="14.25" spans="1:19">
+    <row r="44" ht="14.25" hidden="1" spans="1:19">
       <c r="A44" s="4" t="s">
         <v>247</v>
       </c>
@@ -8598,7 +8613,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="45" ht="14.25" spans="1:19">
+    <row r="45" ht="14.25" hidden="1" spans="1:19">
       <c r="A45" s="4" t="s">
         <v>251</v>
       </c>
@@ -8710,7 +8725,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" ht="14.25" spans="1:19">
+    <row r="47" ht="14.25" hidden="1" spans="1:19">
       <c r="A47" s="4" t="s">
         <v>262</v>
       </c>
@@ -8765,7 +8780,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" ht="14.25" spans="1:19">
+    <row r="48" ht="14.25" hidden="1" spans="1:19">
       <c r="A48" s="4" t="s">
         <v>266</v>
       </c>
@@ -8820,7 +8835,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" ht="27" spans="1:19">
+    <row r="49" ht="27" hidden="1" spans="1:19">
       <c r="A49" s="4" t="s">
         <v>270</v>
       </c>
@@ -8877,7 +8892,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="14.25" spans="1:19">
+    <row r="50" ht="14.25" hidden="1" spans="1:19">
       <c r="A50" s="4" t="s">
         <v>278</v>
       </c>
@@ -8932,7 +8947,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" ht="14.25" spans="1:19">
+    <row r="51" ht="14.25" hidden="1" spans="1:19">
       <c r="A51" s="4" t="s">
         <v>283</v>
       </c>
@@ -8989,7 +9004,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" ht="27.75" spans="1:19">
+    <row r="52" ht="27.75" hidden="1" spans="1:19">
       <c r="A52" s="4" t="s">
         <v>286</v>
       </c>
@@ -9046,7 +9061,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="53" ht="15" spans="1:19">
+    <row r="53" ht="15" hidden="1" spans="1:19">
       <c r="A53" s="4" t="s">
         <v>291</v>
       </c>
@@ -9101,7 +9116,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="1:19">
+    <row r="54" ht="14.25" hidden="1" spans="1:19">
       <c r="A54" s="4" t="s">
         <v>297</v>
       </c>
@@ -9158,7 +9173,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" ht="14.25" spans="1:19">
+    <row r="55" ht="14.25" hidden="1" spans="1:19">
       <c r="A55" s="4" t="s">
         <v>304</v>
       </c>
@@ -9213,7 +9228,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" ht="14.25" spans="1:19">
+    <row r="56" ht="14.25" hidden="1" spans="1:19">
       <c r="A56" s="4" t="s">
         <v>308</v>
       </c>
@@ -9270,7 +9285,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="1:19">
+    <row r="57" ht="14.25" hidden="1" spans="1:19">
       <c r="A57" s="4" t="s">
         <v>312</v>
       </c>
@@ -9329,7 +9344,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="58" ht="27" spans="1:19">
+    <row r="58" ht="27" hidden="1" spans="1:19">
       <c r="A58" s="4" t="s">
         <v>316</v>
       </c>
@@ -9384,7 +9399,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:19">
+    <row r="59" ht="14.25" hidden="1" spans="1:19">
       <c r="A59" s="4" t="s">
         <v>322</v>
       </c>
@@ -9441,7 +9456,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="60" ht="14.25" spans="1:19">
+    <row r="60" ht="14.25" hidden="1" spans="1:19">
       <c r="A60" s="4" t="s">
         <v>327</v>
       </c>
@@ -9498,7 +9513,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" ht="14.25" spans="1:19">
+    <row r="61" ht="14.25" hidden="1" spans="1:19">
       <c r="A61" s="4" t="s">
         <v>333</v>
       </c>
@@ -9555,7 +9570,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" ht="14.25" spans="1:19">
+    <row r="62" ht="14.25" hidden="1" spans="1:19">
       <c r="A62" s="5" t="s">
         <v>339</v>
       </c>
@@ -9610,7 +9625,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" ht="27" spans="1:19">
+    <row r="63" ht="27" hidden="1" spans="1:19">
       <c r="A63" s="4" t="s">
         <v>343</v>
       </c>
@@ -9667,7 +9682,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="64" ht="27" spans="1:19">
+    <row r="64" ht="27" hidden="1" spans="1:19">
       <c r="A64" s="4" t="s">
         <v>348</v>
       </c>
@@ -9724,7 +9739,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="65" ht="14.25" spans="1:19">
+    <row r="65" ht="14.25" hidden="1" spans="1:19">
       <c r="A65" s="4" t="s">
         <v>352</v>
       </c>
@@ -9781,7 +9796,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="66" ht="14.25" spans="1:19">
+    <row r="66" ht="14.25" hidden="1" spans="1:19">
       <c r="A66" s="4" t="s">
         <v>356</v>
       </c>
@@ -9838,7 +9853,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="67" ht="14.25" spans="1:19">
+    <row r="67" ht="14.25" hidden="1" spans="1:19">
       <c r="A67" s="4" t="s">
         <v>360</v>
       </c>
@@ -9895,7 +9910,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" ht="14.25" spans="1:19">
+    <row r="68" ht="14.25" hidden="1" spans="1:19">
       <c r="A68" s="4" t="s">
         <v>364</v>
       </c>
@@ -9952,7 +9967,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="69" ht="27" spans="1:19">
+    <row r="69" ht="27" hidden="1" spans="1:19">
       <c r="A69" s="4" t="s">
         <v>367</v>
       </c>
@@ -10009,7 +10024,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="70" ht="14.25" spans="1:19">
+    <row r="70" ht="14.25" hidden="1" spans="1:19">
       <c r="A70" s="4" t="s">
         <v>371</v>
       </c>
@@ -10066,7 +10081,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" ht="14.25" spans="1:19">
+    <row r="71" ht="14.25" hidden="1" spans="1:19">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -10123,7 +10138,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" ht="14.25" spans="1:19">
+    <row r="72" ht="14.25" hidden="1" spans="1:19">
       <c r="A72" s="4" t="s">
         <v>378</v>
       </c>
@@ -10180,7 +10195,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" ht="27" spans="1:19">
+    <row r="73" ht="27" hidden="1" spans="1:19">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10237,7 +10252,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74" ht="27" spans="1:19">
+    <row r="74" ht="27" hidden="1" spans="1:19">
       <c r="A74" s="4" t="s">
         <v>385</v>
       </c>
@@ -10294,7 +10309,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" ht="14.25" spans="1:19">
+    <row r="75" ht="14.25" hidden="1" spans="1:19">
       <c r="A75" s="4" t="s">
         <v>389</v>
       </c>
@@ -10351,7 +10366,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="76" ht="27" spans="1:19">
+    <row r="76" ht="27" hidden="1" spans="1:19">
       <c r="A76" s="4" t="s">
         <v>393</v>
       </c>
@@ -10408,7 +10423,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" ht="14.25" spans="1:19">
+    <row r="77" ht="14.25" hidden="1" spans="1:19">
       <c r="A77" s="4" t="s">
         <v>397</v>
       </c>
@@ -10467,7 +10482,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" ht="27" spans="1:19">
+    <row r="78" ht="27" hidden="1" spans="1:19">
       <c r="A78" s="4" t="s">
         <v>401</v>
       </c>
@@ -10524,7 +10539,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" ht="14.25" spans="1:19">
+    <row r="79" ht="14.25" hidden="1" spans="1:19">
       <c r="A79" s="4" t="s">
         <v>405</v>
       </c>
@@ -10581,7 +10596,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="80" ht="14.25" spans="1:19">
+    <row r="80" ht="14.25" hidden="1" spans="1:19">
       <c r="A80" s="4" t="s">
         <v>409</v>
       </c>
@@ -10638,7 +10653,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="81" ht="14.25" spans="1:19">
+    <row r="81" ht="14.25" hidden="1" spans="1:19">
       <c r="A81" s="4" t="s">
         <v>413</v>
       </c>
@@ -10695,7 +10710,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="82" ht="14.25" spans="1:19">
+    <row r="82" ht="14.25" hidden="1" spans="1:19">
       <c r="A82" s="4" t="s">
         <v>418</v>
       </c>
@@ -10752,7 +10767,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="83" ht="14.25" spans="1:19">
+    <row r="83" ht="14.25" hidden="1" spans="1:19">
       <c r="A83" s="4" t="s">
         <v>422</v>
       </c>
@@ -10809,7 +10824,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="84" ht="14.25" spans="1:19">
+    <row r="84" ht="14.25" hidden="1" spans="1:19">
       <c r="A84" s="4" t="s">
         <v>426</v>
       </c>
@@ -10866,7 +10881,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="85" ht="27" spans="1:19">
+    <row r="85" ht="27" hidden="1" spans="1:19">
       <c r="A85" s="4" t="s">
         <v>429</v>
       </c>
@@ -10923,7 +10938,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="86" ht="27" spans="1:19">
+    <row r="86" ht="27" hidden="1" spans="1:19">
       <c r="A86" s="4" t="s">
         <v>433</v>
       </c>
@@ -10980,7 +10995,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="87" ht="14.25" spans="1:19">
+    <row r="87" ht="14.25" hidden="1" spans="1:19">
       <c r="A87" s="4" t="s">
         <v>436</v>
       </c>
@@ -11037,7 +11052,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="88" ht="14.25" spans="1:19">
+    <row r="88" ht="14.25" hidden="1" spans="1:19">
       <c r="A88" s="4" t="s">
         <v>440</v>
       </c>
@@ -11094,7 +11109,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="89" ht="14.25" spans="1:19">
+    <row r="89" ht="14.25" hidden="1" spans="1:19">
       <c r="A89" s="4" t="s">
         <v>444</v>
       </c>
@@ -11151,7 +11166,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90" ht="27" spans="1:19">
+    <row r="90" ht="27" hidden="1" spans="1:19">
       <c r="A90" s="4" t="s">
         <v>448</v>
       </c>
@@ -11208,7 +11223,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="91" ht="14.25" spans="1:19">
+    <row r="91" ht="14.25" hidden="1" spans="1:19">
       <c r="A91" s="4" t="s">
         <v>452</v>
       </c>
@@ -11265,7 +11280,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" ht="14.25" spans="1:19">
+    <row r="92" ht="14.25" hidden="1" spans="1:19">
       <c r="A92" s="4" t="s">
         <v>454</v>
       </c>
@@ -11322,7 +11337,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" ht="14.25" spans="1:19">
+    <row r="93" ht="14.25" hidden="1" spans="1:19">
       <c r="A93" s="4" t="s">
         <v>456</v>
       </c>
@@ -11379,7 +11394,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" ht="14.25" spans="1:19">
+    <row r="94" ht="14.25" hidden="1" spans="1:19">
       <c r="A94" s="4" t="s">
         <v>458</v>
       </c>
@@ -11436,7 +11451,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" ht="14.25" spans="1:19">
+    <row r="95" ht="14.25" hidden="1" spans="1:19">
       <c r="A95" s="4" t="s">
         <v>461</v>
       </c>
@@ -11493,7 +11508,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="96" ht="14.25" spans="1:19">
+    <row r="96" ht="14.25" hidden="1" spans="1:19">
       <c r="A96" s="4" t="s">
         <v>465</v>
       </c>
@@ -11550,7 +11565,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="97" ht="14.25" spans="1:19">
+    <row r="97" ht="14.25" hidden="1" spans="1:19">
       <c r="A97" s="4" t="s">
         <v>469</v>
       </c>
@@ -11607,7 +11622,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" ht="14.25" spans="1:19">
+    <row r="98" ht="14.25" hidden="1" spans="1:19">
       <c r="A98" s="4" t="s">
         <v>474</v>
       </c>
@@ -11664,7 +11679,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" ht="14.25" spans="1:19">
+    <row r="99" ht="14.25" hidden="1" spans="1:19">
       <c r="A99" s="4" t="s">
         <v>476</v>
       </c>
@@ -11721,7 +11736,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" ht="14.25" spans="1:19">
+    <row r="100" ht="14.25" hidden="1" spans="1:19">
       <c r="A100" s="4" t="s">
         <v>479</v>
       </c>
@@ -11778,7 +11793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" ht="14.25" spans="1:19">
+    <row r="101" ht="14.25" hidden="1" spans="1:19">
       <c r="A101" s="4" t="s">
         <v>481</v>
       </c>
@@ -11835,7 +11850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" ht="14.25" spans="1:19">
+    <row r="102" ht="14.25" hidden="1" spans="1:19">
       <c r="A102" s="4" t="s">
         <v>483</v>
       </c>
@@ -11892,7 +11907,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" ht="14.25" spans="1:19">
+    <row r="103" ht="14.25" hidden="1" spans="1:19">
       <c r="A103" s="4" t="s">
         <v>485</v>
       </c>
@@ -11949,7 +11964,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" ht="14.25" spans="1:19">
+    <row r="104" ht="14.25" hidden="1" spans="1:19">
       <c r="A104" s="4" t="s">
         <v>487</v>
       </c>
@@ -12006,7 +12021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" ht="14.25" spans="1:19">
+    <row r="105" ht="14.25" hidden="1" spans="1:19">
       <c r="A105" s="4" t="s">
         <v>489</v>
       </c>
@@ -12063,7 +12078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" ht="14.25" spans="1:19">
+    <row r="106" ht="14.25" hidden="1" spans="1:19">
       <c r="A106" s="4" t="s">
         <v>491</v>
       </c>
@@ -12120,7 +12135,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="107" ht="14.25" spans="1:19">
+    <row r="107" ht="14.25" hidden="1" spans="1:19">
       <c r="A107" s="4" t="s">
         <v>495</v>
       </c>
@@ -12177,7 +12192,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="108" ht="14.25" spans="1:19">
+    <row r="108" ht="14.25" hidden="1" spans="1:19">
       <c r="A108" s="4" t="s">
         <v>497</v>
       </c>
@@ -12232,7 +12247,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="109" ht="14.25" spans="1:19">
+    <row r="109" ht="14.25" hidden="1" spans="1:19">
       <c r="A109" s="4" t="s">
         <v>502</v>
       </c>
@@ -12289,7 +12304,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="110" ht="14.25" spans="1:19">
+    <row r="110" ht="14.25" hidden="1" spans="1:19">
       <c r="A110" s="4" t="s">
         <v>504</v>
       </c>
@@ -12346,7 +12361,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" ht="14.25" spans="1:19">
+    <row r="111" ht="14.25" hidden="1" spans="1:19">
       <c r="A111" s="4" t="s">
         <v>506</v>
       </c>
@@ -12403,7 +12418,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="112" ht="14.25" spans="1:19">
+    <row r="112" ht="14.25" hidden="1" spans="1:19">
       <c r="A112" s="4" t="s">
         <v>508</v>
       </c>
@@ -12460,7 +12475,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="113" ht="14.25" spans="1:19">
+    <row r="113" ht="14.25" hidden="1" spans="1:19">
       <c r="A113" s="4" t="s">
         <v>510</v>
       </c>
@@ -12517,7 +12532,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" ht="27" spans="1:19">
+    <row r="114" ht="27" hidden="1" spans="1:19">
       <c r="A114" s="4" t="s">
         <v>513</v>
       </c>
@@ -12574,7 +12589,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="115" ht="27" spans="1:19">
+    <row r="115" ht="27" hidden="1" spans="1:19">
       <c r="A115" s="4" t="s">
         <v>517</v>
       </c>
@@ -12631,7 +12646,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="116" ht="27" spans="1:19">
+    <row r="116" ht="27" hidden="1" spans="1:19">
       <c r="A116" s="4" t="s">
         <v>520</v>
       </c>
@@ -12688,7 +12703,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="117" ht="14.25" spans="1:19">
+    <row r="117" ht="14.25" hidden="1" spans="1:19">
       <c r="A117" s="4" t="s">
         <v>523</v>
       </c>
@@ -12743,7 +12758,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="118" ht="14.25" spans="1:19">
+    <row r="118" ht="14.25" hidden="1" spans="1:19">
       <c r="A118" s="4" t="s">
         <v>528</v>
       </c>
@@ -12800,7 +12815,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" ht="14.25" spans="1:19">
+    <row r="119" ht="14.25" hidden="1" spans="1:19">
       <c r="A119" s="4" t="s">
         <v>530</v>
       </c>
@@ -12857,7 +12872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" ht="14.25" spans="1:19">
+    <row r="120" ht="14.25" hidden="1" spans="1:19">
       <c r="A120" s="4" t="s">
         <v>532</v>
       </c>
@@ -12914,7 +12929,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121" ht="14.25" spans="1:19">
+    <row r="121" ht="14.25" hidden="1" spans="1:19">
       <c r="A121" s="4" t="s">
         <v>534</v>
       </c>
@@ -12971,7 +12986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="122" ht="14.25" spans="1:19">
+    <row r="122" ht="14.25" hidden="1" spans="1:19">
       <c r="A122" s="4" t="s">
         <v>536</v>
       </c>
@@ -13028,7 +13043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" ht="14.25" spans="1:19">
+    <row r="123" ht="14.25" hidden="1" spans="1:19">
       <c r="A123" s="4" t="s">
         <v>539</v>
       </c>
@@ -13085,7 +13100,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" ht="14.25" spans="1:19">
+    <row r="124" ht="14.25" hidden="1" spans="1:19">
       <c r="A124" s="4" t="s">
         <v>542</v>
       </c>
@@ -13142,7 +13157,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" ht="14.25" spans="1:19">
+    <row r="125" ht="14.25" hidden="1" spans="1:19">
       <c r="A125" s="4" t="s">
         <v>544</v>
       </c>
@@ -13199,7 +13214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" ht="14.25" spans="1:19">
+    <row r="126" ht="14.25" hidden="1" spans="1:19">
       <c r="A126" s="4" t="s">
         <v>546</v>
       </c>
@@ -13256,7 +13271,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="127" ht="14.25" spans="1:19">
+    <row r="127" ht="14.25" hidden="1" spans="1:19">
       <c r="A127" s="4" t="s">
         <v>551</v>
       </c>
@@ -13313,7 +13328,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="128" ht="14.25" spans="1:19">
+    <row r="128" ht="14.25" hidden="1" spans="1:19">
       <c r="A128" s="4" t="s">
         <v>553</v>
       </c>
@@ -13370,7 +13385,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="129" ht="14.25" spans="1:19">
+    <row r="129" ht="14.25" hidden="1" spans="1:19">
       <c r="A129" s="4" t="s">
         <v>556</v>
       </c>
@@ -13425,7 +13440,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" ht="14.25" spans="1:19">
+    <row r="130" ht="14.25" hidden="1" spans="1:19">
       <c r="A130" s="4" t="s">
         <v>560</v>
       </c>
@@ -13480,7 +13495,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="131" ht="14.25" spans="1:19">
+    <row r="131" ht="14.25" hidden="1" spans="1:19">
       <c r="A131" s="4" t="s">
         <v>562</v>
       </c>
@@ -13535,7 +13550,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="132" ht="14.25" spans="1:19">
+    <row r="132" ht="14.25" hidden="1" spans="1:19">
       <c r="A132" s="4" t="s">
         <v>564</v>
       </c>
@@ -13590,7 +13605,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="133" ht="14.25" spans="1:19">
+    <row r="133" ht="14.25" hidden="1" spans="1:19">
       <c r="A133" s="4" t="s">
         <v>566</v>
       </c>
@@ -13645,7 +13660,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="134" ht="14.25" spans="1:19">
+    <row r="134" ht="14.25" hidden="1" spans="1:19">
       <c r="A134" s="4" t="s">
         <v>568</v>
       </c>
@@ -13700,7 +13715,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="135" ht="14.25" spans="1:19">
+    <row r="135" ht="14.25" hidden="1" spans="1:19">
       <c r="A135" s="4" t="s">
         <v>572</v>
       </c>
@@ -13755,7 +13770,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="136" ht="14.25" spans="1:19">
+    <row r="136" ht="14.25" hidden="1" spans="1:19">
       <c r="A136" s="4" t="s">
         <v>574</v>
       </c>
@@ -13810,7 +13825,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="137" ht="14.25" spans="1:19">
+    <row r="137" ht="14.25" hidden="1" spans="1:19">
       <c r="A137" s="4" t="s">
         <v>576</v>
       </c>
@@ -13865,7 +13880,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="138" ht="14.25" spans="1:19">
+    <row r="138" ht="14.25" hidden="1" spans="1:19">
       <c r="A138" s="4" t="s">
         <v>578</v>
       </c>
@@ -13920,7 +13935,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="139" ht="14.25" spans="1:19">
+    <row r="139" ht="14.25" hidden="1" spans="1:19">
       <c r="A139" s="4" t="s">
         <v>580</v>
       </c>
@@ -13975,7 +13990,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="140" ht="14.25" spans="1:19">
+    <row r="140" ht="14.25" hidden="1" spans="1:19">
       <c r="A140" s="4" t="s">
         <v>582</v>
       </c>
@@ -14032,7 +14047,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="141" ht="14.25" spans="1:19">
+    <row r="141" ht="14.25" hidden="1" spans="1:19">
       <c r="A141" s="4" t="s">
         <v>585</v>
       </c>
@@ -14089,7 +14104,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="142" ht="14.25" spans="1:19">
+    <row r="142" ht="14.25" hidden="1" spans="1:19">
       <c r="A142" s="4" t="s">
         <v>587</v>
       </c>
@@ -14146,7 +14161,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="143" ht="14.25" spans="1:19">
+    <row r="143" ht="14.25" hidden="1" spans="1:19">
       <c r="A143" s="4" t="s">
         <v>589</v>
       </c>
@@ -14205,7 +14220,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="144" ht="14.25" spans="1:19">
+    <row r="144" ht="14.25" hidden="1" spans="1:19">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
@@ -14262,7 +14277,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="145" ht="27" spans="1:19">
+    <row r="145" ht="27" hidden="1" spans="1:19">
       <c r="A145" s="4" t="s">
         <v>594</v>
       </c>
@@ -14317,7 +14332,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" ht="14.25" spans="1:19">
+    <row r="146" ht="14.25" hidden="1" spans="1:19">
       <c r="A146" s="4" t="s">
         <v>595</v>
       </c>
@@ -14372,7 +14387,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="147" ht="14.25" spans="1:19">
+    <row r="147" ht="14.25" hidden="1" spans="1:19">
       <c r="A147" s="4" t="s">
         <v>599</v>
       </c>
@@ -14425,7 +14440,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" ht="14.25" spans="1:19">
+    <row r="148" ht="14.25" hidden="1" spans="1:19">
       <c r="A148" s="4" t="s">
         <v>605</v>
       </c>
@@ -14478,7 +14493,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="149" ht="14.25" spans="1:19">
+    <row r="149" ht="14.25" hidden="1" spans="1:19">
       <c r="A149" s="4" t="s">
         <v>609</v>
       </c>
@@ -14531,7 +14546,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="150" ht="14.25" spans="1:19">
+    <row r="150" ht="14.25" hidden="1" spans="1:19">
       <c r="A150" s="4" t="s">
         <v>613</v>
       </c>
@@ -14590,7 +14605,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="151" ht="14.25" spans="1:19">
+    <row r="151" ht="14.25" hidden="1" spans="1:19">
       <c r="A151" s="4" t="s">
         <v>615</v>
       </c>
@@ -14647,7 +14662,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="152" ht="14.25" spans="1:19">
+    <row r="152" ht="14.25" hidden="1" spans="1:19">
       <c r="A152" s="4" t="s">
         <v>617</v>
       </c>
@@ -14704,7 +14719,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" ht="14.25" spans="1:19">
+    <row r="153" ht="14.25" hidden="1" spans="1:19">
       <c r="A153" s="4" t="s">
         <v>619</v>
       </c>
@@ -14761,7 +14776,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="154" ht="14.25" spans="1:19">
+    <row r="154" ht="14.25" hidden="1" spans="1:19">
       <c r="A154" s="4" t="s">
         <v>621</v>
       </c>
@@ -14818,7 +14833,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="155" ht="27" spans="1:19">
+    <row r="155" ht="27" hidden="1" spans="1:19">
       <c r="A155" s="4" t="s">
         <v>624</v>
       </c>
@@ -14875,7 +14890,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" ht="27" spans="1:19">
+    <row r="156" ht="27" hidden="1" spans="1:19">
       <c r="A156" s="4" t="s">
         <v>628</v>
       </c>
@@ -14932,7 +14947,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="157" ht="14.25" spans="1:19">
+    <row r="157" ht="14.25" hidden="1" spans="1:19">
       <c r="A157" s="4" t="s">
         <v>630</v>
       </c>
@@ -14989,7 +15004,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" ht="14.25" spans="1:19">
+    <row r="158" ht="14.25" hidden="1" spans="1:19">
       <c r="A158" s="4" t="s">
         <v>632</v>
       </c>
@@ -15046,7 +15061,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" ht="14.25" spans="1:19">
+    <row r="159" ht="14.25" hidden="1" spans="1:19">
       <c r="A159" s="4" t="s">
         <v>634</v>
       </c>
@@ -15103,7 +15118,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" ht="14.25" spans="1:19">
+    <row r="160" ht="14.25" hidden="1" spans="1:19">
       <c r="A160" s="4" t="s">
         <v>636</v>
       </c>
@@ -15160,7 +15175,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" ht="14.25" spans="1:19">
+    <row r="161" ht="14.25" hidden="1" spans="1:19">
       <c r="A161" s="4" t="s">
         <v>638</v>
       </c>
@@ -15217,7 +15232,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" ht="14.25" spans="1:19">
+    <row r="162" ht="14.25" hidden="1" spans="1:19">
       <c r="A162" s="4" t="s">
         <v>640</v>
       </c>
@@ -15274,7 +15289,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="163" ht="14.25" spans="1:19">
+    <row r="163" ht="14.25" hidden="1" spans="1:19">
       <c r="A163" s="4" t="s">
         <v>642</v>
       </c>
@@ -15331,7 +15346,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="164" ht="14.25" spans="1:19">
+    <row r="164" ht="14.25" hidden="1" spans="1:19">
       <c r="A164" s="4" t="s">
         <v>644</v>
       </c>
@@ -15388,7 +15403,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="165" ht="14.25" spans="1:19">
+    <row r="165" ht="14.25" hidden="1" spans="1:19">
       <c r="A165" s="4" t="s">
         <v>646</v>
       </c>
@@ -15445,7 +15460,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="166" ht="14.25" spans="1:19">
+    <row r="166" ht="14.25" hidden="1" spans="1:19">
       <c r="A166" s="4" t="s">
         <v>651</v>
       </c>
@@ -15502,7 +15517,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="167" ht="14.25" spans="1:19">
+    <row r="167" ht="14.25" hidden="1" spans="1:19">
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
@@ -15559,7 +15574,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="168" ht="14.25" spans="1:19">
+    <row r="168" ht="14.25" hidden="1" spans="1:19">
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
@@ -15616,7 +15631,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="169" ht="14.25" spans="1:19">
+    <row r="169" ht="14.25" hidden="1" spans="1:19">
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
@@ -15673,7 +15688,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="170" ht="14.25" spans="1:19">
+    <row r="170" ht="14.25" hidden="1" spans="1:19">
       <c r="A170" s="4" t="s">
         <v>659</v>
       </c>
@@ -15730,7 +15745,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="171" ht="14.25" spans="1:19">
+    <row r="171" ht="14.25" hidden="1" spans="1:19">
       <c r="A171" s="4" t="s">
         <v>661</v>
       </c>
@@ -15787,7 +15802,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="172" ht="14.25" spans="1:19">
+    <row r="172" ht="14.25" hidden="1" spans="1:19">
       <c r="A172" s="4" t="s">
         <v>663</v>
       </c>
@@ -15844,7 +15859,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="173" ht="14.25" spans="1:19">
+    <row r="173" ht="14.25" hidden="1" spans="1:19">
       <c r="A173" s="4" t="s">
         <v>665</v>
       </c>
@@ -15901,7 +15916,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="174" ht="14.25" spans="1:19">
+    <row r="174" ht="14.25" hidden="1" spans="1:19">
       <c r="A174" s="4" t="s">
         <v>667</v>
       </c>
@@ -15958,7 +15973,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" ht="14.25" spans="1:19">
+    <row r="175" ht="14.25" hidden="1" spans="1:19">
       <c r="A175" s="4" t="s">
         <v>669</v>
       </c>
@@ -16015,7 +16030,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="176" ht="14.25" spans="1:19">
+    <row r="176" ht="14.25" hidden="1" spans="1:19">
       <c r="A176" s="4" t="s">
         <v>671</v>
       </c>
@@ -16072,7 +16087,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="177" ht="14.25" spans="1:19">
+    <row r="177" ht="14.25" hidden="1" spans="1:19">
       <c r="A177" s="4" t="s">
         <v>673</v>
       </c>
@@ -16129,7 +16144,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="178" ht="14.25" spans="1:19">
+    <row r="178" ht="14.25" hidden="1" spans="1:19">
       <c r="A178" s="4" t="s">
         <v>677</v>
       </c>
@@ -16186,7 +16201,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="179" ht="14.25" spans="1:19">
+    <row r="179" ht="14.25" hidden="1" spans="1:19">
       <c r="A179" s="4" t="s">
         <v>679</v>
       </c>
@@ -16243,7 +16258,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" ht="14.25" spans="1:19">
+    <row r="180" ht="14.25" hidden="1" spans="1:19">
       <c r="A180" s="4" t="s">
         <v>681</v>
       </c>
@@ -16300,7 +16315,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" ht="14.25" spans="1:19">
+    <row r="181" ht="14.25" hidden="1" spans="1:19">
       <c r="A181" s="4" t="s">
         <v>683</v>
       </c>
@@ -16357,7 +16372,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" ht="14.25" spans="1:19">
+    <row r="182" ht="14.25" hidden="1" spans="1:19">
       <c r="A182" s="4" t="s">
         <v>685</v>
       </c>
@@ -16414,7 +16429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" ht="14.25" spans="1:19">
+    <row r="183" ht="14.25" hidden="1" spans="1:19">
       <c r="A183" s="4" t="s">
         <v>687</v>
       </c>
@@ -16471,7 +16486,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" ht="14.25" spans="1:19">
+    <row r="184" ht="14.25" hidden="1" spans="1:19">
       <c r="A184" s="4" t="s">
         <v>690</v>
       </c>
@@ -16528,7 +16543,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" ht="14.25" spans="1:19">
+    <row r="185" ht="14.25" hidden="1" spans="1:19">
       <c r="A185" s="4" t="s">
         <v>692</v>
       </c>
@@ -16585,7 +16600,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" ht="14.25" spans="1:19">
+    <row r="186" ht="14.25" hidden="1" spans="1:19">
       <c r="A186" s="4" t="s">
         <v>694</v>
       </c>
@@ -16640,7 +16655,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="187" ht="14.25" spans="1:19">
+    <row r="187" ht="14.25" hidden="1" spans="1:19">
       <c r="A187" s="4" t="s">
         <v>698</v>
       </c>
@@ -16697,7 +16712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" ht="14.25" spans="1:19">
+    <row r="188" ht="14.25" hidden="1" spans="1:19">
       <c r="A188" s="4" t="s">
         <v>700</v>
       </c>
@@ -16754,7 +16769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" ht="14.25" spans="1:19">
+    <row r="189" ht="14.25" hidden="1" spans="1:19">
       <c r="A189" s="4" t="s">
         <v>702</v>
       </c>
@@ -16813,7 +16828,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" ht="14.25" spans="1:19">
+    <row r="190" ht="14.25" hidden="1" spans="1:19">
       <c r="A190" s="4" t="s">
         <v>706</v>
       </c>
@@ -16868,7 +16883,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" ht="14.25" spans="1:19">
+    <row r="191" ht="14.25" hidden="1" spans="1:19">
       <c r="A191" s="4" t="s">
         <v>708</v>
       </c>
@@ -16927,7 +16942,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" ht="14.25" spans="1:19">
+    <row r="192" ht="14.25" hidden="1" spans="1:19">
       <c r="A192" s="4" t="s">
         <v>710</v>
       </c>
@@ -16986,7 +17001,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="193" ht="14.25" spans="1:19">
+    <row r="193" ht="14.25" hidden="1" spans="1:19">
       <c r="A193" s="4" t="s">
         <v>714</v>
       </c>
@@ -17045,7 +17060,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="194" ht="14.25" spans="1:19">
+    <row r="194" ht="14.25" hidden="1" spans="1:19">
       <c r="A194" s="4" t="s">
         <v>717</v>
       </c>
@@ -17104,7 +17119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="195" ht="14.25" spans="1:19">
+    <row r="195" ht="14.25" hidden="1" spans="1:19">
       <c r="A195" s="4" t="s">
         <v>719</v>
       </c>
@@ -17163,7 +17178,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="196" ht="14.25" spans="1:19">
+    <row r="196" ht="14.25" hidden="1" spans="1:19">
       <c r="A196" s="4" t="s">
         <v>722</v>
       </c>
@@ -17220,7 +17235,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="197" ht="14.25" spans="1:19">
+    <row r="197" ht="14.25" hidden="1" spans="1:19">
       <c r="A197" s="4" t="s">
         <v>723</v>
       </c>
@@ -17277,7 +17292,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="198" ht="14.25" spans="1:19">
+    <row r="198" ht="14.25" hidden="1" spans="1:19">
       <c r="A198" s="4" t="s">
         <v>725</v>
       </c>
@@ -17334,7 +17349,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="199" ht="27" spans="1:19">
+    <row r="199" ht="27" hidden="1" spans="1:19">
       <c r="A199" s="4" t="s">
         <v>727</v>
       </c>
@@ -17391,7 +17406,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="200" ht="14.25" spans="1:19">
+    <row r="200" ht="14.25" hidden="1" spans="1:19">
       <c r="A200" s="4" t="s">
         <v>731</v>
       </c>
@@ -17448,7 +17463,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="201" ht="14.25" spans="1:19">
+    <row r="201" ht="14.25" hidden="1" spans="1:19">
       <c r="A201" s="4" t="s">
         <v>735</v>
       </c>
@@ -17505,7 +17520,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="202" ht="14.25" spans="1:19">
+    <row r="202" ht="14.25" hidden="1" spans="1:19">
       <c r="A202" s="4" t="s">
         <v>738</v>
       </c>
@@ -17562,7 +17577,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="203" ht="14.25" spans="1:19">
+    <row r="203" ht="14.25" hidden="1" spans="1:19">
       <c r="A203" s="4" t="s">
         <v>740</v>
       </c>
@@ -17619,7 +17634,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="204" ht="14.25" spans="1:19">
+    <row r="204" ht="14.25" hidden="1" spans="1:19">
       <c r="A204" s="4" t="s">
         <v>742</v>
       </c>
@@ -17676,7 +17691,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="205" ht="14.25" spans="1:19">
+    <row r="205" ht="14.25" hidden="1" spans="1:19">
       <c r="A205" s="4" t="s">
         <v>745</v>
       </c>
@@ -17735,7 +17750,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" ht="14.25" spans="1:19">
+    <row r="206" ht="14.25" hidden="1" spans="1:19">
       <c r="A206" s="4" t="s">
         <v>749</v>
       </c>
@@ -17792,7 +17807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" ht="14.25" spans="1:19">
+    <row r="207" ht="14.25" hidden="1" spans="1:19">
       <c r="A207" s="4" t="s">
         <v>751</v>
       </c>
@@ -17849,7 +17864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" ht="14.25" spans="1:19">
+    <row r="208" ht="14.25" hidden="1" spans="1:19">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -17906,7 +17921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" ht="14.25" spans="1:19">
+    <row r="209" ht="14.25" hidden="1" spans="1:19">
       <c r="A209" s="4" t="s">
         <v>755</v>
       </c>
@@ -17961,7 +17976,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" ht="14.25" spans="1:19">
+    <row r="210" ht="14.25" hidden="1" spans="1:19">
       <c r="A210" s="4" t="s">
         <v>757</v>
       </c>
@@ -18018,7 +18033,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" ht="14.25" spans="1:19">
+    <row r="211" ht="14.25" hidden="1" spans="1:19">
       <c r="A211" s="4" t="s">
         <v>759</v>
       </c>
@@ -18075,7 +18090,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="212" ht="14.25" spans="1:19">
+    <row r="212" ht="14.25" hidden="1" spans="1:19">
       <c r="A212" s="4" t="s">
         <v>761</v>
       </c>
@@ -18132,7 +18147,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="213" ht="14.25" spans="1:19">
+    <row r="213" ht="14.25" hidden="1" spans="1:19">
       <c r="A213" s="4" t="s">
         <v>763</v>
       </c>
@@ -18189,7 +18204,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="214" ht="14.25" spans="1:19">
+    <row r="214" ht="14.25" hidden="1" spans="1:19">
       <c r="A214" s="4" t="s">
         <v>765</v>
       </c>
@@ -18246,7 +18261,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="215" ht="14.25" spans="1:19">
+    <row r="215" ht="14.25" hidden="1" spans="1:19">
       <c r="A215" s="4" t="s">
         <v>768</v>
       </c>
@@ -18303,7 +18318,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="216" ht="14.25" spans="1:19">
+    <row r="216" ht="14.25" hidden="1" spans="1:19">
       <c r="A216" s="4" t="s">
         <v>770</v>
       </c>
@@ -18362,7 +18377,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="217" ht="14.25" spans="1:19">
+    <row r="217" ht="14.25" hidden="1" spans="1:19">
       <c r="A217" s="4" t="s">
         <v>773</v>
       </c>
@@ -18419,7 +18434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="218" ht="14.25" spans="1:19">
+    <row r="218" ht="14.25" hidden="1" spans="1:19">
       <c r="A218" s="4" t="s">
         <v>775</v>
       </c>
@@ -18476,7 +18491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="219" ht="27" spans="1:19">
+    <row r="219" ht="27" hidden="1" spans="1:19">
       <c r="A219" s="4" t="s">
         <v>777</v>
       </c>
@@ -18531,7 +18546,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="220" ht="27" spans="1:19">
+    <row r="220" ht="27" hidden="1" spans="1:19">
       <c r="A220" s="4" t="s">
         <v>781</v>
       </c>
@@ -18586,7 +18601,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="221" ht="27" spans="1:19">
+    <row r="221" ht="27" hidden="1" spans="1:19">
       <c r="A221" s="4" t="s">
         <v>783</v>
       </c>
@@ -18641,7 +18656,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="222" ht="27" spans="1:19">
+    <row r="222" ht="27" hidden="1" spans="1:19">
       <c r="A222" s="4" t="s">
         <v>785</v>
       </c>
@@ -18696,7 +18711,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="223" ht="27" spans="1:19">
+    <row r="223" ht="27" hidden="1" spans="1:19">
       <c r="A223" s="4" t="s">
         <v>787</v>
       </c>
@@ -18751,7 +18766,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="224" ht="27" spans="1:19">
+    <row r="224" ht="27" hidden="1" spans="1:19">
       <c r="A224" s="4" t="s">
         <v>789</v>
       </c>
@@ -18806,7 +18821,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="225" ht="14.25" spans="1:19">
+    <row r="225" ht="14.25" hidden="1" spans="1:19">
       <c r="A225" s="4" t="s">
         <v>791</v>
       </c>
@@ -18863,7 +18878,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="226" ht="14.25" spans="1:19">
+    <row r="226" ht="14.25" hidden="1" spans="1:19">
       <c r="A226" s="4" t="s">
         <v>793</v>
       </c>
@@ -18920,7 +18935,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="227" ht="14.25" spans="1:19">
+    <row r="227" ht="14.25" hidden="1" spans="1:19">
       <c r="A227" s="4" t="s">
         <v>794</v>
       </c>
@@ -18977,7 +18992,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="228" ht="14.25" spans="1:19">
+    <row r="228" ht="14.25" hidden="1" spans="1:19">
       <c r="A228" s="4" t="s">
         <v>796</v>
       </c>
@@ -19034,7 +19049,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" ht="14.25" spans="1:19">
+    <row r="229" ht="14.25" hidden="1" spans="1:19">
       <c r="A229" s="4" t="s">
         <v>798</v>
       </c>
@@ -19091,7 +19106,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="230" ht="14.25" spans="1:19">
+    <row r="230" ht="14.25" hidden="1" spans="1:19">
       <c r="A230" s="4" t="s">
         <v>800</v>
       </c>
@@ -19148,7 +19163,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="231" ht="14.25" spans="1:19">
+    <row r="231" ht="14.25" hidden="1" spans="1:19">
       <c r="A231" s="4" t="s">
         <v>802</v>
       </c>
@@ -19205,7 +19220,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="232" ht="14.25" spans="1:19">
+    <row r="232" ht="14.25" hidden="1" spans="1:19">
       <c r="A232" s="4" t="s">
         <v>804</v>
       </c>
@@ -19262,7 +19277,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="233" ht="14.25" spans="1:19">
+    <row r="233" ht="14.25" hidden="1" spans="1:19">
       <c r="A233" s="4" t="s">
         <v>806</v>
       </c>
@@ -19319,7 +19334,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" ht="14.25" spans="1:19">
+    <row r="234" ht="14.25" hidden="1" spans="1:19">
       <c r="A234" s="4" t="s">
         <v>808</v>
       </c>
@@ -19376,7 +19391,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="235" ht="14.25" spans="1:19">
+    <row r="235" ht="14.25" hidden="1" spans="1:19">
       <c r="A235" s="4" t="s">
         <v>810</v>
       </c>
@@ -19433,7 +19448,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="236" ht="27" spans="1:19">
+    <row r="236" ht="27" hidden="1" spans="1:19">
       <c r="A236" s="4" t="s">
         <v>812</v>
       </c>
@@ -19488,7 +19503,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="237" ht="27" spans="1:19">
+    <row r="237" ht="27" hidden="1" spans="1:19">
       <c r="A237" s="4" t="s">
         <v>817</v>
       </c>
@@ -19543,7 +19558,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="238" ht="27" spans="1:19">
+    <row r="238" ht="27" hidden="1" spans="1:19">
       <c r="A238" s="4" t="s">
         <v>819</v>
       </c>
@@ -19598,7 +19613,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="239" ht="14.25" spans="1:19">
+    <row r="239" ht="14.25" hidden="1" spans="1:19">
       <c r="A239" s="4" t="s">
         <v>821</v>
       </c>
@@ -19653,7 +19668,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="240" ht="14.25" spans="1:19">
+    <row r="240" ht="14.25" hidden="1" spans="1:19">
       <c r="A240" s="4" t="s">
         <v>825</v>
       </c>
@@ -19710,7 +19725,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" ht="14.25" spans="1:19">
+    <row r="241" ht="14.25" hidden="1" spans="1:19">
       <c r="A241" s="4" t="s">
         <v>827</v>
       </c>
@@ -19767,7 +19782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" ht="14.25" spans="1:19">
+    <row r="242" ht="14.25" hidden="1" spans="1:19">
       <c r="A242" s="4" t="s">
         <v>829</v>
       </c>
@@ -19824,7 +19839,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="243" ht="14.25" spans="1:19">
+    <row r="243" ht="14.25" hidden="1" spans="1:19">
       <c r="A243" s="4" t="s">
         <v>832</v>
       </c>
@@ -19881,7 +19896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" ht="14.25" spans="1:19">
+    <row r="244" ht="14.25" hidden="1" spans="1:19">
       <c r="A244" s="4" t="s">
         <v>836</v>
       </c>
@@ -19938,7 +19953,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="245" ht="14.25" spans="1:19">
+    <row r="245" ht="14.25" hidden="1" spans="1:19">
       <c r="A245" s="4" t="s">
         <v>838</v>
       </c>
@@ -19995,7 +20010,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="246" ht="14.25" spans="1:19">
+    <row r="246" ht="14.25" hidden="1" spans="1:19">
       <c r="A246" s="4" t="s">
         <v>842</v>
       </c>
@@ -20050,7 +20065,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="247" ht="14.25" spans="1:19">
+    <row r="247" ht="14.25" hidden="1" spans="1:19">
       <c r="A247" s="4" t="s">
         <v>846</v>
       </c>
@@ -20105,7 +20120,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" ht="14.25" spans="1:19">
+    <row r="248" ht="14.25" hidden="1" spans="1:19">
       <c r="A248" s="4" t="s">
         <v>849</v>
       </c>
@@ -20160,7 +20175,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" ht="14.25" spans="1:19">
+    <row r="249" ht="14.25" hidden="1" spans="1:19">
       <c r="A249" s="4" t="s">
         <v>851</v>
       </c>
@@ -20215,7 +20230,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" ht="14.25" spans="1:19">
+    <row r="250" ht="14.25" hidden="1" spans="1:19">
       <c r="A250" s="4" t="s">
         <v>853</v>
       </c>
@@ -20270,7 +20285,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" ht="14.25" spans="1:19">
+    <row r="251" ht="14.25" hidden="1" spans="1:19">
       <c r="A251" s="4" t="s">
         <v>855</v>
       </c>
@@ -20327,7 +20342,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="252" ht="14.25" spans="1:19">
+    <row r="252" ht="14.25" hidden="1" spans="1:19">
       <c r="A252" s="4" t="s">
         <v>857</v>
       </c>
@@ -20384,7 +20399,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="253" ht="14.25" spans="1:19">
+    <row r="253" ht="14.25" hidden="1" spans="1:19">
       <c r="A253" s="4" t="s">
         <v>859</v>
       </c>
@@ -20441,7 +20456,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="254" ht="14.25" spans="1:19">
+    <row r="254" ht="14.25" hidden="1" spans="1:19">
       <c r="A254" s="4" t="s">
         <v>861</v>
       </c>
@@ -20498,7 +20513,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="255" ht="14.25" spans="1:19">
+    <row r="255" ht="14.25" hidden="1" spans="1:19">
       <c r="A255" s="4" t="s">
         <v>863</v>
       </c>
@@ -20557,7 +20572,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="256" ht="14.25" spans="1:19">
+    <row r="256" ht="14.25" hidden="1" spans="1:19">
       <c r="A256" s="4" t="s">
         <v>866</v>
       </c>
@@ -20614,7 +20629,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="257" ht="15" spans="1:19">
+    <row r="257" ht="15" hidden="1" spans="1:19">
       <c r="A257" s="4" t="s">
         <v>868</v>
       </c>
@@ -20671,7 +20686,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="258" ht="27.75" spans="1:19">
+    <row r="258" ht="27.75" hidden="1" spans="1:19">
       <c r="A258" s="4" t="s">
         <v>870</v>
       </c>
@@ -20728,7 +20743,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="259" ht="27.75" spans="1:19">
+    <row r="259" ht="27.75" hidden="1" spans="1:19">
       <c r="A259" s="4" t="s">
         <v>874</v>
       </c>
@@ -20785,7 +20800,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="260" ht="14.25" spans="1:19">
+    <row r="260" ht="14.25" hidden="1" spans="1:19">
       <c r="A260" s="4" t="s">
         <v>877</v>
       </c>
@@ -20836,7 +20851,7 @@
       <c r="R260" s="7"/>
       <c r="S260" s="7"/>
     </row>
-    <row r="261" ht="14.25" spans="1:19">
+    <row r="261" ht="14.25" hidden="1" spans="1:19">
       <c r="A261" s="4" t="s">
         <v>881</v>
       </c>
@@ -20887,7 +20902,7 @@
       <c r="R261" s="7"/>
       <c r="S261" s="7"/>
     </row>
-    <row r="262" ht="14.25" spans="1:19">
+    <row r="262" ht="14.25" hidden="1" spans="1:19">
       <c r="A262" s="4" t="s">
         <v>886</v>
       </c>
@@ -20938,7 +20953,7 @@
       <c r="R262" s="7"/>
       <c r="S262" s="7"/>
     </row>
-    <row r="263" ht="14.25" spans="1:19">
+    <row r="263" ht="14.25" hidden="1" spans="1:19">
       <c r="A263" s="4" t="s">
         <v>889</v>
       </c>
@@ -20989,7 +21004,7 @@
       <c r="R263" s="7"/>
       <c r="S263" s="7"/>
     </row>
-    <row r="264" ht="14.25" spans="1:19">
+    <row r="264" ht="14.25" hidden="1" spans="1:19">
       <c r="A264" s="4" t="s">
         <v>893</v>
       </c>
@@ -21040,7 +21055,7 @@
       <c r="R264" s="7"/>
       <c r="S264" s="7"/>
     </row>
-    <row r="265" ht="14.25" spans="1:19">
+    <row r="265" ht="14.25" hidden="1" spans="1:19">
       <c r="A265" s="4" t="s">
         <v>896</v>
       </c>
@@ -21091,7 +21106,7 @@
       <c r="R265" s="7"/>
       <c r="S265" s="7"/>
     </row>
-    <row r="266" ht="14.25" spans="1:19">
+    <row r="266" ht="14.25" hidden="1" spans="1:19">
       <c r="A266" s="4" t="s">
         <v>900</v>
       </c>
@@ -21142,7 +21157,7 @@
       <c r="R266" s="7"/>
       <c r="S266" s="7"/>
     </row>
-    <row r="267" ht="14.25" spans="1:19">
+    <row r="267" ht="14.25" hidden="1" spans="1:19">
       <c r="A267" s="4" t="s">
         <v>904</v>
       </c>
@@ -21193,7 +21208,7 @@
       <c r="R267" s="7"/>
       <c r="S267" s="7"/>
     </row>
-    <row r="268" ht="14.25" spans="1:19">
+    <row r="268" ht="14.25" hidden="1" spans="1:19">
       <c r="A268" s="4" t="s">
         <v>907</v>
       </c>
@@ -21244,7 +21259,7 @@
       <c r="R268" s="7"/>
       <c r="S268" s="7"/>
     </row>
-    <row r="269" ht="14.25" spans="1:19">
+    <row r="269" ht="14.25" hidden="1" spans="1:19">
       <c r="A269" s="4" t="s">
         <v>909</v>
       </c>
@@ -21295,7 +21310,7 @@
       <c r="R269" s="7"/>
       <c r="S269" s="7"/>
     </row>
-    <row r="270" ht="14.25" spans="1:19">
+    <row r="270" ht="14.25" hidden="1" spans="1:19">
       <c r="A270" s="4" t="s">
         <v>912</v>
       </c>
@@ -21346,7 +21361,7 @@
       <c r="R270" s="7"/>
       <c r="S270" s="7"/>
     </row>
-    <row r="271" ht="14.25" spans="1:19">
+    <row r="271" ht="14.25" hidden="1" spans="1:19">
       <c r="A271" s="4" t="s">
         <v>914</v>
       </c>
@@ -21399,7 +21414,7 @@
       <c r="R271" s="7"/>
       <c r="S271" s="7"/>
     </row>
-    <row r="272" ht="14.25" spans="1:19">
+    <row r="272" ht="14.25" hidden="1" spans="1:19">
       <c r="A272" s="4" t="s">
         <v>918</v>
       </c>
@@ -21452,7 +21467,7 @@
       <c r="R272" s="7"/>
       <c r="S272" s="7"/>
     </row>
-    <row r="273" ht="14.25" spans="1:19">
+    <row r="273" ht="14.25" hidden="1" spans="1:19">
       <c r="A273" s="4" t="s">
         <v>920</v>
       </c>
@@ -21505,7 +21520,7 @@
       <c r="R273" s="7"/>
       <c r="S273" s="7"/>
     </row>
-    <row r="274" ht="14.25" spans="1:19">
+    <row r="274" ht="14.25" hidden="1" spans="1:19">
       <c r="A274" s="4" t="s">
         <v>923</v>
       </c>
@@ -21556,7 +21571,7 @@
       <c r="R274" s="7"/>
       <c r="S274" s="7"/>
     </row>
-    <row r="275" ht="14.25" spans="1:19">
+    <row r="275" ht="14.25" hidden="1" spans="1:19">
       <c r="A275" s="4" t="s">
         <v>927</v>
       </c>
@@ -21607,7 +21622,7 @@
       <c r="R275" s="7"/>
       <c r="S275" s="7"/>
     </row>
-    <row r="276" ht="14.25" spans="1:19">
+    <row r="276" ht="14.25" hidden="1" spans="1:19">
       <c r="A276" s="4" t="s">
         <v>930</v>
       </c>
@@ -21658,7 +21673,7 @@
       <c r="R276" s="7"/>
       <c r="S276" s="7"/>
     </row>
-    <row r="277" ht="14.25" spans="1:19">
+    <row r="277" ht="14.25" hidden="1" spans="1:19">
       <c r="A277" s="4" t="s">
         <v>932</v>
       </c>
@@ -21709,7 +21724,7 @@
       <c r="R277" s="7"/>
       <c r="S277" s="7"/>
     </row>
-    <row r="278" ht="14.25" spans="1:19">
+    <row r="278" ht="14.25" hidden="1" spans="1:19">
       <c r="A278" s="4" t="s">
         <v>935</v>
       </c>
@@ -21760,7 +21775,7 @@
       <c r="R278" s="7"/>
       <c r="S278" s="7"/>
     </row>
-    <row r="279" ht="14.25" spans="1:19">
+    <row r="279" ht="14.25" hidden="1" spans="1:19">
       <c r="A279" s="4" t="s">
         <v>937</v>
       </c>
@@ -21813,7 +21828,7 @@
       <c r="R279" s="7"/>
       <c r="S279" s="7"/>
     </row>
-    <row r="280" ht="14.25" spans="1:19">
+    <row r="280" ht="14.25" hidden="1" spans="1:19">
       <c r="A280" s="4" t="s">
         <v>940</v>
       </c>
@@ -21866,7 +21881,7 @@
       <c r="R280" s="7"/>
       <c r="S280" s="7"/>
     </row>
-    <row r="281" ht="14.25" spans="1:19">
+    <row r="281" ht="14.25" hidden="1" spans="1:19">
       <c r="A281" s="4" t="s">
         <v>943</v>
       </c>
@@ -21917,7 +21932,7 @@
       <c r="R281" s="7"/>
       <c r="S281" s="7"/>
     </row>
-    <row r="282" ht="14.25" spans="1:19">
+    <row r="282" ht="14.25" hidden="1" spans="1:19">
       <c r="A282" s="4" t="s">
         <v>946</v>
       </c>
@@ -21968,7 +21983,7 @@
       <c r="R282" s="7"/>
       <c r="S282" s="7"/>
     </row>
-    <row r="283" ht="14.25" spans="1:19">
+    <row r="283" ht="14.25" hidden="1" spans="1:19">
       <c r="A283" s="4" t="s">
         <v>950</v>
       </c>
@@ -22019,7 +22034,7 @@
       <c r="R283" s="7"/>
       <c r="S283" s="7"/>
     </row>
-    <row r="284" ht="14.25" spans="1:19">
+    <row r="284" ht="14.25" hidden="1" spans="1:19">
       <c r="A284" s="4" t="s">
         <v>953</v>
       </c>
@@ -22070,7 +22085,7 @@
       <c r="R284" s="7"/>
       <c r="S284" s="7"/>
     </row>
-    <row r="285" ht="14.25" spans="1:19">
+    <row r="285" ht="14.25" hidden="1" spans="1:19">
       <c r="A285" s="4" t="s">
         <v>937</v>
       </c>
@@ -22121,7 +22136,7 @@
       <c r="R285" s="7"/>
       <c r="S285" s="7"/>
     </row>
-    <row r="286" ht="14.25" spans="1:19">
+    <row r="286" ht="14.25" hidden="1" spans="1:19">
       <c r="A286" s="4" t="s">
         <v>940</v>
       </c>
@@ -22172,7 +22187,7 @@
       <c r="R286" s="7"/>
       <c r="S286" s="7"/>
     </row>
-    <row r="287" ht="14.25" spans="1:19">
+    <row r="287" ht="14.25" hidden="1" spans="1:19">
       <c r="A287" s="4" t="s">
         <v>959</v>
       </c>
@@ -22223,7 +22238,7 @@
       <c r="R287" s="7"/>
       <c r="S287" s="7"/>
     </row>
-    <row r="288" ht="14.25" spans="1:19">
+    <row r="288" ht="14.25" hidden="1" spans="1:19">
       <c r="A288" s="4" t="s">
         <v>963</v>
       </c>
@@ -22274,7 +22289,7 @@
       <c r="R288" s="7"/>
       <c r="S288" s="7"/>
     </row>
-    <row r="289" ht="14.25" spans="1:19">
+    <row r="289" ht="14.25" hidden="1" spans="1:19">
       <c r="A289" s="4" t="s">
         <v>965</v>
       </c>
@@ -22325,7 +22340,7 @@
       <c r="R289" s="7"/>
       <c r="S289" s="7"/>
     </row>
-    <row r="290" ht="14.25" spans="1:19">
+    <row r="290" ht="14.25" hidden="1" spans="1:19">
       <c r="A290" s="4" t="s">
         <v>967</v>
       </c>
@@ -22376,7 +22391,7 @@
       <c r="R290" s="7"/>
       <c r="S290" s="7"/>
     </row>
-    <row r="291" ht="14.25" spans="1:19">
+    <row r="291" ht="14.25" hidden="1" spans="1:19">
       <c r="A291" s="4" t="s">
         <v>969</v>
       </c>
@@ -22427,7 +22442,7 @@
       <c r="R291" s="7"/>
       <c r="S291" s="7"/>
     </row>
-    <row r="292" ht="27" spans="1:19">
+    <row r="292" ht="27" hidden="1" spans="1:19">
       <c r="A292" s="4" t="s">
         <v>973</v>
       </c>
@@ -22478,7 +22493,7 @@
       <c r="R292" s="7"/>
       <c r="S292" s="7"/>
     </row>
-    <row r="293" ht="14.25" spans="1:19">
+    <row r="293" ht="14.25" hidden="1" spans="1:19">
       <c r="A293" s="4" t="s">
         <v>977</v>
       </c>
@@ -22529,7 +22544,7 @@
       <c r="R293" s="7"/>
       <c r="S293" s="7"/>
     </row>
-    <row r="294" ht="14.25" spans="1:19">
+    <row r="294" ht="14.25" hidden="1" spans="1:19">
       <c r="A294" s="4" t="s">
         <v>981</v>
       </c>
@@ -22580,7 +22595,7 @@
       <c r="R294" s="7"/>
       <c r="S294" s="7"/>
     </row>
-    <row r="295" ht="14.25" spans="1:19">
+    <row r="295" ht="14.25" hidden="1" spans="1:19">
       <c r="A295" s="4" t="s">
         <v>984</v>
       </c>
@@ -22631,7 +22646,7 @@
       <c r="R295" s="7"/>
       <c r="S295" s="7"/>
     </row>
-    <row r="296" ht="14.25" spans="1:19">
+    <row r="296" ht="14.25" hidden="1" spans="1:19">
       <c r="A296" s="4" t="s">
         <v>987</v>
       </c>
@@ -22682,7 +22697,7 @@
       <c r="R296" s="7"/>
       <c r="S296" s="7"/>
     </row>
-    <row r="297" ht="14.25" spans="1:19">
+    <row r="297" ht="14.25" hidden="1" spans="1:19">
       <c r="A297" s="4" t="s">
         <v>990</v>
       </c>
@@ -22733,7 +22748,7 @@
       <c r="R297" s="7"/>
       <c r="S297" s="7"/>
     </row>
-    <row r="298" ht="14.25" spans="1:19">
+    <row r="298" ht="14.25" hidden="1" spans="1:19">
       <c r="A298" s="4" t="s">
         <v>992</v>
       </c>
@@ -22784,7 +22799,7 @@
       <c r="R298" s="7"/>
       <c r="S298" s="7"/>
     </row>
-    <row r="299" ht="14.25" spans="1:19">
+    <row r="299" ht="14.25" hidden="1" spans="1:19">
       <c r="A299" s="4" t="s">
         <v>996</v>
       </c>
@@ -22835,7 +22850,7 @@
       <c r="R299" s="7"/>
       <c r="S299" s="7"/>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" hidden="1" spans="1:19">
       <c r="A300" s="4" t="s">
         <v>999</v>
       </c>
@@ -22888,7 +22903,7 @@
       <c r="R300" s="7"/>
       <c r="S300" s="7"/>
     </row>
-    <row r="301" spans="1:19">
+    <row r="301" hidden="1" spans="1:19">
       <c r="A301" s="4" t="s">
         <v>1004</v>
       </c>
@@ -22941,7 +22956,7 @@
       <c r="R301" s="7"/>
       <c r="S301" s="7"/>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" hidden="1" spans="1:19">
       <c r="A302" s="4" t="s">
         <v>1008</v>
       </c>
@@ -22994,7 +23009,7 @@
       <c r="R302" s="7"/>
       <c r="S302" s="7"/>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" hidden="1" spans="1:19">
       <c r="A303" s="4" t="s">
         <v>1011</v>
       </c>
@@ -23047,7 +23062,7 @@
       <c r="R303" s="7"/>
       <c r="S303" s="7"/>
     </row>
-    <row r="304" ht="14.25" spans="1:19">
+    <row r="304" ht="14.25" hidden="1" spans="1:19">
       <c r="A304" s="4" t="s">
         <v>1014</v>
       </c>
@@ -23100,7 +23115,7 @@
       <c r="R304" s="7"/>
       <c r="S304" s="7"/>
     </row>
-    <row r="305" ht="27.75" spans="1:19">
+    <row r="305" ht="27.75" hidden="1" spans="1:19">
       <c r="A305" s="4" t="s">
         <v>1017</v>
       </c>
@@ -23153,7 +23168,7 @@
       <c r="R305" s="7"/>
       <c r="S305" s="7"/>
     </row>
-    <row r="306" ht="27" spans="1:19">
+    <row r="306" ht="27" hidden="1" spans="1:19">
       <c r="A306" s="4" t="s">
         <v>1021</v>
       </c>
@@ -23206,7 +23221,7 @@
       <c r="R306" s="7"/>
       <c r="S306" s="7"/>
     </row>
-    <row r="307" spans="1:19">
+    <row r="307" hidden="1" spans="1:19">
       <c r="A307" s="4" t="s">
         <v>1024</v>
       </c>
@@ -23259,7 +23274,7 @@
       <c r="R307" s="7"/>
       <c r="S307" s="7"/>
     </row>
-    <row r="308" spans="1:19">
+    <row r="308" hidden="1" spans="1:19">
       <c r="A308" s="4" t="s">
         <v>1028</v>
       </c>
@@ -23314,7 +23329,7 @@
       <c r="R308" s="7"/>
       <c r="S308" s="7"/>
     </row>
-    <row r="309" spans="1:19">
+    <row r="309" hidden="1" spans="1:19">
       <c r="A309" s="4" t="s">
         <v>1032</v>
       </c>
@@ -23369,7 +23384,7 @@
       <c r="R309" s="7"/>
       <c r="S309" s="7"/>
     </row>
-    <row r="310" spans="1:19">
+    <row r="310" hidden="1" spans="1:19">
       <c r="A310" s="4" t="s">
         <v>1035</v>
       </c>
@@ -23422,7 +23437,7 @@
       <c r="R310" s="7"/>
       <c r="S310" s="7"/>
     </row>
-    <row r="311" ht="27" spans="1:19">
+    <row r="311" ht="27" hidden="1" spans="1:19">
       <c r="A311" s="4" t="s">
         <v>1038</v>
       </c>
@@ -23475,7 +23490,7 @@
       <c r="R311" s="7"/>
       <c r="S311" s="7"/>
     </row>
-    <row r="312" ht="27" spans="1:19">
+    <row r="312" ht="27" hidden="1" spans="1:19">
       <c r="A312" s="4" t="s">
         <v>1042</v>
       </c>
@@ -23528,7 +23543,7 @@
       <c r="R312" s="7"/>
       <c r="S312" s="7"/>
     </row>
-    <row r="313" ht="27" spans="1:19">
+    <row r="313" ht="27" hidden="1" spans="1:19">
       <c r="A313" s="4" t="s">
         <v>1046</v>
       </c>
@@ -23581,7 +23596,7 @@
       <c r="R313" s="7"/>
       <c r="S313" s="7"/>
     </row>
-    <row r="314" spans="1:19">
+    <row r="314" hidden="1" spans="1:19">
       <c r="A314" s="4" t="s">
         <v>1050</v>
       </c>
@@ -23634,7 +23649,7 @@
       <c r="R314" s="7"/>
       <c r="S314" s="7"/>
     </row>
-    <row r="315" spans="1:19">
+    <row r="315" hidden="1" spans="1:19">
       <c r="A315" s="4" t="s">
         <v>1054</v>
       </c>
@@ -23687,7 +23702,7 @@
       <c r="R315" s="7"/>
       <c r="S315" s="7"/>
     </row>
-    <row r="316" spans="1:19">
+    <row r="316" hidden="1" spans="1:19">
       <c r="A316" s="4" t="s">
         <v>1058</v>
       </c>
@@ -23740,7 +23755,7 @@
       <c r="R316" s="7"/>
       <c r="S316" s="7"/>
     </row>
-    <row r="317" spans="1:19">
+    <row r="317" hidden="1" spans="1:19">
       <c r="A317" s="4" t="s">
         <v>1062</v>
       </c>
@@ -23789,7 +23804,7 @@
       <c r="R317" s="7"/>
       <c r="S317" s="7"/>
     </row>
-    <row r="318" spans="1:19">
+    <row r="318" hidden="1" spans="1:19">
       <c r="A318" s="4" t="s">
         <v>1065</v>
       </c>
@@ -23838,7 +23853,7 @@
       <c r="R318" s="7"/>
       <c r="S318" s="7"/>
     </row>
-    <row r="319" spans="1:15">
+    <row r="319" hidden="1" spans="1:15">
       <c r="A319" s="4" t="s">
         <v>1067</v>
       </c>
@@ -23883,7 +23898,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="320" spans="1:15">
+    <row r="320" hidden="1" spans="1:15">
       <c r="A320" s="4" t="s">
         <v>1072</v>
       </c>
@@ -23928,7 +23943,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="321" spans="1:15">
+    <row r="321" hidden="1" spans="1:15">
       <c r="A321" s="4" t="s">
         <v>1075</v>
       </c>
@@ -23973,7 +23988,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="322" spans="1:15">
+    <row r="322" hidden="1" spans="1:15">
       <c r="A322" s="4" t="s">
         <v>1077</v>
       </c>
@@ -24018,7 +24033,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="323" spans="1:15">
+    <row r="323" hidden="1" spans="1:15">
       <c r="A323" s="4" t="s">
         <v>1080</v>
       </c>
@@ -24063,7 +24078,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="324" spans="1:15">
+    <row r="324" hidden="1" spans="1:15">
       <c r="A324" s="4" t="s">
         <v>1083</v>
       </c>
@@ -24108,7 +24123,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="325" spans="1:15">
+    <row r="325" hidden="1" spans="1:15">
       <c r="A325" s="4" t="s">
         <v>1086</v>
       </c>
@@ -24153,7 +24168,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="326" spans="1:15">
+    <row r="326" hidden="1" spans="1:15">
       <c r="A326" s="4" t="s">
         <v>1088</v>
       </c>
@@ -24198,7 +24213,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="327" spans="1:15">
+    <row r="327" hidden="1" spans="1:15">
       <c r="A327" s="4" t="s">
         <v>1091</v>
       </c>
@@ -24243,7 +24258,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="328" spans="1:15">
+    <row r="328" hidden="1" spans="1:15">
       <c r="A328" s="4" t="s">
         <v>1093</v>
       </c>
@@ -24288,7 +24303,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="329" spans="1:15">
+    <row r="329" hidden="1" spans="1:15">
       <c r="A329" s="4" t="s">
         <v>1095</v>
       </c>
@@ -24333,7 +24348,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="330" spans="1:15">
+    <row r="330" hidden="1" spans="1:15">
       <c r="A330" s="4" t="s">
         <v>1098</v>
       </c>
@@ -24378,7 +24393,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="331" spans="1:15">
+    <row r="331" hidden="1" spans="1:15">
       <c r="A331" s="4" t="s">
         <v>1100</v>
       </c>
@@ -24423,7 +24438,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="332" spans="1:15">
+    <row r="332" hidden="1" spans="1:15">
       <c r="A332" s="4" t="s">
         <v>1102</v>
       </c>
@@ -24468,7 +24483,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="333" spans="1:15">
+    <row r="333" hidden="1" spans="1:15">
       <c r="A333" s="4" t="s">
         <v>1104</v>
       </c>
@@ -24513,7 +24528,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="334" spans="1:15">
+    <row r="334" hidden="1" spans="1:15">
       <c r="A334" s="4" t="s">
         <v>1106</v>
       </c>
@@ -24558,7 +24573,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="335" spans="1:15">
+    <row r="335" hidden="1" spans="1:15">
       <c r="A335" s="4" t="s">
         <v>1109</v>
       </c>
@@ -24603,7 +24618,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="336" spans="1:15">
+    <row r="336" hidden="1" spans="1:15">
       <c r="A336" s="4" t="s">
         <v>1111</v>
       </c>
@@ -24648,7 +24663,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" hidden="1" spans="1:15">
       <c r="A337" s="4" t="s">
         <v>1113</v>
       </c>
@@ -24693,7 +24708,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="338" spans="1:15">
+    <row r="338" hidden="1" spans="1:15">
       <c r="A338" s="4" t="s">
         <v>1116</v>
       </c>
@@ -24738,7 +24753,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="339" ht="14.25" spans="1:15">
+    <row r="339" ht="14.25" hidden="1" spans="1:15">
       <c r="A339" s="4" t="s">
         <v>1118</v>
       </c>
@@ -24783,7 +24798,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="340" ht="14.25" spans="1:15">
+    <row r="340" ht="14.25" hidden="1" spans="1:15">
       <c r="A340" s="4" t="s">
         <v>1120</v>
       </c>
@@ -24828,7 +24843,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="341" spans="1:15">
+    <row r="341" hidden="1" spans="1:15">
       <c r="A341" s="4" t="s">
         <v>1122</v>
       </c>
@@ -24873,7 +24888,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="342" spans="1:15">
+    <row r="342" hidden="1" spans="1:15">
       <c r="A342" s="4" t="s">
         <v>1126</v>
       </c>
@@ -24918,7 +24933,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="343" spans="1:15">
+    <row r="343" hidden="1" spans="1:15">
       <c r="A343" s="4" t="s">
         <v>1128</v>
       </c>
@@ -24963,7 +24978,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="344" spans="1:15">
+    <row r="344" hidden="1" spans="1:15">
       <c r="A344" s="4" t="s">
         <v>1130</v>
       </c>
@@ -25008,7 +25023,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="345" spans="1:15">
+    <row r="345" hidden="1" spans="1:15">
       <c r="A345" s="4" t="s">
         <v>1132</v>
       </c>
@@ -25053,7 +25068,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="346" spans="1:15">
+    <row r="346" hidden="1" spans="1:15">
       <c r="A346" s="4" t="s">
         <v>1135</v>
       </c>
@@ -25098,7 +25113,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="347" spans="1:15">
+    <row r="347" hidden="1" spans="1:15">
       <c r="A347" s="4" t="s">
         <v>1137</v>
       </c>
@@ -25143,7 +25158,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="348" spans="1:15">
+    <row r="348" hidden="1" spans="1:15">
       <c r="A348" s="4" t="s">
         <v>1139</v>
       </c>
@@ -25188,7 +25203,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="349" spans="1:15">
+    <row r="349" hidden="1" spans="1:15">
       <c r="A349" s="4" t="s">
         <v>1141</v>
       </c>
@@ -25233,7 +25248,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="350" spans="1:15">
+    <row r="350" hidden="1" spans="1:15">
       <c r="A350" s="4" t="s">
         <v>1143</v>
       </c>
@@ -25278,7 +25293,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="351" spans="1:15">
+    <row r="351" hidden="1" spans="1:15">
       <c r="A351" s="4" t="s">
         <v>1145</v>
       </c>
@@ -25323,7 +25338,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="352" spans="1:15">
+    <row r="352" hidden="1" spans="1:15">
       <c r="A352" s="4" t="s">
         <v>1147</v>
       </c>
@@ -25368,7 +25383,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="353" spans="1:15">
+    <row r="353" hidden="1" spans="1:15">
       <c r="A353" s="4" t="s">
         <v>1149</v>
       </c>
@@ -25413,7 +25428,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="354" spans="1:15">
+    <row r="354" hidden="1" spans="1:15">
       <c r="A354" s="4" t="s">
         <v>1151</v>
       </c>
@@ -25458,7 +25473,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" hidden="1" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>1154</v>
       </c>
@@ -25506,7 +25521,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="356" spans="1:15">
+    <row r="356" hidden="1" spans="1:15">
       <c r="A356" s="4" t="s">
         <v>1157</v>
       </c>
@@ -25551,7 +25566,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="357" spans="1:15">
+    <row r="357" hidden="1" spans="1:15">
       <c r="A357" s="4" t="s">
         <v>1159</v>
       </c>
@@ -25596,7 +25611,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="358" spans="1:15">
+    <row r="358" hidden="1" spans="1:15">
       <c r="A358" s="4" t="s">
         <v>1161</v>
       </c>
@@ -25641,7 +25656,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="359" spans="1:15">
+    <row r="359" hidden="1" spans="1:15">
       <c r="A359" s="4" t="s">
         <v>1163</v>
       </c>
@@ -25686,7 +25701,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="360" spans="1:15">
+    <row r="360" hidden="1" spans="1:15">
       <c r="A360" s="4" t="s">
         <v>1165</v>
       </c>
@@ -25731,7 +25746,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="361" spans="1:15">
+    <row r="361" hidden="1" spans="1:15">
       <c r="A361" s="4" t="s">
         <v>1168</v>
       </c>
@@ -25776,7 +25791,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="362" spans="1:15">
+    <row r="362" hidden="1" spans="1:15">
       <c r="A362" s="4" t="s">
         <v>1170</v>
       </c>
@@ -25821,7 +25836,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="363" spans="1:15">
+    <row r="363" hidden="1" spans="1:15">
       <c r="A363" s="4" t="s">
         <v>1172</v>
       </c>
@@ -25866,7 +25881,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="364" spans="1:15">
+    <row r="364" hidden="1" spans="1:15">
       <c r="A364" s="4" t="s">
         <v>1174</v>
       </c>
@@ -25911,7 +25926,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="365" spans="1:15">
+    <row r="365" hidden="1" spans="1:15">
       <c r="A365" s="4" t="s">
         <v>1176</v>
       </c>
@@ -25956,7 +25971,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="366" spans="1:15">
+    <row r="366" hidden="1" spans="1:15">
       <c r="A366" s="4" t="s">
         <v>1178</v>
       </c>
@@ -26001,7 +26016,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="367" spans="1:15">
+    <row r="367" hidden="1" spans="1:15">
       <c r="A367" s="4" t="s">
         <v>1180</v>
       </c>
@@ -26046,7 +26061,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="368" spans="1:15">
+    <row r="368" hidden="1" spans="1:15">
       <c r="A368" s="4" t="s">
         <v>1183</v>
       </c>
@@ -26091,7 +26106,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="369" spans="1:15">
+    <row r="369" hidden="1" spans="1:15">
       <c r="A369" s="4" t="s">
         <v>1185</v>
       </c>
@@ -26136,7 +26151,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="370" spans="1:15">
+    <row r="370" hidden="1" spans="1:15">
       <c r="A370" s="4" t="s">
         <v>1188</v>
       </c>
@@ -26181,7 +26196,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="371" ht="14.25" spans="1:15">
+    <row r="371" ht="14.25" hidden="1" spans="1:15">
       <c r="A371" s="4" t="s">
         <v>1190</v>
       </c>
@@ -26226,7 +26241,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="372" ht="14.25" spans="1:15">
+    <row r="372" ht="14.25" hidden="1" spans="1:15">
       <c r="A372" s="4" t="s">
         <v>1193</v>
       </c>
@@ -26271,7 +26286,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="373" ht="14.25" spans="1:15">
+    <row r="373" ht="14.25" hidden="1" spans="1:15">
       <c r="A373" s="4" t="s">
         <v>1195</v>
       </c>
@@ -26316,7 +26331,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="374" ht="14.25" spans="1:15">
+    <row r="374" ht="14.25" hidden="1" spans="1:15">
       <c r="A374" s="4" t="s">
         <v>1197</v>
       </c>
@@ -26361,7 +26376,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="375" spans="1:15">
+    <row r="375" hidden="1" spans="1:15">
       <c r="A375" s="4" t="s">
         <v>1199</v>
       </c>
@@ -26406,7 +26421,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="376" spans="1:15">
+    <row r="376" hidden="1" spans="1:15">
       <c r="A376" s="4" t="s">
         <v>1201</v>
       </c>
@@ -26451,7 +26466,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="377" spans="1:15">
+    <row r="377" hidden="1" spans="1:15">
       <c r="A377" s="4" t="s">
         <v>1203</v>
       </c>
@@ -26496,7 +26511,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="378" spans="1:15">
+    <row r="378" hidden="1" spans="1:15">
       <c r="A378" s="4" t="s">
         <v>1205</v>
       </c>
@@ -26541,7 +26556,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="379" spans="1:15">
+    <row r="379" hidden="1" spans="1:15">
       <c r="A379" s="4" t="s">
         <v>1207</v>
       </c>
@@ -26586,7 +26601,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="380" spans="1:15">
+    <row r="380" hidden="1" spans="1:15">
       <c r="A380" s="4" t="s">
         <v>1210</v>
       </c>
@@ -26631,7 +26646,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="381" spans="1:15">
+    <row r="381" hidden="1" spans="1:15">
       <c r="A381" s="4" t="s">
         <v>1212</v>
       </c>
@@ -26676,7 +26691,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="382" spans="1:15">
+    <row r="382" hidden="1" spans="1:15">
       <c r="A382" s="4" t="s">
         <v>1215</v>
       </c>
@@ -26721,7 +26736,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="383" spans="1:15">
+    <row r="383" hidden="1" spans="1:15">
       <c r="A383" s="4" t="s">
         <v>1217</v>
       </c>
@@ -26766,7 +26781,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="384" spans="1:15">
+    <row r="384" hidden="1" spans="1:15">
       <c r="A384" s="4" t="s">
         <v>1219</v>
       </c>
@@ -26811,7 +26826,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="385" spans="1:15">
+    <row r="385" hidden="1" spans="1:15">
       <c r="A385" s="4" t="s">
         <v>1221</v>
       </c>
@@ -26856,7 +26871,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="386" spans="1:15">
+    <row r="386" hidden="1" spans="1:15">
       <c r="A386" s="4" t="s">
         <v>1224</v>
       </c>
@@ -26901,7 +26916,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="387" spans="1:15">
+    <row r="387" hidden="1" spans="1:15">
       <c r="A387" s="4" t="s">
         <v>1225</v>
       </c>
@@ -26946,7 +26961,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="388" spans="1:15">
+    <row r="388" hidden="1" spans="1:15">
       <c r="A388" s="4" t="s">
         <v>1228</v>
       </c>
@@ -26991,7 +27006,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="389" spans="1:15">
+    <row r="389" hidden="1" spans="1:15">
       <c r="A389" s="4" t="s">
         <v>1231</v>
       </c>
@@ -27036,7 +27051,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="390" spans="1:15">
+    <row r="390" hidden="1" spans="1:15">
       <c r="A390" s="4" t="s">
         <v>1234</v>
       </c>
@@ -27079,7 +27094,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="391" spans="1:15">
+    <row r="391" hidden="1" spans="1:15">
       <c r="A391" s="4" t="s">
         <v>1237</v>
       </c>
@@ -27122,7 +27137,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="392" spans="1:15">
+    <row r="392" hidden="1" spans="1:15">
       <c r="A392" s="4" t="s">
         <v>1240</v>
       </c>
@@ -27165,7 +27180,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="393" spans="1:15">
+    <row r="393" hidden="1" spans="1:15">
       <c r="A393" s="4" t="s">
         <v>1243</v>
       </c>
@@ -27208,7 +27223,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" spans="1:15">
+    <row r="394" hidden="1" spans="1:15">
       <c r="A394" s="4" t="s">
         <v>1246</v>
       </c>
@@ -27251,7 +27266,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="395" spans="1:15">
+    <row r="395" hidden="1" spans="1:15">
       <c r="A395" s="4" t="s">
         <v>1248</v>
       </c>
@@ -27294,7 +27309,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="396" spans="1:15">
+    <row r="396" hidden="1" spans="1:15">
       <c r="A396" s="4" t="s">
         <v>1250</v>
       </c>
@@ -27337,7 +27352,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="397" spans="1:15">
+    <row r="397" hidden="1" spans="1:15">
       <c r="A397" s="4" t="s">
         <v>1253</v>
       </c>
@@ -27380,7 +27395,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="398" spans="1:15">
+    <row r="398" hidden="1" spans="1:15">
       <c r="A398" s="4" t="s">
         <v>1255</v>
       </c>
@@ -27423,7 +27438,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="399" spans="1:15">
+    <row r="399" hidden="1" spans="1:15">
       <c r="A399" s="4" t="s">
         <v>1258</v>
       </c>
@@ -27466,7 +27481,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="400" spans="1:15">
+    <row r="400" hidden="1" spans="1:15">
       <c r="A400" s="4" t="s">
         <v>1260</v>
       </c>
@@ -27509,7 +27524,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="401" spans="1:15">
+    <row r="401" hidden="1" spans="1:15">
       <c r="A401" s="4" t="s">
         <v>1262</v>
       </c>
@@ -27552,7 +27567,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="402" spans="1:15">
+    <row r="402" hidden="1" spans="1:15">
       <c r="A402" s="4" t="s">
         <v>1264</v>
       </c>
@@ -27595,7 +27610,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="403" spans="1:15">
+    <row r="403" hidden="1" spans="1:15">
       <c r="A403" s="4" t="s">
         <v>1266</v>
       </c>
@@ -27638,7 +27653,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="404" spans="1:15">
+    <row r="404" hidden="1" spans="1:15">
       <c r="A404" s="4" t="s">
         <v>1268</v>
       </c>
@@ -27681,7 +27696,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="405" spans="1:15">
+    <row r="405" hidden="1" spans="1:15">
       <c r="A405" s="4" t="s">
         <v>1270</v>
       </c>
@@ -27724,7 +27739,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="406" spans="1:15">
+    <row r="406" hidden="1" spans="1:15">
       <c r="A406" s="4" t="s">
         <v>1273</v>
       </c>
@@ -27767,7 +27782,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="407" spans="1:15">
+    <row r="407" hidden="1" spans="1:15">
       <c r="A407" s="4" t="s">
         <v>1275</v>
       </c>
@@ -27810,7 +27825,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="408" spans="1:15">
+    <row r="408" hidden="1" spans="1:15">
       <c r="A408" s="4" t="s">
         <v>1278</v>
       </c>
@@ -27853,7 +27868,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="409" spans="1:15">
+    <row r="409" hidden="1" spans="1:15">
       <c r="A409" s="4" t="s">
         <v>1280</v>
       </c>
@@ -27896,7 +27911,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" hidden="1" spans="1:15">
       <c r="A410" s="4" t="s">
         <v>1282</v>
       </c>
@@ -27939,7 +27954,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="411" spans="1:15">
+    <row r="411" hidden="1" spans="1:15">
       <c r="A411" s="4" t="s">
         <v>1285</v>
       </c>
@@ -28068,7 +28083,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" spans="1:15">
+    <row r="414" hidden="1" spans="1:15">
       <c r="A414" s="4" t="s">
         <v>1291</v>
       </c>
@@ -28111,7 +28126,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="415" spans="1:15">
+    <row r="415" hidden="1" spans="1:15">
       <c r="A415" s="4" t="s">
         <v>1293</v>
       </c>
@@ -28154,7 +28169,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="416" spans="1:15">
+    <row r="416" hidden="1" spans="1:15">
       <c r="A416" s="4" t="s">
         <v>1296</v>
       </c>
@@ -28197,7 +28212,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="417" spans="1:15">
+    <row r="417" hidden="1" spans="1:15">
       <c r="A417" s="4" t="s">
         <v>1298</v>
       </c>
@@ -28240,7 +28255,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="418" spans="1:15">
+    <row r="418" hidden="1" spans="1:15">
       <c r="A418" s="4" t="s">
         <v>1300</v>
       </c>
@@ -28283,7 +28298,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="419" spans="1:15">
+    <row r="419" hidden="1" spans="1:15">
       <c r="A419" s="4" t="s">
         <v>1302</v>
       </c>
@@ -28326,7 +28341,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="420" spans="1:15">
+    <row r="420" hidden="1" spans="1:15">
       <c r="A420" s="4" t="s">
         <v>1305</v>
       </c>
@@ -28369,7 +28384,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="421" spans="1:15">
+    <row r="421" hidden="1" spans="1:15">
       <c r="A421" s="4" t="s">
         <v>1307</v>
       </c>
@@ -28412,7 +28427,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" hidden="1" spans="1:15">
       <c r="A422" s="4" t="s">
         <v>1309</v>
       </c>
@@ -28455,7 +28470,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" hidden="1" spans="1:15">
       <c r="A423" s="4" t="s">
         <v>1311</v>
       </c>
@@ -28498,7 +28513,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" hidden="1" spans="1:15">
       <c r="A424" s="4" t="s">
         <v>1313</v>
       </c>
@@ -28541,7 +28556,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" hidden="1" spans="1:15">
       <c r="A425" s="4" t="s">
         <v>1315</v>
       </c>
@@ -28584,7 +28599,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" hidden="1" spans="1:15">
       <c r="A426" s="4" t="s">
         <v>1317</v>
       </c>
@@ -28627,7 +28642,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" hidden="1" spans="1:15">
       <c r="A427" s="4" t="s">
         <v>1319</v>
       </c>
@@ -28670,7 +28685,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" hidden="1" spans="1:15">
       <c r="A428" s="4" t="s">
         <v>1322</v>
       </c>
@@ -28713,7 +28728,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" hidden="1" spans="1:15">
       <c r="A429" s="4" t="s">
         <v>1324</v>
       </c>
@@ -28756,7 +28771,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" hidden="1" spans="1:15">
       <c r="A430" s="4" t="s">
         <v>1326</v>
       </c>
@@ -28799,7 +28814,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" hidden="1" spans="1:15">
       <c r="A431" s="4" t="s">
         <v>1329</v>
       </c>
@@ -28842,7 +28857,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" hidden="1" spans="1:15">
       <c r="A432" s="4" t="s">
         <v>1331</v>
       </c>
@@ -28885,7 +28900,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" hidden="1" spans="1:15">
       <c r="A433" s="4" t="s">
         <v>1333</v>
       </c>
@@ -28928,7 +28943,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" hidden="1" spans="1:15">
       <c r="A434" s="4" t="s">
         <v>1336</v>
       </c>
@@ -28971,7 +28986,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" hidden="1" spans="1:15">
       <c r="A435" s="4" t="s">
         <v>1339</v>
       </c>
@@ -29014,7 +29029,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" hidden="1" spans="1:15">
       <c r="A436" s="4" t="s">
         <v>1341</v>
       </c>
@@ -29057,7 +29072,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" hidden="1" spans="1:15">
       <c r="A437" s="4" t="s">
         <v>1343</v>
       </c>
@@ -29100,7 +29115,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" hidden="1" spans="1:15">
       <c r="A438" s="4" t="s">
         <v>1345</v>
       </c>
@@ -29143,7 +29158,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="439" ht="14.25" spans="1:15">
+    <row r="439" ht="14.25" hidden="1" spans="1:15">
       <c r="A439" s="4" t="s">
         <v>1347</v>
       </c>
@@ -29186,7 +29201,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="440" ht="14.25" spans="1:15">
+    <row r="440" ht="14.25" hidden="1" spans="1:15">
       <c r="A440" s="4" t="s">
         <v>1349</v>
       </c>
@@ -29229,7 +29244,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" hidden="1" spans="1:15">
       <c r="A441" s="4" t="s">
         <v>1351</v>
       </c>
@@ -29272,7 +29287,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="442" ht="18" spans="1:17">
+    <row r="442" ht="18" hidden="1" spans="1:17">
       <c r="A442" s="4" t="s">
         <v>1354</v>
       </c>
@@ -29319,7 +29334,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="443" ht="18" spans="1:17">
+    <row r="443" ht="18" hidden="1" spans="1:17">
       <c r="A443" s="4" t="s">
         <v>1359</v>
       </c>
@@ -29366,7 +29381,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="444" ht="17.25" spans="1:17">
+    <row r="444" ht="17.25" hidden="1" spans="1:17">
       <c r="A444" s="4" t="s">
         <v>1363</v>
       </c>
@@ -29413,7 +29428,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="445" ht="17.25" spans="1:17">
+    <row r="445" ht="17.25" hidden="1" spans="1:17">
       <c r="A445" s="4" t="s">
         <v>1368</v>
       </c>
@@ -29460,7 +29475,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="446" ht="17.25" spans="1:17">
+    <row r="446" ht="17.25" hidden="1" spans="1:17">
       <c r="A446" s="4" t="s">
         <v>1372</v>
       </c>
@@ -29507,7 +29522,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="447" ht="17.25" spans="1:17">
+    <row r="447" ht="17.25" hidden="1" spans="1:17">
       <c r="A447" s="4" t="s">
         <v>1377</v>
       </c>
@@ -29554,7 +29569,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="448" ht="17.25" spans="1:17">
+    <row r="448" ht="17.25" hidden="1" spans="1:17">
       <c r="A448" s="4" t="s">
         <v>1381</v>
       </c>
@@ -29604,7 +29619,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="449" ht="18" spans="1:17">
+    <row r="449" ht="18" hidden="1" spans="1:17">
       <c r="A449" s="4" t="s">
         <v>1384</v>
       </c>
@@ -29654,7 +29669,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="450" ht="18" spans="1:17">
+    <row r="450" ht="18" hidden="1" spans="1:17">
       <c r="A450" s="4" t="s">
         <v>1387</v>
       </c>
@@ -29704,7 +29719,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="451" ht="17.25" spans="1:17">
+    <row r="451" ht="17.25" hidden="1" spans="1:17">
       <c r="A451" s="4" t="s">
         <v>1391</v>
       </c>
@@ -29754,7 +29769,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="452" ht="17.25" spans="1:17">
+    <row r="452" ht="17.25" hidden="1" spans="1:17">
       <c r="A452" s="4" t="s">
         <v>1394</v>
       </c>
@@ -29804,7 +29819,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="453" ht="17.25" spans="1:17">
+    <row r="453" ht="17.25" hidden="1" spans="1:17">
       <c r="A453" s="4" t="s">
         <v>1398</v>
       </c>
@@ -29854,7 +29869,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="454" ht="17.25" spans="1:17">
+    <row r="454" ht="17.25" hidden="1" spans="1:17">
       <c r="A454" s="4" t="s">
         <v>1402</v>
       </c>
@@ -29901,7 +29916,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="455" ht="17.25" spans="1:17">
+    <row r="455" ht="17.25" hidden="1" spans="1:17">
       <c r="A455" s="4" t="s">
         <v>1405</v>
       </c>
@@ -29951,7 +29966,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="456" ht="18" spans="1:17">
+    <row r="456" ht="18" hidden="1" spans="1:17">
       <c r="A456" s="4" t="s">
         <v>1409</v>
       </c>
@@ -30001,7 +30016,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="457" ht="18" spans="1:17">
+    <row r="457" ht="18" hidden="1" spans="1:17">
       <c r="A457" s="4" t="s">
         <v>1412</v>
       </c>
@@ -30051,7 +30066,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="458" ht="17.25" spans="1:17">
+    <row r="458" ht="17.25" hidden="1" spans="1:17">
       <c r="A458" s="4" t="s">
         <v>1416</v>
       </c>
@@ -30098,7 +30113,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="459" ht="17.25" spans="1:17">
+    <row r="459" ht="17.25" hidden="1" spans="1:17">
       <c r="A459" s="4" t="s">
         <v>1420</v>
       </c>
@@ -30148,7 +30163,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="460" ht="17.25" spans="1:17">
+    <row r="460" ht="17.25" hidden="1" spans="1:17">
       <c r="A460" s="4" t="s">
         <v>1424</v>
       </c>
@@ -30198,7 +30213,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="461" ht="17.25" spans="1:17">
+    <row r="461" ht="17.25" hidden="1" spans="1:17">
       <c r="A461" s="4" t="s">
         <v>1428</v>
       </c>
@@ -30248,7 +30263,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="462" ht="17.25" spans="1:17">
+    <row r="462" ht="17.25" hidden="1" spans="1:17">
       <c r="A462" s="4" t="s">
         <v>1431</v>
       </c>
@@ -30298,7 +30313,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="463" ht="17.25" spans="1:17">
+    <row r="463" ht="17.25" hidden="1" spans="1:17">
       <c r="A463" s="4" t="s">
         <v>1435</v>
       </c>
@@ -30348,7 +30363,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="464" ht="17.25" spans="1:17">
+    <row r="464" ht="17.25" hidden="1" spans="1:17">
       <c r="A464" s="4" t="s">
         <v>1439</v>
       </c>
@@ -30398,7 +30413,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="465" ht="17.25" spans="1:17">
+    <row r="465" ht="17.25" hidden="1" spans="1:17">
       <c r="A465" s="4" t="s">
         <v>1443</v>
       </c>
@@ -30448,7 +30463,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="466" ht="17.25" spans="1:17">
+    <row r="466" ht="17.25" hidden="1" spans="1:17">
       <c r="A466" s="4" t="s">
         <v>1446</v>
       </c>
@@ -30498,7 +30513,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="467" ht="17.25" spans="1:17">
+    <row r="467" ht="17.25" hidden="1" spans="1:17">
       <c r="A467" s="4" t="s">
         <v>1451</v>
       </c>
@@ -30551,7 +30566,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="468" ht="17.25" spans="1:17">
+    <row r="468" ht="17.25" hidden="1" spans="1:17">
       <c r="A468" s="4" t="s">
         <v>1455</v>
       </c>
@@ -30601,7 +30616,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="469" ht="17.25" spans="1:17">
+    <row r="469" ht="17.25" hidden="1" spans="1:17">
       <c r="A469" s="4" t="s">
         <v>1459</v>
       </c>
@@ -30651,7 +30666,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="470" ht="17.25" spans="1:17">
+    <row r="470" ht="17.25" hidden="1" spans="1:17">
       <c r="A470" s="4" t="s">
         <v>1463</v>
       </c>
@@ -30701,7 +30716,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="471" ht="17.25" spans="1:17">
+    <row r="471" ht="17.25" hidden="1" spans="1:17">
       <c r="A471" s="4" t="s">
         <v>1468</v>
       </c>
@@ -30751,7 +30766,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="472" ht="17.25" spans="1:17">
+    <row r="472" ht="17.25" hidden="1" spans="1:17">
       <c r="A472" s="4" t="s">
         <v>1472</v>
       </c>
@@ -30804,7 +30819,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="473" ht="17.25" spans="1:17">
+    <row r="473" ht="17.25" hidden="1" spans="1:17">
       <c r="A473" s="4" t="s">
         <v>1474</v>
       </c>
@@ -30854,7 +30869,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="474" ht="17.25" spans="1:17">
+    <row r="474" ht="17.25" hidden="1" spans="1:17">
       <c r="A474" s="4" t="s">
         <v>1478</v>
       </c>
@@ -30904,7 +30919,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="475" ht="17.25" spans="1:17">
+    <row r="475" ht="17.25" hidden="1" spans="1:17">
       <c r="A475" s="4" t="s">
         <v>1481</v>
       </c>
@@ -30954,7 +30969,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="476" ht="17.25" spans="1:17">
+    <row r="476" ht="17.25" hidden="1" spans="1:17">
       <c r="A476" s="4" t="s">
         <v>1484</v>
       </c>
@@ -31004,7 +31019,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="477" ht="17.25" spans="1:17">
+    <row r="477" ht="17.25" hidden="1" spans="1:17">
       <c r="A477" s="4" t="s">
         <v>1486</v>
       </c>
@@ -31054,7 +31069,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="478" ht="17.25" spans="1:17">
+    <row r="478" ht="17.25" hidden="1" spans="1:17">
       <c r="A478" s="4" t="s">
         <v>1490</v>
       </c>
@@ -31104,7 +31119,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="479" ht="17.25" spans="1:17">
+    <row r="479" ht="17.25" hidden="1" spans="1:17">
       <c r="A479" s="4" t="s">
         <v>1495</v>
       </c>
@@ -31157,7 +31172,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="480" ht="17.25" spans="1:17">
+    <row r="480" ht="17.25" hidden="1" spans="1:17">
       <c r="A480" s="4" t="s">
         <v>1499</v>
       </c>
@@ -31207,7 +31222,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="481" ht="17.25" spans="1:17">
+    <row r="481" ht="17.25" hidden="1" spans="1:17">
       <c r="A481" s="4" t="s">
         <v>1503</v>
       </c>
@@ -31257,7 +31272,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="482" ht="17.25" spans="1:17">
+    <row r="482" ht="17.25" hidden="1" spans="1:17">
       <c r="A482" s="4" t="s">
         <v>1506</v>
       </c>
@@ -31304,7 +31319,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="483" ht="17.25" spans="1:17">
+    <row r="483" ht="17.25" hidden="1" spans="1:17">
       <c r="A483" s="4" t="s">
         <v>1510</v>
       </c>
@@ -31351,7 +31366,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="484" ht="17.25" spans="1:17">
+    <row r="484" ht="17.25" hidden="1" spans="1:17">
       <c r="A484" s="4" t="s">
         <v>1512</v>
       </c>
@@ -31398,7 +31413,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="485" ht="17.25" spans="1:17">
+    <row r="485" ht="17.25" hidden="1" spans="1:17">
       <c r="A485" s="4" t="s">
         <v>1514</v>
       </c>
@@ -31441,7 +31456,7 @@
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>
     </row>
-    <row r="486" ht="17.25" spans="1:17">
+    <row r="486" ht="17.25" hidden="1" spans="1:17">
       <c r="A486" s="4" t="s">
         <v>1516</v>
       </c>
@@ -31488,7 +31503,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="487" ht="17.25" spans="1:17">
+    <row r="487" ht="17.25" hidden="1" spans="1:17">
       <c r="A487" s="4" t="s">
         <v>1520</v>
       </c>
@@ -31535,7 +31550,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="488" ht="17.25" spans="1:17">
+    <row r="488" ht="17.25" hidden="1" spans="1:17">
       <c r="A488" s="4" t="s">
         <v>1523</v>
       </c>
@@ -31582,7 +31597,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="489" ht="17.25" spans="1:17">
+    <row r="489" ht="17.25" hidden="1" spans="1:17">
       <c r="A489" s="4" t="s">
         <v>1526</v>
       </c>
@@ -31629,7 +31644,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="490" ht="17.25" spans="1:17">
+    <row r="490" ht="17.25" hidden="1" spans="1:17">
       <c r="A490" s="4" t="s">
         <v>1529</v>
       </c>
@@ -31676,7 +31691,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="491" ht="17.25" spans="1:17">
+    <row r="491" ht="17.25" hidden="1" spans="1:17">
       <c r="A491" s="4" t="s">
         <v>1532</v>
       </c>
@@ -31723,7 +31738,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="492" ht="17.25" spans="1:17">
+    <row r="492" ht="17.25" hidden="1" spans="1:17">
       <c r="A492" s="4" t="s">
         <v>1535</v>
       </c>
@@ -31770,7 +31785,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="493" ht="17.25" spans="1:17">
+    <row r="493" ht="17.25" hidden="1" spans="1:17">
       <c r="A493" s="4" t="s">
         <v>1538</v>
       </c>
@@ -31817,7 +31832,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="494" ht="17.25" spans="1:17">
+    <row r="494" ht="17.25" hidden="1" spans="1:17">
       <c r="A494" s="4" t="s">
         <v>1540</v>
       </c>
@@ -31864,7 +31879,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="495" ht="17.25" spans="1:17">
+    <row r="495" ht="17.25" hidden="1" spans="1:17">
       <c r="A495" s="4" t="s">
         <v>1541</v>
       </c>
@@ -31914,7 +31929,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="496" ht="17.25" spans="1:17">
+    <row r="496" ht="17.25" hidden="1" spans="1:17">
       <c r="A496" s="4" t="s">
         <v>1545</v>
       </c>
@@ -31964,7 +31979,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="497" ht="17.25" spans="1:17">
+    <row r="497" ht="17.25" hidden="1" spans="1:17">
       <c r="A497" s="4" t="s">
         <v>1549</v>
       </c>
@@ -32014,7 +32029,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="498" ht="17.25" spans="1:17">
+    <row r="498" ht="17.25" hidden="1" spans="1:17">
       <c r="A498" s="4" t="s">
         <v>1553</v>
       </c>
@@ -32064,7 +32079,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="499" ht="17.25" spans="1:17">
+    <row r="499" ht="17.25" hidden="1" spans="1:17">
       <c r="A499" s="4" t="s">
         <v>1557</v>
       </c>
@@ -32114,7 +32129,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="500" ht="17.25" spans="1:17">
+    <row r="500" ht="17.25" hidden="1" spans="1:17">
       <c r="A500" s="4" t="s">
         <v>1561</v>
       </c>
@@ -32164,7 +32179,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="501" ht="17.25" spans="1:17">
+    <row r="501" ht="17.25" hidden="1" spans="1:17">
       <c r="A501" s="4" t="s">
         <v>1564</v>
       </c>
@@ -32214,7 +32229,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="502" ht="17.25" spans="1:17">
+    <row r="502" ht="17.25" hidden="1" spans="1:17">
       <c r="A502" s="4" t="s">
         <v>1568</v>
       </c>
@@ -32264,7 +32279,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="503" ht="17.25" spans="1:17">
+    <row r="503" ht="17.25" hidden="1" spans="1:17">
       <c r="A503" s="4" t="s">
         <v>1572</v>
       </c>
@@ -32314,7 +32329,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="504" ht="17.25" spans="1:17">
+    <row r="504" ht="17.25" hidden="1" spans="1:17">
       <c r="A504" s="4" t="s">
         <v>1574</v>
       </c>
@@ -32367,7 +32382,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="505" ht="17.25" spans="1:17">
+    <row r="505" ht="17.25" hidden="1" spans="1:17">
       <c r="A505" s="4" t="s">
         <v>1576</v>
       </c>
@@ -32414,7 +32429,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="506" ht="17.25" spans="1:17">
+    <row r="506" ht="17.25" hidden="1" spans="1:17">
       <c r="A506" s="4" t="s">
         <v>1580</v>
       </c>
@@ -32461,7 +32476,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="507" ht="17.25" spans="1:17">
+    <row r="507" ht="17.25" hidden="1" spans="1:17">
       <c r="A507" s="4" t="s">
         <v>1584</v>
       </c>
@@ -32508,7 +32523,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="508" ht="17.25" spans="1:17">
+    <row r="508" ht="17.25" hidden="1" spans="1:17">
       <c r="A508" s="4" t="s">
         <v>1588</v>
       </c>
@@ -32555,7 +32570,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="509" ht="17.25" spans="1:17">
+    <row r="509" ht="17.25" hidden="1" spans="1:17">
       <c r="A509" s="4" t="s">
         <v>1592</v>
       </c>
@@ -32602,7 +32617,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="510" spans="1:15">
+    <row r="510" hidden="1" spans="1:15">
       <c r="A510" s="4" t="s">
         <v>1595</v>
       </c>
@@ -32643,7 +32658,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="511" spans="1:15">
+    <row r="511" hidden="1" spans="1:15">
       <c r="A511" s="4" t="s">
         <v>1596</v>
       </c>
@@ -32684,7 +32699,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="512" spans="1:15">
+    <row r="512" hidden="1" spans="1:15">
       <c r="A512" s="4" t="s">
         <v>1598</v>
       </c>
@@ -32725,7 +32740,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="513" spans="1:15">
+    <row r="513" hidden="1" spans="1:15">
       <c r="A513" s="4" t="s">
         <v>1601</v>
       </c>
@@ -32766,7 +32781,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="514" spans="1:15">
+    <row r="514" hidden="1" spans="1:15">
       <c r="A514" s="4" t="s">
         <v>1606</v>
       </c>
@@ -32807,7 +32822,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="515" spans="1:15">
+    <row r="515" hidden="1" spans="1:15">
       <c r="A515" s="4" t="s">
         <v>1608</v>
       </c>
@@ -32848,7 +32863,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="516" spans="1:15">
+    <row r="516" hidden="1" spans="1:15">
       <c r="A516" s="4" t="s">
         <v>1610</v>
       </c>
@@ -32889,7 +32904,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="517" spans="1:15">
+    <row r="517" hidden="1" spans="1:15">
       <c r="A517" s="4" t="s">
         <v>1611</v>
       </c>
@@ -32930,7 +32945,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="518" spans="1:15">
+    <row r="518" hidden="1" spans="1:15">
       <c r="A518" t="s">
         <v>1613</v>
       </c>
@@ -32971,7 +32986,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="519" spans="1:15">
+    <row r="519" hidden="1" spans="1:15">
       <c r="A519" s="4" t="s">
         <v>1615</v>
       </c>
@@ -33012,7 +33027,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="520" spans="1:15">
+    <row r="520" hidden="1" spans="1:15">
       <c r="A520" t="s">
         <v>1617</v>
       </c>
@@ -33053,7 +33068,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="521" spans="1:15">
+    <row r="521" hidden="1" spans="1:15">
       <c r="A521" t="s">
         <v>1619</v>
       </c>
@@ -33135,7 +33150,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="523" spans="1:15">
+    <row r="523" hidden="1" spans="1:15">
       <c r="A523" s="4" t="s">
         <v>1624</v>
       </c>
@@ -33176,8 +33191,8 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="524" spans="1:15">
-      <c r="A524" t="s">
+    <row r="524" hidden="1" spans="1:15">
+      <c r="A524" s="4" t="s">
         <v>1627</v>
       </c>
       <c r="B524" t="s">
@@ -33187,16 +33202,16 @@
         <v>88</v>
       </c>
       <c r="D524" t="s">
-        <v>1290</v>
+        <v>1628</v>
       </c>
       <c r="E524">
         <v>0</v>
       </c>
       <c r="F524">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="G524">
-        <v>3723</v>
+        <v>800</v>
       </c>
       <c r="H524">
         <v>0</v>
@@ -33208,19 +33223,27 @@
         <v>2035</v>
       </c>
       <c r="L524" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="N524" s="4" t="s">
-        <v>1284</v>
+        <v>1153</v>
+      </c>
+      <c r="N524" s="1" t="s">
+        <v>1623</v>
       </c>
       <c r="O524" s="1" t="s">
-        <v>173</v>
+        <v>1629</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T524">
+    <filterColumn colId="14">
+      <customFilters>
+        <customFilter operator="equal" val="工信局"/>
+      </customFilters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
+  <conditionalFormatting sqref="D$1:D$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="1630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="1633">
   <si>
     <t>单号</t>
   </si>
@@ -4907,6 +4907,15 @@
   </si>
   <si>
     <t>泉江镇事业</t>
+  </si>
+  <si>
+    <t>[2021]第342号</t>
+  </si>
+  <si>
+    <t>古小玲</t>
+  </si>
+  <si>
+    <t>自然资源局</t>
   </si>
 </sst>
 </file>
@@ -4914,10 +4923,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
@@ -4966,44 +4975,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5011,6 +4983,28 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5024,11 +5018,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5040,6 +5034,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -5047,19 +5042,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5072,6 +5066,21 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
@@ -5079,14 +5088,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -5103,7 +5112,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5178,31 +5187,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5226,13 +5211,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5244,13 +5241,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5262,13 +5265,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5280,13 +5277,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5304,7 +5325,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5316,49 +5367,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5402,30 +5411,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -5437,6 +5422,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5459,17 +5453,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5485,6 +5470,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5507,10 +5516,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5519,133 +5528,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6076,8 +6085,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
-  <dimension ref="A1:T524"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:T525"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="14.625" customWidth="1"/>
@@ -6156,7 +6165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="14.25" hidden="1" spans="1:19">
+    <row r="2" ht="14.25" spans="1:19">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -6215,7 +6224,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="14.25" hidden="1" spans="1:19">
+    <row r="3" ht="14.25" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -6274,7 +6283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="14.25" hidden="1" spans="1:19">
+    <row r="4" ht="14.25" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
@@ -6333,7 +6342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="14.25" hidden="1" spans="1:19">
+    <row r="5" ht="14.25" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>37</v>
       </c>
@@ -6390,7 +6399,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="14.25" hidden="1" spans="1:19">
+    <row r="6" ht="14.25" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -6449,7 +6458,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="14.25" hidden="1" spans="1:19">
+    <row r="7" ht="14.25" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
@@ -6508,7 +6517,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="14.25" hidden="1" spans="1:19">
+    <row r="8" ht="14.25" spans="1:19">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -6567,7 +6576,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="14.25" hidden="1" spans="1:19">
+    <row r="9" ht="14.25" spans="1:19">
       <c r="A9" s="4" t="s">
         <v>63</v>
       </c>
@@ -6626,7 +6635,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" ht="14.25" hidden="1" spans="1:19">
+    <row r="10" ht="14.25" spans="1:19">
       <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
@@ -6683,7 +6692,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" ht="14.25" hidden="1" spans="1:19">
+    <row r="11" ht="14.25" spans="1:19">
       <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
@@ -6742,7 +6751,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="14.25" hidden="1" spans="1:19">
+    <row r="12" ht="14.25" spans="1:19">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -6799,7 +6808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" ht="14.25" hidden="1" spans="1:19">
+    <row r="13" ht="14.25" spans="1:19">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -6854,7 +6863,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" ht="14.25" hidden="1" spans="1:19">
+    <row r="14" ht="14.25" spans="1:19">
       <c r="A14" s="4" t="s">
         <v>93</v>
       </c>
@@ -6913,7 +6922,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" ht="14.25" hidden="1" spans="1:19">
+    <row r="15" ht="14.25" spans="1:19">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -6972,7 +6981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" ht="14.25" hidden="1" spans="1:19">
+    <row r="16" ht="14.25" spans="1:19">
       <c r="A16" s="4" t="s">
         <v>103</v>
       </c>
@@ -7031,7 +7040,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" ht="14.25" hidden="1" spans="1:19">
+    <row r="17" ht="14.25" spans="1:19">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -7086,7 +7095,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" ht="14.25" hidden="1" spans="1:19">
+    <row r="18" ht="14.25" spans="1:19">
       <c r="A18" s="4" t="s">
         <v>113</v>
       </c>
@@ -7145,7 +7154,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" ht="14.25" hidden="1" spans="1:20">
+    <row r="19" ht="14.25" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
@@ -7206,7 +7215,7 @@
         <v>87662.6773333333</v>
       </c>
     </row>
-    <row r="20" ht="14.25" hidden="1" spans="1:19">
+    <row r="20" ht="14.25" spans="1:19">
       <c r="A20" s="4" t="s">
         <v>122</v>
       </c>
@@ -7263,7 +7272,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" ht="14.25" hidden="1" spans="1:20">
+    <row r="21" ht="14.25" spans="1:20">
       <c r="A21" s="4" t="s">
         <v>125</v>
       </c>
@@ -7324,7 +7333,7 @@
         <v>53992.6</v>
       </c>
     </row>
-    <row r="22" ht="14.25" hidden="1" spans="1:19">
+    <row r="22" ht="14.25" spans="1:19">
       <c r="A22" s="4" t="s">
         <v>131</v>
       </c>
@@ -7379,7 +7388,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" ht="14.25" hidden="1" spans="1:19">
+    <row r="23" ht="14.25" spans="1:19">
       <c r="A23" s="4" t="s">
         <v>137</v>
       </c>
@@ -7434,7 +7443,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="14.25" hidden="1" spans="1:19">
+    <row r="24" ht="14.25" spans="1:19">
       <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
@@ -7489,7 +7498,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" ht="14.25" hidden="1" spans="1:19">
+    <row r="25" ht="14.25" spans="1:19">
       <c r="A25" s="4" t="s">
         <v>146</v>
       </c>
@@ -7548,7 +7557,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" ht="14.25" hidden="1" spans="1:19">
+    <row r="26" ht="14.25" spans="1:19">
       <c r="A26" s="4" t="s">
         <v>150</v>
       </c>
@@ -7605,7 +7614,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" ht="14.25" hidden="1" spans="1:19">
+    <row r="27" ht="14.25" spans="1:19">
       <c r="A27" s="4" t="s">
         <v>157</v>
       </c>
@@ -7662,7 +7671,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" ht="14.25" hidden="1" spans="1:19">
+    <row r="28" ht="14.25" spans="1:19">
       <c r="A28" s="4" t="s">
         <v>165</v>
       </c>
@@ -7721,7 +7730,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" ht="14.25" hidden="1" spans="1:19">
+    <row r="29" ht="14.25" spans="1:19">
       <c r="A29" s="4" t="s">
         <v>171</v>
       </c>
@@ -7778,7 +7787,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="14.25" hidden="1" spans="1:19">
+    <row r="30" ht="14.25" spans="1:19">
       <c r="A30" s="4" t="s">
         <v>176</v>
       </c>
@@ -7835,7 +7844,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" ht="14.25" hidden="1" spans="1:19">
+    <row r="31" ht="14.25" spans="1:19">
       <c r="A31" s="4" t="s">
         <v>180</v>
       </c>
@@ -7892,7 +7901,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" ht="14.25" hidden="1" spans="1:19">
+    <row r="32" ht="14.25" spans="1:19">
       <c r="A32" s="4" t="s">
         <v>185</v>
       </c>
@@ -7947,7 +7956,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" ht="27" hidden="1" spans="1:19">
+    <row r="33" ht="27" spans="1:19">
       <c r="A33" s="4" t="s">
         <v>190</v>
       </c>
@@ -8004,7 +8013,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" ht="27" hidden="1" spans="1:19">
+    <row r="34" ht="27" spans="1:19">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -8059,7 +8068,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" ht="14.25" hidden="1" spans="1:19">
+    <row r="35" ht="14.25" spans="1:19">
       <c r="A35" s="4" t="s">
         <v>201</v>
       </c>
@@ -8114,7 +8123,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" ht="14.25" hidden="1" spans="1:19">
+    <row r="36" ht="14.25" spans="1:19">
       <c r="A36" s="4" t="s">
         <v>207</v>
       </c>
@@ -8169,7 +8178,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" ht="14.25" hidden="1" spans="1:19">
+    <row r="37" ht="14.25" spans="1:19">
       <c r="A37" s="4" t="s">
         <v>211</v>
       </c>
@@ -8224,7 +8233,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" ht="14.25" hidden="1" spans="1:19">
+    <row r="38" ht="14.25" spans="1:19">
       <c r="A38" s="4" t="s">
         <v>215</v>
       </c>
@@ -8281,7 +8290,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" ht="14.25" hidden="1" spans="1:19">
+    <row r="39" ht="14.25" spans="1:19">
       <c r="A39" s="4" t="s">
         <v>219</v>
       </c>
@@ -8336,7 +8345,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" ht="27" hidden="1" spans="1:19">
+    <row r="40" ht="27" spans="1:19">
       <c r="A40" s="4" t="s">
         <v>224</v>
       </c>
@@ -8391,7 +8400,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" ht="14.25" hidden="1" spans="1:19">
+    <row r="41" ht="14.25" spans="1:19">
       <c r="A41" s="4" t="s">
         <v>229</v>
       </c>
@@ -8448,7 +8457,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" ht="14.25" hidden="1" spans="1:19">
+    <row r="42" ht="14.25" spans="1:19">
       <c r="A42" s="4" t="s">
         <v>235</v>
       </c>
@@ -8503,7 +8512,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" ht="14.25" hidden="1" spans="1:19">
+    <row r="43" ht="14.25" spans="1:19">
       <c r="A43" s="4" t="s">
         <v>241</v>
       </c>
@@ -8558,7 +8567,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" ht="14.25" hidden="1" spans="1:19">
+    <row r="44" ht="14.25" spans="1:19">
       <c r="A44" s="4" t="s">
         <v>247</v>
       </c>
@@ -8613,7 +8622,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="45" ht="14.25" hidden="1" spans="1:19">
+    <row r="45" ht="14.25" spans="1:19">
       <c r="A45" s="4" t="s">
         <v>251</v>
       </c>
@@ -8725,7 +8734,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" ht="14.25" hidden="1" spans="1:19">
+    <row r="47" ht="14.25" spans="1:19">
       <c r="A47" s="4" t="s">
         <v>262</v>
       </c>
@@ -8780,7 +8789,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" ht="14.25" hidden="1" spans="1:19">
+    <row r="48" ht="14.25" spans="1:19">
       <c r="A48" s="4" t="s">
         <v>266</v>
       </c>
@@ -8835,7 +8844,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" ht="27" hidden="1" spans="1:19">
+    <row r="49" ht="27" spans="1:19">
       <c r="A49" s="4" t="s">
         <v>270</v>
       </c>
@@ -8892,7 +8901,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="14.25" hidden="1" spans="1:19">
+    <row r="50" ht="14.25" spans="1:19">
       <c r="A50" s="4" t="s">
         <v>278</v>
       </c>
@@ -8947,7 +8956,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" ht="14.25" hidden="1" spans="1:19">
+    <row r="51" ht="14.25" spans="1:19">
       <c r="A51" s="4" t="s">
         <v>283</v>
       </c>
@@ -9004,7 +9013,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" ht="27.75" hidden="1" spans="1:19">
+    <row r="52" ht="27.75" spans="1:19">
       <c r="A52" s="4" t="s">
         <v>286</v>
       </c>
@@ -9061,7 +9070,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="53" ht="15" hidden="1" spans="1:19">
+    <row r="53" ht="15" spans="1:19">
       <c r="A53" s="4" t="s">
         <v>291</v>
       </c>
@@ -9116,7 +9125,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="54" ht="14.25" hidden="1" spans="1:19">
+    <row r="54" ht="14.25" spans="1:19">
       <c r="A54" s="4" t="s">
         <v>297</v>
       </c>
@@ -9173,7 +9182,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" ht="14.25" hidden="1" spans="1:19">
+    <row r="55" ht="14.25" spans="1:19">
       <c r="A55" s="4" t="s">
         <v>304</v>
       </c>
@@ -9228,7 +9237,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" ht="14.25" hidden="1" spans="1:19">
+    <row r="56" ht="14.25" spans="1:19">
       <c r="A56" s="4" t="s">
         <v>308</v>
       </c>
@@ -9285,7 +9294,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="57" ht="14.25" hidden="1" spans="1:19">
+    <row r="57" ht="14.25" spans="1:19">
       <c r="A57" s="4" t="s">
         <v>312</v>
       </c>
@@ -9344,7 +9353,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="58" ht="27" hidden="1" spans="1:19">
+    <row r="58" ht="27" spans="1:19">
       <c r="A58" s="4" t="s">
         <v>316</v>
       </c>
@@ -9399,7 +9408,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" ht="14.25" hidden="1" spans="1:19">
+    <row r="59" ht="14.25" spans="1:19">
       <c r="A59" s="4" t="s">
         <v>322</v>
       </c>
@@ -9456,7 +9465,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="60" ht="14.25" hidden="1" spans="1:19">
+    <row r="60" ht="14.25" spans="1:19">
       <c r="A60" s="4" t="s">
         <v>327</v>
       </c>
@@ -9513,7 +9522,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" ht="14.25" hidden="1" spans="1:19">
+    <row r="61" ht="14.25" spans="1:19">
       <c r="A61" s="4" t="s">
         <v>333</v>
       </c>
@@ -9570,7 +9579,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" ht="14.25" hidden="1" spans="1:19">
+    <row r="62" ht="14.25" spans="1:19">
       <c r="A62" s="5" t="s">
         <v>339</v>
       </c>
@@ -9625,7 +9634,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" ht="27" hidden="1" spans="1:19">
+    <row r="63" ht="27" spans="1:19">
       <c r="A63" s="4" t="s">
         <v>343</v>
       </c>
@@ -9682,7 +9691,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="64" ht="27" hidden="1" spans="1:19">
+    <row r="64" ht="27" spans="1:19">
       <c r="A64" s="4" t="s">
         <v>348</v>
       </c>
@@ -9739,7 +9748,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="65" ht="14.25" hidden="1" spans="1:19">
+    <row r="65" ht="14.25" spans="1:19">
       <c r="A65" s="4" t="s">
         <v>352</v>
       </c>
@@ -9796,7 +9805,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="66" ht="14.25" hidden="1" spans="1:19">
+    <row r="66" ht="14.25" spans="1:19">
       <c r="A66" s="4" t="s">
         <v>356</v>
       </c>
@@ -9853,7 +9862,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="67" ht="14.25" hidden="1" spans="1:19">
+    <row r="67" ht="14.25" spans="1:19">
       <c r="A67" s="4" t="s">
         <v>360</v>
       </c>
@@ -9910,7 +9919,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" ht="14.25" hidden="1" spans="1:19">
+    <row r="68" ht="14.25" spans="1:19">
       <c r="A68" s="4" t="s">
         <v>364</v>
       </c>
@@ -9967,7 +9976,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="69" ht="27" hidden="1" spans="1:19">
+    <row r="69" ht="27" spans="1:19">
       <c r="A69" s="4" t="s">
         <v>367</v>
       </c>
@@ -10024,7 +10033,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="70" ht="14.25" hidden="1" spans="1:19">
+    <row r="70" ht="14.25" spans="1:19">
       <c r="A70" s="4" t="s">
         <v>371</v>
       </c>
@@ -10081,7 +10090,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" ht="14.25" hidden="1" spans="1:19">
+    <row r="71" ht="14.25" spans="1:19">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -10138,7 +10147,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" ht="14.25" hidden="1" spans="1:19">
+    <row r="72" ht="14.25" spans="1:19">
       <c r="A72" s="4" t="s">
         <v>378</v>
       </c>
@@ -10195,7 +10204,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" ht="27" hidden="1" spans="1:19">
+    <row r="73" ht="27" spans="1:19">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10252,7 +10261,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74" ht="27" hidden="1" spans="1:19">
+    <row r="74" ht="27" spans="1:19">
       <c r="A74" s="4" t="s">
         <v>385</v>
       </c>
@@ -10309,7 +10318,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" ht="14.25" hidden="1" spans="1:19">
+    <row r="75" ht="14.25" spans="1:19">
       <c r="A75" s="4" t="s">
         <v>389</v>
       </c>
@@ -10366,7 +10375,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="76" ht="27" hidden="1" spans="1:19">
+    <row r="76" ht="27" spans="1:19">
       <c r="A76" s="4" t="s">
         <v>393</v>
       </c>
@@ -10423,7 +10432,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" ht="14.25" hidden="1" spans="1:19">
+    <row r="77" ht="14.25" spans="1:19">
       <c r="A77" s="4" t="s">
         <v>397</v>
       </c>
@@ -10482,7 +10491,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" ht="27" hidden="1" spans="1:19">
+    <row r="78" ht="27" spans="1:19">
       <c r="A78" s="4" t="s">
         <v>401</v>
       </c>
@@ -10539,7 +10548,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" ht="14.25" hidden="1" spans="1:19">
+    <row r="79" ht="14.25" spans="1:19">
       <c r="A79" s="4" t="s">
         <v>405</v>
       </c>
@@ -10596,7 +10605,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="80" ht="14.25" hidden="1" spans="1:19">
+    <row r="80" ht="14.25" spans="1:19">
       <c r="A80" s="4" t="s">
         <v>409</v>
       </c>
@@ -10653,7 +10662,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="81" ht="14.25" hidden="1" spans="1:19">
+    <row r="81" ht="14.25" spans="1:19">
       <c r="A81" s="4" t="s">
         <v>413</v>
       </c>
@@ -10710,7 +10719,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="82" ht="14.25" hidden="1" spans="1:19">
+    <row r="82" ht="14.25" spans="1:19">
       <c r="A82" s="4" t="s">
         <v>418</v>
       </c>
@@ -10767,7 +10776,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="83" ht="14.25" hidden="1" spans="1:19">
+    <row r="83" ht="14.25" spans="1:19">
       <c r="A83" s="4" t="s">
         <v>422</v>
       </c>
@@ -10824,7 +10833,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="84" ht="14.25" hidden="1" spans="1:19">
+    <row r="84" ht="14.25" spans="1:19">
       <c r="A84" s="4" t="s">
         <v>426</v>
       </c>
@@ -10881,7 +10890,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="85" ht="27" hidden="1" spans="1:19">
+    <row r="85" ht="27" spans="1:19">
       <c r="A85" s="4" t="s">
         <v>429</v>
       </c>
@@ -10938,7 +10947,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="86" ht="27" hidden="1" spans="1:19">
+    <row r="86" ht="27" spans="1:19">
       <c r="A86" s="4" t="s">
         <v>433</v>
       </c>
@@ -10995,7 +11004,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="87" ht="14.25" hidden="1" spans="1:19">
+    <row r="87" ht="14.25" spans="1:19">
       <c r="A87" s="4" t="s">
         <v>436</v>
       </c>
@@ -11052,7 +11061,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="88" ht="14.25" hidden="1" spans="1:19">
+    <row r="88" ht="14.25" spans="1:19">
       <c r="A88" s="4" t="s">
         <v>440</v>
       </c>
@@ -11109,7 +11118,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="89" ht="14.25" hidden="1" spans="1:19">
+    <row r="89" ht="14.25" spans="1:19">
       <c r="A89" s="4" t="s">
         <v>444</v>
       </c>
@@ -11166,7 +11175,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90" ht="27" hidden="1" spans="1:19">
+    <row r="90" ht="27" spans="1:19">
       <c r="A90" s="4" t="s">
         <v>448</v>
       </c>
@@ -11223,7 +11232,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="91" ht="14.25" hidden="1" spans="1:19">
+    <row r="91" ht="14.25" spans="1:19">
       <c r="A91" s="4" t="s">
         <v>452</v>
       </c>
@@ -11280,7 +11289,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" ht="14.25" hidden="1" spans="1:19">
+    <row r="92" ht="14.25" spans="1:19">
       <c r="A92" s="4" t="s">
         <v>454</v>
       </c>
@@ -11337,7 +11346,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" ht="14.25" hidden="1" spans="1:19">
+    <row r="93" ht="14.25" spans="1:19">
       <c r="A93" s="4" t="s">
         <v>456</v>
       </c>
@@ -11394,7 +11403,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" ht="14.25" hidden="1" spans="1:19">
+    <row r="94" ht="14.25" spans="1:19">
       <c r="A94" s="4" t="s">
         <v>458</v>
       </c>
@@ -11451,7 +11460,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" ht="14.25" hidden="1" spans="1:19">
+    <row r="95" ht="14.25" spans="1:19">
       <c r="A95" s="4" t="s">
         <v>461</v>
       </c>
@@ -11508,7 +11517,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="96" ht="14.25" hidden="1" spans="1:19">
+    <row r="96" ht="14.25" spans="1:19">
       <c r="A96" s="4" t="s">
         <v>465</v>
       </c>
@@ -11565,7 +11574,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="97" ht="14.25" hidden="1" spans="1:19">
+    <row r="97" ht="14.25" spans="1:19">
       <c r="A97" s="4" t="s">
         <v>469</v>
       </c>
@@ -11622,7 +11631,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" ht="14.25" hidden="1" spans="1:19">
+    <row r="98" ht="14.25" spans="1:19">
       <c r="A98" s="4" t="s">
         <v>474</v>
       </c>
@@ -11679,7 +11688,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" ht="14.25" hidden="1" spans="1:19">
+    <row r="99" ht="14.25" spans="1:19">
       <c r="A99" s="4" t="s">
         <v>476</v>
       </c>
@@ -11736,7 +11745,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" ht="14.25" hidden="1" spans="1:19">
+    <row r="100" ht="14.25" spans="1:19">
       <c r="A100" s="4" t="s">
         <v>479</v>
       </c>
@@ -11793,7 +11802,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" ht="14.25" hidden="1" spans="1:19">
+    <row r="101" ht="14.25" spans="1:19">
       <c r="A101" s="4" t="s">
         <v>481</v>
       </c>
@@ -11850,7 +11859,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" ht="14.25" hidden="1" spans="1:19">
+    <row r="102" ht="14.25" spans="1:19">
       <c r="A102" s="4" t="s">
         <v>483</v>
       </c>
@@ -11907,7 +11916,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" ht="14.25" hidden="1" spans="1:19">
+    <row r="103" ht="14.25" spans="1:19">
       <c r="A103" s="4" t="s">
         <v>485</v>
       </c>
@@ -11964,7 +11973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" ht="14.25" hidden="1" spans="1:19">
+    <row r="104" ht="14.25" spans="1:19">
       <c r="A104" s="4" t="s">
         <v>487</v>
       </c>
@@ -12021,7 +12030,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" ht="14.25" hidden="1" spans="1:19">
+    <row r="105" ht="14.25" spans="1:19">
       <c r="A105" s="4" t="s">
         <v>489</v>
       </c>
@@ -12078,7 +12087,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" ht="14.25" hidden="1" spans="1:19">
+    <row r="106" ht="14.25" spans="1:19">
       <c r="A106" s="4" t="s">
         <v>491</v>
       </c>
@@ -12135,7 +12144,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="107" ht="14.25" hidden="1" spans="1:19">
+    <row r="107" ht="14.25" spans="1:19">
       <c r="A107" s="4" t="s">
         <v>495</v>
       </c>
@@ -12192,7 +12201,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="108" ht="14.25" hidden="1" spans="1:19">
+    <row r="108" ht="14.25" spans="1:19">
       <c r="A108" s="4" t="s">
         <v>497</v>
       </c>
@@ -12247,7 +12256,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="109" ht="14.25" hidden="1" spans="1:19">
+    <row r="109" ht="14.25" spans="1:19">
       <c r="A109" s="4" t="s">
         <v>502</v>
       </c>
@@ -12304,7 +12313,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="110" ht="14.25" hidden="1" spans="1:19">
+    <row r="110" ht="14.25" spans="1:19">
       <c r="A110" s="4" t="s">
         <v>504</v>
       </c>
@@ -12361,7 +12370,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" ht="14.25" hidden="1" spans="1:19">
+    <row r="111" ht="14.25" spans="1:19">
       <c r="A111" s="4" t="s">
         <v>506</v>
       </c>
@@ -12418,7 +12427,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="112" ht="14.25" hidden="1" spans="1:19">
+    <row r="112" ht="14.25" spans="1:19">
       <c r="A112" s="4" t="s">
         <v>508</v>
       </c>
@@ -12475,7 +12484,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="113" ht="14.25" hidden="1" spans="1:19">
+    <row r="113" ht="14.25" spans="1:19">
       <c r="A113" s="4" t="s">
         <v>510</v>
       </c>
@@ -12532,7 +12541,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" ht="27" hidden="1" spans="1:19">
+    <row r="114" ht="27" spans="1:19">
       <c r="A114" s="4" t="s">
         <v>513</v>
       </c>
@@ -12589,7 +12598,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="115" ht="27" hidden="1" spans="1:19">
+    <row r="115" ht="27" spans="1:19">
       <c r="A115" s="4" t="s">
         <v>517</v>
       </c>
@@ -12646,7 +12655,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="116" ht="27" hidden="1" spans="1:19">
+    <row r="116" ht="27" spans="1:19">
       <c r="A116" s="4" t="s">
         <v>520</v>
       </c>
@@ -12703,7 +12712,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="117" ht="14.25" hidden="1" spans="1:19">
+    <row r="117" ht="14.25" spans="1:19">
       <c r="A117" s="4" t="s">
         <v>523</v>
       </c>
@@ -12758,7 +12767,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="118" ht="14.25" hidden="1" spans="1:19">
+    <row r="118" ht="14.25" spans="1:19">
       <c r="A118" s="4" t="s">
         <v>528</v>
       </c>
@@ -12815,7 +12824,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" ht="14.25" hidden="1" spans="1:19">
+    <row r="119" ht="14.25" spans="1:19">
       <c r="A119" s="4" t="s">
         <v>530</v>
       </c>
@@ -12872,7 +12881,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" ht="14.25" hidden="1" spans="1:19">
+    <row r="120" ht="14.25" spans="1:19">
       <c r="A120" s="4" t="s">
         <v>532</v>
       </c>
@@ -12929,7 +12938,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121" ht="14.25" hidden="1" spans="1:19">
+    <row r="121" ht="14.25" spans="1:19">
       <c r="A121" s="4" t="s">
         <v>534</v>
       </c>
@@ -12986,7 +12995,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="122" ht="14.25" hidden="1" spans="1:19">
+    <row r="122" ht="14.25" spans="1:19">
       <c r="A122" s="4" t="s">
         <v>536</v>
       </c>
@@ -13043,7 +13052,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" ht="14.25" hidden="1" spans="1:19">
+    <row r="123" ht="14.25" spans="1:19">
       <c r="A123" s="4" t="s">
         <v>539</v>
       </c>
@@ -13100,7 +13109,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" ht="14.25" hidden="1" spans="1:19">
+    <row r="124" ht="14.25" spans="1:19">
       <c r="A124" s="4" t="s">
         <v>542</v>
       </c>
@@ -13157,7 +13166,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" ht="14.25" hidden="1" spans="1:19">
+    <row r="125" ht="14.25" spans="1:19">
       <c r="A125" s="4" t="s">
         <v>544</v>
       </c>
@@ -13214,7 +13223,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" ht="14.25" hidden="1" spans="1:19">
+    <row r="126" ht="14.25" spans="1:19">
       <c r="A126" s="4" t="s">
         <v>546</v>
       </c>
@@ -13271,7 +13280,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="127" ht="14.25" hidden="1" spans="1:19">
+    <row r="127" ht="14.25" spans="1:19">
       <c r="A127" s="4" t="s">
         <v>551</v>
       </c>
@@ -13328,7 +13337,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="128" ht="14.25" hidden="1" spans="1:19">
+    <row r="128" ht="14.25" spans="1:19">
       <c r="A128" s="4" t="s">
         <v>553</v>
       </c>
@@ -13385,7 +13394,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="129" ht="14.25" hidden="1" spans="1:19">
+    <row r="129" ht="14.25" spans="1:19">
       <c r="A129" s="4" t="s">
         <v>556</v>
       </c>
@@ -13440,7 +13449,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" ht="14.25" hidden="1" spans="1:19">
+    <row r="130" ht="14.25" spans="1:19">
       <c r="A130" s="4" t="s">
         <v>560</v>
       </c>
@@ -13495,7 +13504,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="131" ht="14.25" hidden="1" spans="1:19">
+    <row r="131" ht="14.25" spans="1:19">
       <c r="A131" s="4" t="s">
         <v>562</v>
       </c>
@@ -13550,7 +13559,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="132" ht="14.25" hidden="1" spans="1:19">
+    <row r="132" ht="14.25" spans="1:19">
       <c r="A132" s="4" t="s">
         <v>564</v>
       </c>
@@ -13605,7 +13614,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="133" ht="14.25" hidden="1" spans="1:19">
+    <row r="133" ht="14.25" spans="1:19">
       <c r="A133" s="4" t="s">
         <v>566</v>
       </c>
@@ -13660,7 +13669,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="134" ht="14.25" hidden="1" spans="1:19">
+    <row r="134" ht="14.25" spans="1:19">
       <c r="A134" s="4" t="s">
         <v>568</v>
       </c>
@@ -13715,7 +13724,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="135" ht="14.25" hidden="1" spans="1:19">
+    <row r="135" ht="14.25" spans="1:19">
       <c r="A135" s="4" t="s">
         <v>572</v>
       </c>
@@ -13770,7 +13779,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="136" ht="14.25" hidden="1" spans="1:19">
+    <row r="136" ht="14.25" spans="1:19">
       <c r="A136" s="4" t="s">
         <v>574</v>
       </c>
@@ -13825,7 +13834,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="137" ht="14.25" hidden="1" spans="1:19">
+    <row r="137" ht="14.25" spans="1:19">
       <c r="A137" s="4" t="s">
         <v>576</v>
       </c>
@@ -13880,7 +13889,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="138" ht="14.25" hidden="1" spans="1:19">
+    <row r="138" ht="14.25" spans="1:19">
       <c r="A138" s="4" t="s">
         <v>578</v>
       </c>
@@ -13935,7 +13944,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="139" ht="14.25" hidden="1" spans="1:19">
+    <row r="139" ht="14.25" spans="1:19">
       <c r="A139" s="4" t="s">
         <v>580</v>
       </c>
@@ -13990,7 +13999,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="140" ht="14.25" hidden="1" spans="1:19">
+    <row r="140" ht="14.25" spans="1:19">
       <c r="A140" s="4" t="s">
         <v>582</v>
       </c>
@@ -14047,7 +14056,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="141" ht="14.25" hidden="1" spans="1:19">
+    <row r="141" ht="14.25" spans="1:19">
       <c r="A141" s="4" t="s">
         <v>585</v>
       </c>
@@ -14104,7 +14113,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="142" ht="14.25" hidden="1" spans="1:19">
+    <row r="142" ht="14.25" spans="1:19">
       <c r="A142" s="4" t="s">
         <v>587</v>
       </c>
@@ -14161,7 +14170,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="143" ht="14.25" hidden="1" spans="1:19">
+    <row r="143" ht="14.25" spans="1:19">
       <c r="A143" s="4" t="s">
         <v>589</v>
       </c>
@@ -14220,7 +14229,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="144" ht="14.25" hidden="1" spans="1:19">
+    <row r="144" ht="14.25" spans="1:19">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
@@ -14277,7 +14286,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="145" ht="27" hidden="1" spans="1:19">
+    <row r="145" ht="27" spans="1:19">
       <c r="A145" s="4" t="s">
         <v>594</v>
       </c>
@@ -14332,7 +14341,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" ht="14.25" hidden="1" spans="1:19">
+    <row r="146" ht="14.25" spans="1:19">
       <c r="A146" s="4" t="s">
         <v>595</v>
       </c>
@@ -14387,7 +14396,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="147" ht="14.25" hidden="1" spans="1:19">
+    <row r="147" ht="14.25" spans="1:19">
       <c r="A147" s="4" t="s">
         <v>599</v>
       </c>
@@ -14440,7 +14449,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" ht="14.25" hidden="1" spans="1:19">
+    <row r="148" ht="14.25" spans="1:19">
       <c r="A148" s="4" t="s">
         <v>605</v>
       </c>
@@ -14493,7 +14502,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="149" ht="14.25" hidden="1" spans="1:19">
+    <row r="149" ht="14.25" spans="1:19">
       <c r="A149" s="4" t="s">
         <v>609</v>
       </c>
@@ -14546,7 +14555,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="150" ht="14.25" hidden="1" spans="1:19">
+    <row r="150" ht="14.25" spans="1:19">
       <c r="A150" s="4" t="s">
         <v>613</v>
       </c>
@@ -14605,7 +14614,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="151" ht="14.25" hidden="1" spans="1:19">
+    <row r="151" ht="14.25" spans="1:19">
       <c r="A151" s="4" t="s">
         <v>615</v>
       </c>
@@ -14662,7 +14671,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="152" ht="14.25" hidden="1" spans="1:19">
+    <row r="152" ht="14.25" spans="1:19">
       <c r="A152" s="4" t="s">
         <v>617</v>
       </c>
@@ -14719,7 +14728,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" ht="14.25" hidden="1" spans="1:19">
+    <row r="153" ht="14.25" spans="1:19">
       <c r="A153" s="4" t="s">
         <v>619</v>
       </c>
@@ -14776,7 +14785,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="154" ht="14.25" hidden="1" spans="1:19">
+    <row r="154" ht="14.25" spans="1:19">
       <c r="A154" s="4" t="s">
         <v>621</v>
       </c>
@@ -14833,7 +14842,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="155" ht="27" hidden="1" spans="1:19">
+    <row r="155" ht="27" spans="1:19">
       <c r="A155" s="4" t="s">
         <v>624</v>
       </c>
@@ -14890,7 +14899,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" ht="27" hidden="1" spans="1:19">
+    <row r="156" ht="27" spans="1:19">
       <c r="A156" s="4" t="s">
         <v>628</v>
       </c>
@@ -14947,7 +14956,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="157" ht="14.25" hidden="1" spans="1:19">
+    <row r="157" ht="14.25" spans="1:19">
       <c r="A157" s="4" t="s">
         <v>630</v>
       </c>
@@ -15004,7 +15013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" ht="14.25" hidden="1" spans="1:19">
+    <row r="158" ht="14.25" spans="1:19">
       <c r="A158" s="4" t="s">
         <v>632</v>
       </c>
@@ -15061,7 +15070,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" ht="14.25" hidden="1" spans="1:19">
+    <row r="159" ht="14.25" spans="1:19">
       <c r="A159" s="4" t="s">
         <v>634</v>
       </c>
@@ -15118,7 +15127,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" ht="14.25" hidden="1" spans="1:19">
+    <row r="160" ht="14.25" spans="1:19">
       <c r="A160" s="4" t="s">
         <v>636</v>
       </c>
@@ -15175,7 +15184,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" ht="14.25" hidden="1" spans="1:19">
+    <row r="161" ht="14.25" spans="1:19">
       <c r="A161" s="4" t="s">
         <v>638</v>
       </c>
@@ -15232,7 +15241,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" ht="14.25" hidden="1" spans="1:19">
+    <row r="162" ht="14.25" spans="1:19">
       <c r="A162" s="4" t="s">
         <v>640</v>
       </c>
@@ -15289,7 +15298,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="163" ht="14.25" hidden="1" spans="1:19">
+    <row r="163" ht="14.25" spans="1:19">
       <c r="A163" s="4" t="s">
         <v>642</v>
       </c>
@@ -15346,7 +15355,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="164" ht="14.25" hidden="1" spans="1:19">
+    <row r="164" ht="14.25" spans="1:19">
       <c r="A164" s="4" t="s">
         <v>644</v>
       </c>
@@ -15403,7 +15412,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="165" ht="14.25" hidden="1" spans="1:19">
+    <row r="165" ht="14.25" spans="1:19">
       <c r="A165" s="4" t="s">
         <v>646</v>
       </c>
@@ -15460,7 +15469,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="166" ht="14.25" hidden="1" spans="1:19">
+    <row r="166" ht="14.25" spans="1:19">
       <c r="A166" s="4" t="s">
         <v>651</v>
       </c>
@@ -15517,7 +15526,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="167" ht="14.25" hidden="1" spans="1:19">
+    <row r="167" ht="14.25" spans="1:19">
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
@@ -15574,7 +15583,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="168" ht="14.25" hidden="1" spans="1:19">
+    <row r="168" ht="14.25" spans="1:19">
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
@@ -15631,7 +15640,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="169" ht="14.25" hidden="1" spans="1:19">
+    <row r="169" ht="14.25" spans="1:19">
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
@@ -15688,7 +15697,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="170" ht="14.25" hidden="1" spans="1:19">
+    <row r="170" ht="14.25" spans="1:19">
       <c r="A170" s="4" t="s">
         <v>659</v>
       </c>
@@ -15745,7 +15754,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="171" ht="14.25" hidden="1" spans="1:19">
+    <row r="171" ht="14.25" spans="1:19">
       <c r="A171" s="4" t="s">
         <v>661</v>
       </c>
@@ -15802,7 +15811,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="172" ht="14.25" hidden="1" spans="1:19">
+    <row r="172" ht="14.25" spans="1:19">
       <c r="A172" s="4" t="s">
         <v>663</v>
       </c>
@@ -15859,7 +15868,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="173" ht="14.25" hidden="1" spans="1:19">
+    <row r="173" ht="14.25" spans="1:19">
       <c r="A173" s="4" t="s">
         <v>665</v>
       </c>
@@ -15916,7 +15925,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="174" ht="14.25" hidden="1" spans="1:19">
+    <row r="174" ht="14.25" spans="1:19">
       <c r="A174" s="4" t="s">
         <v>667</v>
       </c>
@@ -15973,7 +15982,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" ht="14.25" hidden="1" spans="1:19">
+    <row r="175" ht="14.25" spans="1:19">
       <c r="A175" s="4" t="s">
         <v>669</v>
       </c>
@@ -16030,7 +16039,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="176" ht="14.25" hidden="1" spans="1:19">
+    <row r="176" ht="14.25" spans="1:19">
       <c r="A176" s="4" t="s">
         <v>671</v>
       </c>
@@ -16087,7 +16096,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="177" ht="14.25" hidden="1" spans="1:19">
+    <row r="177" ht="14.25" spans="1:19">
       <c r="A177" s="4" t="s">
         <v>673</v>
       </c>
@@ -16144,7 +16153,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="178" ht="14.25" hidden="1" spans="1:19">
+    <row r="178" ht="14.25" spans="1:19">
       <c r="A178" s="4" t="s">
         <v>677</v>
       </c>
@@ -16201,7 +16210,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="179" ht="14.25" hidden="1" spans="1:19">
+    <row r="179" ht="14.25" spans="1:19">
       <c r="A179" s="4" t="s">
         <v>679</v>
       </c>
@@ -16258,7 +16267,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" ht="14.25" hidden="1" spans="1:19">
+    <row r="180" ht="14.25" spans="1:19">
       <c r="A180" s="4" t="s">
         <v>681</v>
       </c>
@@ -16315,7 +16324,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" ht="14.25" hidden="1" spans="1:19">
+    <row r="181" ht="14.25" spans="1:19">
       <c r="A181" s="4" t="s">
         <v>683</v>
       </c>
@@ -16372,7 +16381,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" ht="14.25" hidden="1" spans="1:19">
+    <row r="182" ht="14.25" spans="1:19">
       <c r="A182" s="4" t="s">
         <v>685</v>
       </c>
@@ -16429,7 +16438,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" ht="14.25" hidden="1" spans="1:19">
+    <row r="183" ht="14.25" spans="1:19">
       <c r="A183" s="4" t="s">
         <v>687</v>
       </c>
@@ -16486,7 +16495,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" ht="14.25" hidden="1" spans="1:19">
+    <row r="184" ht="14.25" spans="1:19">
       <c r="A184" s="4" t="s">
         <v>690</v>
       </c>
@@ -16543,7 +16552,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" ht="14.25" hidden="1" spans="1:19">
+    <row r="185" ht="14.25" spans="1:19">
       <c r="A185" s="4" t="s">
         <v>692</v>
       </c>
@@ -16600,7 +16609,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" ht="14.25" hidden="1" spans="1:19">
+    <row r="186" ht="14.25" spans="1:19">
       <c r="A186" s="4" t="s">
         <v>694</v>
       </c>
@@ -16655,7 +16664,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="187" ht="14.25" hidden="1" spans="1:19">
+    <row r="187" ht="14.25" spans="1:19">
       <c r="A187" s="4" t="s">
         <v>698</v>
       </c>
@@ -16712,7 +16721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" ht="14.25" hidden="1" spans="1:19">
+    <row r="188" ht="14.25" spans="1:19">
       <c r="A188" s="4" t="s">
         <v>700</v>
       </c>
@@ -16769,7 +16778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" ht="14.25" hidden="1" spans="1:19">
+    <row r="189" ht="14.25" spans="1:19">
       <c r="A189" s="4" t="s">
         <v>702</v>
       </c>
@@ -16828,7 +16837,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" ht="14.25" hidden="1" spans="1:19">
+    <row r="190" ht="14.25" spans="1:19">
       <c r="A190" s="4" t="s">
         <v>706</v>
       </c>
@@ -16883,7 +16892,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" ht="14.25" hidden="1" spans="1:19">
+    <row r="191" ht="14.25" spans="1:19">
       <c r="A191" s="4" t="s">
         <v>708</v>
       </c>
@@ -16942,7 +16951,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" ht="14.25" hidden="1" spans="1:19">
+    <row r="192" ht="14.25" spans="1:19">
       <c r="A192" s="4" t="s">
         <v>710</v>
       </c>
@@ -17001,7 +17010,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="193" ht="14.25" hidden="1" spans="1:19">
+    <row r="193" ht="14.25" spans="1:19">
       <c r="A193" s="4" t="s">
         <v>714</v>
       </c>
@@ -17060,7 +17069,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="194" ht="14.25" hidden="1" spans="1:19">
+    <row r="194" ht="14.25" spans="1:19">
       <c r="A194" s="4" t="s">
         <v>717</v>
       </c>
@@ -17119,7 +17128,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="195" ht="14.25" hidden="1" spans="1:19">
+    <row r="195" ht="14.25" spans="1:19">
       <c r="A195" s="4" t="s">
         <v>719</v>
       </c>
@@ -17178,7 +17187,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="196" ht="14.25" hidden="1" spans="1:19">
+    <row r="196" ht="14.25" spans="1:19">
       <c r="A196" s="4" t="s">
         <v>722</v>
       </c>
@@ -17235,7 +17244,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="197" ht="14.25" hidden="1" spans="1:19">
+    <row r="197" ht="14.25" spans="1:19">
       <c r="A197" s="4" t="s">
         <v>723</v>
       </c>
@@ -17292,7 +17301,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="198" ht="14.25" hidden="1" spans="1:19">
+    <row r="198" ht="14.25" spans="1:19">
       <c r="A198" s="4" t="s">
         <v>725</v>
       </c>
@@ -17349,7 +17358,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="199" ht="27" hidden="1" spans="1:19">
+    <row r="199" ht="27" spans="1:19">
       <c r="A199" s="4" t="s">
         <v>727</v>
       </c>
@@ -17406,7 +17415,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="200" ht="14.25" hidden="1" spans="1:19">
+    <row r="200" ht="14.25" spans="1:19">
       <c r="A200" s="4" t="s">
         <v>731</v>
       </c>
@@ -17463,7 +17472,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="201" ht="14.25" hidden="1" spans="1:19">
+    <row r="201" ht="14.25" spans="1:19">
       <c r="A201" s="4" t="s">
         <v>735</v>
       </c>
@@ -17520,7 +17529,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="202" ht="14.25" hidden="1" spans="1:19">
+    <row r="202" ht="14.25" spans="1:19">
       <c r="A202" s="4" t="s">
         <v>738</v>
       </c>
@@ -17577,7 +17586,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="203" ht="14.25" hidden="1" spans="1:19">
+    <row r="203" ht="14.25" spans="1:19">
       <c r="A203" s="4" t="s">
         <v>740</v>
       </c>
@@ -17634,7 +17643,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="204" ht="14.25" hidden="1" spans="1:19">
+    <row r="204" ht="14.25" spans="1:19">
       <c r="A204" s="4" t="s">
         <v>742</v>
       </c>
@@ -17691,7 +17700,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="205" ht="14.25" hidden="1" spans="1:19">
+    <row r="205" ht="14.25" spans="1:19">
       <c r="A205" s="4" t="s">
         <v>745</v>
       </c>
@@ -17750,7 +17759,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" ht="14.25" hidden="1" spans="1:19">
+    <row r="206" ht="14.25" spans="1:19">
       <c r="A206" s="4" t="s">
         <v>749</v>
       </c>
@@ -17807,7 +17816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" ht="14.25" hidden="1" spans="1:19">
+    <row r="207" ht="14.25" spans="1:19">
       <c r="A207" s="4" t="s">
         <v>751</v>
       </c>
@@ -17864,7 +17873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" ht="14.25" hidden="1" spans="1:19">
+    <row r="208" ht="14.25" spans="1:19">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -17921,7 +17930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" ht="14.25" hidden="1" spans="1:19">
+    <row r="209" ht="14.25" spans="1:19">
       <c r="A209" s="4" t="s">
         <v>755</v>
       </c>
@@ -17976,7 +17985,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" ht="14.25" hidden="1" spans="1:19">
+    <row r="210" ht="14.25" spans="1:19">
       <c r="A210" s="4" t="s">
         <v>757</v>
       </c>
@@ -18033,7 +18042,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" ht="14.25" hidden="1" spans="1:19">
+    <row r="211" ht="14.25" spans="1:19">
       <c r="A211" s="4" t="s">
         <v>759</v>
       </c>
@@ -18090,7 +18099,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="212" ht="14.25" hidden="1" spans="1:19">
+    <row r="212" ht="14.25" spans="1:19">
       <c r="A212" s="4" t="s">
         <v>761</v>
       </c>
@@ -18147,7 +18156,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="213" ht="14.25" hidden="1" spans="1:19">
+    <row r="213" ht="14.25" spans="1:19">
       <c r="A213" s="4" t="s">
         <v>763</v>
       </c>
@@ -18204,7 +18213,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="214" ht="14.25" hidden="1" spans="1:19">
+    <row r="214" ht="14.25" spans="1:19">
       <c r="A214" s="4" t="s">
         <v>765</v>
       </c>
@@ -18261,7 +18270,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="215" ht="14.25" hidden="1" spans="1:19">
+    <row r="215" ht="14.25" spans="1:19">
       <c r="A215" s="4" t="s">
         <v>768</v>
       </c>
@@ -18318,7 +18327,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="216" ht="14.25" hidden="1" spans="1:19">
+    <row r="216" ht="14.25" spans="1:19">
       <c r="A216" s="4" t="s">
         <v>770</v>
       </c>
@@ -18377,7 +18386,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="217" ht="14.25" hidden="1" spans="1:19">
+    <row r="217" ht="14.25" spans="1:19">
       <c r="A217" s="4" t="s">
         <v>773</v>
       </c>
@@ -18434,7 +18443,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="218" ht="14.25" hidden="1" spans="1:19">
+    <row r="218" ht="14.25" spans="1:19">
       <c r="A218" s="4" t="s">
         <v>775</v>
       </c>
@@ -18491,7 +18500,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="219" ht="27" hidden="1" spans="1:19">
+    <row r="219" ht="27" spans="1:19">
       <c r="A219" s="4" t="s">
         <v>777</v>
       </c>
@@ -18546,7 +18555,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="220" ht="27" hidden="1" spans="1:19">
+    <row r="220" ht="27" spans="1:19">
       <c r="A220" s="4" t="s">
         <v>781</v>
       </c>
@@ -18601,7 +18610,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="221" ht="27" hidden="1" spans="1:19">
+    <row r="221" ht="27" spans="1:19">
       <c r="A221" s="4" t="s">
         <v>783</v>
       </c>
@@ -18656,7 +18665,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="222" ht="27" hidden="1" spans="1:19">
+    <row r="222" ht="27" spans="1:19">
       <c r="A222" s="4" t="s">
         <v>785</v>
       </c>
@@ -18711,7 +18720,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="223" ht="27" hidden="1" spans="1:19">
+    <row r="223" ht="27" spans="1:19">
       <c r="A223" s="4" t="s">
         <v>787</v>
       </c>
@@ -18766,7 +18775,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="224" ht="27" hidden="1" spans="1:19">
+    <row r="224" ht="27" spans="1:19">
       <c r="A224" s="4" t="s">
         <v>789</v>
       </c>
@@ -18821,7 +18830,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="225" ht="14.25" hidden="1" spans="1:19">
+    <row r="225" ht="14.25" spans="1:19">
       <c r="A225" s="4" t="s">
         <v>791</v>
       </c>
@@ -18878,7 +18887,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="226" ht="14.25" hidden="1" spans="1:19">
+    <row r="226" ht="14.25" spans="1:19">
       <c r="A226" s="4" t="s">
         <v>793</v>
       </c>
@@ -18935,7 +18944,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="227" ht="14.25" hidden="1" spans="1:19">
+    <row r="227" ht="14.25" spans="1:19">
       <c r="A227" s="4" t="s">
         <v>794</v>
       </c>
@@ -18992,7 +19001,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="228" ht="14.25" hidden="1" spans="1:19">
+    <row r="228" ht="14.25" spans="1:19">
       <c r="A228" s="4" t="s">
         <v>796</v>
       </c>
@@ -19049,7 +19058,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" ht="14.25" hidden="1" spans="1:19">
+    <row r="229" ht="14.25" spans="1:19">
       <c r="A229" s="4" t="s">
         <v>798</v>
       </c>
@@ -19106,7 +19115,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="230" ht="14.25" hidden="1" spans="1:19">
+    <row r="230" ht="14.25" spans="1:19">
       <c r="A230" s="4" t="s">
         <v>800</v>
       </c>
@@ -19163,7 +19172,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="231" ht="14.25" hidden="1" spans="1:19">
+    <row r="231" ht="14.25" spans="1:19">
       <c r="A231" s="4" t="s">
         <v>802</v>
       </c>
@@ -19220,7 +19229,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="232" ht="14.25" hidden="1" spans="1:19">
+    <row r="232" ht="14.25" spans="1:19">
       <c r="A232" s="4" t="s">
         <v>804</v>
       </c>
@@ -19277,7 +19286,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="233" ht="14.25" hidden="1" spans="1:19">
+    <row r="233" ht="14.25" spans="1:19">
       <c r="A233" s="4" t="s">
         <v>806</v>
       </c>
@@ -19334,7 +19343,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" ht="14.25" hidden="1" spans="1:19">
+    <row r="234" ht="14.25" spans="1:19">
       <c r="A234" s="4" t="s">
         <v>808</v>
       </c>
@@ -19391,7 +19400,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="235" ht="14.25" hidden="1" spans="1:19">
+    <row r="235" ht="14.25" spans="1:19">
       <c r="A235" s="4" t="s">
         <v>810</v>
       </c>
@@ -19448,7 +19457,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="236" ht="27" hidden="1" spans="1:19">
+    <row r="236" ht="27" spans="1:19">
       <c r="A236" s="4" t="s">
         <v>812</v>
       </c>
@@ -19503,7 +19512,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="237" ht="27" hidden="1" spans="1:19">
+    <row r="237" ht="27" spans="1:19">
       <c r="A237" s="4" t="s">
         <v>817</v>
       </c>
@@ -19558,7 +19567,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="238" ht="27" hidden="1" spans="1:19">
+    <row r="238" ht="27" spans="1:19">
       <c r="A238" s="4" t="s">
         <v>819</v>
       </c>
@@ -19613,7 +19622,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="239" ht="14.25" hidden="1" spans="1:19">
+    <row r="239" ht="14.25" spans="1:19">
       <c r="A239" s="4" t="s">
         <v>821</v>
       </c>
@@ -19668,7 +19677,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="240" ht="14.25" hidden="1" spans="1:19">
+    <row r="240" ht="14.25" spans="1:19">
       <c r="A240" s="4" t="s">
         <v>825</v>
       </c>
@@ -19725,7 +19734,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" ht="14.25" hidden="1" spans="1:19">
+    <row r="241" ht="14.25" spans="1:19">
       <c r="A241" s="4" t="s">
         <v>827</v>
       </c>
@@ -19782,7 +19791,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" ht="14.25" hidden="1" spans="1:19">
+    <row r="242" ht="14.25" spans="1:19">
       <c r="A242" s="4" t="s">
         <v>829</v>
       </c>
@@ -19839,7 +19848,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="243" ht="14.25" hidden="1" spans="1:19">
+    <row r="243" ht="14.25" spans="1:19">
       <c r="A243" s="4" t="s">
         <v>832</v>
       </c>
@@ -19896,7 +19905,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="244" ht="14.25" hidden="1" spans="1:19">
+    <row r="244" ht="14.25" spans="1:19">
       <c r="A244" s="4" t="s">
         <v>836</v>
       </c>
@@ -19953,7 +19962,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="245" ht="14.25" hidden="1" spans="1:19">
+    <row r="245" ht="14.25" spans="1:19">
       <c r="A245" s="4" t="s">
         <v>838</v>
       </c>
@@ -20010,7 +20019,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="246" ht="14.25" hidden="1" spans="1:19">
+    <row r="246" ht="14.25" spans="1:19">
       <c r="A246" s="4" t="s">
         <v>842</v>
       </c>
@@ -20065,7 +20074,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="247" ht="14.25" hidden="1" spans="1:19">
+    <row r="247" ht="14.25" spans="1:19">
       <c r="A247" s="4" t="s">
         <v>846</v>
       </c>
@@ -20120,7 +20129,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" ht="14.25" hidden="1" spans="1:19">
+    <row r="248" ht="14.25" spans="1:19">
       <c r="A248" s="4" t="s">
         <v>849</v>
       </c>
@@ -20175,7 +20184,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" ht="14.25" hidden="1" spans="1:19">
+    <row r="249" ht="14.25" spans="1:19">
       <c r="A249" s="4" t="s">
         <v>851</v>
       </c>
@@ -20230,7 +20239,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" ht="14.25" hidden="1" spans="1:19">
+    <row r="250" ht="14.25" spans="1:19">
       <c r="A250" s="4" t="s">
         <v>853</v>
       </c>
@@ -20285,7 +20294,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" ht="14.25" hidden="1" spans="1:19">
+    <row r="251" ht="14.25" spans="1:19">
       <c r="A251" s="4" t="s">
         <v>855</v>
       </c>
@@ -20342,7 +20351,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="252" ht="14.25" hidden="1" spans="1:19">
+    <row r="252" ht="14.25" spans="1:19">
       <c r="A252" s="4" t="s">
         <v>857</v>
       </c>
@@ -20399,7 +20408,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="253" ht="14.25" hidden="1" spans="1:19">
+    <row r="253" ht="14.25" spans="1:19">
       <c r="A253" s="4" t="s">
         <v>859</v>
       </c>
@@ -20456,7 +20465,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="254" ht="14.25" hidden="1" spans="1:19">
+    <row r="254" ht="14.25" spans="1:19">
       <c r="A254" s="4" t="s">
         <v>861</v>
       </c>
@@ -20513,7 +20522,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="255" ht="14.25" hidden="1" spans="1:19">
+    <row r="255" ht="14.25" spans="1:19">
       <c r="A255" s="4" t="s">
         <v>863</v>
       </c>
@@ -20572,7 +20581,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="256" ht="14.25" hidden="1" spans="1:19">
+    <row r="256" ht="14.25" spans="1:19">
       <c r="A256" s="4" t="s">
         <v>866</v>
       </c>
@@ -20629,7 +20638,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="257" ht="15" hidden="1" spans="1:19">
+    <row r="257" ht="15" spans="1:19">
       <c r="A257" s="4" t="s">
         <v>868</v>
       </c>
@@ -20686,7 +20695,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="258" ht="27.75" hidden="1" spans="1:19">
+    <row r="258" ht="27.75" spans="1:19">
       <c r="A258" s="4" t="s">
         <v>870</v>
       </c>
@@ -20743,7 +20752,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="259" ht="27.75" hidden="1" spans="1:19">
+    <row r="259" ht="27.75" spans="1:19">
       <c r="A259" s="4" t="s">
         <v>874</v>
       </c>
@@ -20800,7 +20809,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="260" ht="14.25" hidden="1" spans="1:19">
+    <row r="260" ht="14.25" spans="1:19">
       <c r="A260" s="4" t="s">
         <v>877</v>
       </c>
@@ -20851,7 +20860,7 @@
       <c r="R260" s="7"/>
       <c r="S260" s="7"/>
     </row>
-    <row r="261" ht="14.25" hidden="1" spans="1:19">
+    <row r="261" ht="14.25" spans="1:19">
       <c r="A261" s="4" t="s">
         <v>881</v>
       </c>
@@ -20902,7 +20911,7 @@
       <c r="R261" s="7"/>
       <c r="S261" s="7"/>
     </row>
-    <row r="262" ht="14.25" hidden="1" spans="1:19">
+    <row r="262" ht="14.25" spans="1:19">
       <c r="A262" s="4" t="s">
         <v>886</v>
       </c>
@@ -20953,7 +20962,7 @@
       <c r="R262" s="7"/>
       <c r="S262" s="7"/>
     </row>
-    <row r="263" ht="14.25" hidden="1" spans="1:19">
+    <row r="263" ht="14.25" spans="1:19">
       <c r="A263" s="4" t="s">
         <v>889</v>
       </c>
@@ -21004,7 +21013,7 @@
       <c r="R263" s="7"/>
       <c r="S263" s="7"/>
     </row>
-    <row r="264" ht="14.25" hidden="1" spans="1:19">
+    <row r="264" ht="14.25" spans="1:19">
       <c r="A264" s="4" t="s">
         <v>893</v>
       </c>
@@ -21055,7 +21064,7 @@
       <c r="R264" s="7"/>
       <c r="S264" s="7"/>
     </row>
-    <row r="265" ht="14.25" hidden="1" spans="1:19">
+    <row r="265" ht="14.25" spans="1:19">
       <c r="A265" s="4" t="s">
         <v>896</v>
       </c>
@@ -21106,7 +21115,7 @@
       <c r="R265" s="7"/>
       <c r="S265" s="7"/>
     </row>
-    <row r="266" ht="14.25" hidden="1" spans="1:19">
+    <row r="266" ht="14.25" spans="1:19">
       <c r="A266" s="4" t="s">
         <v>900</v>
       </c>
@@ -21157,7 +21166,7 @@
       <c r="R266" s="7"/>
       <c r="S266" s="7"/>
     </row>
-    <row r="267" ht="14.25" hidden="1" spans="1:19">
+    <row r="267" ht="14.25" spans="1:19">
       <c r="A267" s="4" t="s">
         <v>904</v>
       </c>
@@ -21208,7 +21217,7 @@
       <c r="R267" s="7"/>
       <c r="S267" s="7"/>
     </row>
-    <row r="268" ht="14.25" hidden="1" spans="1:19">
+    <row r="268" ht="14.25" spans="1:19">
       <c r="A268" s="4" t="s">
         <v>907</v>
       </c>
@@ -21259,7 +21268,7 @@
       <c r="R268" s="7"/>
       <c r="S268" s="7"/>
     </row>
-    <row r="269" ht="14.25" hidden="1" spans="1:19">
+    <row r="269" ht="14.25" spans="1:19">
       <c r="A269" s="4" t="s">
         <v>909</v>
       </c>
@@ -21310,7 +21319,7 @@
       <c r="R269" s="7"/>
       <c r="S269" s="7"/>
     </row>
-    <row r="270" ht="14.25" hidden="1" spans="1:19">
+    <row r="270" ht="14.25" spans="1:19">
       <c r="A270" s="4" t="s">
         <v>912</v>
       </c>
@@ -21361,7 +21370,7 @@
       <c r="R270" s="7"/>
       <c r="S270" s="7"/>
     </row>
-    <row r="271" ht="14.25" hidden="1" spans="1:19">
+    <row r="271" ht="14.25" spans="1:19">
       <c r="A271" s="4" t="s">
         <v>914</v>
       </c>
@@ -21414,7 +21423,7 @@
       <c r="R271" s="7"/>
       <c r="S271" s="7"/>
     </row>
-    <row r="272" ht="14.25" hidden="1" spans="1:19">
+    <row r="272" ht="14.25" spans="1:19">
       <c r="A272" s="4" t="s">
         <v>918</v>
       </c>
@@ -21467,7 +21476,7 @@
       <c r="R272" s="7"/>
       <c r="S272" s="7"/>
     </row>
-    <row r="273" ht="14.25" hidden="1" spans="1:19">
+    <row r="273" ht="14.25" spans="1:19">
       <c r="A273" s="4" t="s">
         <v>920</v>
       </c>
@@ -21520,7 +21529,7 @@
       <c r="R273" s="7"/>
       <c r="S273" s="7"/>
     </row>
-    <row r="274" ht="14.25" hidden="1" spans="1:19">
+    <row r="274" ht="14.25" spans="1:19">
       <c r="A274" s="4" t="s">
         <v>923</v>
       </c>
@@ -21571,7 +21580,7 @@
       <c r="R274" s="7"/>
       <c r="S274" s="7"/>
     </row>
-    <row r="275" ht="14.25" hidden="1" spans="1:19">
+    <row r="275" ht="14.25" spans="1:19">
       <c r="A275" s="4" t="s">
         <v>927</v>
       </c>
@@ -21622,7 +21631,7 @@
       <c r="R275" s="7"/>
       <c r="S275" s="7"/>
     </row>
-    <row r="276" ht="14.25" hidden="1" spans="1:19">
+    <row r="276" ht="14.25" spans="1:19">
       <c r="A276" s="4" t="s">
         <v>930</v>
       </c>
@@ -21673,7 +21682,7 @@
       <c r="R276" s="7"/>
       <c r="S276" s="7"/>
     </row>
-    <row r="277" ht="14.25" hidden="1" spans="1:19">
+    <row r="277" ht="14.25" spans="1:19">
       <c r="A277" s="4" t="s">
         <v>932</v>
       </c>
@@ -21724,7 +21733,7 @@
       <c r="R277" s="7"/>
       <c r="S277" s="7"/>
     </row>
-    <row r="278" ht="14.25" hidden="1" spans="1:19">
+    <row r="278" ht="14.25" spans="1:19">
       <c r="A278" s="4" t="s">
         <v>935</v>
       </c>
@@ -21775,7 +21784,7 @@
       <c r="R278" s="7"/>
       <c r="S278" s="7"/>
     </row>
-    <row r="279" ht="14.25" hidden="1" spans="1:19">
+    <row r="279" ht="14.25" spans="1:19">
       <c r="A279" s="4" t="s">
         <v>937</v>
       </c>
@@ -21828,7 +21837,7 @@
       <c r="R279" s="7"/>
       <c r="S279" s="7"/>
     </row>
-    <row r="280" ht="14.25" hidden="1" spans="1:19">
+    <row r="280" ht="14.25" spans="1:19">
       <c r="A280" s="4" t="s">
         <v>940</v>
       </c>
@@ -21881,7 +21890,7 @@
       <c r="R280" s="7"/>
       <c r="S280" s="7"/>
     </row>
-    <row r="281" ht="14.25" hidden="1" spans="1:19">
+    <row r="281" ht="14.25" spans="1:19">
       <c r="A281" s="4" t="s">
         <v>943</v>
       </c>
@@ -21932,7 +21941,7 @@
       <c r="R281" s="7"/>
       <c r="S281" s="7"/>
     </row>
-    <row r="282" ht="14.25" hidden="1" spans="1:19">
+    <row r="282" ht="14.25" spans="1:19">
       <c r="A282" s="4" t="s">
         <v>946</v>
       </c>
@@ -21983,7 +21992,7 @@
       <c r="R282" s="7"/>
       <c r="S282" s="7"/>
     </row>
-    <row r="283" ht="14.25" hidden="1" spans="1:19">
+    <row r="283" ht="14.25" spans="1:19">
       <c r="A283" s="4" t="s">
         <v>950</v>
       </c>
@@ -22034,7 +22043,7 @@
       <c r="R283" s="7"/>
       <c r="S283" s="7"/>
     </row>
-    <row r="284" ht="14.25" hidden="1" spans="1:19">
+    <row r="284" ht="14.25" spans="1:19">
       <c r="A284" s="4" t="s">
         <v>953</v>
       </c>
@@ -22085,7 +22094,7 @@
       <c r="R284" s="7"/>
       <c r="S284" s="7"/>
     </row>
-    <row r="285" ht="14.25" hidden="1" spans="1:19">
+    <row r="285" ht="14.25" spans="1:19">
       <c r="A285" s="4" t="s">
         <v>937</v>
       </c>
@@ -22136,7 +22145,7 @@
       <c r="R285" s="7"/>
       <c r="S285" s="7"/>
     </row>
-    <row r="286" ht="14.25" hidden="1" spans="1:19">
+    <row r="286" ht="14.25" spans="1:19">
       <c r="A286" s="4" t="s">
         <v>940</v>
       </c>
@@ -22187,7 +22196,7 @@
       <c r="R286" s="7"/>
       <c r="S286" s="7"/>
     </row>
-    <row r="287" ht="14.25" hidden="1" spans="1:19">
+    <row r="287" ht="14.25" spans="1:19">
       <c r="A287" s="4" t="s">
         <v>959</v>
       </c>
@@ -22238,7 +22247,7 @@
       <c r="R287" s="7"/>
       <c r="S287" s="7"/>
     </row>
-    <row r="288" ht="14.25" hidden="1" spans="1:19">
+    <row r="288" ht="14.25" spans="1:19">
       <c r="A288" s="4" t="s">
         <v>963</v>
       </c>
@@ -22289,7 +22298,7 @@
       <c r="R288" s="7"/>
       <c r="S288" s="7"/>
     </row>
-    <row r="289" ht="14.25" hidden="1" spans="1:19">
+    <row r="289" ht="14.25" spans="1:19">
       <c r="A289" s="4" t="s">
         <v>965</v>
       </c>
@@ -22340,7 +22349,7 @@
       <c r="R289" s="7"/>
       <c r="S289" s="7"/>
     </row>
-    <row r="290" ht="14.25" hidden="1" spans="1:19">
+    <row r="290" ht="14.25" spans="1:19">
       <c r="A290" s="4" t="s">
         <v>967</v>
       </c>
@@ -22391,7 +22400,7 @@
       <c r="R290" s="7"/>
       <c r="S290" s="7"/>
     </row>
-    <row r="291" ht="14.25" hidden="1" spans="1:19">
+    <row r="291" ht="14.25" spans="1:19">
       <c r="A291" s="4" t="s">
         <v>969</v>
       </c>
@@ -22442,7 +22451,7 @@
       <c r="R291" s="7"/>
       <c r="S291" s="7"/>
     </row>
-    <row r="292" ht="27" hidden="1" spans="1:19">
+    <row r="292" ht="27" spans="1:19">
       <c r="A292" s="4" t="s">
         <v>973</v>
       </c>
@@ -22493,7 +22502,7 @@
       <c r="R292" s="7"/>
       <c r="S292" s="7"/>
     </row>
-    <row r="293" ht="14.25" hidden="1" spans="1:19">
+    <row r="293" ht="14.25" spans="1:19">
       <c r="A293" s="4" t="s">
         <v>977</v>
       </c>
@@ -22544,7 +22553,7 @@
       <c r="R293" s="7"/>
       <c r="S293" s="7"/>
     </row>
-    <row r="294" ht="14.25" hidden="1" spans="1:19">
+    <row r="294" ht="14.25" spans="1:19">
       <c r="A294" s="4" t="s">
         <v>981</v>
       </c>
@@ -22595,7 +22604,7 @@
       <c r="R294" s="7"/>
       <c r="S294" s="7"/>
     </row>
-    <row r="295" ht="14.25" hidden="1" spans="1:19">
+    <row r="295" ht="14.25" spans="1:19">
       <c r="A295" s="4" t="s">
         <v>984</v>
       </c>
@@ -22646,7 +22655,7 @@
       <c r="R295" s="7"/>
       <c r="S295" s="7"/>
     </row>
-    <row r="296" ht="14.25" hidden="1" spans="1:19">
+    <row r="296" ht="14.25" spans="1:19">
       <c r="A296" s="4" t="s">
         <v>987</v>
       </c>
@@ -22697,7 +22706,7 @@
       <c r="R296" s="7"/>
       <c r="S296" s="7"/>
     </row>
-    <row r="297" ht="14.25" hidden="1" spans="1:19">
+    <row r="297" ht="14.25" spans="1:19">
       <c r="A297" s="4" t="s">
         <v>990</v>
       </c>
@@ -22748,7 +22757,7 @@
       <c r="R297" s="7"/>
       <c r="S297" s="7"/>
     </row>
-    <row r="298" ht="14.25" hidden="1" spans="1:19">
+    <row r="298" ht="14.25" spans="1:19">
       <c r="A298" s="4" t="s">
         <v>992</v>
       </c>
@@ -22799,7 +22808,7 @@
       <c r="R298" s="7"/>
       <c r="S298" s="7"/>
     </row>
-    <row r="299" ht="14.25" hidden="1" spans="1:19">
+    <row r="299" ht="14.25" spans="1:19">
       <c r="A299" s="4" t="s">
         <v>996</v>
       </c>
@@ -22850,7 +22859,7 @@
       <c r="R299" s="7"/>
       <c r="S299" s="7"/>
     </row>
-    <row r="300" hidden="1" spans="1:19">
+    <row r="300" spans="1:19">
       <c r="A300" s="4" t="s">
         <v>999</v>
       </c>
@@ -22903,7 +22912,7 @@
       <c r="R300" s="7"/>
       <c r="S300" s="7"/>
     </row>
-    <row r="301" hidden="1" spans="1:19">
+    <row r="301" spans="1:19">
       <c r="A301" s="4" t="s">
         <v>1004</v>
       </c>
@@ -22956,7 +22965,7 @@
       <c r="R301" s="7"/>
       <c r="S301" s="7"/>
     </row>
-    <row r="302" hidden="1" spans="1:19">
+    <row r="302" spans="1:19">
       <c r="A302" s="4" t="s">
         <v>1008</v>
       </c>
@@ -23009,7 +23018,7 @@
       <c r="R302" s="7"/>
       <c r="S302" s="7"/>
     </row>
-    <row r="303" hidden="1" spans="1:19">
+    <row r="303" spans="1:19">
       <c r="A303" s="4" t="s">
         <v>1011</v>
       </c>
@@ -23062,7 +23071,7 @@
       <c r="R303" s="7"/>
       <c r="S303" s="7"/>
     </row>
-    <row r="304" ht="14.25" hidden="1" spans="1:19">
+    <row r="304" ht="14.25" spans="1:19">
       <c r="A304" s="4" t="s">
         <v>1014</v>
       </c>
@@ -23115,7 +23124,7 @@
       <c r="R304" s="7"/>
       <c r="S304" s="7"/>
     </row>
-    <row r="305" ht="27.75" hidden="1" spans="1:19">
+    <row r="305" ht="27.75" spans="1:19">
       <c r="A305" s="4" t="s">
         <v>1017</v>
       </c>
@@ -23168,7 +23177,7 @@
       <c r="R305" s="7"/>
       <c r="S305" s="7"/>
     </row>
-    <row r="306" ht="27" hidden="1" spans="1:19">
+    <row r="306" ht="27" spans="1:19">
       <c r="A306" s="4" t="s">
         <v>1021</v>
       </c>
@@ -23221,7 +23230,7 @@
       <c r="R306" s="7"/>
       <c r="S306" s="7"/>
     </row>
-    <row r="307" hidden="1" spans="1:19">
+    <row r="307" spans="1:19">
       <c r="A307" s="4" t="s">
         <v>1024</v>
       </c>
@@ -23274,7 +23283,7 @@
       <c r="R307" s="7"/>
       <c r="S307" s="7"/>
     </row>
-    <row r="308" hidden="1" spans="1:19">
+    <row r="308" spans="1:19">
       <c r="A308" s="4" t="s">
         <v>1028</v>
       </c>
@@ -23329,7 +23338,7 @@
       <c r="R308" s="7"/>
       <c r="S308" s="7"/>
     </row>
-    <row r="309" hidden="1" spans="1:19">
+    <row r="309" spans="1:19">
       <c r="A309" s="4" t="s">
         <v>1032</v>
       </c>
@@ -23384,7 +23393,7 @@
       <c r="R309" s="7"/>
       <c r="S309" s="7"/>
     </row>
-    <row r="310" hidden="1" spans="1:19">
+    <row r="310" spans="1:19">
       <c r="A310" s="4" t="s">
         <v>1035</v>
       </c>
@@ -23437,7 +23446,7 @@
       <c r="R310" s="7"/>
       <c r="S310" s="7"/>
     </row>
-    <row r="311" ht="27" hidden="1" spans="1:19">
+    <row r="311" ht="27" spans="1:19">
       <c r="A311" s="4" t="s">
         <v>1038</v>
       </c>
@@ -23490,7 +23499,7 @@
       <c r="R311" s="7"/>
       <c r="S311" s="7"/>
     </row>
-    <row r="312" ht="27" hidden="1" spans="1:19">
+    <row r="312" ht="27" spans="1:19">
       <c r="A312" s="4" t="s">
         <v>1042</v>
       </c>
@@ -23543,7 +23552,7 @@
       <c r="R312" s="7"/>
       <c r="S312" s="7"/>
     </row>
-    <row r="313" ht="27" hidden="1" spans="1:19">
+    <row r="313" ht="27" spans="1:19">
       <c r="A313" s="4" t="s">
         <v>1046</v>
       </c>
@@ -23596,7 +23605,7 @@
       <c r="R313" s="7"/>
       <c r="S313" s="7"/>
     </row>
-    <row r="314" hidden="1" spans="1:19">
+    <row r="314" spans="1:19">
       <c r="A314" s="4" t="s">
         <v>1050</v>
       </c>
@@ -23649,7 +23658,7 @@
       <c r="R314" s="7"/>
       <c r="S314" s="7"/>
     </row>
-    <row r="315" hidden="1" spans="1:19">
+    <row r="315" spans="1:19">
       <c r="A315" s="4" t="s">
         <v>1054</v>
       </c>
@@ -23702,7 +23711,7 @@
       <c r="R315" s="7"/>
       <c r="S315" s="7"/>
     </row>
-    <row r="316" hidden="1" spans="1:19">
+    <row r="316" spans="1:19">
       <c r="A316" s="4" t="s">
         <v>1058</v>
       </c>
@@ -23755,7 +23764,7 @@
       <c r="R316" s="7"/>
       <c r="S316" s="7"/>
     </row>
-    <row r="317" hidden="1" spans="1:19">
+    <row r="317" spans="1:19">
       <c r="A317" s="4" t="s">
         <v>1062</v>
       </c>
@@ -23804,7 +23813,7 @@
       <c r="R317" s="7"/>
       <c r="S317" s="7"/>
     </row>
-    <row r="318" hidden="1" spans="1:19">
+    <row r="318" spans="1:19">
       <c r="A318" s="4" t="s">
         <v>1065</v>
       </c>
@@ -23853,7 +23862,7 @@
       <c r="R318" s="7"/>
       <c r="S318" s="7"/>
     </row>
-    <row r="319" hidden="1" spans="1:15">
+    <row r="319" spans="1:15">
       <c r="A319" s="4" t="s">
         <v>1067</v>
       </c>
@@ -23898,7 +23907,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:15">
+    <row r="320" spans="1:15">
       <c r="A320" s="4" t="s">
         <v>1072</v>
       </c>
@@ -23943,7 +23952,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:15">
+    <row r="321" spans="1:15">
       <c r="A321" s="4" t="s">
         <v>1075</v>
       </c>
@@ -23988,7 +23997,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:15">
+    <row r="322" spans="1:15">
       <c r="A322" s="4" t="s">
         <v>1077</v>
       </c>
@@ -24033,7 +24042,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:15">
+    <row r="323" spans="1:15">
       <c r="A323" s="4" t="s">
         <v>1080</v>
       </c>
@@ -24078,7 +24087,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:15">
+    <row r="324" spans="1:15">
       <c r="A324" s="4" t="s">
         <v>1083</v>
       </c>
@@ -24123,7 +24132,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:15">
+    <row r="325" spans="1:15">
       <c r="A325" s="4" t="s">
         <v>1086</v>
       </c>
@@ -24168,7 +24177,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:15">
+    <row r="326" spans="1:15">
       <c r="A326" s="4" t="s">
         <v>1088</v>
       </c>
@@ -24213,7 +24222,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:15">
+    <row r="327" spans="1:15">
       <c r="A327" s="4" t="s">
         <v>1091</v>
       </c>
@@ -24258,7 +24267,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:15">
+    <row r="328" spans="1:15">
       <c r="A328" s="4" t="s">
         <v>1093</v>
       </c>
@@ -24303,7 +24312,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:15">
+    <row r="329" spans="1:15">
       <c r="A329" s="4" t="s">
         <v>1095</v>
       </c>
@@ -24348,7 +24357,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:15">
+    <row r="330" spans="1:15">
       <c r="A330" s="4" t="s">
         <v>1098</v>
       </c>
@@ -24393,7 +24402,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:15">
+    <row r="331" spans="1:15">
       <c r="A331" s="4" t="s">
         <v>1100</v>
       </c>
@@ -24438,7 +24447,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:15">
+    <row r="332" spans="1:15">
       <c r="A332" s="4" t="s">
         <v>1102</v>
       </c>
@@ -24483,7 +24492,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:15">
+    <row r="333" spans="1:15">
       <c r="A333" s="4" t="s">
         <v>1104</v>
       </c>
@@ -24528,7 +24537,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:15">
+    <row r="334" spans="1:15">
       <c r="A334" s="4" t="s">
         <v>1106</v>
       </c>
@@ -24573,7 +24582,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:15">
+    <row r="335" spans="1:15">
       <c r="A335" s="4" t="s">
         <v>1109</v>
       </c>
@@ -24618,7 +24627,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:15">
+    <row r="336" spans="1:15">
       <c r="A336" s="4" t="s">
         <v>1111</v>
       </c>
@@ -24663,7 +24672,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:15">
+    <row r="337" spans="1:15">
       <c r="A337" s="4" t="s">
         <v>1113</v>
       </c>
@@ -24708,7 +24717,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:15">
+    <row r="338" spans="1:15">
       <c r="A338" s="4" t="s">
         <v>1116</v>
       </c>
@@ -24753,7 +24762,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="339" ht="14.25" hidden="1" spans="1:15">
+    <row r="339" ht="14.25" spans="1:15">
       <c r="A339" s="4" t="s">
         <v>1118</v>
       </c>
@@ -24798,7 +24807,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="340" ht="14.25" hidden="1" spans="1:15">
+    <row r="340" ht="14.25" spans="1:15">
       <c r="A340" s="4" t="s">
         <v>1120</v>
       </c>
@@ -24843,7 +24852,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:15">
+    <row r="341" spans="1:15">
       <c r="A341" s="4" t="s">
         <v>1122</v>
       </c>
@@ -24888,7 +24897,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:15">
+    <row r="342" spans="1:15">
       <c r="A342" s="4" t="s">
         <v>1126</v>
       </c>
@@ -24933,7 +24942,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:15">
+    <row r="343" spans="1:15">
       <c r="A343" s="4" t="s">
         <v>1128</v>
       </c>
@@ -24978,7 +24987,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:15">
+    <row r="344" spans="1:15">
       <c r="A344" s="4" t="s">
         <v>1130</v>
       </c>
@@ -25023,7 +25032,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:15">
+    <row r="345" spans="1:15">
       <c r="A345" s="4" t="s">
         <v>1132</v>
       </c>
@@ -25068,7 +25077,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="346" hidden="1" spans="1:15">
+    <row r="346" spans="1:15">
       <c r="A346" s="4" t="s">
         <v>1135</v>
       </c>
@@ -25113,7 +25122,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:15">
+    <row r="347" spans="1:15">
       <c r="A347" s="4" t="s">
         <v>1137</v>
       </c>
@@ -25158,7 +25167,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:15">
+    <row r="348" spans="1:15">
       <c r="A348" s="4" t="s">
         <v>1139</v>
       </c>
@@ -25203,7 +25212,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:15">
+    <row r="349" spans="1:15">
       <c r="A349" s="4" t="s">
         <v>1141</v>
       </c>
@@ -25248,7 +25257,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:15">
+    <row r="350" spans="1:15">
       <c r="A350" s="4" t="s">
         <v>1143</v>
       </c>
@@ -25293,7 +25302,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:15">
+    <row r="351" spans="1:15">
       <c r="A351" s="4" t="s">
         <v>1145</v>
       </c>
@@ -25338,7 +25347,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:15">
+    <row r="352" spans="1:15">
       <c r="A352" s="4" t="s">
         <v>1147</v>
       </c>
@@ -25383,7 +25392,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:15">
+    <row r="353" spans="1:15">
       <c r="A353" s="4" t="s">
         <v>1149</v>
       </c>
@@ -25428,7 +25437,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:15">
+    <row r="354" spans="1:15">
       <c r="A354" s="4" t="s">
         <v>1151</v>
       </c>
@@ -25473,7 +25482,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:16">
+    <row r="355" spans="1:16">
       <c r="A355" s="4" t="s">
         <v>1154</v>
       </c>
@@ -25521,7 +25530,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:15">
+    <row r="356" spans="1:15">
       <c r="A356" s="4" t="s">
         <v>1157</v>
       </c>
@@ -25566,7 +25575,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:15">
+    <row r="357" spans="1:15">
       <c r="A357" s="4" t="s">
         <v>1159</v>
       </c>
@@ -25611,7 +25620,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:15">
+    <row r="358" spans="1:15">
       <c r="A358" s="4" t="s">
         <v>1161</v>
       </c>
@@ -25656,7 +25665,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:15">
+    <row r="359" spans="1:15">
       <c r="A359" s="4" t="s">
         <v>1163</v>
       </c>
@@ -25701,7 +25710,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:15">
+    <row r="360" spans="1:15">
       <c r="A360" s="4" t="s">
         <v>1165</v>
       </c>
@@ -25746,7 +25755,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:15">
+    <row r="361" spans="1:15">
       <c r="A361" s="4" t="s">
         <v>1168</v>
       </c>
@@ -25791,7 +25800,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:15">
+    <row r="362" spans="1:15">
       <c r="A362" s="4" t="s">
         <v>1170</v>
       </c>
@@ -25836,7 +25845,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:15">
+    <row r="363" spans="1:15">
       <c r="A363" s="4" t="s">
         <v>1172</v>
       </c>
@@ -25881,7 +25890,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:15">
+    <row r="364" spans="1:15">
       <c r="A364" s="4" t="s">
         <v>1174</v>
       </c>
@@ -25926,7 +25935,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:15">
+    <row r="365" spans="1:15">
       <c r="A365" s="4" t="s">
         <v>1176</v>
       </c>
@@ -25971,7 +25980,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:15">
+    <row r="366" spans="1:15">
       <c r="A366" s="4" t="s">
         <v>1178</v>
       </c>
@@ -26016,7 +26025,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:15">
+    <row r="367" spans="1:15">
       <c r="A367" s="4" t="s">
         <v>1180</v>
       </c>
@@ -26061,7 +26070,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:15">
+    <row r="368" spans="1:15">
       <c r="A368" s="4" t="s">
         <v>1183</v>
       </c>
@@ -26106,7 +26115,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:15">
+    <row r="369" spans="1:15">
       <c r="A369" s="4" t="s">
         <v>1185</v>
       </c>
@@ -26151,7 +26160,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:15">
+    <row r="370" spans="1:15">
       <c r="A370" s="4" t="s">
         <v>1188</v>
       </c>
@@ -26196,7 +26205,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="371" ht="14.25" hidden="1" spans="1:15">
+    <row r="371" ht="14.25" spans="1:15">
       <c r="A371" s="4" t="s">
         <v>1190</v>
       </c>
@@ -26241,7 +26250,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="372" ht="14.25" hidden="1" spans="1:15">
+    <row r="372" ht="14.25" spans="1:15">
       <c r="A372" s="4" t="s">
         <v>1193</v>
       </c>
@@ -26286,7 +26295,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="373" ht="14.25" hidden="1" spans="1:15">
+    <row r="373" ht="14.25" spans="1:15">
       <c r="A373" s="4" t="s">
         <v>1195</v>
       </c>
@@ -26331,7 +26340,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="374" ht="14.25" hidden="1" spans="1:15">
+    <row r="374" ht="14.25" spans="1:15">
       <c r="A374" s="4" t="s">
         <v>1197</v>
       </c>
@@ -26376,7 +26385,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:15">
+    <row r="375" spans="1:15">
       <c r="A375" s="4" t="s">
         <v>1199</v>
       </c>
@@ -26421,7 +26430,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:15">
+    <row r="376" spans="1:15">
       <c r="A376" s="4" t="s">
         <v>1201</v>
       </c>
@@ -26466,7 +26475,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:15">
+    <row r="377" spans="1:15">
       <c r="A377" s="4" t="s">
         <v>1203</v>
       </c>
@@ -26511,7 +26520,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:15">
+    <row r="378" spans="1:15">
       <c r="A378" s="4" t="s">
         <v>1205</v>
       </c>
@@ -26556,7 +26565,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:15">
+    <row r="379" spans="1:15">
       <c r="A379" s="4" t="s">
         <v>1207</v>
       </c>
@@ -26601,7 +26610,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:15">
+    <row r="380" spans="1:15">
       <c r="A380" s="4" t="s">
         <v>1210</v>
       </c>
@@ -26646,7 +26655,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:15">
+    <row r="381" spans="1:15">
       <c r="A381" s="4" t="s">
         <v>1212</v>
       </c>
@@ -26691,7 +26700,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:15">
+    <row r="382" spans="1:15">
       <c r="A382" s="4" t="s">
         <v>1215</v>
       </c>
@@ -26736,7 +26745,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:15">
+    <row r="383" spans="1:15">
       <c r="A383" s="4" t="s">
         <v>1217</v>
       </c>
@@ -26781,7 +26790,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:15">
+    <row r="384" spans="1:15">
       <c r="A384" s="4" t="s">
         <v>1219</v>
       </c>
@@ -26826,7 +26835,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:15">
+    <row r="385" spans="1:15">
       <c r="A385" s="4" t="s">
         <v>1221</v>
       </c>
@@ -26871,7 +26880,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:15">
+    <row r="386" spans="1:15">
       <c r="A386" s="4" t="s">
         <v>1224</v>
       </c>
@@ -26916,7 +26925,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:15">
+    <row r="387" spans="1:15">
       <c r="A387" s="4" t="s">
         <v>1225</v>
       </c>
@@ -26961,7 +26970,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:15">
+    <row r="388" spans="1:15">
       <c r="A388" s="4" t="s">
         <v>1228</v>
       </c>
@@ -27006,7 +27015,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:15">
+    <row r="389" spans="1:15">
       <c r="A389" s="4" t="s">
         <v>1231</v>
       </c>
@@ -27051,7 +27060,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:15">
+    <row r="390" spans="1:15">
       <c r="A390" s="4" t="s">
         <v>1234</v>
       </c>
@@ -27094,7 +27103,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:15">
+    <row r="391" spans="1:15">
       <c r="A391" s="4" t="s">
         <v>1237</v>
       </c>
@@ -27137,7 +27146,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:15">
+    <row r="392" spans="1:15">
       <c r="A392" s="4" t="s">
         <v>1240</v>
       </c>
@@ -27180,7 +27189,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:15">
+    <row r="393" spans="1:15">
       <c r="A393" s="4" t="s">
         <v>1243</v>
       </c>
@@ -27223,7 +27232,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:15">
+    <row r="394" spans="1:15">
       <c r="A394" s="4" t="s">
         <v>1246</v>
       </c>
@@ -27266,7 +27275,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:15">
+    <row r="395" spans="1:15">
       <c r="A395" s="4" t="s">
         <v>1248</v>
       </c>
@@ -27309,7 +27318,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:15">
+    <row r="396" spans="1:15">
       <c r="A396" s="4" t="s">
         <v>1250</v>
       </c>
@@ -27352,7 +27361,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:15">
+    <row r="397" spans="1:15">
       <c r="A397" s="4" t="s">
         <v>1253</v>
       </c>
@@ -27395,7 +27404,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:15">
+    <row r="398" spans="1:15">
       <c r="A398" s="4" t="s">
         <v>1255</v>
       </c>
@@ -27438,7 +27447,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:15">
+    <row r="399" spans="1:15">
       <c r="A399" s="4" t="s">
         <v>1258</v>
       </c>
@@ -27481,7 +27490,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:15">
+    <row r="400" spans="1:15">
       <c r="A400" s="4" t="s">
         <v>1260</v>
       </c>
@@ -27524,7 +27533,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:15">
+    <row r="401" spans="1:15">
       <c r="A401" s="4" t="s">
         <v>1262</v>
       </c>
@@ -27567,7 +27576,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:15">
+    <row r="402" spans="1:15">
       <c r="A402" s="4" t="s">
         <v>1264</v>
       </c>
@@ -27610,7 +27619,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:15">
+    <row r="403" spans="1:15">
       <c r="A403" s="4" t="s">
         <v>1266</v>
       </c>
@@ -27653,7 +27662,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:15">
+    <row r="404" spans="1:15">
       <c r="A404" s="4" t="s">
         <v>1268</v>
       </c>
@@ -27696,7 +27705,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:15">
+    <row r="405" spans="1:15">
       <c r="A405" s="4" t="s">
         <v>1270</v>
       </c>
@@ -27739,7 +27748,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:15">
+    <row r="406" spans="1:15">
       <c r="A406" s="4" t="s">
         <v>1273</v>
       </c>
@@ -27782,7 +27791,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:15">
+    <row r="407" spans="1:15">
       <c r="A407" s="4" t="s">
         <v>1275</v>
       </c>
@@ -27825,7 +27834,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:15">
+    <row r="408" spans="1:15">
       <c r="A408" s="4" t="s">
         <v>1278</v>
       </c>
@@ -27868,7 +27877,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:15">
+    <row r="409" spans="1:15">
       <c r="A409" s="4" t="s">
         <v>1280</v>
       </c>
@@ -27911,7 +27920,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:15">
+    <row r="410" spans="1:15">
       <c r="A410" s="4" t="s">
         <v>1282</v>
       </c>
@@ -27954,7 +27963,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:15">
+    <row r="411" spans="1:15">
       <c r="A411" s="4" t="s">
         <v>1285</v>
       </c>
@@ -28083,7 +28092,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:15">
+    <row r="414" spans="1:15">
       <c r="A414" s="4" t="s">
         <v>1291</v>
       </c>
@@ -28126,7 +28135,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:15">
+    <row r="415" spans="1:15">
       <c r="A415" s="4" t="s">
         <v>1293</v>
       </c>
@@ -28169,7 +28178,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:15">
+    <row r="416" spans="1:15">
       <c r="A416" s="4" t="s">
         <v>1296</v>
       </c>
@@ -28212,7 +28221,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:15">
+    <row r="417" spans="1:15">
       <c r="A417" s="4" t="s">
         <v>1298</v>
       </c>
@@ -28255,7 +28264,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:15">
+    <row r="418" spans="1:15">
       <c r="A418" s="4" t="s">
         <v>1300</v>
       </c>
@@ -28298,7 +28307,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:15">
+    <row r="419" spans="1:15">
       <c r="A419" s="4" t="s">
         <v>1302</v>
       </c>
@@ -28341,7 +28350,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:15">
+    <row r="420" spans="1:15">
       <c r="A420" s="4" t="s">
         <v>1305</v>
       </c>
@@ -28384,7 +28393,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:15">
+    <row r="421" spans="1:15">
       <c r="A421" s="4" t="s">
         <v>1307</v>
       </c>
@@ -28427,7 +28436,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:15">
+    <row r="422" spans="1:15">
       <c r="A422" s="4" t="s">
         <v>1309</v>
       </c>
@@ -28470,7 +28479,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:15">
+    <row r="423" spans="1:15">
       <c r="A423" s="4" t="s">
         <v>1311</v>
       </c>
@@ -28513,7 +28522,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:15">
+    <row r="424" spans="1:15">
       <c r="A424" s="4" t="s">
         <v>1313</v>
       </c>
@@ -28556,7 +28565,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:15">
+    <row r="425" spans="1:15">
       <c r="A425" s="4" t="s">
         <v>1315</v>
       </c>
@@ -28599,7 +28608,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:15">
+    <row r="426" spans="1:15">
       <c r="A426" s="4" t="s">
         <v>1317</v>
       </c>
@@ -28642,7 +28651,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:15">
+    <row r="427" spans="1:15">
       <c r="A427" s="4" t="s">
         <v>1319</v>
       </c>
@@ -28685,7 +28694,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:15">
+    <row r="428" spans="1:15">
       <c r="A428" s="4" t="s">
         <v>1322</v>
       </c>
@@ -28728,7 +28737,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:15">
+    <row r="429" spans="1:15">
       <c r="A429" s="4" t="s">
         <v>1324</v>
       </c>
@@ -28771,7 +28780,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:15">
+    <row r="430" spans="1:15">
       <c r="A430" s="4" t="s">
         <v>1326</v>
       </c>
@@ -28814,7 +28823,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:15">
+    <row r="431" spans="1:15">
       <c r="A431" s="4" t="s">
         <v>1329</v>
       </c>
@@ -28857,7 +28866,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:15">
+    <row r="432" spans="1:15">
       <c r="A432" s="4" t="s">
         <v>1331</v>
       </c>
@@ -28900,7 +28909,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:15">
+    <row r="433" spans="1:15">
       <c r="A433" s="4" t="s">
         <v>1333</v>
       </c>
@@ -28943,7 +28952,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:15">
+    <row r="434" spans="1:15">
       <c r="A434" s="4" t="s">
         <v>1336</v>
       </c>
@@ -28986,7 +28995,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:15">
+    <row r="435" spans="1:15">
       <c r="A435" s="4" t="s">
         <v>1339</v>
       </c>
@@ -29029,7 +29038,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:15">
+    <row r="436" spans="1:15">
       <c r="A436" s="4" t="s">
         <v>1341</v>
       </c>
@@ -29072,7 +29081,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:15">
+    <row r="437" spans="1:15">
       <c r="A437" s="4" t="s">
         <v>1343</v>
       </c>
@@ -29115,7 +29124,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:15">
+    <row r="438" spans="1:15">
       <c r="A438" s="4" t="s">
         <v>1345</v>
       </c>
@@ -29158,7 +29167,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="439" ht="14.25" hidden="1" spans="1:15">
+    <row r="439" ht="14.25" spans="1:15">
       <c r="A439" s="4" t="s">
         <v>1347</v>
       </c>
@@ -29201,7 +29210,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="440" ht="14.25" hidden="1" spans="1:15">
+    <row r="440" ht="14.25" spans="1:15">
       <c r="A440" s="4" t="s">
         <v>1349</v>
       </c>
@@ -29244,7 +29253,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:15">
+    <row r="441" spans="1:15">
       <c r="A441" s="4" t="s">
         <v>1351</v>
       </c>
@@ -29287,7 +29296,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="442" ht="18" hidden="1" spans="1:17">
+    <row r="442" ht="18" spans="1:17">
       <c r="A442" s="4" t="s">
         <v>1354</v>
       </c>
@@ -29334,7 +29343,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="443" ht="18" hidden="1" spans="1:17">
+    <row r="443" ht="18" spans="1:17">
       <c r="A443" s="4" t="s">
         <v>1359</v>
       </c>
@@ -29381,7 +29390,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="444" ht="17.25" hidden="1" spans="1:17">
+    <row r="444" ht="17.25" spans="1:17">
       <c r="A444" s="4" t="s">
         <v>1363</v>
       </c>
@@ -29428,7 +29437,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="445" ht="17.25" hidden="1" spans="1:17">
+    <row r="445" ht="17.25" spans="1:17">
       <c r="A445" s="4" t="s">
         <v>1368</v>
       </c>
@@ -29475,7 +29484,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="446" ht="17.25" hidden="1" spans="1:17">
+    <row r="446" ht="17.25" spans="1:17">
       <c r="A446" s="4" t="s">
         <v>1372</v>
       </c>
@@ -29522,7 +29531,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="447" ht="17.25" hidden="1" spans="1:17">
+    <row r="447" ht="17.25" spans="1:17">
       <c r="A447" s="4" t="s">
         <v>1377</v>
       </c>
@@ -29569,7 +29578,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="448" ht="17.25" hidden="1" spans="1:17">
+    <row r="448" ht="17.25" spans="1:17">
       <c r="A448" s="4" t="s">
         <v>1381</v>
       </c>
@@ -29619,7 +29628,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="449" ht="18" hidden="1" spans="1:17">
+    <row r="449" ht="18" spans="1:17">
       <c r="A449" s="4" t="s">
         <v>1384</v>
       </c>
@@ -29669,7 +29678,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="450" ht="18" hidden="1" spans="1:17">
+    <row r="450" ht="18" spans="1:17">
       <c r="A450" s="4" t="s">
         <v>1387</v>
       </c>
@@ -29719,7 +29728,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="451" ht="17.25" hidden="1" spans="1:17">
+    <row r="451" ht="17.25" spans="1:17">
       <c r="A451" s="4" t="s">
         <v>1391</v>
       </c>
@@ -29769,7 +29778,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="452" ht="17.25" hidden="1" spans="1:17">
+    <row r="452" ht="17.25" spans="1:17">
       <c r="A452" s="4" t="s">
         <v>1394</v>
       </c>
@@ -29819,7 +29828,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="453" ht="17.25" hidden="1" spans="1:17">
+    <row r="453" ht="17.25" spans="1:17">
       <c r="A453" s="4" t="s">
         <v>1398</v>
       </c>
@@ -29869,7 +29878,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="454" ht="17.25" hidden="1" spans="1:17">
+    <row r="454" ht="17.25" spans="1:17">
       <c r="A454" s="4" t="s">
         <v>1402</v>
       </c>
@@ -29916,7 +29925,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="455" ht="17.25" hidden="1" spans="1:17">
+    <row r="455" ht="17.25" spans="1:17">
       <c r="A455" s="4" t="s">
         <v>1405</v>
       </c>
@@ -29966,7 +29975,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="456" ht="18" hidden="1" spans="1:17">
+    <row r="456" ht="18" spans="1:17">
       <c r="A456" s="4" t="s">
         <v>1409</v>
       </c>
@@ -30016,7 +30025,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="457" ht="18" hidden="1" spans="1:17">
+    <row r="457" ht="18" spans="1:17">
       <c r="A457" s="4" t="s">
         <v>1412</v>
       </c>
@@ -30066,7 +30075,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="458" ht="17.25" hidden="1" spans="1:17">
+    <row r="458" ht="17.25" spans="1:17">
       <c r="A458" s="4" t="s">
         <v>1416</v>
       </c>
@@ -30113,7 +30122,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="459" ht="17.25" hidden="1" spans="1:17">
+    <row r="459" ht="17.25" spans="1:17">
       <c r="A459" s="4" t="s">
         <v>1420</v>
       </c>
@@ -30163,7 +30172,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="460" ht="17.25" hidden="1" spans="1:17">
+    <row r="460" ht="17.25" spans="1:17">
       <c r="A460" s="4" t="s">
         <v>1424</v>
       </c>
@@ -30213,7 +30222,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="461" ht="17.25" hidden="1" spans="1:17">
+    <row r="461" ht="17.25" spans="1:17">
       <c r="A461" s="4" t="s">
         <v>1428</v>
       </c>
@@ -30263,7 +30272,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="462" ht="17.25" hidden="1" spans="1:17">
+    <row r="462" ht="17.25" spans="1:17">
       <c r="A462" s="4" t="s">
         <v>1431</v>
       </c>
@@ -30313,7 +30322,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="463" ht="17.25" hidden="1" spans="1:17">
+    <row r="463" ht="17.25" spans="1:17">
       <c r="A463" s="4" t="s">
         <v>1435</v>
       </c>
@@ -30363,7 +30372,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="464" ht="17.25" hidden="1" spans="1:17">
+    <row r="464" ht="17.25" spans="1:17">
       <c r="A464" s="4" t="s">
         <v>1439</v>
       </c>
@@ -30413,7 +30422,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="465" ht="17.25" hidden="1" spans="1:17">
+    <row r="465" ht="17.25" spans="1:17">
       <c r="A465" s="4" t="s">
         <v>1443</v>
       </c>
@@ -30463,7 +30472,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="466" ht="17.25" hidden="1" spans="1:17">
+    <row r="466" ht="17.25" spans="1:17">
       <c r="A466" s="4" t="s">
         <v>1446</v>
       </c>
@@ -30513,7 +30522,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="467" ht="17.25" hidden="1" spans="1:17">
+    <row r="467" ht="17.25" spans="1:17">
       <c r="A467" s="4" t="s">
         <v>1451</v>
       </c>
@@ -30566,7 +30575,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="468" ht="17.25" hidden="1" spans="1:17">
+    <row r="468" ht="17.25" spans="1:17">
       <c r="A468" s="4" t="s">
         <v>1455</v>
       </c>
@@ -30616,7 +30625,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="469" ht="17.25" hidden="1" spans="1:17">
+    <row r="469" ht="17.25" spans="1:17">
       <c r="A469" s="4" t="s">
         <v>1459</v>
       </c>
@@ -30666,7 +30675,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="470" ht="17.25" hidden="1" spans="1:17">
+    <row r="470" ht="17.25" spans="1:17">
       <c r="A470" s="4" t="s">
         <v>1463</v>
       </c>
@@ -30716,7 +30725,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="471" ht="17.25" hidden="1" spans="1:17">
+    <row r="471" ht="17.25" spans="1:17">
       <c r="A471" s="4" t="s">
         <v>1468</v>
       </c>
@@ -30766,7 +30775,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="472" ht="17.25" hidden="1" spans="1:17">
+    <row r="472" ht="17.25" spans="1:17">
       <c r="A472" s="4" t="s">
         <v>1472</v>
       </c>
@@ -30819,7 +30828,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="473" ht="17.25" hidden="1" spans="1:17">
+    <row r="473" ht="17.25" spans="1:17">
       <c r="A473" s="4" t="s">
         <v>1474</v>
       </c>
@@ -30869,7 +30878,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="474" ht="17.25" hidden="1" spans="1:17">
+    <row r="474" ht="17.25" spans="1:17">
       <c r="A474" s="4" t="s">
         <v>1478</v>
       </c>
@@ -30919,7 +30928,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="475" ht="17.25" hidden="1" spans="1:17">
+    <row r="475" ht="17.25" spans="1:17">
       <c r="A475" s="4" t="s">
         <v>1481</v>
       </c>
@@ -30969,7 +30978,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="476" ht="17.25" hidden="1" spans="1:17">
+    <row r="476" ht="17.25" spans="1:17">
       <c r="A476" s="4" t="s">
         <v>1484</v>
       </c>
@@ -31019,7 +31028,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="477" ht="17.25" hidden="1" spans="1:17">
+    <row r="477" ht="17.25" spans="1:17">
       <c r="A477" s="4" t="s">
         <v>1486</v>
       </c>
@@ -31069,7 +31078,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="478" ht="17.25" hidden="1" spans="1:17">
+    <row r="478" ht="17.25" spans="1:17">
       <c r="A478" s="4" t="s">
         <v>1490</v>
       </c>
@@ -31119,7 +31128,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="479" ht="17.25" hidden="1" spans="1:17">
+    <row r="479" ht="17.25" spans="1:17">
       <c r="A479" s="4" t="s">
         <v>1495</v>
       </c>
@@ -31172,7 +31181,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="480" ht="17.25" hidden="1" spans="1:17">
+    <row r="480" ht="17.25" spans="1:17">
       <c r="A480" s="4" t="s">
         <v>1499</v>
       </c>
@@ -31222,7 +31231,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="481" ht="17.25" hidden="1" spans="1:17">
+    <row r="481" ht="17.25" spans="1:17">
       <c r="A481" s="4" t="s">
         <v>1503</v>
       </c>
@@ -31272,7 +31281,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="482" ht="17.25" hidden="1" spans="1:17">
+    <row r="482" ht="17.25" spans="1:17">
       <c r="A482" s="4" t="s">
         <v>1506</v>
       </c>
@@ -31319,7 +31328,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="483" ht="17.25" hidden="1" spans="1:17">
+    <row r="483" ht="17.25" spans="1:17">
       <c r="A483" s="4" t="s">
         <v>1510</v>
       </c>
@@ -31366,7 +31375,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="484" ht="17.25" hidden="1" spans="1:17">
+    <row r="484" ht="17.25" spans="1:17">
       <c r="A484" s="4" t="s">
         <v>1512</v>
       </c>
@@ -31413,7 +31422,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="485" ht="17.25" hidden="1" spans="1:17">
+    <row r="485" ht="17.25" spans="1:17">
       <c r="A485" s="4" t="s">
         <v>1514</v>
       </c>
@@ -31456,7 +31465,7 @@
       <c r="P485" s="28"/>
       <c r="Q485" s="4"/>
     </row>
-    <row r="486" ht="17.25" hidden="1" spans="1:17">
+    <row r="486" ht="17.25" spans="1:17">
       <c r="A486" s="4" t="s">
         <v>1516</v>
       </c>
@@ -31503,7 +31512,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="487" ht="17.25" hidden="1" spans="1:17">
+    <row r="487" ht="17.25" spans="1:17">
       <c r="A487" s="4" t="s">
         <v>1520</v>
       </c>
@@ -31550,7 +31559,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="488" ht="17.25" hidden="1" spans="1:17">
+    <row r="488" ht="17.25" spans="1:17">
       <c r="A488" s="4" t="s">
         <v>1523</v>
       </c>
@@ -31597,7 +31606,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="489" ht="17.25" hidden="1" spans="1:17">
+    <row r="489" ht="17.25" spans="1:17">
       <c r="A489" s="4" t="s">
         <v>1526</v>
       </c>
@@ -31644,7 +31653,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="490" ht="17.25" hidden="1" spans="1:17">
+    <row r="490" ht="17.25" spans="1:17">
       <c r="A490" s="4" t="s">
         <v>1529</v>
       </c>
@@ -31691,7 +31700,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="491" ht="17.25" hidden="1" spans="1:17">
+    <row r="491" ht="17.25" spans="1:17">
       <c r="A491" s="4" t="s">
         <v>1532</v>
       </c>
@@ -31738,7 +31747,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="492" ht="17.25" hidden="1" spans="1:17">
+    <row r="492" ht="17.25" spans="1:17">
       <c r="A492" s="4" t="s">
         <v>1535</v>
       </c>
@@ -31785,7 +31794,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="493" ht="17.25" hidden="1" spans="1:17">
+    <row r="493" ht="17.25" spans="1:17">
       <c r="A493" s="4" t="s">
         <v>1538</v>
       </c>
@@ -31832,7 +31841,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="494" ht="17.25" hidden="1" spans="1:17">
+    <row r="494" ht="17.25" spans="1:17">
       <c r="A494" s="4" t="s">
         <v>1540</v>
       </c>
@@ -31879,7 +31888,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="495" ht="17.25" hidden="1" spans="1:17">
+    <row r="495" ht="17.25" spans="1:17">
       <c r="A495" s="4" t="s">
         <v>1541</v>
       </c>
@@ -31929,7 +31938,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="496" ht="17.25" hidden="1" spans="1:17">
+    <row r="496" ht="17.25" spans="1:17">
       <c r="A496" s="4" t="s">
         <v>1545</v>
       </c>
@@ -31979,7 +31988,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="497" ht="17.25" hidden="1" spans="1:17">
+    <row r="497" ht="17.25" spans="1:17">
       <c r="A497" s="4" t="s">
         <v>1549</v>
       </c>
@@ -32029,7 +32038,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="498" ht="17.25" hidden="1" spans="1:17">
+    <row r="498" ht="17.25" spans="1:17">
       <c r="A498" s="4" t="s">
         <v>1553</v>
       </c>
@@ -32079,7 +32088,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="499" ht="17.25" hidden="1" spans="1:17">
+    <row r="499" ht="17.25" spans="1:17">
       <c r="A499" s="4" t="s">
         <v>1557</v>
       </c>
@@ -32129,7 +32138,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="500" ht="17.25" hidden="1" spans="1:17">
+    <row r="500" ht="17.25" spans="1:17">
       <c r="A500" s="4" t="s">
         <v>1561</v>
       </c>
@@ -32179,7 +32188,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="501" ht="17.25" hidden="1" spans="1:17">
+    <row r="501" ht="17.25" spans="1:17">
       <c r="A501" s="4" t="s">
         <v>1564</v>
       </c>
@@ -32229,7 +32238,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="502" ht="17.25" hidden="1" spans="1:17">
+    <row r="502" ht="17.25" spans="1:17">
       <c r="A502" s="4" t="s">
         <v>1568</v>
       </c>
@@ -32279,7 +32288,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="503" ht="17.25" hidden="1" spans="1:17">
+    <row r="503" ht="17.25" spans="1:17">
       <c r="A503" s="4" t="s">
         <v>1572</v>
       </c>
@@ -32329,7 +32338,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="504" ht="17.25" hidden="1" spans="1:17">
+    <row r="504" ht="17.25" spans="1:17">
       <c r="A504" s="4" t="s">
         <v>1574</v>
       </c>
@@ -32382,7 +32391,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="505" ht="17.25" hidden="1" spans="1:17">
+    <row r="505" ht="17.25" spans="1:17">
       <c r="A505" s="4" t="s">
         <v>1576</v>
       </c>
@@ -32429,7 +32438,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="506" ht="17.25" hidden="1" spans="1:17">
+    <row r="506" ht="17.25" spans="1:17">
       <c r="A506" s="4" t="s">
         <v>1580</v>
       </c>
@@ -32476,7 +32485,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="507" ht="17.25" hidden="1" spans="1:17">
+    <row r="507" ht="17.25" spans="1:17">
       <c r="A507" s="4" t="s">
         <v>1584</v>
       </c>
@@ -32523,7 +32532,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="508" ht="17.25" hidden="1" spans="1:17">
+    <row r="508" ht="17.25" spans="1:17">
       <c r="A508" s="4" t="s">
         <v>1588</v>
       </c>
@@ -32570,7 +32579,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="509" ht="17.25" hidden="1" spans="1:17">
+    <row r="509" ht="17.25" spans="1:17">
       <c r="A509" s="4" t="s">
         <v>1592</v>
       </c>
@@ -32617,7 +32626,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="510" hidden="1" spans="1:15">
+    <row r="510" spans="1:15">
       <c r="A510" s="4" t="s">
         <v>1595</v>
       </c>
@@ -32658,7 +32667,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="511" hidden="1" spans="1:15">
+    <row r="511" spans="1:15">
       <c r="A511" s="4" t="s">
         <v>1596</v>
       </c>
@@ -32699,7 +32708,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="512" hidden="1" spans="1:15">
+    <row r="512" spans="1:15">
       <c r="A512" s="4" t="s">
         <v>1598</v>
       </c>
@@ -32740,7 +32749,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="513" hidden="1" spans="1:15">
+    <row r="513" spans="1:15">
       <c r="A513" s="4" t="s">
         <v>1601</v>
       </c>
@@ -32781,7 +32790,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="514" hidden="1" spans="1:15">
+    <row r="514" spans="1:15">
       <c r="A514" s="4" t="s">
         <v>1606</v>
       </c>
@@ -32822,7 +32831,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="515" hidden="1" spans="1:15">
+    <row r="515" spans="1:15">
       <c r="A515" s="4" t="s">
         <v>1608</v>
       </c>
@@ -32863,7 +32872,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="516" hidden="1" spans="1:15">
+    <row r="516" spans="1:15">
       <c r="A516" s="4" t="s">
         <v>1610</v>
       </c>
@@ -32904,7 +32913,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="517" hidden="1" spans="1:15">
+    <row r="517" spans="1:15">
       <c r="A517" s="4" t="s">
         <v>1611</v>
       </c>
@@ -32945,7 +32954,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="518" hidden="1" spans="1:15">
+    <row r="518" spans="1:15">
       <c r="A518" t="s">
         <v>1613</v>
       </c>
@@ -32986,7 +32995,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="519" hidden="1" spans="1:15">
+    <row r="519" spans="1:15">
       <c r="A519" s="4" t="s">
         <v>1615</v>
       </c>
@@ -33027,7 +33036,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="520" hidden="1" spans="1:15">
+    <row r="520" spans="1:15">
       <c r="A520" t="s">
         <v>1617</v>
       </c>
@@ -33068,7 +33077,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="521" hidden="1" spans="1:15">
+    <row r="521" spans="1:15">
       <c r="A521" t="s">
         <v>1619</v>
       </c>
@@ -33150,7 +33159,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="523" hidden="1" spans="1:15">
+    <row r="523" spans="1:15">
       <c r="A523" s="4" t="s">
         <v>1624</v>
       </c>
@@ -33191,7 +33200,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="524" hidden="1" spans="1:15">
+    <row r="524" spans="1:15">
       <c r="A524" s="4" t="s">
         <v>1627</v>
       </c>
@@ -33232,17 +33241,56 @@
         <v>1629</v>
       </c>
     </row>
+    <row r="525" spans="1:15">
+      <c r="A525" s="4" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B525" t="s">
+        <v>38</v>
+      </c>
+      <c r="C525" t="s">
+        <v>88</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E525">
+        <v>0</v>
+      </c>
+      <c r="F525">
+        <v>1840</v>
+      </c>
+      <c r="G525">
+        <v>1200</v>
+      </c>
+      <c r="H525">
+        <v>0</v>
+      </c>
+      <c r="I525">
+        <v>0</v>
+      </c>
+      <c r="J525">
+        <v>2035</v>
+      </c>
+      <c r="L525" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N525" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O525" s="1" t="s">
+        <v>1632</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T524">
-    <filterColumn colId="14">
-      <customFilters>
-        <customFilter operator="equal" val="工信局"/>
-      </customFilters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="D$1:D$1048576">
+  <conditionalFormatting sqref="D525">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D524 D526:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9840"/>
+    <workbookView windowWidth="23325" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表 (数值化)'!$A$1:$T$525</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="1632">
   <si>
     <t>单号</t>
   </si>
@@ -4904,9 +4904,6 @@
   </si>
   <si>
     <t>林远盛</t>
-  </si>
-  <si>
-    <t>泉江镇事业</t>
   </si>
   <si>
     <t>[2021]第342号</t>
@@ -4923,11 +4920,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4975,31 +4972,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5019,6 +5017,21 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -5026,17 +5039,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5058,6 +5062,14 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -5066,15 +5078,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5082,7 +5087,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5097,22 +5102,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5187,7 +5184,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5199,19 +5238,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5223,133 +5340,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5362,12 +5365,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5430,7 +5427,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5454,7 +5451,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5470,6 +5467,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5497,17 +5505,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5516,10 +5513,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5528,16 +5525,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5546,115 +5543,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -33238,12 +33235,12 @@
         <v>1623</v>
       </c>
       <c r="O524" s="1" t="s">
-        <v>1629</v>
+        <v>204</v>
       </c>
     </row>
     <row r="525" spans="1:15">
       <c r="A525" s="4" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B525" t="s">
         <v>38</v>
@@ -33252,7 +33249,7 @@
         <v>88</v>
       </c>
       <c r="D525" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="E525">
         <v>0</v>
@@ -33279,11 +33276,11 @@
         <v>415</v>
       </c>
       <c r="O525" s="1" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T524">
+  <autoFilter ref="A1:T525">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D525">

--- a/excel/2021调动人员登记本.xlsx
+++ b/excel/2021调动人员登记本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9240"/>
+    <workbookView windowWidth="23325" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="总表 (数值化)" sheetId="1" r:id="rId1"/>
@@ -4920,11 +4920,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4972,29 +4972,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -5002,40 +4979,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5047,7 +4993,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5070,6 +5016,29 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -5077,11 +5046,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5095,7 +5095,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5103,13 +5110,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5184,31 +5184,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5226,7 +5214,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5238,73 +5226,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5322,7 +5250,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5334,7 +5298,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5346,13 +5322,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5365,6 +5353,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5423,11 +5423,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5443,41 +5449,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5500,6 +5471,35 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -5513,10 +5513,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5525,133 +5525,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
